--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Documents\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEFFCF6B-BB4B-4597-8B83-3ECACA08F206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1732D3F1-98B1-48A1-B8E3-9DD18E7880B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="41">
   <si>
     <t>TER</t>
   </si>
@@ -167,7 +165,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,6 +199,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -223,7 +229,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -235,10 +241,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percentagem" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -528,7 +535,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -538,7 +545,7 @@
     <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -569,22 +576,54 @@
       <c r="M1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
@@ -648,7 +687,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -688,20 +727,69 @@
       <c r="M2" s="1">
         <v>46079</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
+      <c r="N2" s="1">
+        <v>46084</v>
+      </c>
+      <c r="O2" s="1">
+        <f>N2+2</f>
+        <v>46086</v>
+      </c>
+      <c r="P2" s="1">
+        <f>N2+5</f>
+        <v>46089</v>
+      </c>
+      <c r="Q2" s="1">
+        <f>P2+2</f>
+        <v>46091</v>
+      </c>
+      <c r="R2" s="1">
+        <f>P2+5</f>
+        <v>46094</v>
+      </c>
+      <c r="S2" s="1">
+        <f t="shared" ref="S2:AC2" si="0">R2+2</f>
+        <v>46096</v>
+      </c>
+      <c r="T2" s="1">
+        <f t="shared" ref="T2" si="1">R2+5</f>
+        <v>46099</v>
+      </c>
+      <c r="U2" s="1">
+        <f t="shared" ref="U2:AC2" si="2">T2+2</f>
+        <v>46101</v>
+      </c>
+      <c r="V2" s="1">
+        <f t="shared" ref="V2" si="3">T2+5</f>
+        <v>46104</v>
+      </c>
+      <c r="W2" s="1">
+        <f t="shared" ref="W2:AC2" si="4">V2+2</f>
+        <v>46106</v>
+      </c>
+      <c r="X2" s="1">
+        <f t="shared" ref="X2" si="5">V2+5</f>
+        <v>46109</v>
+      </c>
+      <c r="Y2" s="1">
+        <f t="shared" ref="Y2:AC2" si="6">X2+2</f>
+        <v>46111</v>
+      </c>
+      <c r="Z2" s="1">
+        <f t="shared" ref="Z2" si="7">X2+5</f>
+        <v>46114</v>
+      </c>
+      <c r="AA2" s="1">
+        <f t="shared" ref="AA2:AC2" si="8">Z2+2</f>
+        <v>46116</v>
+      </c>
+      <c r="AB2" s="1">
+        <f t="shared" ref="AB2" si="9">Z2+5</f>
+        <v>46119</v>
+      </c>
+      <c r="AC2" s="1">
+        <f t="shared" ref="AC2" si="10">AB2+2</f>
+        <v>46121</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -746,7 +834,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -783,6 +871,9 @@
         <v>5</v>
       </c>
       <c r="M3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -861,7 +952,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -898,6 +989,9 @@
         <v>5</v>
       </c>
       <c r="M4" t="s">
+        <v>5</v>
+      </c>
+      <c r="N4" t="s">
         <v>5</v>
       </c>
       <c r="AU4" s="2"/>
@@ -976,7 +1070,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1013,6 +1107,9 @@
         <v>5</v>
       </c>
       <c r="M5" t="s">
+        <v>5</v>
+      </c>
+      <c r="N5" t="s">
         <v>5</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1091,7 +1188,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1131,6 +1228,9 @@
         <v>5</v>
       </c>
       <c r="M6" t="s">
+        <v>5</v>
+      </c>
+      <c r="N6" t="s">
         <v>5</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1209,7 +1309,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1247,6 +1347,9 @@
         <v>5</v>
       </c>
       <c r="M7" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" t="s">
         <v>5</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1325,7 +1428,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1363,6 +1466,9 @@
         <v>5</v>
       </c>
       <c r="M8" t="s">
+        <v>5</v>
+      </c>
+      <c r="N8" t="s">
         <v>5</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1441,7 +1547,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1479,6 +1585,9 @@
         <v>5</v>
       </c>
       <c r="M9" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" t="s">
         <v>5</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1557,7 +1666,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -1595,6 +1704,9 @@
         <v>5</v>
       </c>
       <c r="M10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" t="s">
         <v>5</v>
       </c>
       <c r="AU10" s="2"/>
@@ -1673,7 +1785,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -1711,6 +1823,9 @@
         <v>5</v>
       </c>
       <c r="M11" t="s">
+        <v>5</v>
+      </c>
+      <c r="N11" t="s">
         <v>5</v>
       </c>
       <c r="AU11" s="2"/>
@@ -1789,7 +1904,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -1827,6 +1942,9 @@
         <v>5</v>
       </c>
       <c r="M12" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" t="s">
         <v>5</v>
       </c>
       <c r="AU12" s="2"/>
@@ -1905,7 +2023,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -1943,6 +2061,9 @@
         <v>5</v>
       </c>
       <c r="M13" t="s">
+        <v>5</v>
+      </c>
+      <c r="N13" t="s">
         <v>5</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2021,7 +2142,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2060,6 +2181,9 @@
       </c>
       <c r="M14" t="s">
         <v>8</v>
+      </c>
+      <c r="N14" t="s">
+        <v>5</v>
       </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
@@ -2137,7 +2261,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2175,6 +2299,9 @@
         <v>5</v>
       </c>
       <c r="M15" t="s">
+        <v>5</v>
+      </c>
+      <c r="N15" t="s">
         <v>5</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2253,7 +2380,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2291,6 +2418,9 @@
         <v>5</v>
       </c>
       <c r="M16" t="s">
+        <v>5</v>
+      </c>
+      <c r="N16" t="s">
         <v>5</v>
       </c>
       <c r="AU16" s="2"/>
@@ -2369,7 +2499,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -2407,6 +2537,9 @@
         <v>5</v>
       </c>
       <c r="M17" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" t="s">
         <v>5</v>
       </c>
       <c r="AU17" s="2"/>
@@ -2485,7 +2618,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -2523,6 +2656,9 @@
         <v>5</v>
       </c>
       <c r="M18" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" t="s">
         <v>5</v>
       </c>
       <c r="AU18" s="2"/>
@@ -2601,7 +2737,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -2639,6 +2775,9 @@
         <v>5</v>
       </c>
       <c r="M19" t="s">
+        <v>5</v>
+      </c>
+      <c r="N19" t="s">
         <v>5</v>
       </c>
       <c r="AU19" s="2"/>
@@ -2717,7 +2856,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -2755,6 +2894,9 @@
         <v>5</v>
       </c>
       <c r="M20" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" t="s">
         <v>5</v>
       </c>
       <c r="AU20" s="2"/>
@@ -2833,7 +2975,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -2871,6 +3013,9 @@
         <v>5</v>
       </c>
       <c r="M21" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" t="s">
         <v>5</v>
       </c>
       <c r="AU21" s="2"/>
@@ -2949,7 +3094,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -2987,6 +3132,9 @@
         <v>5</v>
       </c>
       <c r="M22" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" t="s">
         <v>5</v>
       </c>
       <c r="AU22" s="2"/>
@@ -3065,7 +3213,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3103,6 +3251,9 @@
         <v>5</v>
       </c>
       <c r="M23" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" t="s">
         <v>5</v>
       </c>
       <c r="AU23" s="2"/>
@@ -3181,7 +3332,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -3219,6 +3370,9 @@
         <v>5</v>
       </c>
       <c r="M24" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" t="s">
         <v>5</v>
       </c>
       <c r="AU24" s="2"/>
@@ -3297,7 +3451,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -3335,6 +3489,9 @@
         <v>5</v>
       </c>
       <c r="M25" t="s">
+        <v>5</v>
+      </c>
+      <c r="N25" t="s">
         <v>5</v>
       </c>
       <c r="AU25" s="2"/>
@@ -3413,7 +3570,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -3451,6 +3608,9 @@
         <v>5</v>
       </c>
       <c r="M26" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" t="s">
         <v>5</v>
       </c>
       <c r="AU26" s="2"/>
@@ -3529,7 +3689,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -3567,6 +3727,9 @@
         <v>5</v>
       </c>
       <c r="M27" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" t="s">
         <v>8</v>
       </c>
       <c r="AU27" s="2"/>
@@ -3645,7 +3808,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -3683,6 +3846,9 @@
         <v>5</v>
       </c>
       <c r="M28" t="s">
+        <v>5</v>
+      </c>
+      <c r="N28" s="9" t="s">
         <v>5</v>
       </c>
       <c r="AU28" s="2"/>
@@ -3761,7 +3927,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -3799,6 +3965,9 @@
         <v>5</v>
       </c>
       <c r="M29" t="s">
+        <v>5</v>
+      </c>
+      <c r="N29" t="s">
         <v>5</v>
       </c>
       <c r="AU29" s="2"/>
@@ -3877,7 +4046,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -3915,6 +4084,9 @@
         <v>5</v>
       </c>
       <c r="M30" t="s">
+        <v>5</v>
+      </c>
+      <c r="N30" t="s">
         <v>5</v>
       </c>
       <c r="AU30" s="2"/>
@@ -3993,7 +4165,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -4031,6 +4203,9 @@
         <v>5</v>
       </c>
       <c r="M31" t="s">
+        <v>5</v>
+      </c>
+      <c r="N31" t="s">
         <v>5</v>
       </c>
       <c r="AU31" s="2"/>
@@ -4109,7 +4284,7 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>0</v>
@@ -4140,8 +4315,11 @@
       <c r="M32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:13">
+      <c r="N32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4162,8 +4340,11 @@
       <c r="M33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4179,6 +4360,9 @@
         <v>5</v>
       </c>
       <c r="M34" t="s">
+        <v>5</v>
+      </c>
+      <c r="N34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4190,7 +4374,7 @@
     <mergeCell ref="J6:J32"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AZ3 BE3:DG3 BB3:BB22 H4:AZ6 BE4:BJ10 D4:G31 BK4:DG31 BC11:BJ22 G32:I32 K23:BJ31 K11:BA22 H7:I31 K7:AZ10">
+  <conditionalFormatting sqref="BE3:DG3 BB3:BB22 H4:M6 BE4:BJ10 D4:G31 BK4:DG31 BC11:BJ22 G32:I32 H7:I31 K7:M31 D3:AZ3 O11:BA22 O23:BJ31 O4:AZ10 N4:N34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4203,7 +4387,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
@@ -4211,7 +4395,7 @@
     <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4219,162 +4403,162 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:2">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="2:2">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="2:2">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="2:2">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="2:2">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:2">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:2">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="2:2">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="2:2">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="2:2">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="2:2">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="2:2">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>40</v>
       </c>
@@ -4388,185 +4572,185 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E8BA54-AA53-4AE8-B8DA-79238D2ECDF5}">
   <dimension ref="A2:A31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Alicia Coelho Gomes de Oliveira</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Ana Klara do Carmo</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Franco de Lima</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Bruno Vascon</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Davi Parreira Cardeal</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Eloísa Macedo da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Enzo Casadei Macedo</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Felipe Martins</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Gabriel Pereira de Oliveira</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Giovana Luísa Cezar</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Guilherme Enrico Barichello</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Isabele Hilary Reis Silva</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabelle Moreira Cezar Barichello</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Jéssica Guedes Vaz</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Joana Fernandes Fabrin</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>João Henrique Leme da Silva</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>João Victor Moraes Lopes</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Kamilly Vitoria Ferreira Silvério</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Leonardo Canina Marchiori</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Lívia Fernandes Morais</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Maria Eduarda Betim Gomes de Moraes</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Mariana Correia Santos</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Miguel Cardoso Pignata</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Mirella Camilotti Perez</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pietro Cardoso Broleze</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Samuel Gomes Silva</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Thiago Lima Amaral</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Vitor Rafael Parisato</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Yasmin Drudi</v>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Documents\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1732D3F1-98B1-48A1-B8E3-9DD18E7880B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AB3AB6-CD7D-4C12-B07C-1598C34A17D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="41">
   <si>
     <t>TER</t>
   </si>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>P/5</t>
-  </si>
-  <si>
-    <t>carnaval</t>
   </si>
   <si>
     <t>F</t>
@@ -160,12 +157,15 @@
   <si>
     <t>Letícia Guarizo Tolloto</t>
   </si>
+  <si>
+    <t>Carnaval</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -207,6 +207,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -229,7 +236,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -238,10 +245,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -747,7 +755,7 @@
         <v>46094</v>
       </c>
       <c r="S2" s="1">
-        <f t="shared" ref="S2:AC2" si="0">R2+2</f>
+        <f t="shared" ref="S2" si="0">R2+2</f>
         <v>46096</v>
       </c>
       <c r="T2" s="1">
@@ -755,7 +763,7 @@
         <v>46099</v>
       </c>
       <c r="U2" s="1">
-        <f t="shared" ref="U2:AC2" si="2">T2+2</f>
+        <f t="shared" ref="U2" si="2">T2+2</f>
         <v>46101</v>
       </c>
       <c r="V2" s="1">
@@ -763,7 +771,7 @@
         <v>46104</v>
       </c>
       <c r="W2" s="1">
-        <f t="shared" ref="W2:AC2" si="4">V2+2</f>
+        <f t="shared" ref="W2" si="4">V2+2</f>
         <v>46106</v>
       </c>
       <c r="X2" s="1">
@@ -771,7 +779,7 @@
         <v>46109</v>
       </c>
       <c r="Y2" s="1">
-        <f t="shared" ref="Y2:AC2" si="6">X2+2</f>
+        <f t="shared" ref="Y2" si="6">X2+2</f>
         <v>46111</v>
       </c>
       <c r="Z2" s="1">
@@ -779,7 +787,7 @@
         <v>46114</v>
       </c>
       <c r="AA2" s="1">
-        <f t="shared" ref="AA2:AC2" si="8">Z2+2</f>
+        <f t="shared" ref="AA2" si="8">Z2+2</f>
         <v>46116</v>
       </c>
       <c r="AB2" s="1">
@@ -834,14 +842,13 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
       </c>
-      <c r="B3" t="str">
-        <f>alunos!B2</f>
-        <v>Alicia Coelho Gomes de Oliveira</v>
+      <c r="B3" t="s">
+        <v>8</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -863,6 +870,9 @@
       </c>
       <c r="I3" t="s">
         <v>5</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="K3" t="s">
         <v>5</v>
@@ -957,9 +967,8 @@
         <f>alunos!A3</f>
         <v>0</v>
       </c>
-      <c r="B4" t="str">
-        <f>alunos!B3</f>
-        <v>Ana Klara do Carmo</v>
+      <c r="B4" t="s">
+        <v>9</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -981,6 +990,9 @@
       </c>
       <c r="I4" t="s">
         <v>5</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="K4" t="s">
         <v>5</v>
@@ -1075,9 +1087,8 @@
         <f>alunos!A4</f>
         <v>0</v>
       </c>
-      <c r="B5" t="str">
-        <f>alunos!B4</f>
-        <v>Breno Franco de Lima</v>
+      <c r="B5" t="s">
+        <v>10</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -1099,6 +1110,9 @@
       </c>
       <c r="I5" t="s">
         <v>5</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="K5" t="s">
         <v>5</v>
@@ -1188,14 +1202,13 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
       </c>
-      <c r="B6" t="str">
-        <f>alunos!B5</f>
-        <v>Bruno Vascon</v>
+      <c r="B6" t="s">
+        <v>11</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1218,8 +1231,8 @@
       <c r="I6" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>7</v>
+      <c r="J6" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="K6" t="s">
         <v>5</v>
@@ -1314,32 +1327,15 @@
         <f>alunos!A6</f>
         <v>0</v>
       </c>
-      <c r="B7" t="str">
-        <f>alunos!B6</f>
-        <v>Davi Parreira Cardeal</v>
+      <c r="B7" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
-      <c r="D7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" s="8"/>
+      <c r="J7" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K7" t="s">
         <v>5</v>
       </c>
@@ -1433,9 +1429,8 @@
         <f>alunos!A7</f>
         <v>0</v>
       </c>
-      <c r="B8" t="str">
-        <f>alunos!B7</f>
-        <v>Eloísa Macedo da Silva</v>
+      <c r="B8" t="s">
+        <v>12</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -1458,7 +1453,9 @@
       <c r="I8" t="s">
         <v>5</v>
       </c>
-      <c r="J8" s="8"/>
+      <c r="J8" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K8" t="s">
         <v>5</v>
       </c>
@@ -1552,9 +1549,8 @@
         <f>alunos!A8</f>
         <v>0</v>
       </c>
-      <c r="B9" t="str">
-        <f>alunos!B8</f>
-        <v>Enzo Casadei Macedo</v>
+      <c r="B9" t="s">
+        <v>13</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -1577,7 +1573,9 @@
       <c r="I9" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="8"/>
+      <c r="J9" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K9" t="s">
         <v>5</v>
       </c>
@@ -1671,9 +1669,8 @@
         <f>alunos!A9</f>
         <v>0</v>
       </c>
-      <c r="B10" t="str">
-        <f>alunos!B9</f>
-        <v>Felipe Martins</v>
+      <c r="B10" t="s">
+        <v>14</v>
       </c>
       <c r="C10">
         <v>8</v>
@@ -1696,7 +1693,9 @@
       <c r="I10" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="8"/>
+      <c r="J10" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K10" t="s">
         <v>5</v>
       </c>
@@ -1790,9 +1789,8 @@
         <f>alunos!A10</f>
         <v>0</v>
       </c>
-      <c r="B11" t="str">
-        <f>alunos!B10</f>
-        <v>Gabriel Pereira de Oliveira</v>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -1815,7 +1813,9 @@
       <c r="I11" t="s">
         <v>5</v>
       </c>
-      <c r="J11" s="8"/>
+      <c r="J11" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K11" t="s">
         <v>5</v>
       </c>
@@ -1909,9 +1909,8 @@
         <f>alunos!A11</f>
         <v>0</v>
       </c>
-      <c r="B12" t="str">
-        <f>alunos!B11</f>
-        <v>Giovana Luísa Cezar</v>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -1934,7 +1933,9 @@
       <c r="I12" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="8"/>
+      <c r="J12" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K12" t="s">
         <v>5</v>
       </c>
@@ -2028,22 +2029,12 @@
         <f>alunos!A12</f>
         <v>0</v>
       </c>
-      <c r="B13" t="str">
-        <f>alunos!B12</f>
-        <v>Guilherme Enrico Barichello</v>
+      <c r="B13" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="C13">
         <v>11</v>
       </c>
-      <c r="D13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>5</v>
-      </c>
       <c r="G13" t="s">
         <v>5</v>
       </c>
@@ -2053,7 +2044,9 @@
       <c r="I13" t="s">
         <v>5</v>
       </c>
-      <c r="J13" s="8"/>
+      <c r="J13" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K13" t="s">
         <v>5</v>
       </c>
@@ -2147,9 +2140,8 @@
         <f>alunos!A13</f>
         <v>0</v>
       </c>
-      <c r="B14" t="str">
-        <f>alunos!B13</f>
-        <v>Isabele Hilary Reis Silva</v>
+      <c r="B14" t="s">
+        <v>17</v>
       </c>
       <c r="C14">
         <v>12</v>
@@ -2172,7 +2164,9 @@
       <c r="I14" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="8"/>
+      <c r="J14" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K14" t="s">
         <v>5</v>
       </c>
@@ -2180,7 +2174,7 @@
         <v>5</v>
       </c>
       <c r="M14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N14" t="s">
         <v>5</v>
@@ -2266,9 +2260,8 @@
         <f>alunos!A14</f>
         <v>0</v>
       </c>
-      <c r="B15" t="str">
-        <f>alunos!B14</f>
-        <v>Isabelle Moreira Cezar Barichello</v>
+      <c r="B15" t="s">
+        <v>18</v>
       </c>
       <c r="C15">
         <v>13</v>
@@ -2291,9 +2284,11 @@
       <c r="I15" t="s">
         <v>5</v>
       </c>
-      <c r="J15" s="8"/>
+      <c r="J15" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L15" t="s">
         <v>5</v>
@@ -2385,9 +2380,8 @@
         <f>alunos!A15</f>
         <v>0</v>
       </c>
-      <c r="B16" t="str">
-        <f>alunos!B15</f>
-        <v>Jéssica Guedes Vaz</v>
+      <c r="B16" t="s">
+        <v>19</v>
       </c>
       <c r="C16">
         <v>14</v>
@@ -2410,7 +2404,9 @@
       <c r="I16" t="s">
         <v>5</v>
       </c>
-      <c r="J16" s="8"/>
+      <c r="J16" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K16" t="s">
         <v>5</v>
       </c>
@@ -2418,7 +2414,7 @@
         <v>5</v>
       </c>
       <c r="M16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N16" t="s">
         <v>5</v>
@@ -2504,9 +2500,8 @@
         <f>alunos!A16</f>
         <v>0</v>
       </c>
-      <c r="B17" t="str">
-        <f>alunos!B16</f>
-        <v>Joana Fernandes Fabrin</v>
+      <c r="B17" t="s">
+        <v>20</v>
       </c>
       <c r="C17">
         <v>15</v>
@@ -2529,9 +2524,11 @@
       <c r="I17" t="s">
         <v>5</v>
       </c>
-      <c r="J17" s="8"/>
+      <c r="J17" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L17" t="s">
         <v>5</v>
@@ -2623,9 +2620,8 @@
         <f>alunos!A17</f>
         <v>0</v>
       </c>
-      <c r="B18" t="str">
-        <f>alunos!B17</f>
-        <v>João Henrique Leme da Silva</v>
+      <c r="B18" t="s">
+        <v>21</v>
       </c>
       <c r="C18">
         <v>16</v>
@@ -2648,7 +2644,9 @@
       <c r="I18" t="s">
         <v>5</v>
       </c>
-      <c r="J18" s="8"/>
+      <c r="J18" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K18" t="s">
         <v>5</v>
       </c>
@@ -2742,9 +2740,8 @@
         <f>alunos!A18</f>
         <v>0</v>
       </c>
-      <c r="B19" t="str">
-        <f>alunos!B18</f>
-        <v>João Victor Moraes Lopes</v>
+      <c r="B19" t="s">
+        <v>22</v>
       </c>
       <c r="C19">
         <v>17</v>
@@ -2767,7 +2764,9 @@
       <c r="I19" t="s">
         <v>5</v>
       </c>
-      <c r="J19" s="8"/>
+      <c r="J19" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K19" t="s">
         <v>5</v>
       </c>
@@ -2861,9 +2860,8 @@
         <f>alunos!A19</f>
         <v>0</v>
       </c>
-      <c r="B20" t="str">
-        <f>alunos!B19</f>
-        <v>Kamilly Vitoria Ferreira Silvério</v>
+      <c r="B20" t="s">
+        <v>23</v>
       </c>
       <c r="C20">
         <v>18</v>
@@ -2886,9 +2884,11 @@
       <c r="I20" t="s">
         <v>5</v>
       </c>
-      <c r="J20" s="8"/>
+      <c r="J20" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K20" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L20" t="s">
         <v>5</v>
@@ -2980,9 +2980,8 @@
         <f>alunos!A20</f>
         <v>0</v>
       </c>
-      <c r="B21" t="str">
-        <f>alunos!B20</f>
-        <v>Leonardo Canina Marchiori</v>
+      <c r="B21" t="s">
+        <v>24</v>
       </c>
       <c r="C21">
         <v>19</v>
@@ -3000,12 +2999,14 @@
         <v>5</v>
       </c>
       <c r="H21" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I21" t="s">
         <v>5</v>
       </c>
-      <c r="J21" s="8"/>
+      <c r="J21" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K21" t="s">
         <v>5</v>
       </c>
@@ -3099,9 +3100,8 @@
         <f>alunos!A21</f>
         <v>0</v>
       </c>
-      <c r="B22" t="str">
-        <f>alunos!B21</f>
-        <v>Lívia Fernandes Morais</v>
+      <c r="B22" t="s">
+        <v>25</v>
       </c>
       <c r="C22">
         <v>20</v>
@@ -3124,9 +3124,11 @@
       <c r="I22" t="s">
         <v>5</v>
       </c>
-      <c r="J22" s="8"/>
+      <c r="J22" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K22" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L22" t="s">
         <v>5</v>
@@ -3218,9 +3220,8 @@
         <f>alunos!A22</f>
         <v>0</v>
       </c>
-      <c r="B23" t="str">
-        <f>alunos!B22</f>
-        <v>Maria Eduarda Betim Gomes de Moraes</v>
+      <c r="B23" t="s">
+        <v>26</v>
       </c>
       <c r="C23">
         <v>21</v>
@@ -3238,12 +3239,14 @@
         <v>5</v>
       </c>
       <c r="H23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I23" t="s">
         <v>5</v>
       </c>
-      <c r="J23" s="8"/>
+      <c r="J23" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K23" t="s">
         <v>5</v>
       </c>
@@ -3337,34 +3340,14 @@
         <f>alunos!A23</f>
         <v>0</v>
       </c>
-      <c r="B24" t="str">
-        <f>alunos!B23</f>
-        <v>Mariana Correia Santos</v>
+      <c r="B24" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="C24">
         <v>22</v>
       </c>
-      <c r="D24" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" t="s">
-        <v>5</v>
-      </c>
-      <c r="H24" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" s="8"/>
-      <c r="K24" t="s">
-        <v>5</v>
+      <c r="J24" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="L24" t="s">
         <v>5</v>
@@ -3456,9 +3439,8 @@
         <f>alunos!A24</f>
         <v>0</v>
       </c>
-      <c r="B25" t="str">
-        <f>alunos!B24</f>
-        <v>Miguel Cardoso Pignata</v>
+      <c r="B25" t="s">
+        <v>27</v>
       </c>
       <c r="C25">
         <v>23</v>
@@ -3481,7 +3463,9 @@
       <c r="I25" t="s">
         <v>5</v>
       </c>
-      <c r="J25" s="8"/>
+      <c r="J25" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K25" t="s">
         <v>5</v>
       </c>
@@ -3575,9 +3559,8 @@
         <f>alunos!A25</f>
         <v>0</v>
       </c>
-      <c r="B26" t="str">
-        <f>alunos!B25</f>
-        <v>Mirella Camilotti Perez</v>
+      <c r="B26" t="s">
+        <v>28</v>
       </c>
       <c r="C26">
         <v>24</v>
@@ -3600,7 +3583,9 @@
       <c r="I26" t="s">
         <v>5</v>
       </c>
-      <c r="J26" s="8"/>
+      <c r="J26" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K26" t="s">
         <v>5</v>
       </c>
@@ -3694,9 +3679,8 @@
         <f>alunos!A26</f>
         <v>0</v>
       </c>
-      <c r="B27" t="str">
-        <f>alunos!B26</f>
-        <v>Pietro Cardoso Broleze</v>
+      <c r="B27" t="s">
+        <v>29</v>
       </c>
       <c r="C27">
         <v>25</v>
@@ -3719,18 +3703,20 @@
       <c r="I27" t="s">
         <v>5</v>
       </c>
-      <c r="J27" s="8"/>
+      <c r="J27" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K27" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L27" t="s">
         <v>5</v>
       </c>
       <c r="M27" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N27" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
@@ -3813,9 +3799,8 @@
         <f>alunos!A27</f>
         <v>0</v>
       </c>
-      <c r="B28" t="str">
-        <f>alunos!B27</f>
-        <v>Samuel Gomes Silva</v>
+      <c r="B28" t="s">
+        <v>30</v>
       </c>
       <c r="C28">
         <v>26</v>
@@ -3838,7 +3823,9 @@
       <c r="I28" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="8"/>
+      <c r="J28" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K28" t="s">
         <v>5</v>
       </c>
@@ -3848,7 +3835,7 @@
       <c r="M28" t="s">
         <v>5</v>
       </c>
-      <c r="N28" s="9" t="s">
+      <c r="N28" t="s">
         <v>5</v>
       </c>
       <c r="AU28" s="2"/>
@@ -3932,9 +3919,8 @@
         <f>alunos!A28</f>
         <v>0</v>
       </c>
-      <c r="B29" t="str">
-        <f>alunos!B28</f>
-        <v>Thiago Lima Amaral</v>
+      <c r="B29" t="s">
+        <v>31</v>
       </c>
       <c r="C29">
         <v>27</v>
@@ -3957,7 +3943,9 @@
       <c r="I29" t="s">
         <v>5</v>
       </c>
-      <c r="J29" s="8"/>
+      <c r="J29" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K29" t="s">
         <v>5</v>
       </c>
@@ -4051,9 +4039,8 @@
         <f>alunos!A29</f>
         <v>0</v>
       </c>
-      <c r="B30" t="str">
-        <f>alunos!B29</f>
-        <v>Vitor Rafael Parisato</v>
+      <c r="B30" t="s">
+        <v>32</v>
       </c>
       <c r="C30">
         <v>28</v>
@@ -4076,18 +4063,20 @@
       <c r="I30" t="s">
         <v>5</v>
       </c>
-      <c r="J30" s="8"/>
+      <c r="J30" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K30" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L30" t="s">
         <v>5</v>
       </c>
       <c r="M30" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N30" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
@@ -4170,9 +4159,8 @@
         <f>alunos!A30</f>
         <v>0</v>
       </c>
-      <c r="B31" t="str">
-        <f>alunos!B30</f>
-        <v>Yasmin Drudi</v>
+      <c r="B31" t="s">
+        <v>33</v>
       </c>
       <c r="C31">
         <v>29</v>
@@ -4195,7 +4183,9 @@
       <c r="I31" t="s">
         <v>5</v>
       </c>
-      <c r="J31" s="8"/>
+      <c r="J31" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K31" t="s">
         <v>5</v>
       </c>
@@ -4205,7 +4195,7 @@
       <c r="M31" t="s">
         <v>5</v>
       </c>
-      <c r="N31" t="s">
+      <c r="N31" s="8" t="s">
         <v>5</v>
       </c>
       <c r="AU31" s="2"/>
@@ -4289,13 +4279,21 @@
         <f>alunos!A31</f>
         <v>0</v>
       </c>
-      <c r="B32" t="str">
-        <f>alunos!B31</f>
-        <v>Giovana Ferreira Remorini</v>
+      <c r="B32" t="s">
+        <v>34</v>
       </c>
       <c r="C32">
         <v>30</v>
       </c>
+      <c r="D32" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" t="s">
+        <v>5</v>
+      </c>
       <c r="G32" t="s">
         <v>5</v>
       </c>
@@ -4305,7 +4303,9 @@
       <c r="I32" t="s">
         <v>5</v>
       </c>
-      <c r="J32" s="8"/>
+      <c r="J32" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K32" t="s">
         <v>5</v>
       </c>
@@ -4324,12 +4324,32 @@
         <f>alunos!A32</f>
         <v>0</v>
       </c>
-      <c r="B33" t="str">
-        <f>alunos!B32</f>
-        <v>Carolina da Silva Santos</v>
+      <c r="B33" t="s">
+        <v>35</v>
       </c>
       <c r="C33">
         <v>31</v>
+      </c>
+      <c r="D33" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
@@ -4349,13 +4369,36 @@
         <f>alunos!A33</f>
         <v>0</v>
       </c>
-      <c r="B34" t="str">
-        <f>alunos!B33</f>
-        <v>Letícia Guarizo Tolloto</v>
+      <c r="B34" t="s">
+        <v>36</v>
       </c>
       <c r="C34">
         <v>32</v>
       </c>
+      <c r="D34" t="s">
+        <v>5</v>
+      </c>
+      <c r="E34" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" t="s">
+        <v>5</v>
+      </c>
+      <c r="G34" t="s">
+        <v>5</v>
+      </c>
+      <c r="H34" t="s">
+        <v>5</v>
+      </c>
+      <c r="I34" t="s">
+        <v>5</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K34" t="s">
+        <v>5</v>
+      </c>
       <c r="L34" t="s">
         <v>5</v>
       </c>
@@ -4367,14 +4410,11 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B31">
-    <sortCondition ref="B3:B31"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:N34">
+    <sortCondition ref="B3:B34"/>
   </sortState>
-  <mergeCells count="1">
-    <mergeCell ref="J6:J32"/>
-  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BE3:DG3 BB3:BB22 H4:M6 BE4:BJ10 D4:G31 BK4:DG31 BC11:BJ22 G32:I32 H7:I31 K7:M31 D3:AZ3 O11:BA22 O23:BJ31 O4:AZ10 N4:N34">
+  <conditionalFormatting sqref="BE3:DG3 BB3:BB22 O4:AZ10 BE4:BJ10 BK4:DG31 N4:N34 O11:BA22 BC11:BJ22 O23:BJ31 G32:I32 D4:I31 D3:AZ3 K4:M31 J4:J34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4405,162 +4445,162 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AB3AB6-CD7D-4C12-B07C-1598C34A17D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4506BD3F-C8F1-4C8B-AFBD-61298F6555D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,7 +165,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,14 +193,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -236,7 +228,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -245,11 +237,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -871,7 +862,7 @@
       <c r="I3" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K3" t="s">
@@ -991,7 +982,7 @@
       <c r="I4" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K4" t="s">
@@ -1111,7 +1102,7 @@
       <c r="I5" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K5" t="s">
@@ -1231,7 +1222,7 @@
       <c r="I6" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K6" t="s">
@@ -1327,13 +1318,13 @@
         <f>alunos!A6</f>
         <v>0</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" t="s">
         <v>38</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K7" t="s">
@@ -1453,7 +1444,7 @@
       <c r="I8" t="s">
         <v>5</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K8" t="s">
@@ -1573,7 +1564,7 @@
       <c r="I9" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K9" t="s">
@@ -1693,7 +1684,7 @@
       <c r="I10" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K10" t="s">
@@ -1813,7 +1804,7 @@
       <c r="I11" t="s">
         <v>5</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K11" t="s">
@@ -1933,7 +1924,7 @@
       <c r="I12" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K12" t="s">
@@ -2029,7 +2020,7 @@
         <f>alunos!A12</f>
         <v>0</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" t="s">
         <v>37</v>
       </c>
       <c r="C13">
@@ -2044,7 +2035,7 @@
       <c r="I13" t="s">
         <v>5</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K13" t="s">
@@ -2164,7 +2155,7 @@
       <c r="I14" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="J14" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K14" t="s">
@@ -2284,7 +2275,7 @@
       <c r="I15" t="s">
         <v>5</v>
       </c>
-      <c r="J15" s="10" t="s">
+      <c r="J15" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K15" t="s">
@@ -2404,7 +2395,7 @@
       <c r="I16" t="s">
         <v>5</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="J16" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K16" t="s">
@@ -2524,7 +2515,7 @@
       <c r="I17" t="s">
         <v>5</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="J17" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K17" t="s">
@@ -2644,7 +2635,7 @@
       <c r="I18" t="s">
         <v>5</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="J18" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K18" t="s">
@@ -2764,7 +2755,7 @@
       <c r="I19" t="s">
         <v>5</v>
       </c>
-      <c r="J19" s="10" t="s">
+      <c r="J19" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K19" t="s">
@@ -2884,7 +2875,7 @@
       <c r="I20" t="s">
         <v>5</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J20" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K20" t="s">
@@ -3004,7 +2995,7 @@
       <c r="I21" t="s">
         <v>5</v>
       </c>
-      <c r="J21" s="10" t="s">
+      <c r="J21" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K21" t="s">
@@ -3124,7 +3115,7 @@
       <c r="I22" t="s">
         <v>5</v>
       </c>
-      <c r="J22" s="10" t="s">
+      <c r="J22" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K22" t="s">
@@ -3244,7 +3235,7 @@
       <c r="I23" t="s">
         <v>5</v>
       </c>
-      <c r="J23" s="10" t="s">
+      <c r="J23" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K23" t="s">
@@ -3340,13 +3331,13 @@
         <f>alunos!A23</f>
         <v>0</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" t="s">
         <v>39</v>
       </c>
       <c r="C24">
         <v>22</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="J24" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L24" t="s">
@@ -3463,7 +3454,7 @@
       <c r="I25" t="s">
         <v>5</v>
       </c>
-      <c r="J25" s="10" t="s">
+      <c r="J25" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K25" t="s">
@@ -3583,7 +3574,7 @@
       <c r="I26" t="s">
         <v>5</v>
       </c>
-      <c r="J26" s="10" t="s">
+      <c r="J26" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K26" t="s">
@@ -3703,7 +3694,7 @@
       <c r="I27" t="s">
         <v>5</v>
       </c>
-      <c r="J27" s="10" t="s">
+      <c r="J27" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K27" t="s">
@@ -3823,7 +3814,7 @@
       <c r="I28" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="10" t="s">
+      <c r="J28" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K28" t="s">
@@ -3943,7 +3934,7 @@
       <c r="I29" t="s">
         <v>5</v>
       </c>
-      <c r="J29" s="10" t="s">
+      <c r="J29" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K29" t="s">
@@ -4063,7 +4054,7 @@
       <c r="I30" t="s">
         <v>5</v>
       </c>
-      <c r="J30" s="10" t="s">
+      <c r="J30" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K30" t="s">
@@ -4183,7 +4174,7 @@
       <c r="I31" t="s">
         <v>5</v>
       </c>
-      <c r="J31" s="10" t="s">
+      <c r="J31" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K31" t="s">
@@ -4195,7 +4186,7 @@
       <c r="M31" t="s">
         <v>5</v>
       </c>
-      <c r="N31" s="8" t="s">
+      <c r="N31" s="9" t="s">
         <v>5</v>
       </c>
       <c r="AU31" s="2"/>
@@ -4303,7 +4294,7 @@
       <c r="I32" t="s">
         <v>5</v>
       </c>
-      <c r="J32" s="10" t="s">
+      <c r="J32" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K32" t="s">
@@ -4348,7 +4339,7 @@
       <c r="I33" t="s">
         <v>5</v>
       </c>
-      <c r="J33" s="10" t="s">
+      <c r="J33" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K33" t="s">
@@ -4393,7 +4384,7 @@
       <c r="I34" t="s">
         <v>5</v>
       </c>
-      <c r="J34" s="10" t="s">
+      <c r="J34" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K34" t="s">
@@ -4414,7 +4405,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BE3:DG3 BB3:BB22 O4:AZ10 BE4:BJ10 BK4:DG31 N4:N34 O11:BA22 BC11:BJ22 O23:BJ31 G32:I32 D4:I31 D3:AZ3 K4:M31 J4:J34">
+  <conditionalFormatting sqref="D3:AZ3 BE3:DG3 BB3:BB22 O4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 O11:BA22 BC11:BJ22 O23:BJ31 G32:I32">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4506BD3F-C8F1-4C8B-AFBD-61298F6555D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EF5BE8-9674-4C57-AF8C-89CDD3E75872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,21 +22,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="42">
   <si>
     <t>TER</t>
   </si>
@@ -160,6 +151,9 @@
   <si>
     <t>Carnaval</t>
   </si>
+  <si>
+    <t>p</t>
+  </si>
 </sst>
 </file>
 
@@ -228,7 +222,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -240,7 +234,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -877,6 +870,9 @@
       <c r="N3" t="s">
         <v>5</v>
       </c>
+      <c r="O3" t="s">
+        <v>5</v>
+      </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2"/>
       <c r="AW3" s="2"/>
@@ -997,6 +993,9 @@
       <c r="N4" t="s">
         <v>5</v>
       </c>
+      <c r="O4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1115,7 +1114,10 @@
         <v>5</v>
       </c>
       <c r="N5" t="s">
-        <v>5</v>
+        <v>41</v>
+      </c>
+      <c r="O5" t="s">
+        <v>7</v>
       </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
@@ -1237,6 +1239,9 @@
       <c r="N6" t="s">
         <v>5</v>
       </c>
+      <c r="O6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1339,6 +1344,9 @@
       <c r="N7" t="s">
         <v>5</v>
       </c>
+      <c r="O7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1459,6 +1467,9 @@
       <c r="N8" t="s">
         <v>5</v>
       </c>
+      <c r="O8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1579,6 +1590,9 @@
       <c r="N9" t="s">
         <v>5</v>
       </c>
+      <c r="O9" t="s">
+        <v>7</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1699,6 +1713,9 @@
       <c r="N10" t="s">
         <v>5</v>
       </c>
+      <c r="O10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1819,6 +1836,9 @@
       <c r="N11" t="s">
         <v>5</v>
       </c>
+      <c r="O11" t="s">
+        <v>5</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1939,6 +1959,9 @@
       <c r="N12" t="s">
         <v>5</v>
       </c>
+      <c r="O12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2050,6 +2073,9 @@
       <c r="N13" t="s">
         <v>5</v>
       </c>
+      <c r="O13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2170,6 +2196,9 @@
       <c r="N14" t="s">
         <v>5</v>
       </c>
+      <c r="O14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2290,6 +2319,9 @@
       <c r="N15" t="s">
         <v>5</v>
       </c>
+      <c r="O15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2410,6 +2442,9 @@
       <c r="N16" t="s">
         <v>5</v>
       </c>
+      <c r="O16" t="s">
+        <v>5</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2530,6 +2565,9 @@
       <c r="N17" t="s">
         <v>5</v>
       </c>
+      <c r="O17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2650,6 +2688,9 @@
       <c r="N18" t="s">
         <v>5</v>
       </c>
+      <c r="O18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2770,6 +2811,9 @@
       <c r="N19" t="s">
         <v>5</v>
       </c>
+      <c r="O19" t="s">
+        <v>5</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2890,6 +2934,9 @@
       <c r="N20" t="s">
         <v>5</v>
       </c>
+      <c r="O20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3010,6 +3057,9 @@
       <c r="N21" t="s">
         <v>5</v>
       </c>
+      <c r="O21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3130,6 +3180,9 @@
       <c r="N22" t="s">
         <v>5</v>
       </c>
+      <c r="O22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3250,6 +3303,9 @@
       <c r="N23" t="s">
         <v>5</v>
       </c>
+      <c r="O23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3349,6 +3405,9 @@
       <c r="N24" t="s">
         <v>5</v>
       </c>
+      <c r="O24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3469,6 +3528,9 @@
       <c r="N25" t="s">
         <v>5</v>
       </c>
+      <c r="O25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3589,6 +3651,9 @@
       <c r="N26" t="s">
         <v>5</v>
       </c>
+      <c r="O26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3709,6 +3774,9 @@
       <c r="N27" t="s">
         <v>5</v>
       </c>
+      <c r="O27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3829,6 +3897,9 @@
       <c r="N28" t="s">
         <v>5</v>
       </c>
+      <c r="O28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3949,6 +4020,9 @@
       <c r="N29" t="s">
         <v>5</v>
       </c>
+      <c r="O29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4069,6 +4143,9 @@
       <c r="N30" t="s">
         <v>7</v>
       </c>
+      <c r="O30" t="s">
+        <v>7</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4186,7 +4263,10 @@
       <c r="M31" t="s">
         <v>5</v>
       </c>
-      <c r="N31" s="9" t="s">
+      <c r="N31" t="s">
+        <v>5</v>
+      </c>
+      <c r="O31" t="s">
         <v>5</v>
       </c>
       <c r="AU31" s="2"/>
@@ -4309,8 +4389,11 @@
       <c r="N32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4354,8 +4437,11 @@
       <c r="N33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4397,6 +4483,9 @@
         <v>5</v>
       </c>
       <c r="N34" t="s">
+        <v>5</v>
+      </c>
+      <c r="O34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4405,7 +4494,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AZ3 BE3:DG3 BB3:BB22 O4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 O11:BA22 BC11:BJ22 O23:BJ31 G32:I32">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 BB3:BB22 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P3:AZ10 O3:O34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EF5BE8-9674-4C57-AF8C-89CDD3E75872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A02F62-1D1E-4F89-9C0C-2F561F36DB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,17 +17,28 @@
     <sheet name="alunos" sheetId="2" r:id="rId2"/>
     <sheet name="vistos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="42">
   <si>
     <t>TER</t>
   </si>
@@ -727,61 +738,23 @@
         <v>46086</v>
       </c>
       <c r="P2" s="1">
-        <f>N2+5</f>
-        <v>46089</v>
+        <v>46091</v>
       </c>
       <c r="Q2" s="1">
-        <f>P2+2</f>
-        <v>46091</v>
-      </c>
-      <c r="R2" s="1">
-        <f>P2+5</f>
-        <v>46094</v>
-      </c>
-      <c r="S2" s="1">
-        <f t="shared" ref="S2" si="0">R2+2</f>
-        <v>46096</v>
-      </c>
-      <c r="T2" s="1">
-        <f t="shared" ref="T2" si="1">R2+5</f>
-        <v>46099</v>
-      </c>
-      <c r="U2" s="1">
-        <f t="shared" ref="U2" si="2">T2+2</f>
-        <v>46101</v>
-      </c>
-      <c r="V2" s="1">
-        <f t="shared" ref="V2" si="3">T2+5</f>
-        <v>46104</v>
-      </c>
-      <c r="W2" s="1">
-        <f t="shared" ref="W2" si="4">V2+2</f>
-        <v>46106</v>
-      </c>
-      <c r="X2" s="1">
-        <f t="shared" ref="X2" si="5">V2+5</f>
-        <v>46109</v>
-      </c>
-      <c r="Y2" s="1">
-        <f t="shared" ref="Y2" si="6">X2+2</f>
-        <v>46111</v>
-      </c>
-      <c r="Z2" s="1">
-        <f t="shared" ref="Z2" si="7">X2+5</f>
-        <v>46114</v>
-      </c>
-      <c r="AA2" s="1">
-        <f t="shared" ref="AA2" si="8">Z2+2</f>
-        <v>46116</v>
-      </c>
-      <c r="AB2" s="1">
-        <f t="shared" ref="AB2" si="9">Z2+5</f>
-        <v>46119</v>
-      </c>
-      <c r="AC2" s="1">
-        <f t="shared" ref="AC2" si="10">AB2+2</f>
-        <v>46121</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -871,6 +844,12 @@
         <v>5</v>
       </c>
       <c r="O3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -996,6 +975,12 @@
       <c r="O4" t="s">
         <v>5</v>
       </c>
+      <c r="P4" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1119,6 +1104,12 @@
       <c r="O5" t="s">
         <v>7</v>
       </c>
+      <c r="P5" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1242,6 +1233,12 @@
       <c r="O6" t="s">
         <v>5</v>
       </c>
+      <c r="P6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1347,6 +1344,12 @@
       <c r="O7" t="s">
         <v>5</v>
       </c>
+      <c r="P7" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1470,6 +1473,12 @@
       <c r="O8" t="s">
         <v>5</v>
       </c>
+      <c r="P8" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1593,6 +1602,12 @@
       <c r="O9" t="s">
         <v>7</v>
       </c>
+      <c r="P9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1716,6 +1731,12 @@
       <c r="O10" t="s">
         <v>5</v>
       </c>
+      <c r="P10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1839,6 +1860,12 @@
       <c r="O11" t="s">
         <v>5</v>
       </c>
+      <c r="P11" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>7</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1962,6 +1989,12 @@
       <c r="O12" t="s">
         <v>5</v>
       </c>
+      <c r="P12" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>7</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2076,6 +2109,12 @@
       <c r="O13" t="s">
         <v>5</v>
       </c>
+      <c r="P13" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2199,6 +2238,12 @@
       <c r="O14" t="s">
         <v>5</v>
       </c>
+      <c r="P14" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2322,6 +2367,12 @@
       <c r="O15" t="s">
         <v>5</v>
       </c>
+      <c r="P15" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2445,6 +2496,12 @@
       <c r="O16" t="s">
         <v>5</v>
       </c>
+      <c r="P16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>7</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2568,6 +2625,12 @@
       <c r="O17" t="s">
         <v>5</v>
       </c>
+      <c r="P17" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2691,6 +2754,12 @@
       <c r="O18" t="s">
         <v>5</v>
       </c>
+      <c r="P18" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2814,6 +2883,12 @@
       <c r="O19" t="s">
         <v>5</v>
       </c>
+      <c r="P19" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>5</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2937,6 +3012,12 @@
       <c r="O20" t="s">
         <v>5</v>
       </c>
+      <c r="P20" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3060,6 +3141,12 @@
       <c r="O21" t="s">
         <v>5</v>
       </c>
+      <c r="P21" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3183,6 +3270,12 @@
       <c r="O22" t="s">
         <v>5</v>
       </c>
+      <c r="P22" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3306,6 +3399,12 @@
       <c r="O23" t="s">
         <v>5</v>
       </c>
+      <c r="P23" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3408,6 +3507,12 @@
       <c r="O24" t="s">
         <v>5</v>
       </c>
+      <c r="P24" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3531,6 +3636,12 @@
       <c r="O25" t="s">
         <v>5</v>
       </c>
+      <c r="P25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3654,6 +3765,12 @@
       <c r="O26" t="s">
         <v>5</v>
       </c>
+      <c r="P26" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3777,6 +3894,12 @@
       <c r="O27" t="s">
         <v>5</v>
       </c>
+      <c r="P27" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3900,6 +4023,12 @@
       <c r="O28" t="s">
         <v>5</v>
       </c>
+      <c r="P28" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4023,6 +4152,12 @@
       <c r="O29" t="s">
         <v>5</v>
       </c>
+      <c r="P29" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4146,6 +4281,12 @@
       <c r="O30" t="s">
         <v>7</v>
       </c>
+      <c r="P30" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4269,6 +4410,12 @@
       <c r="O31" t="s">
         <v>5</v>
       </c>
+      <c r="P31" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4392,8 +4539,14 @@
       <c r="O32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P32" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4440,8 +4593,14 @@
       <c r="O33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P33" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4486,6 +4645,12 @@
         <v>5</v>
       </c>
       <c r="O34" t="s">
+        <v>5</v>
+      </c>
+      <c r="P34" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4494,7 +4659,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 BB3:BB22 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P3:AZ10 O3:O34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:Q34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A02F62-1D1E-4F89-9C0C-2F561F36DB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D58894-21E3-40B8-9071-E047DD20ACF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="42">
   <si>
     <t>TER</t>
   </si>
@@ -538,17 +538,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,7 +690,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -743,7 +743,9 @@
       <c r="Q2" s="1">
         <v>12</v>
       </c>
-      <c r="R2" s="1"/>
+      <c r="R2" s="1">
+        <v>46098</v>
+      </c>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
@@ -799,7 +801,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -850,6 +852,9 @@
         <v>5</v>
       </c>
       <c r="Q3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -928,7 +933,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -979,6 +984,9 @@
         <v>5</v>
       </c>
       <c r="Q4" t="s">
+        <v>5</v>
+      </c>
+      <c r="R4" t="s">
         <v>5</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1057,7 +1065,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1109,6 +1117,9 @@
       </c>
       <c r="Q5" t="s">
         <v>5</v>
+      </c>
+      <c r="R5" t="s">
+        <v>7</v>
       </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
@@ -1186,7 +1197,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1237,6 +1248,9 @@
         <v>5</v>
       </c>
       <c r="Q6" t="s">
+        <v>5</v>
+      </c>
+      <c r="R6" t="s">
         <v>5</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1315,7 +1329,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1348,6 +1362,9 @@
         <v>5</v>
       </c>
       <c r="Q7" t="s">
+        <v>5</v>
+      </c>
+      <c r="R7" t="s">
         <v>5</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1426,7 +1443,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1477,6 +1494,9 @@
         <v>5</v>
       </c>
       <c r="Q8" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" t="s">
         <v>5</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1555,7 +1575,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1606,6 +1626,9 @@
         <v>5</v>
       </c>
       <c r="Q9" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" t="s">
         <v>5</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1684,7 +1707,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -1735,6 +1758,9 @@
         <v>5</v>
       </c>
       <c r="Q10" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" t="s">
         <v>5</v>
       </c>
       <c r="AU10" s="2"/>
@@ -1813,7 +1839,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -1865,6 +1891,9 @@
       </c>
       <c r="Q11" t="s">
         <v>7</v>
+      </c>
+      <c r="R11" t="s">
+        <v>5</v>
       </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
@@ -1942,7 +1971,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -1993,6 +2022,9 @@
         <v>5</v>
       </c>
       <c r="Q12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R12" t="s">
         <v>7</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2071,7 +2103,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2113,6 +2145,9 @@
         <v>5</v>
       </c>
       <c r="Q13" t="s">
+        <v>5</v>
+      </c>
+      <c r="R13" t="s">
         <v>5</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2191,7 +2226,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2242,6 +2277,9 @@
         <v>5</v>
       </c>
       <c r="Q14" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" t="s">
         <v>5</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2320,7 +2358,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2371,6 +2409,9 @@
         <v>5</v>
       </c>
       <c r="Q15" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" t="s">
         <v>5</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2449,7 +2490,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2501,6 +2542,9 @@
       </c>
       <c r="Q16" t="s">
         <v>7</v>
+      </c>
+      <c r="R16" t="s">
+        <v>5</v>
       </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
@@ -2578,7 +2622,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -2629,6 +2673,9 @@
         <v>5</v>
       </c>
       <c r="Q17" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" t="s">
         <v>5</v>
       </c>
       <c r="AU17" s="2"/>
@@ -2707,7 +2754,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -2758,6 +2805,9 @@
         <v>5</v>
       </c>
       <c r="Q18" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" t="s">
         <v>5</v>
       </c>
       <c r="AU18" s="2"/>
@@ -2836,7 +2886,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -2887,6 +2937,9 @@
         <v>5</v>
       </c>
       <c r="Q19" t="s">
+        <v>5</v>
+      </c>
+      <c r="R19" t="s">
         <v>5</v>
       </c>
       <c r="AU19" s="2"/>
@@ -2965,7 +3018,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -3016,6 +3069,9 @@
         <v>5</v>
       </c>
       <c r="Q20" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" t="s">
         <v>5</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3094,7 +3150,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3145,6 +3201,9 @@
         <v>5</v>
       </c>
       <c r="Q21" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" t="s">
         <v>5</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3223,7 +3282,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3274,6 +3333,9 @@
         <v>5</v>
       </c>
       <c r="Q22" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" t="s">
         <v>5</v>
       </c>
       <c r="AU22" s="2"/>
@@ -3352,7 +3414,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3403,6 +3465,9 @@
         <v>5</v>
       </c>
       <c r="Q23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" t="s">
         <v>5</v>
       </c>
       <c r="AU23" s="2"/>
@@ -3481,7 +3546,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -3511,6 +3576,9 @@
         <v>5</v>
       </c>
       <c r="Q24" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" t="s">
         <v>5</v>
       </c>
       <c r="AU24" s="2"/>
@@ -3589,7 +3657,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -3640,6 +3708,9 @@
         <v>5</v>
       </c>
       <c r="Q25" t="s">
+        <v>5</v>
+      </c>
+      <c r="R25" t="s">
         <v>5</v>
       </c>
       <c r="AU25" s="2"/>
@@ -3718,7 +3789,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -3769,6 +3840,9 @@
         <v>5</v>
       </c>
       <c r="Q26" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" t="s">
         <v>5</v>
       </c>
       <c r="AU26" s="2"/>
@@ -3847,7 +3921,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -3898,6 +3972,9 @@
         <v>5</v>
       </c>
       <c r="Q27" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" t="s">
         <v>5</v>
       </c>
       <c r="AU27" s="2"/>
@@ -3976,7 +4053,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -4027,6 +4104,9 @@
         <v>5</v>
       </c>
       <c r="Q28" t="s">
+        <v>5</v>
+      </c>
+      <c r="R28" t="s">
         <v>5</v>
       </c>
       <c r="AU28" s="2"/>
@@ -4105,7 +4185,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -4156,6 +4236,9 @@
         <v>5</v>
       </c>
       <c r="Q29" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" t="s">
         <v>5</v>
       </c>
       <c r="AU29" s="2"/>
@@ -4234,7 +4317,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -4285,6 +4368,9 @@
         <v>5</v>
       </c>
       <c r="Q30" t="s">
+        <v>5</v>
+      </c>
+      <c r="R30" t="s">
         <v>5</v>
       </c>
       <c r="AU30" s="2"/>
@@ -4363,7 +4449,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -4414,6 +4500,9 @@
         <v>5</v>
       </c>
       <c r="Q31" t="s">
+        <v>5</v>
+      </c>
+      <c r="R31" t="s">
         <v>5</v>
       </c>
       <c r="AU31" s="2"/>
@@ -4492,7 +4581,7 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>0</v>
@@ -4545,8 +4634,11 @@
       <c r="Q32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4599,8 +4691,11 @@
       <c r="Q33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4651,6 +4746,9 @@
         <v>5</v>
       </c>
       <c r="Q34" t="s">
+        <v>5</v>
+      </c>
+      <c r="R34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4659,7 +4757,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:Q34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:R34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4672,15 +4770,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4688,162 +4786,162 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>39</v>
       </c>
@@ -4857,185 +4955,185 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E8BA54-AA53-4AE8-B8DA-79238D2ECDF5}">
   <dimension ref="A2:A31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Alicia Coelho Gomes de Oliveira</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Ana Klara do Carmo</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Franco de Lima</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Bruno Vascon</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Davi Parreira Cardeal</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Eloísa Macedo da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Enzo Casadei Macedo</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Felipe Martins</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Gabriel Pereira de Oliveira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Giovana Luísa Cezar</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Guilherme Enrico Barichello</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Isabele Hilary Reis Silva</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabelle Moreira Cezar Barichello</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Jéssica Guedes Vaz</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Joana Fernandes Fabrin</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>João Henrique Leme da Silva</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>João Victor Moraes Lopes</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Kamilly Vitoria Ferreira Silvério</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Leonardo Canina Marchiori</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Lívia Fernandes Morais</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Maria Eduarda Betim Gomes de Moraes</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Mariana Correia Santos</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Miguel Cardoso Pignata</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Mirella Camilotti Perez</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pietro Cardoso Broleze</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Samuel Gomes Silva</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Thiago Lima Amaral</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Vitor Rafael Parisato</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Yasmin Drudi</v>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D58894-21E3-40B8-9071-E047DD20ACF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C6D85C-8136-4B45-8F2C-4F647A776A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="42">
   <si>
     <t>TER</t>
   </si>
@@ -538,17 +538,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,7 +690,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -746,7 +746,9 @@
       <c r="R2" s="1">
         <v>46098</v>
       </c>
-      <c r="S2" s="1"/>
+      <c r="S2" s="1">
+        <v>46100</v>
+      </c>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -801,7 +803,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -855,6 +857,9 @@
         <v>5</v>
       </c>
       <c r="R3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -933,7 +938,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -987,6 +992,9 @@
         <v>5</v>
       </c>
       <c r="R4" t="s">
+        <v>5</v>
+      </c>
+      <c r="S4" t="s">
         <v>5</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1065,7 +1073,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1120,6 +1128,9 @@
       </c>
       <c r="R5" t="s">
         <v>7</v>
+      </c>
+      <c r="S5" t="s">
+        <v>5</v>
       </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
@@ -1197,7 +1208,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1251,6 +1262,9 @@
         <v>5</v>
       </c>
       <c r="R6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S6" t="s">
         <v>5</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1329,7 +1343,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1365,6 +1379,9 @@
         <v>5</v>
       </c>
       <c r="R7" t="s">
+        <v>5</v>
+      </c>
+      <c r="S7" t="s">
         <v>5</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1443,7 +1460,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1497,6 +1514,9 @@
         <v>5</v>
       </c>
       <c r="R8" t="s">
+        <v>5</v>
+      </c>
+      <c r="S8" t="s">
         <v>5</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1575,7 +1595,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1629,6 +1649,9 @@
         <v>5</v>
       </c>
       <c r="R9" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" t="s">
         <v>5</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1707,7 +1730,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -1761,6 +1784,9 @@
         <v>5</v>
       </c>
       <c r="R10" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" t="s">
         <v>5</v>
       </c>
       <c r="AU10" s="2"/>
@@ -1839,7 +1865,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -1893,6 +1919,9 @@
         <v>7</v>
       </c>
       <c r="R11" t="s">
+        <v>5</v>
+      </c>
+      <c r="S11" t="s">
         <v>5</v>
       </c>
       <c r="AU11" s="2"/>
@@ -1971,7 +2000,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -2026,6 +2055,9 @@
       </c>
       <c r="R12" t="s">
         <v>7</v>
+      </c>
+      <c r="S12" t="s">
+        <v>5</v>
       </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
@@ -2103,7 +2135,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2148,6 +2180,9 @@
         <v>5</v>
       </c>
       <c r="R13" t="s">
+        <v>5</v>
+      </c>
+      <c r="S13" t="s">
         <v>5</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2226,7 +2261,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2280,6 +2315,9 @@
         <v>5</v>
       </c>
       <c r="R14" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" t="s">
         <v>5</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2358,7 +2396,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2412,6 +2450,9 @@
         <v>5</v>
       </c>
       <c r="R15" t="s">
+        <v>5</v>
+      </c>
+      <c r="S15" t="s">
         <v>5</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2490,7 +2531,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2544,6 +2585,9 @@
         <v>7</v>
       </c>
       <c r="R16" t="s">
+        <v>5</v>
+      </c>
+      <c r="S16" t="s">
         <v>5</v>
       </c>
       <c r="AU16" s="2"/>
@@ -2622,7 +2666,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -2676,6 +2720,9 @@
         <v>5</v>
       </c>
       <c r="R17" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" t="s">
         <v>5</v>
       </c>
       <c r="AU17" s="2"/>
@@ -2754,7 +2801,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -2808,6 +2855,9 @@
         <v>5</v>
       </c>
       <c r="R18" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" t="s">
         <v>5</v>
       </c>
       <c r="AU18" s="2"/>
@@ -2886,7 +2936,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -2940,6 +2990,9 @@
         <v>5</v>
       </c>
       <c r="R19" t="s">
+        <v>5</v>
+      </c>
+      <c r="S19" t="s">
         <v>5</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3018,7 +3071,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -3072,6 +3125,9 @@
         <v>5</v>
       </c>
       <c r="R20" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" t="s">
         <v>5</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3150,7 +3206,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3204,6 +3260,9 @@
         <v>5</v>
       </c>
       <c r="R21" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" t="s">
         <v>5</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3282,7 +3341,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3336,6 +3395,9 @@
         <v>5</v>
       </c>
       <c r="R22" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" t="s">
         <v>5</v>
       </c>
       <c r="AU22" s="2"/>
@@ -3414,7 +3476,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3468,6 +3530,9 @@
         <v>5</v>
       </c>
       <c r="R23" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" t="s">
         <v>5</v>
       </c>
       <c r="AU23" s="2"/>
@@ -3546,7 +3611,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -3580,6 +3645,9 @@
       </c>
       <c r="R24" t="s">
         <v>5</v>
+      </c>
+      <c r="S24" t="s">
+        <v>7</v>
       </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
@@ -3657,7 +3725,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -3711,6 +3779,9 @@
         <v>5</v>
       </c>
       <c r="R25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S25" t="s">
         <v>5</v>
       </c>
       <c r="AU25" s="2"/>
@@ -3789,7 +3860,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -3843,6 +3914,9 @@
         <v>5</v>
       </c>
       <c r="R26" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" t="s">
         <v>5</v>
       </c>
       <c r="AU26" s="2"/>
@@ -3921,7 +3995,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -3975,6 +4049,9 @@
         <v>5</v>
       </c>
       <c r="R27" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" t="s">
         <v>5</v>
       </c>
       <c r="AU27" s="2"/>
@@ -4053,7 +4130,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -4107,6 +4184,9 @@
         <v>5</v>
       </c>
       <c r="R28" t="s">
+        <v>5</v>
+      </c>
+      <c r="S28" t="s">
         <v>5</v>
       </c>
       <c r="AU28" s="2"/>
@@ -4185,7 +4265,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -4239,6 +4319,9 @@
         <v>5</v>
       </c>
       <c r="R29" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" t="s">
         <v>5</v>
       </c>
       <c r="AU29" s="2"/>
@@ -4317,7 +4400,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -4371,6 +4454,9 @@
         <v>5</v>
       </c>
       <c r="R30" t="s">
+        <v>5</v>
+      </c>
+      <c r="S30" t="s">
         <v>5</v>
       </c>
       <c r="AU30" s="2"/>
@@ -4449,7 +4535,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -4503,6 +4589,9 @@
         <v>5</v>
       </c>
       <c r="R31" t="s">
+        <v>5</v>
+      </c>
+      <c r="S31" t="s">
         <v>5</v>
       </c>
       <c r="AU31" s="2"/>
@@ -4581,7 +4670,7 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>0</v>
@@ -4637,8 +4726,11 @@
       <c r="R32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4694,8 +4786,11 @@
       <c r="R33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4749,6 +4844,9 @@
         <v>5</v>
       </c>
       <c r="R34" t="s">
+        <v>5</v>
+      </c>
+      <c r="S34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4757,7 +4855,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:R34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:S34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4770,15 +4868,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4786,162 +4884,162 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>39</v>
       </c>
@@ -4955,185 +5053,185 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E8BA54-AA53-4AE8-B8DA-79238D2ECDF5}">
   <dimension ref="A2:A31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Alicia Coelho Gomes de Oliveira</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Ana Klara do Carmo</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Franco de Lima</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Bruno Vascon</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Davi Parreira Cardeal</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Eloísa Macedo da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Enzo Casadei Macedo</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Felipe Martins</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Gabriel Pereira de Oliveira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Giovana Luísa Cezar</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Guilherme Enrico Barichello</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Isabele Hilary Reis Silva</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabelle Moreira Cezar Barichello</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Jéssica Guedes Vaz</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Joana Fernandes Fabrin</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>João Henrique Leme da Silva</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>João Victor Moraes Lopes</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Kamilly Vitoria Ferreira Silvério</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Leonardo Canina Marchiori</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Lívia Fernandes Morais</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Maria Eduarda Betim Gomes de Moraes</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Mariana Correia Santos</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Miguel Cardoso Pignata</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Mirella Camilotti Perez</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pietro Cardoso Broleze</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Samuel Gomes Silva</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Thiago Lima Amaral</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Vitor Rafael Parisato</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Yasmin Drudi</v>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C6D85C-8136-4B45-8F2C-4F647A776A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558FA925-E168-4ADE-9432-489E603D7C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="42">
   <si>
     <t>TER</t>
   </si>
@@ -749,7 +749,9 @@
       <c r="S2" s="1">
         <v>46100</v>
       </c>
-      <c r="T2" s="1"/>
+      <c r="T2" s="1">
+        <v>46105</v>
+      </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
@@ -860,6 +862,9 @@
         <v>5</v>
       </c>
       <c r="S3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -997,6 +1002,9 @@
       <c r="S4" t="s">
         <v>5</v>
       </c>
+      <c r="T4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1132,6 +1140,9 @@
       <c r="S5" t="s">
         <v>5</v>
       </c>
+      <c r="T5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1267,6 +1278,9 @@
       <c r="S6" t="s">
         <v>5</v>
       </c>
+      <c r="T6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1384,6 +1398,9 @@
       <c r="S7" t="s">
         <v>5</v>
       </c>
+      <c r="T7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1519,6 +1536,9 @@
       <c r="S8" t="s">
         <v>5</v>
       </c>
+      <c r="T8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1654,6 +1674,9 @@
       <c r="S9" t="s">
         <v>5</v>
       </c>
+      <c r="T9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1789,6 +1812,9 @@
       <c r="S10" t="s">
         <v>5</v>
       </c>
+      <c r="T10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1924,6 +1950,9 @@
       <c r="S11" t="s">
         <v>5</v>
       </c>
+      <c r="T11" t="s">
+        <v>5</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2059,6 +2088,9 @@
       <c r="S12" t="s">
         <v>5</v>
       </c>
+      <c r="T12" t="s">
+        <v>7</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2185,6 +2217,9 @@
       <c r="S13" t="s">
         <v>5</v>
       </c>
+      <c r="T13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2320,6 +2355,9 @@
       <c r="S14" t="s">
         <v>5</v>
       </c>
+      <c r="T14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2455,6 +2493,9 @@
       <c r="S15" t="s">
         <v>5</v>
       </c>
+      <c r="T15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2590,6 +2631,9 @@
       <c r="S16" t="s">
         <v>5</v>
       </c>
+      <c r="T16" t="s">
+        <v>5</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2725,6 +2769,9 @@
       <c r="S17" t="s">
         <v>5</v>
       </c>
+      <c r="T17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2860,6 +2907,9 @@
       <c r="S18" t="s">
         <v>5</v>
       </c>
+      <c r="T18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2995,6 +3045,9 @@
       <c r="S19" t="s">
         <v>5</v>
       </c>
+      <c r="T19" t="s">
+        <v>5</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3130,6 +3183,9 @@
       <c r="S20" t="s">
         <v>5</v>
       </c>
+      <c r="T20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3265,6 +3321,9 @@
       <c r="S21" t="s">
         <v>5</v>
       </c>
+      <c r="T21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3400,6 +3459,9 @@
       <c r="S22" t="s">
         <v>5</v>
       </c>
+      <c r="T22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3535,6 +3597,9 @@
       <c r="S23" t="s">
         <v>5</v>
       </c>
+      <c r="T23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3649,6 +3714,9 @@
       <c r="S24" t="s">
         <v>7</v>
       </c>
+      <c r="T24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3784,6 +3852,9 @@
       <c r="S25" t="s">
         <v>5</v>
       </c>
+      <c r="T25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3919,6 +3990,9 @@
       <c r="S26" t="s">
         <v>5</v>
       </c>
+      <c r="T26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4054,6 +4128,9 @@
       <c r="S27" t="s">
         <v>5</v>
       </c>
+      <c r="T27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4189,6 +4266,9 @@
       <c r="S28" t="s">
         <v>5</v>
       </c>
+      <c r="T28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4324,6 +4404,9 @@
       <c r="S29" t="s">
         <v>5</v>
       </c>
+      <c r="T29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4459,6 +4542,9 @@
       <c r="S30" t="s">
         <v>5</v>
       </c>
+      <c r="T30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4594,6 +4680,9 @@
       <c r="S31" t="s">
         <v>5</v>
       </c>
+      <c r="T31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4729,8 +4818,11 @@
       <c r="S32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4789,8 +4881,11 @@
       <c r="S33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4847,6 +4942,9 @@
         <v>5</v>
       </c>
       <c r="S34" t="s">
+        <v>5</v>
+      </c>
+      <c r="T34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4855,7 +4953,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:S34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:T34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558FA925-E168-4ADE-9432-489E603D7C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF093D06-A0A3-4620-9275-5A0C48CC46BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="42">
   <si>
     <t>TER</t>
   </si>
@@ -752,7 +752,9 @@
       <c r="T2" s="1">
         <v>46105</v>
       </c>
-      <c r="U2" s="1"/>
+      <c r="U2" s="1">
+        <v>46107</v>
+      </c>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
@@ -865,6 +867,9 @@
         <v>5</v>
       </c>
       <c r="T3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1005,6 +1010,9 @@
       <c r="T4" t="s">
         <v>5</v>
       </c>
+      <c r="U4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1143,6 +1151,9 @@
       <c r="T5" t="s">
         <v>5</v>
       </c>
+      <c r="U5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1281,6 +1292,9 @@
       <c r="T6" t="s">
         <v>5</v>
       </c>
+      <c r="U6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1401,6 +1415,9 @@
       <c r="T7" t="s">
         <v>5</v>
       </c>
+      <c r="U7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1539,6 +1556,9 @@
       <c r="T8" t="s">
         <v>5</v>
       </c>
+      <c r="U8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1677,6 +1697,9 @@
       <c r="T9" t="s">
         <v>5</v>
       </c>
+      <c r="U9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1815,6 +1838,9 @@
       <c r="T10" t="s">
         <v>5</v>
       </c>
+      <c r="U10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1953,6 +1979,9 @@
       <c r="T11" t="s">
         <v>5</v>
       </c>
+      <c r="U11" t="s">
+        <v>5</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2091,6 +2120,9 @@
       <c r="T12" t="s">
         <v>7</v>
       </c>
+      <c r="U12" t="s">
+        <v>7</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2220,6 +2252,9 @@
       <c r="T13" t="s">
         <v>5</v>
       </c>
+      <c r="U13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2358,6 +2393,9 @@
       <c r="T14" t="s">
         <v>5</v>
       </c>
+      <c r="U14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2496,6 +2534,9 @@
       <c r="T15" t="s">
         <v>5</v>
       </c>
+      <c r="U15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2634,6 +2675,9 @@
       <c r="T16" t="s">
         <v>5</v>
       </c>
+      <c r="U16" t="s">
+        <v>5</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2772,6 +2816,9 @@
       <c r="T17" t="s">
         <v>5</v>
       </c>
+      <c r="U17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2910,6 +2957,9 @@
       <c r="T18" t="s">
         <v>5</v>
       </c>
+      <c r="U18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3048,6 +3098,9 @@
       <c r="T19" t="s">
         <v>5</v>
       </c>
+      <c r="U19" t="s">
+        <v>5</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3186,6 +3239,9 @@
       <c r="T20" t="s">
         <v>5</v>
       </c>
+      <c r="U20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3324,6 +3380,9 @@
       <c r="T21" t="s">
         <v>5</v>
       </c>
+      <c r="U21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3462,6 +3521,9 @@
       <c r="T22" t="s">
         <v>5</v>
       </c>
+      <c r="U22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3600,6 +3662,9 @@
       <c r="T23" t="s">
         <v>5</v>
       </c>
+      <c r="U23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3717,6 +3782,9 @@
       <c r="T24" t="s">
         <v>5</v>
       </c>
+      <c r="U24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3855,6 +3923,9 @@
       <c r="T25" t="s">
         <v>5</v>
       </c>
+      <c r="U25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3993,6 +4064,9 @@
       <c r="T26" t="s">
         <v>5</v>
       </c>
+      <c r="U26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4131,6 +4205,9 @@
       <c r="T27" t="s">
         <v>5</v>
       </c>
+      <c r="U27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4269,6 +4346,9 @@
       <c r="T28" t="s">
         <v>5</v>
       </c>
+      <c r="U28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4407,6 +4487,9 @@
       <c r="T29" t="s">
         <v>5</v>
       </c>
+      <c r="U29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4545,6 +4628,9 @@
       <c r="T30" t="s">
         <v>5</v>
       </c>
+      <c r="U30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4683,6 +4769,9 @@
       <c r="T31" t="s">
         <v>5</v>
       </c>
+      <c r="U31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4821,8 +4910,11 @@
       <c r="T32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4884,8 +4976,11 @@
       <c r="T33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4945,6 +5040,9 @@
         <v>5</v>
       </c>
       <c r="T34" t="s">
+        <v>5</v>
+      </c>
+      <c r="U34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4953,7 +5051,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:T34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:U34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF093D06-A0A3-4620-9275-5A0C48CC46BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD84AC70-0ADA-4448-814A-C3305D6380F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="42">
   <si>
     <t>TER</t>
   </si>
@@ -755,7 +755,9 @@
       <c r="U2" s="1">
         <v>46107</v>
       </c>
-      <c r="V2" s="1"/>
+      <c r="V2" s="1">
+        <v>46112</v>
+      </c>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
@@ -870,6 +872,9 @@
         <v>5</v>
       </c>
       <c r="U3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1013,6 +1018,9 @@
       <c r="U4" t="s">
         <v>5</v>
       </c>
+      <c r="V4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1154,6 +1162,9 @@
       <c r="U5" t="s">
         <v>5</v>
       </c>
+      <c r="V5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1295,6 +1306,9 @@
       <c r="U6" t="s">
         <v>5</v>
       </c>
+      <c r="V6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1418,6 +1432,9 @@
       <c r="U7" t="s">
         <v>5</v>
       </c>
+      <c r="V7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1559,6 +1576,9 @@
       <c r="U8" t="s">
         <v>5</v>
       </c>
+      <c r="V8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1700,6 +1720,9 @@
       <c r="U9" t="s">
         <v>5</v>
       </c>
+      <c r="V9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1841,6 +1864,9 @@
       <c r="U10" t="s">
         <v>5</v>
       </c>
+      <c r="V10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1982,6 +2008,9 @@
       <c r="U11" t="s">
         <v>5</v>
       </c>
+      <c r="V11" t="s">
+        <v>5</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2123,6 +2152,9 @@
       <c r="U12" t="s">
         <v>7</v>
       </c>
+      <c r="V12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2255,6 +2287,9 @@
       <c r="U13" t="s">
         <v>5</v>
       </c>
+      <c r="V13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2396,6 +2431,9 @@
       <c r="U14" t="s">
         <v>5</v>
       </c>
+      <c r="V14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2537,6 +2575,9 @@
       <c r="U15" t="s">
         <v>5</v>
       </c>
+      <c r="V15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2678,6 +2719,9 @@
       <c r="U16" t="s">
         <v>5</v>
       </c>
+      <c r="V16" t="s">
+        <v>5</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2819,6 +2863,9 @@
       <c r="U17" t="s">
         <v>5</v>
       </c>
+      <c r="V17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2960,6 +3007,9 @@
       <c r="U18" t="s">
         <v>5</v>
       </c>
+      <c r="V18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3101,6 +3151,9 @@
       <c r="U19" t="s">
         <v>5</v>
       </c>
+      <c r="V19" t="s">
+        <v>5</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3242,6 +3295,9 @@
       <c r="U20" t="s">
         <v>5</v>
       </c>
+      <c r="V20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3383,6 +3439,9 @@
       <c r="U21" t="s">
         <v>5</v>
       </c>
+      <c r="V21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3524,6 +3583,9 @@
       <c r="U22" t="s">
         <v>5</v>
       </c>
+      <c r="V22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3665,6 +3727,9 @@
       <c r="U23" t="s">
         <v>5</v>
       </c>
+      <c r="V23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3785,6 +3850,9 @@
       <c r="U24" t="s">
         <v>5</v>
       </c>
+      <c r="V24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3926,6 +3994,9 @@
       <c r="U25" t="s">
         <v>5</v>
       </c>
+      <c r="V25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4067,6 +4138,9 @@
       <c r="U26" t="s">
         <v>5</v>
       </c>
+      <c r="V26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4208,6 +4282,9 @@
       <c r="U27" t="s">
         <v>5</v>
       </c>
+      <c r="V27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4349,6 +4426,9 @@
       <c r="U28" t="s">
         <v>5</v>
       </c>
+      <c r="V28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4490,6 +4570,9 @@
       <c r="U29" t="s">
         <v>5</v>
       </c>
+      <c r="V29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4631,6 +4714,9 @@
       <c r="U30" t="s">
         <v>5</v>
       </c>
+      <c r="V30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4772,6 +4858,9 @@
       <c r="U31" t="s">
         <v>5</v>
       </c>
+      <c r="V31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4913,8 +5002,11 @@
       <c r="U32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4979,8 +5071,11 @@
       <c r="U33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -5043,6 +5138,9 @@
         <v>5</v>
       </c>
       <c r="U34" t="s">
+        <v>5</v>
+      </c>
+      <c r="V34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5051,7 +5149,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:U34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:V34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD84AC70-0ADA-4448-814A-C3305D6380F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B619CE4-DF18-4D74-901E-E7096B4D1C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="42">
   <si>
     <t>TER</t>
   </si>
@@ -758,8 +758,12 @@
       <c r="V2" s="1">
         <v>46112</v>
       </c>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
+      <c r="W2" s="1">
+        <v>46114</v>
+      </c>
+      <c r="X2" s="1">
+        <v>46119</v>
+      </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
@@ -875,6 +879,12 @@
         <v>5</v>
       </c>
       <c r="V3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1021,6 +1031,12 @@
       <c r="V4" t="s">
         <v>5</v>
       </c>
+      <c r="W4" t="s">
+        <v>5</v>
+      </c>
+      <c r="X4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1165,6 +1181,12 @@
       <c r="V5" t="s">
         <v>5</v>
       </c>
+      <c r="W5" t="s">
+        <v>5</v>
+      </c>
+      <c r="X5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1309,6 +1331,12 @@
       <c r="V6" t="s">
         <v>5</v>
       </c>
+      <c r="W6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1435,6 +1463,12 @@
       <c r="V7" t="s">
         <v>5</v>
       </c>
+      <c r="W7" t="s">
+        <v>5</v>
+      </c>
+      <c r="X7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1579,6 +1613,12 @@
       <c r="V8" t="s">
         <v>5</v>
       </c>
+      <c r="W8" t="s">
+        <v>5</v>
+      </c>
+      <c r="X8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1723,6 +1763,12 @@
       <c r="V9" t="s">
         <v>5</v>
       </c>
+      <c r="W9" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1867,6 +1913,12 @@
       <c r="V10" t="s">
         <v>5</v>
       </c>
+      <c r="W10" t="s">
+        <v>7</v>
+      </c>
+      <c r="X10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2011,6 +2063,12 @@
       <c r="V11" t="s">
         <v>5</v>
       </c>
+      <c r="W11" t="s">
+        <v>7</v>
+      </c>
+      <c r="X11" t="s">
+        <v>5</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2155,6 +2213,12 @@
       <c r="V12" t="s">
         <v>5</v>
       </c>
+      <c r="W12" t="s">
+        <v>5</v>
+      </c>
+      <c r="X12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2290,6 +2354,12 @@
       <c r="V13" t="s">
         <v>5</v>
       </c>
+      <c r="W13" t="s">
+        <v>5</v>
+      </c>
+      <c r="X13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2434,6 +2504,12 @@
       <c r="V14" t="s">
         <v>5</v>
       </c>
+      <c r="W14" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2578,6 +2654,12 @@
       <c r="V15" t="s">
         <v>5</v>
       </c>
+      <c r="W15" t="s">
+        <v>5</v>
+      </c>
+      <c r="X15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2722,6 +2804,12 @@
       <c r="V16" t="s">
         <v>5</v>
       </c>
+      <c r="W16" t="s">
+        <v>5</v>
+      </c>
+      <c r="X16" t="s">
+        <v>5</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2866,6 +2954,12 @@
       <c r="V17" t="s">
         <v>5</v>
       </c>
+      <c r="W17" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3010,6 +3104,12 @@
       <c r="V18" t="s">
         <v>5</v>
       </c>
+      <c r="W18" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3154,6 +3254,12 @@
       <c r="V19" t="s">
         <v>5</v>
       </c>
+      <c r="W19" t="s">
+        <v>5</v>
+      </c>
+      <c r="X19" t="s">
+        <v>5</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3298,6 +3404,12 @@
       <c r="V20" t="s">
         <v>5</v>
       </c>
+      <c r="W20" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3442,6 +3554,12 @@
       <c r="V21" t="s">
         <v>5</v>
       </c>
+      <c r="W21" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3586,6 +3704,12 @@
       <c r="V22" t="s">
         <v>5</v>
       </c>
+      <c r="W22" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3730,6 +3854,12 @@
       <c r="V23" t="s">
         <v>5</v>
       </c>
+      <c r="W23" t="s">
+        <v>7</v>
+      </c>
+      <c r="X23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3853,6 +3983,12 @@
       <c r="V24" t="s">
         <v>5</v>
       </c>
+      <c r="W24" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3997,6 +4133,12 @@
       <c r="V25" t="s">
         <v>5</v>
       </c>
+      <c r="W25" t="s">
+        <v>5</v>
+      </c>
+      <c r="X25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4141,6 +4283,12 @@
       <c r="V26" t="s">
         <v>5</v>
       </c>
+      <c r="W26" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4285,6 +4433,12 @@
       <c r="V27" t="s">
         <v>5</v>
       </c>
+      <c r="W27" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4429,6 +4583,12 @@
       <c r="V28" t="s">
         <v>5</v>
       </c>
+      <c r="W28" t="s">
+        <v>7</v>
+      </c>
+      <c r="X28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4573,6 +4733,12 @@
       <c r="V29" t="s">
         <v>5</v>
       </c>
+      <c r="W29" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4717,6 +4883,12 @@
       <c r="V30" t="s">
         <v>5</v>
       </c>
+      <c r="W30" t="s">
+        <v>5</v>
+      </c>
+      <c r="X30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4861,6 +5033,12 @@
       <c r="V31" t="s">
         <v>5</v>
       </c>
+      <c r="W31" t="s">
+        <v>5</v>
+      </c>
+      <c r="X31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -5005,8 +5183,14 @@
       <c r="V32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W32" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -5074,8 +5258,14 @@
       <c r="V33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W33" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -5141,6 +5331,12 @@
         <v>5</v>
       </c>
       <c r="V34" t="s">
+        <v>5</v>
+      </c>
+      <c r="W34" t="s">
+        <v>5</v>
+      </c>
+      <c r="X34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5149,7 +5345,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:V34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:X34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B619CE4-DF18-4D74-901E-E7096B4D1C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07345F94-A46F-4EDF-91EC-8C5F7C87C354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="42">
   <si>
     <t>TER</t>
   </si>
@@ -540,10 +540,22 @@
   <dimension ref="A1:DS34"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="50" width="7.7109375" customWidth="1"/>
+    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="50" width="7.7109375" customWidth="1"/>
     <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
     <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
@@ -764,7 +776,9 @@
       <c r="X2" s="1">
         <v>46119</v>
       </c>
-      <c r="Y2" s="1"/>
+      <c r="Y2" s="1">
+        <v>46121</v>
+      </c>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
@@ -885,6 +899,9 @@
         <v>5</v>
       </c>
       <c r="X3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1037,6 +1054,9 @@
       <c r="X4" t="s">
         <v>5</v>
       </c>
+      <c r="Y4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1187,6 +1207,9 @@
       <c r="X5" t="s">
         <v>5</v>
       </c>
+      <c r="Y5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1337,6 +1360,9 @@
       <c r="X6" t="s">
         <v>5</v>
       </c>
+      <c r="Y6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1469,6 +1495,9 @@
       <c r="X7" t="s">
         <v>5</v>
       </c>
+      <c r="Y7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1619,6 +1648,9 @@
       <c r="X8" t="s">
         <v>5</v>
       </c>
+      <c r="Y8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1769,6 +1801,9 @@
       <c r="X9" t="s">
         <v>5</v>
       </c>
+      <c r="Y9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1919,6 +1954,9 @@
       <c r="X10" t="s">
         <v>5</v>
       </c>
+      <c r="Y10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2069,6 +2107,9 @@
       <c r="X11" t="s">
         <v>5</v>
       </c>
+      <c r="Y11" t="s">
+        <v>5</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2219,6 +2260,9 @@
       <c r="X12" t="s">
         <v>5</v>
       </c>
+      <c r="Y12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2360,6 +2404,9 @@
       <c r="X13" t="s">
         <v>5</v>
       </c>
+      <c r="Y13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2510,6 +2557,9 @@
       <c r="X14" t="s">
         <v>5</v>
       </c>
+      <c r="Y14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2660,6 +2710,9 @@
       <c r="X15" t="s">
         <v>5</v>
       </c>
+      <c r="Y15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2810,6 +2863,9 @@
       <c r="X16" t="s">
         <v>5</v>
       </c>
+      <c r="Y16" t="s">
+        <v>7</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2960,6 +3016,9 @@
       <c r="X17" t="s">
         <v>5</v>
       </c>
+      <c r="Y17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3110,6 +3169,9 @@
       <c r="X18" t="s">
         <v>5</v>
       </c>
+      <c r="Y18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3260,6 +3322,9 @@
       <c r="X19" t="s">
         <v>5</v>
       </c>
+      <c r="Y19" t="s">
+        <v>5</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3410,6 +3475,9 @@
       <c r="X20" t="s">
         <v>5</v>
       </c>
+      <c r="Y20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3560,6 +3628,9 @@
       <c r="X21" t="s">
         <v>5</v>
       </c>
+      <c r="Y21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3710,6 +3781,9 @@
       <c r="X22" t="s">
         <v>5</v>
       </c>
+      <c r="Y22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3860,6 +3934,9 @@
       <c r="X23" t="s">
         <v>5</v>
       </c>
+      <c r="Y23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3989,6 +4066,9 @@
       <c r="X24" t="s">
         <v>5</v>
       </c>
+      <c r="Y24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4139,6 +4219,9 @@
       <c r="X25" t="s">
         <v>5</v>
       </c>
+      <c r="Y25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4289,6 +4372,9 @@
       <c r="X26" t="s">
         <v>5</v>
       </c>
+      <c r="Y26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4439,6 +4525,9 @@
       <c r="X27" t="s">
         <v>5</v>
       </c>
+      <c r="Y27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4589,6 +4678,9 @@
       <c r="X28" t="s">
         <v>5</v>
       </c>
+      <c r="Y28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4739,6 +4831,9 @@
       <c r="X29" t="s">
         <v>5</v>
       </c>
+      <c r="Y29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4889,6 +4984,9 @@
       <c r="X30" t="s">
         <v>5</v>
       </c>
+      <c r="Y30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -5039,6 +5137,9 @@
       <c r="X31" t="s">
         <v>5</v>
       </c>
+      <c r="Y31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -5189,8 +5290,11 @@
       <c r="X32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -5264,8 +5368,11 @@
       <c r="X33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -5337,6 +5444,9 @@
         <v>5</v>
       </c>
       <c r="X34" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5345,7 +5455,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:X34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:Y34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07345F94-A46F-4EDF-91EC-8C5F7C87C354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171D7AA5-A10E-4ADD-AA71-5C00165EABA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="42">
   <si>
     <t>TER</t>
   </si>
@@ -550,8 +550,7 @@
     <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="4.140625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="4.28515625" bestFit="1" customWidth="1"/>
@@ -779,7 +778,9 @@
       <c r="Y2" s="1">
         <v>46121</v>
       </c>
-      <c r="Z2" s="1"/>
+      <c r="Z2" s="1">
+        <v>46125</v>
+      </c>
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
@@ -902,6 +903,9 @@
         <v>5</v>
       </c>
       <c r="Y3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1057,6 +1061,9 @@
       <c r="Y4" t="s">
         <v>5</v>
       </c>
+      <c r="Z4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1210,6 +1217,9 @@
       <c r="Y5" t="s">
         <v>5</v>
       </c>
+      <c r="Z5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1363,6 +1373,9 @@
       <c r="Y6" t="s">
         <v>5</v>
       </c>
+      <c r="Z6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1498,6 +1511,9 @@
       <c r="Y7" t="s">
         <v>5</v>
       </c>
+      <c r="Z7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1651,6 +1667,9 @@
       <c r="Y8" t="s">
         <v>5</v>
       </c>
+      <c r="Z8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1804,6 +1823,9 @@
       <c r="Y9" t="s">
         <v>5</v>
       </c>
+      <c r="Z9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1957,6 +1979,9 @@
       <c r="Y10" t="s">
         <v>5</v>
       </c>
+      <c r="Z10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2110,6 +2135,9 @@
       <c r="Y11" t="s">
         <v>5</v>
       </c>
+      <c r="Z11" t="s">
+        <v>7</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2263,6 +2291,9 @@
       <c r="Y12" t="s">
         <v>5</v>
       </c>
+      <c r="Z12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2407,6 +2438,9 @@
       <c r="Y13" t="s">
         <v>5</v>
       </c>
+      <c r="Z13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2560,6 +2594,9 @@
       <c r="Y14" t="s">
         <v>5</v>
       </c>
+      <c r="Z14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2713,6 +2750,9 @@
       <c r="Y15" t="s">
         <v>5</v>
       </c>
+      <c r="Z15" t="s">
+        <v>7</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2866,6 +2906,9 @@
       <c r="Y16" t="s">
         <v>7</v>
       </c>
+      <c r="Z16" t="s">
+        <v>7</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3019,6 +3062,9 @@
       <c r="Y17" t="s">
         <v>5</v>
       </c>
+      <c r="Z17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3172,6 +3218,9 @@
       <c r="Y18" t="s">
         <v>5</v>
       </c>
+      <c r="Z18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3325,6 +3374,9 @@
       <c r="Y19" t="s">
         <v>5</v>
       </c>
+      <c r="Z19" t="s">
+        <v>5</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3478,6 +3530,9 @@
       <c r="Y20" t="s">
         <v>5</v>
       </c>
+      <c r="Z20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3631,6 +3686,9 @@
       <c r="Y21" t="s">
         <v>5</v>
       </c>
+      <c r="Z21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3784,6 +3842,9 @@
       <c r="Y22" t="s">
         <v>5</v>
       </c>
+      <c r="Z22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3937,6 +3998,9 @@
       <c r="Y23" t="s">
         <v>5</v>
       </c>
+      <c r="Z23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -4069,6 +4133,9 @@
       <c r="Y24" t="s">
         <v>5</v>
       </c>
+      <c r="Z24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4222,6 +4289,9 @@
       <c r="Y25" t="s">
         <v>5</v>
       </c>
+      <c r="Z25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4375,6 +4445,9 @@
       <c r="Y26" t="s">
         <v>5</v>
       </c>
+      <c r="Z26" t="s">
+        <v>7</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4528,6 +4601,9 @@
       <c r="Y27" t="s">
         <v>5</v>
       </c>
+      <c r="Z27" t="s">
+        <v>7</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4681,6 +4757,9 @@
       <c r="Y28" t="s">
         <v>5</v>
       </c>
+      <c r="Z28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4834,6 +4913,9 @@
       <c r="Y29" t="s">
         <v>5</v>
       </c>
+      <c r="Z29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4987,6 +5069,9 @@
       <c r="Y30" t="s">
         <v>5</v>
       </c>
+      <c r="Z30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -5140,6 +5225,9 @@
       <c r="Y31" t="s">
         <v>5</v>
       </c>
+      <c r="Z31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -5293,8 +5381,11 @@
       <c r="Y32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -5371,8 +5462,11 @@
       <c r="Y33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -5447,6 +5541,9 @@
         <v>5</v>
       </c>
       <c r="Y34" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5455,7 +5552,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:Y34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:Z34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171D7AA5-A10E-4ADD-AA71-5C00165EABA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AF75BC2-B1B9-4A5D-A9D2-449CDA20412E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="43">
   <si>
     <t>TER</t>
   </si>
@@ -165,6 +165,9 @@
   <si>
     <t>p</t>
   </si>
+  <si>
+    <t>4p/4f</t>
+  </si>
 </sst>
 </file>
 
@@ -212,12 +215,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -233,7 +242,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -245,6 +254,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3374,8 +3384,8 @@
       <c r="Y19" t="s">
         <v>5</v>
       </c>
-      <c r="Z19" t="s">
-        <v>5</v>
+      <c r="Z19" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171D7AA5-A10E-4ADD-AA71-5C00165EABA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B00299-DC43-4D0E-820D-8B03FC1BDBF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="43">
   <si>
     <t>TER</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>p</t>
+  </si>
+  <si>
+    <t>Kamilly Vitória Ferreira Silvério</t>
   </si>
 </sst>
 </file>
@@ -538,28 +541,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="30" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -701,7 +704,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -828,10 +831,9 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
-        <f>alunos!A2</f>
-        <v>0</v>
+        <v>26132174</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -984,10 +986,9 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
-        <f>alunos!A3</f>
-        <v>0</v>
+        <v>26132207</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -1140,10 +1141,9 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
-        <f>alunos!A4</f>
-        <v>0</v>
+        <v>26132186</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -1296,10 +1296,9 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
-        <f>alunos!A5</f>
-        <v>0</v>
+        <v>26132259</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -1452,10 +1451,9 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
-        <f>alunos!A6</f>
-        <v>0</v>
+        <v>26133017</v>
       </c>
       <c r="B7" t="s">
         <v>38</v>
@@ -1590,10 +1588,9 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
-        <f>alunos!A7</f>
-        <v>0</v>
+        <v>26132209</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -1746,10 +1743,9 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
-        <f>alunos!A8</f>
-        <v>0</v>
+        <v>26132211</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -1902,10 +1898,9 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
-        <f>alunos!A9</f>
-        <v>0</v>
+        <v>26132215</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -2058,10 +2053,9 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
-        <f>alunos!A10</f>
-        <v>0</v>
+        <v>26132213</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
@@ -2214,10 +2208,9 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
-        <f>alunos!A11</f>
-        <v>0</v>
+        <v>26132261</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
@@ -2370,10 +2363,9 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
-        <f>alunos!A12</f>
-        <v>0</v>
+        <v>26133027</v>
       </c>
       <c r="B13" t="s">
         <v>37</v>
@@ -2517,10 +2509,9 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
-        <f>alunos!A13</f>
-        <v>0</v>
+        <v>26132176</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -2673,10 +2664,9 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
-        <f>alunos!A14</f>
-        <v>0</v>
+        <v>26132254</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
@@ -2829,10 +2819,9 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
-        <f>alunos!A15</f>
-        <v>0</v>
+        <v>26132326</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
@@ -2985,10 +2974,9 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
-        <f>alunos!A16</f>
-        <v>0</v>
+        <v>26132195</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
@@ -3141,10 +3129,9 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
-        <f>alunos!A17</f>
-        <v>0</v>
+        <v>26132193</v>
       </c>
       <c r="B18" t="s">
         <v>21</v>
@@ -3297,10 +3284,9 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
-        <f>alunos!A18</f>
-        <v>0</v>
+        <v>26132263</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
@@ -3453,10 +3439,9 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
-        <f>alunos!A19</f>
-        <v>0</v>
+        <v>26132178</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -3609,10 +3594,9 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
-        <f>alunos!A20</f>
-        <v>0</v>
+        <v>26132222</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -3765,10 +3749,9 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
-        <f>alunos!A21</f>
-        <v>0</v>
+        <v>26132224</v>
       </c>
       <c r="B22" t="s">
         <v>25</v>
@@ -3921,10 +3904,9 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
-        <f>alunos!A22</f>
-        <v>0</v>
+        <v>26132226</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
@@ -4077,10 +4059,9 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
-        <f>alunos!A23</f>
-        <v>0</v>
+        <v>26133031</v>
       </c>
       <c r="B24" t="s">
         <v>39</v>
@@ -4212,10 +4193,9 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
-        <f>alunos!A24</f>
-        <v>0</v>
+        <v>26132228</v>
       </c>
       <c r="B25" t="s">
         <v>27</v>
@@ -4368,10 +4348,9 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
-        <f>alunos!A25</f>
-        <v>0</v>
+        <v>26132284</v>
       </c>
       <c r="B26" t="s">
         <v>28</v>
@@ -4524,10 +4503,9 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
-        <f>alunos!A26</f>
-        <v>0</v>
+        <v>26132267</v>
       </c>
       <c r="B27" t="s">
         <v>29</v>
@@ -4680,10 +4658,9 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
-        <f>alunos!A27</f>
-        <v>0</v>
+        <v>26132279</v>
       </c>
       <c r="B28" t="s">
         <v>30</v>
@@ -4836,10 +4813,9 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
-        <f>alunos!A28</f>
-        <v>0</v>
+        <v>26132230</v>
       </c>
       <c r="B29" t="s">
         <v>31</v>
@@ -4992,10 +4968,9 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
-        <f>alunos!A29</f>
-        <v>0</v>
+        <v>26132191</v>
       </c>
       <c r="B30" t="s">
         <v>32</v>
@@ -5148,10 +5123,9 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
-        <f>alunos!A30</f>
-        <v>0</v>
+        <v>26132182</v>
       </c>
       <c r="B31" t="s">
         <v>33</v>
@@ -5304,10 +5278,9 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
-        <f>alunos!A31</f>
-        <v>0</v>
+        <v>26132236</v>
       </c>
       <c r="B32" t="s">
         <v>34</v>
@@ -5385,10 +5358,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A33">
-        <f>alunos!A32</f>
-        <v>0</v>
+        <v>26132188</v>
       </c>
       <c r="B33" t="s">
         <v>35</v>
@@ -5466,10 +5438,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A34">
-        <f>alunos!A33</f>
-        <v>0</v>
+        <v>26132234</v>
       </c>
       <c r="B34" t="s">
         <v>36</v>
@@ -5565,15 +5536,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5581,164 +5551,260 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>26132174</v>
+      </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>26132207</v>
+      </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>26132186</v>
+      </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>26132259</v>
+      </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>26133017</v>
+      </c>
       <c r="B6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>26132209</v>
+      </c>
+      <c r="B7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>26132211</v>
+      </c>
+      <c r="B8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>26132215</v>
+      </c>
+      <c r="B9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>26132213</v>
+      </c>
+      <c r="B10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>26132261</v>
+      </c>
+      <c r="B11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>26133027</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>26132176</v>
+      </c>
+      <c r="B13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>26132254</v>
+      </c>
+      <c r="B14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>26132326</v>
+      </c>
+      <c r="B15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>26132195</v>
+      </c>
+      <c r="B16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>26132193</v>
+      </c>
+      <c r="B17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>26132263</v>
+      </c>
+      <c r="B18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>26132178</v>
+      </c>
+      <c r="B19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>26132222</v>
+      </c>
+      <c r="B20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>26132224</v>
+      </c>
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>26132226</v>
+      </c>
+      <c r="B22" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>26133031</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>26132228</v>
+      </c>
+      <c r="B24" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>26132284</v>
+      </c>
+      <c r="B25" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>26132267</v>
+      </c>
+      <c r="B26" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26132279</v>
+      </c>
+      <c r="B27" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>26132230</v>
+      </c>
+      <c r="B28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>26132191</v>
+      </c>
+      <c r="B29" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>26132182</v>
+      </c>
+      <c r="B30" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>26132236</v>
+      </c>
+      <c r="B31" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>26132188</v>
+      </c>
+      <c r="B32" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>26132234</v>
+      </c>
+      <c r="B33" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -5750,187 +5816,187 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E8BA54-AA53-4AE8-B8DA-79238D2ECDF5}">
   <dimension ref="A2:A31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Alicia Coelho Gomes de Oliveira</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Ana Klara do Carmo</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Franco de Lima</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Bruno Vascon</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
-        <f>alunos!B6</f>
+        <f>alunos!B7</f>
         <v>Davi Parreira Cardeal</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
-        <f>alunos!B7</f>
+        <f>alunos!B8</f>
         <v>Eloísa Macedo da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
-        <f>alunos!B8</f>
+        <f>alunos!B9</f>
         <v>Enzo Casadei Macedo</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
-        <f>alunos!B9</f>
+        <f>alunos!B10</f>
         <v>Felipe Martins</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
-        <f>alunos!B10</f>
+        <f>alunos!B11</f>
         <v>Gabriel Pereira de Oliveira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
-        <f>alunos!B11</f>
+        <f>alunos!B13</f>
         <v>Giovana Luísa Cezar</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
-        <f>alunos!B12</f>
+        <f>alunos!B14</f>
         <v>Guilherme Enrico Barichello</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
-        <f>alunos!B13</f>
+        <f>alunos!B15</f>
         <v>Isabele Hilary Reis Silva</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
-        <f>alunos!B14</f>
+        <f>alunos!B16</f>
         <v>Isabelle Moreira Cezar Barichello</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
-        <f>alunos!B15</f>
+        <f>alunos!B17</f>
         <v>Jéssica Guedes Vaz</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
-        <f>alunos!B16</f>
+        <f>alunos!B18</f>
         <v>Joana Fernandes Fabrin</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
-        <f>alunos!B17</f>
+        <f>alunos!B19</f>
         <v>João Henrique Leme da Silva</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
-        <f>alunos!B18</f>
+        <f>alunos!B20</f>
         <v>João Victor Moraes Lopes</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
-        <f>alunos!B19</f>
-        <v>Kamilly Vitoria Ferreira Silvério</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <f>alunos!B21</f>
+        <v>Kamilly Vitória Ferreira Silvério</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
-        <f>alunos!B20</f>
+        <f>alunos!B22</f>
         <v>Leonardo Canina Marchiori</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
-        <f>alunos!B21</f>
+        <f>alunos!B24</f>
         <v>Lívia Fernandes Morais</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
-        <f>alunos!B22</f>
+        <f>alunos!B25</f>
         <v>Maria Eduarda Betim Gomes de Moraes</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
-        <f>alunos!B23</f>
+        <f>alunos!B26</f>
         <v>Mariana Correia Santos</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
-        <f>alunos!B24</f>
+        <f>alunos!B27</f>
         <v>Miguel Cardoso Pignata</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
-        <f>alunos!B25</f>
+        <f>alunos!B28</f>
         <v>Mirella Camilotti Perez</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
-        <f>alunos!B26</f>
+        <f>alunos!B29</f>
         <v>Pietro Cardoso Broleze</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
-        <f>alunos!B27</f>
+        <f>alunos!B30</f>
         <v>Samuel Gomes Silva</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
-        <f>alunos!B28</f>
+        <f>alunos!B31</f>
         <v>Thiago Lima Amaral</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
-        <f>alunos!B29</f>
+        <f>alunos!B32</f>
         <v>Vitor Rafael Parisato</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
-        <f>alunos!B30</f>
+        <f>alunos!B33</f>
         <v>Yasmin Drudi</v>
       </c>
     </row>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B00299-DC43-4D0E-820D-8B03FC1BDBF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06039B7-55AA-42F7-97C2-5A604D4CBF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="43">
   <si>
     <t>TER</t>
   </si>
@@ -215,12 +215,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -236,7 +242,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -246,6 +252,10 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -541,28 +551,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -704,7 +714,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -784,7 +794,9 @@
       <c r="Z2" s="1">
         <v>46125</v>
       </c>
-      <c r="AA2" s="1"/>
+      <c r="AA2" s="1">
+        <v>46128</v>
+      </c>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AU2" s="2"/>
@@ -831,7 +843,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -908,6 +920,9 @@
         <v>5</v>
       </c>
       <c r="Z3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -986,7 +1001,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1063,6 +1078,9 @@
         <v>5</v>
       </c>
       <c r="Z4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA4" t="s">
         <v>5</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1141,7 +1159,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1218,6 +1236,9 @@
         <v>5</v>
       </c>
       <c r="Z5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA5" t="s">
         <v>5</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1296,7 +1317,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -1373,6 +1394,9 @@
         <v>5</v>
       </c>
       <c r="Z6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA6" t="s">
         <v>5</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1451,7 +1475,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -1510,6 +1534,9 @@
         <v>5</v>
       </c>
       <c r="Z7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA7" t="s">
         <v>5</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1588,7 +1615,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -1665,6 +1692,9 @@
         <v>5</v>
       </c>
       <c r="Z8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA8" t="s">
         <v>5</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1743,7 +1773,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -1820,6 +1850,9 @@
         <v>5</v>
       </c>
       <c r="Z9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" t="s">
         <v>5</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1898,7 +1931,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -1975,6 +2008,9 @@
         <v>5</v>
       </c>
       <c r="Z10" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" t="s">
         <v>5</v>
       </c>
       <c r="AU10" s="2"/>
@@ -2053,7 +2089,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -2131,6 +2167,9 @@
       </c>
       <c r="Z11" t="s">
         <v>7</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>5</v>
       </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
@@ -2208,7 +2247,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -2285,6 +2324,9 @@
         <v>5</v>
       </c>
       <c r="Z12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA12" t="s">
         <v>5</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2363,7 +2405,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -2431,6 +2473,9 @@
         <v>5</v>
       </c>
       <c r="Z13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="s">
         <v>5</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2509,7 +2554,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -2586,6 +2631,9 @@
         <v>5</v>
       </c>
       <c r="Z14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" t="s">
         <v>5</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2664,7 +2712,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -2741,6 +2789,9 @@
         <v>5</v>
       </c>
       <c r="Z15" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA15" t="s">
         <v>7</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2819,7 +2870,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -2829,73 +2880,76 @@
       <c r="C16">
         <v>14</v>
       </c>
-      <c r="D16" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H16" t="s">
-        <v>5</v>
-      </c>
-      <c r="I16" t="s">
-        <v>5</v>
-      </c>
-      <c r="J16" s="8" t="s">
+      <c r="D16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="K16" t="s">
-        <v>5</v>
-      </c>
-      <c r="L16" t="s">
-        <v>5</v>
-      </c>
-      <c r="M16" t="s">
+      <c r="K16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="M16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="N16" t="s">
-        <v>5</v>
-      </c>
-      <c r="O16" t="s">
-        <v>5</v>
-      </c>
-      <c r="P16" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q16" t="s">
+      <c r="N16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R16" t="s">
-        <v>5</v>
-      </c>
-      <c r="S16" t="s">
-        <v>5</v>
-      </c>
-      <c r="T16" t="s">
-        <v>5</v>
-      </c>
-      <c r="U16" t="s">
-        <v>5</v>
-      </c>
-      <c r="V16" t="s">
-        <v>5</v>
-      </c>
-      <c r="W16" t="s">
-        <v>5</v>
-      </c>
-      <c r="X16" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y16" t="s">
+      <c r="R16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="W16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="X16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Z16" t="s">
+      <c r="Z16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA16" s="9" t="s">
         <v>7</v>
       </c>
       <c r="AU16" s="2"/>
@@ -2974,7 +3028,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -3051,6 +3105,9 @@
         <v>5</v>
       </c>
       <c r="Z17" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="s">
         <v>5</v>
       </c>
       <c r="AU17" s="2"/>
@@ -3129,7 +3186,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -3206,6 +3263,9 @@
         <v>5</v>
       </c>
       <c r="Z18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA18" t="s">
         <v>5</v>
       </c>
       <c r="AU18" s="2"/>
@@ -3284,7 +3344,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -3361,6 +3421,9 @@
         <v>5</v>
       </c>
       <c r="Z19" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA19" t="s">
         <v>5</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3439,7 +3502,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -3516,6 +3579,9 @@
         <v>5</v>
       </c>
       <c r="Z20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA20" t="s">
         <v>5</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3594,7 +3660,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -3671,6 +3737,9 @@
         <v>5</v>
       </c>
       <c r="Z21" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" t="s">
         <v>5</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3749,7 +3818,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -3826,6 +3895,9 @@
         <v>5</v>
       </c>
       <c r="Z22" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" t="s">
         <v>5</v>
       </c>
       <c r="AU22" s="2"/>
@@ -3904,7 +3976,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -3981,6 +4053,9 @@
         <v>5</v>
       </c>
       <c r="Z23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA23" t="s">
         <v>5</v>
       </c>
       <c r="AU23" s="2"/>
@@ -4059,7 +4134,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -4115,6 +4190,9 @@
         <v>5</v>
       </c>
       <c r="Z24" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA24" t="s">
         <v>5</v>
       </c>
       <c r="AU24" s="2"/>
@@ -4193,7 +4271,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -4270,6 +4348,9 @@
         <v>5</v>
       </c>
       <c r="Z25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA25" t="s">
         <v>5</v>
       </c>
       <c r="AU25" s="2"/>
@@ -4348,7 +4429,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -4426,6 +4507,9 @@
       </c>
       <c r="Z26" t="s">
         <v>7</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>5</v>
       </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
@@ -4503,7 +4587,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -4581,6 +4665,9 @@
       </c>
       <c r="Z27" t="s">
         <v>7</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>5</v>
       </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
@@ -4658,7 +4745,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -4735,6 +4822,9 @@
         <v>5</v>
       </c>
       <c r="Z28" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA28" t="s">
         <v>5</v>
       </c>
       <c r="AU28" s="2"/>
@@ -4813,7 +4903,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -4890,6 +4980,9 @@
         <v>5</v>
       </c>
       <c r="Z29" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" t="s">
         <v>5</v>
       </c>
       <c r="AU29" s="2"/>
@@ -4968,7 +5061,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -5045,6 +5138,9 @@
         <v>5</v>
       </c>
       <c r="Z30" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA30" t="s">
         <v>5</v>
       </c>
       <c r="AU30" s="2"/>
@@ -5123,7 +5219,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -5200,6 +5296,9 @@
         <v>5</v>
       </c>
       <c r="Z31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA31" t="s">
         <v>5</v>
       </c>
       <c r="AU31" s="2"/>
@@ -5278,7 +5377,7 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -5357,8 +5456,11 @@
       <c r="Z32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -5437,8 +5539,11 @@
       <c r="Z33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -5515,6 +5620,9 @@
         <v>5</v>
       </c>
       <c r="Z34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5523,7 +5631,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 P3:AZ10 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P11:BA22 BC11:BJ22 P23:BJ31 G32:I32 P32:Z34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 BC11:BJ22 G32:I32 P3:AZ3 AB4:AZ10 AB23:BJ31 AB11:BA22 P4:AA34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -5536,14 +5644,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5551,7 +5659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -5559,7 +5667,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -5567,7 +5675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -5575,7 +5683,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -5583,7 +5691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -5591,7 +5699,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -5599,7 +5707,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -5607,7 +5715,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -5615,7 +5723,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -5623,7 +5731,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -5631,7 +5739,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -5639,7 +5747,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -5647,7 +5755,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -5655,7 +5763,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -5663,7 +5771,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -5671,7 +5779,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -5679,7 +5787,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -5687,7 +5795,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -5695,7 +5803,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -5703,7 +5811,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -5711,7 +5819,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -5719,7 +5827,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -5727,7 +5835,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -5735,7 +5843,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -5743,7 +5851,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -5751,7 +5859,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -5759,7 +5867,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -5767,7 +5875,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -5775,7 +5883,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -5783,7 +5891,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -5791,7 +5899,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -5799,7 +5907,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132234</v>
       </c>
@@ -5816,185 +5924,185 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E8BA54-AA53-4AE8-B8DA-79238D2ECDF5}">
   <dimension ref="A2:A31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Alicia Coelho Gomes de Oliveira</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Ana Klara do Carmo</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Franco de Lima</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Bruno Vascon</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B7</f>
         <v>Davi Parreira Cardeal</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B8</f>
         <v>Eloísa Macedo da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B9</f>
         <v>Enzo Casadei Macedo</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B10</f>
         <v>Felipe Martins</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B11</f>
         <v>Gabriel Pereira de Oliveira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B13</f>
         <v>Giovana Luísa Cezar</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B14</f>
         <v>Guilherme Enrico Barichello</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B15</f>
         <v>Isabele Hilary Reis Silva</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B16</f>
         <v>Isabelle Moreira Cezar Barichello</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B17</f>
         <v>Jéssica Guedes Vaz</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B18</f>
         <v>Joana Fernandes Fabrin</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B19</f>
         <v>João Henrique Leme da Silva</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B20</f>
         <v>João Victor Moraes Lopes</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B21</f>
         <v>Kamilly Vitória Ferreira Silvério</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B22</f>
         <v>Leonardo Canina Marchiori</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B24</f>
         <v>Lívia Fernandes Morais</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B25</f>
         <v>Maria Eduarda Betim Gomes de Moraes</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B26</f>
         <v>Mariana Correia Santos</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B27</f>
         <v>Miguel Cardoso Pignata</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B28</f>
         <v>Mirella Camilotti Perez</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B29</f>
         <v>Pietro Cardoso Broleze</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B30</f>
         <v>Samuel Gomes Silva</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B31</f>
         <v>Thiago Lima Amaral</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B32</f>
         <v>Vitor Rafael Parisato</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B33</f>
         <v>Yasmin Drudi</v>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06039B7-55AA-42F7-97C2-5A604D4CBF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A4366E-679D-414F-A221-FE24E48C6B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="44">
   <si>
     <t>TER</t>
   </si>
@@ -167,6 +167,9 @@
   </si>
   <si>
     <t>Kamilly Vitória Ferreira Silvério</t>
+  </si>
+  <si>
+    <t>Feriado</t>
   </si>
 </sst>
 </file>
@@ -553,7 +556,7 @@
   <dimension ref="A1:DS34"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
@@ -563,10 +566,9 @@
     <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="30" max="50" width="7.7109375" customWidth="1"/>
     <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
     <col min="52" max="106" width="7.7109375" customWidth="1"/>
@@ -797,8 +799,12 @@
       <c r="AA2" s="1">
         <v>46128</v>
       </c>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
+      <c r="AB2" s="1">
+        <v>46133</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>46135</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -923,6 +929,12 @@
         <v>5</v>
       </c>
       <c r="AA3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1083,6 +1095,12 @@
       <c r="AA4" t="s">
         <v>5</v>
       </c>
+      <c r="AB4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1241,6 +1259,12 @@
       <c r="AA5" t="s">
         <v>5</v>
       </c>
+      <c r="AB5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1399,6 +1423,12 @@
       <c r="AA6" t="s">
         <v>5</v>
       </c>
+      <c r="AB6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1539,6 +1569,12 @@
       <c r="AA7" t="s">
         <v>5</v>
       </c>
+      <c r="AB7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1697,6 +1733,12 @@
       <c r="AA8" t="s">
         <v>5</v>
       </c>
+      <c r="AB8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1855,6 +1897,12 @@
       <c r="AA9" t="s">
         <v>5</v>
       </c>
+      <c r="AB9" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2013,6 +2061,12 @@
       <c r="AA10" t="s">
         <v>5</v>
       </c>
+      <c r="AB10" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2171,6 +2225,12 @@
       <c r="AA11" t="s">
         <v>5</v>
       </c>
+      <c r="AB11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>5</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2329,6 +2389,12 @@
       <c r="AA12" t="s">
         <v>5</v>
       </c>
+      <c r="AB12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2478,6 +2544,12 @@
       <c r="AA13" t="s">
         <v>5</v>
       </c>
+      <c r="AB13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2636,6 +2708,12 @@
       <c r="AA14" t="s">
         <v>5</v>
       </c>
+      <c r="AB14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2794,6 +2872,12 @@
       <c r="AA15" t="s">
         <v>7</v>
       </c>
+      <c r="AB15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2952,6 +3036,12 @@
       <c r="AA16" s="9" t="s">
         <v>7</v>
       </c>
+      <c r="AB16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC16" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3110,6 +3200,12 @@
       <c r="AA17" t="s">
         <v>5</v>
       </c>
+      <c r="AB17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3268,6 +3364,12 @@
       <c r="AA18" t="s">
         <v>5</v>
       </c>
+      <c r="AB18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3426,6 +3528,12 @@
       <c r="AA19" t="s">
         <v>5</v>
       </c>
+      <c r="AB19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>5</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3584,6 +3692,12 @@
       <c r="AA20" t="s">
         <v>5</v>
       </c>
+      <c r="AB20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3742,6 +3856,12 @@
       <c r="AA21" t="s">
         <v>5</v>
       </c>
+      <c r="AB21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3900,6 +4020,12 @@
       <c r="AA22" t="s">
         <v>5</v>
       </c>
+      <c r="AB22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -4058,6 +4184,12 @@
       <c r="AA23" t="s">
         <v>5</v>
       </c>
+      <c r="AB23" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -4195,6 +4327,12 @@
       <c r="AA24" t="s">
         <v>5</v>
       </c>
+      <c r="AB24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4353,6 +4491,12 @@
       <c r="AA25" t="s">
         <v>5</v>
       </c>
+      <c r="AB25" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4511,6 +4655,12 @@
       <c r="AA26" t="s">
         <v>5</v>
       </c>
+      <c r="AB26" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4669,6 +4819,12 @@
       <c r="AA27" t="s">
         <v>5</v>
       </c>
+      <c r="AB27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4827,6 +4983,12 @@
       <c r="AA28" t="s">
         <v>5</v>
       </c>
+      <c r="AB28" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4985,6 +5147,12 @@
       <c r="AA29" t="s">
         <v>5</v>
       </c>
+      <c r="AB29" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -5143,6 +5311,12 @@
       <c r="AA30" t="s">
         <v>5</v>
       </c>
+      <c r="AB30" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -5301,6 +5475,12 @@
       <c r="AA31" t="s">
         <v>5</v>
       </c>
+      <c r="AB31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -5459,8 +5639,14 @@
       <c r="AA32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB32" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -5542,8 +5728,14 @@
       <c r="AA33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB33" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -5623,6 +5815,12 @@
         <v>5</v>
       </c>
       <c r="AA34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5631,7 +5829,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 BB3:BB22 O3:O34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 BC11:BJ22 G32:I32 P3:AZ3 AB4:AZ10 AB23:BJ31 AB11:BA22 P4:AA34">
+  <conditionalFormatting sqref="D3:N3 P3:AZ3 BE3:DG3 BB3:BB22 O3:O34 AC4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AC11:BA22 BC11:BJ22 AC23:BJ31 G32:I32 P4:AB34 AC32:AC34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A4366E-679D-414F-A221-FE24E48C6B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216382F8-79F9-42D3-B50C-9D3F5D209902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="44">
   <si>
     <t>TER</t>
   </si>
@@ -653,7 +653,9 @@
       <c r="AC1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AD1" s="1"/>
+      <c r="AD1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
@@ -805,6 +807,12 @@
       <c r="AC2" s="1">
         <v>46135</v>
       </c>
+      <c r="AD2" s="1">
+        <v>46140</v>
+      </c>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -935,6 +943,9 @@
         <v>43</v>
       </c>
       <c r="AC3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1101,6 +1112,9 @@
       <c r="AC4" t="s">
         <v>5</v>
       </c>
+      <c r="AD4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1265,6 +1279,9 @@
       <c r="AC5" t="s">
         <v>5</v>
       </c>
+      <c r="AD5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1429,6 +1446,9 @@
       <c r="AC6" t="s">
         <v>5</v>
       </c>
+      <c r="AD6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1575,6 +1595,9 @@
       <c r="AC7" t="s">
         <v>5</v>
       </c>
+      <c r="AD7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1739,6 +1762,9 @@
       <c r="AC8" t="s">
         <v>5</v>
       </c>
+      <c r="AD8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1903,6 +1929,9 @@
       <c r="AC9" t="s">
         <v>5</v>
       </c>
+      <c r="AD9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2067,6 +2096,9 @@
       <c r="AC10" t="s">
         <v>5</v>
       </c>
+      <c r="AD10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2231,6 +2263,9 @@
       <c r="AC11" t="s">
         <v>5</v>
       </c>
+      <c r="AD11" t="s">
+        <v>5</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2395,6 +2430,9 @@
       <c r="AC12" t="s">
         <v>5</v>
       </c>
+      <c r="AD12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2550,6 +2588,9 @@
       <c r="AC13" t="s">
         <v>5</v>
       </c>
+      <c r="AD13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2714,6 +2755,9 @@
       <c r="AC14" t="s">
         <v>5</v>
       </c>
+      <c r="AD14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2878,6 +2922,9 @@
       <c r="AC15" t="s">
         <v>5</v>
       </c>
+      <c r="AD15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3042,6 +3089,9 @@
       <c r="AC16" s="9" t="s">
         <v>7</v>
       </c>
+      <c r="AD16" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3206,6 +3256,9 @@
       <c r="AC17" t="s">
         <v>5</v>
       </c>
+      <c r="AD17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3370,6 +3423,9 @@
       <c r="AC18" t="s">
         <v>5</v>
       </c>
+      <c r="AD18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3534,6 +3590,9 @@
       <c r="AC19" t="s">
         <v>5</v>
       </c>
+      <c r="AD19" t="s">
+        <v>5</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3698,6 +3757,9 @@
       <c r="AC20" t="s">
         <v>5</v>
       </c>
+      <c r="AD20" t="s">
+        <v>7</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3862,6 +3924,9 @@
       <c r="AC21" t="s">
         <v>5</v>
       </c>
+      <c r="AD21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -4026,6 +4091,9 @@
       <c r="AC22" t="s">
         <v>5</v>
       </c>
+      <c r="AD22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -4190,6 +4258,9 @@
       <c r="AC23" t="s">
         <v>5</v>
       </c>
+      <c r="AD23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -4333,6 +4404,9 @@
       <c r="AC24" t="s">
         <v>5</v>
       </c>
+      <c r="AD24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4497,6 +4571,9 @@
       <c r="AC25" t="s">
         <v>5</v>
       </c>
+      <c r="AD25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4661,6 +4738,9 @@
       <c r="AC26" t="s">
         <v>5</v>
       </c>
+      <c r="AD26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4825,6 +4905,9 @@
       <c r="AC27" t="s">
         <v>5</v>
       </c>
+      <c r="AD27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4989,6 +5072,9 @@
       <c r="AC28" t="s">
         <v>5</v>
       </c>
+      <c r="AD28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -5153,6 +5239,9 @@
       <c r="AC29" t="s">
         <v>5</v>
       </c>
+      <c r="AD29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -5317,6 +5406,9 @@
       <c r="AC30" t="s">
         <v>5</v>
       </c>
+      <c r="AD30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -5481,6 +5573,9 @@
       <c r="AC31" t="s">
         <v>5</v>
       </c>
+      <c r="AD31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -5645,8 +5740,11 @@
       <c r="AC32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -5734,8 +5832,11 @@
       <c r="AC33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -5821,6 +5922,9 @@
         <v>43</v>
       </c>
       <c r="AC34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5829,7 +5933,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 P3:AZ3 BE3:DG3 BB3:BB22 O3:O34 AC4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AC11:BA22 BC11:BJ22 AC23:BJ31 G32:I32 P4:AB34 AC32:AC34">
+  <conditionalFormatting sqref="D3:N3 P3:AZ3 BE3:DG3 BB3:BB22 O3:O34 AC4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P4:AB34 AC11:BA22 BC11:BJ22 AC23:BJ31 G32:I32 AC32:AD34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216382F8-79F9-42D3-B50C-9D3F5D209902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF195BC4-CACD-4CF1-8D89-B75E81CEE145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="44">
   <si>
     <t>TER</t>
   </si>
@@ -656,7 +656,9 @@
       <c r="AD1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="1"/>
+      <c r="AE1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
       <c r="AH1" s="1"/>
@@ -810,7 +812,9 @@
       <c r="AD2" s="1">
         <v>46140</v>
       </c>
-      <c r="AE2" s="1"/>
+      <c r="AE2" s="1">
+        <v>46142</v>
+      </c>
       <c r="AF2" s="1"/>
       <c r="AG2" s="1"/>
       <c r="AU2" s="2"/>
@@ -946,6 +950,9 @@
         <v>5</v>
       </c>
       <c r="AD3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1115,6 +1122,9 @@
       <c r="AD4" t="s">
         <v>5</v>
       </c>
+      <c r="AE4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1282,6 +1292,9 @@
       <c r="AD5" t="s">
         <v>5</v>
       </c>
+      <c r="AE5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1449,6 +1462,9 @@
       <c r="AD6" t="s">
         <v>5</v>
       </c>
+      <c r="AE6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1598,6 +1614,9 @@
       <c r="AD7" t="s">
         <v>5</v>
       </c>
+      <c r="AE7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1765,6 +1784,9 @@
       <c r="AD8" t="s">
         <v>5</v>
       </c>
+      <c r="AE8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1932,6 +1954,9 @@
       <c r="AD9" t="s">
         <v>5</v>
       </c>
+      <c r="AE9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2099,6 +2124,9 @@
       <c r="AD10" t="s">
         <v>5</v>
       </c>
+      <c r="AE10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2266,6 +2294,9 @@
       <c r="AD11" t="s">
         <v>5</v>
       </c>
+      <c r="AE11" t="s">
+        <v>5</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2433,6 +2464,9 @@
       <c r="AD12" t="s">
         <v>5</v>
       </c>
+      <c r="AE12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2591,6 +2625,9 @@
       <c r="AD13" t="s">
         <v>5</v>
       </c>
+      <c r="AE13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2758,6 +2795,9 @@
       <c r="AD14" t="s">
         <v>5</v>
       </c>
+      <c r="AE14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2925,6 +2965,9 @@
       <c r="AD15" t="s">
         <v>5</v>
       </c>
+      <c r="AE15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3092,6 +3135,9 @@
       <c r="AD16" s="9" t="s">
         <v>7</v>
       </c>
+      <c r="AE16" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3259,6 +3305,9 @@
       <c r="AD17" t="s">
         <v>5</v>
       </c>
+      <c r="AE17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3426,6 +3475,9 @@
       <c r="AD18" t="s">
         <v>5</v>
       </c>
+      <c r="AE18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3593,6 +3645,9 @@
       <c r="AD19" t="s">
         <v>5</v>
       </c>
+      <c r="AE19" t="s">
+        <v>5</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3760,6 +3815,9 @@
       <c r="AD20" t="s">
         <v>7</v>
       </c>
+      <c r="AE20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3927,6 +3985,9 @@
       <c r="AD21" t="s">
         <v>5</v>
       </c>
+      <c r="AE21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -4094,6 +4155,9 @@
       <c r="AD22" t="s">
         <v>5</v>
       </c>
+      <c r="AE22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -4261,6 +4325,9 @@
       <c r="AD23" t="s">
         <v>5</v>
       </c>
+      <c r="AE23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -4407,6 +4474,9 @@
       <c r="AD24" t="s">
         <v>5</v>
       </c>
+      <c r="AE24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4574,6 +4644,9 @@
       <c r="AD25" t="s">
         <v>5</v>
       </c>
+      <c r="AE25" t="s">
+        <v>7</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4741,6 +4814,9 @@
       <c r="AD26" t="s">
         <v>5</v>
       </c>
+      <c r="AE26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4908,6 +4984,9 @@
       <c r="AD27" t="s">
         <v>5</v>
       </c>
+      <c r="AE27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -5075,6 +5154,9 @@
       <c r="AD28" t="s">
         <v>5</v>
       </c>
+      <c r="AE28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -5242,6 +5324,9 @@
       <c r="AD29" t="s">
         <v>5</v>
       </c>
+      <c r="AE29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -5409,6 +5494,9 @@
       <c r="AD30" t="s">
         <v>5</v>
       </c>
+      <c r="AE30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -5576,6 +5664,9 @@
       <c r="AD31" t="s">
         <v>5</v>
       </c>
+      <c r="AE31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -5743,8 +5834,11 @@
       <c r="AD32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -5835,8 +5929,11 @@
       <c r="AD33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -5925,6 +6022,9 @@
         <v>5</v>
       </c>
       <c r="AD34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5933,7 +6033,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 P3:AZ3 BE3:DG3 BB3:BB22 O3:O34 AC4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P4:AB34 AC11:BA22 BC11:BJ22 AC23:BJ31 G32:I32 AC32:AD34">
+  <conditionalFormatting sqref="D3:N3 P3:AZ3 BE3:DG3 BB3:BB22 O3:O34 AC4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P4:AB34 AC11:BA22 BC11:BJ22 AC23:BJ31 G32:I32 AC32:AE34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF195BC4-CACD-4CF1-8D89-B75E81CEE145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417F4166-59FA-471A-9E7E-236D6E65AE1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="44">
   <si>
     <t>TER</t>
   </si>
@@ -659,8 +659,12 @@
       <c r="AE1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
+      <c r="AF1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
@@ -815,8 +819,12 @@
       <c r="AE2" s="1">
         <v>46142</v>
       </c>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
+      <c r="AF2" s="1">
+        <v>46147</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>46149</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -953,6 +961,9 @@
         <v>5</v>
       </c>
       <c r="AE3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1125,6 +1136,9 @@
       <c r="AE4" t="s">
         <v>5</v>
       </c>
+      <c r="AF4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1295,6 +1309,9 @@
       <c r="AE5" t="s">
         <v>5</v>
       </c>
+      <c r="AF5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1465,6 +1482,9 @@
       <c r="AE6" t="s">
         <v>5</v>
       </c>
+      <c r="AF6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1617,6 +1637,9 @@
       <c r="AE7" t="s">
         <v>5</v>
       </c>
+      <c r="AF7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1787,6 +1810,9 @@
       <c r="AE8" t="s">
         <v>5</v>
       </c>
+      <c r="AF8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1957,6 +1983,9 @@
       <c r="AE9" t="s">
         <v>5</v>
       </c>
+      <c r="AF9" t="s">
+        <v>7</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2127,6 +2156,9 @@
       <c r="AE10" t="s">
         <v>5</v>
       </c>
+      <c r="AF10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2297,6 +2329,9 @@
       <c r="AE11" t="s">
         <v>5</v>
       </c>
+      <c r="AF11" t="s">
+        <v>5</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2467,6 +2502,9 @@
       <c r="AE12" t="s">
         <v>5</v>
       </c>
+      <c r="AF12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2628,6 +2666,9 @@
       <c r="AE13" t="s">
         <v>5</v>
       </c>
+      <c r="AF13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2798,6 +2839,9 @@
       <c r="AE14" t="s">
         <v>5</v>
       </c>
+      <c r="AF14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2968,6 +3012,9 @@
       <c r="AE15" t="s">
         <v>5</v>
       </c>
+      <c r="AF15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3138,6 +3185,9 @@
       <c r="AE16" s="9" t="s">
         <v>7</v>
       </c>
+      <c r="AF16" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3308,6 +3358,9 @@
       <c r="AE17" t="s">
         <v>5</v>
       </c>
+      <c r="AF17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3478,6 +3531,9 @@
       <c r="AE18" t="s">
         <v>5</v>
       </c>
+      <c r="AF18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3648,6 +3704,9 @@
       <c r="AE19" t="s">
         <v>5</v>
       </c>
+      <c r="AF19" t="s">
+        <v>5</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3818,6 +3877,9 @@
       <c r="AE20" t="s">
         <v>5</v>
       </c>
+      <c r="AF20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3988,6 +4050,9 @@
       <c r="AE21" t="s">
         <v>5</v>
       </c>
+      <c r="AF21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -4158,6 +4223,9 @@
       <c r="AE22" t="s">
         <v>5</v>
       </c>
+      <c r="AF22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -4328,6 +4396,9 @@
       <c r="AE23" t="s">
         <v>5</v>
       </c>
+      <c r="AF23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -4477,6 +4548,9 @@
       <c r="AE24" t="s">
         <v>5</v>
       </c>
+      <c r="AF24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4647,6 +4721,9 @@
       <c r="AE25" t="s">
         <v>7</v>
       </c>
+      <c r="AF25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4817,6 +4894,9 @@
       <c r="AE26" t="s">
         <v>5</v>
       </c>
+      <c r="AF26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4987,6 +5067,9 @@
       <c r="AE27" t="s">
         <v>5</v>
       </c>
+      <c r="AF27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -5157,6 +5240,9 @@
       <c r="AE28" t="s">
         <v>5</v>
       </c>
+      <c r="AF28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -5327,6 +5413,9 @@
       <c r="AE29" t="s">
         <v>5</v>
       </c>
+      <c r="AF29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -5497,6 +5586,9 @@
       <c r="AE30" t="s">
         <v>5</v>
       </c>
+      <c r="AF30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -5667,6 +5759,9 @@
       <c r="AE31" t="s">
         <v>5</v>
       </c>
+      <c r="AF31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -5837,8 +5932,11 @@
       <c r="AE32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -5932,8 +6030,11 @@
       <c r="AE33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -6025,6 +6126,9 @@
         <v>5</v>
       </c>
       <c r="AE34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6033,7 +6137,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 P3:AZ3 BE3:DG3 BB3:BB22 O3:O34 AC4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P4:AB34 AC11:BA22 BC11:BJ22 AC23:BJ31 G32:I32 AC32:AE34">
+  <conditionalFormatting sqref="D3:N3 P3:AZ3 BE3:DG3 BB3:BB22 O3:O34 AC4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P4:AB34 AC11:BA22 BC11:BJ22 AC23:BJ31 G32:I32 AC32:AF34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417F4166-59FA-471A-9E7E-236D6E65AE1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAFEE0BD-494E-4BC6-8002-92B0AF024FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="45">
   <si>
     <t>TER</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>Feriado</t>
+  </si>
+  <si>
+    <t>4P/4F</t>
   </si>
 </sst>
 </file>
@@ -3705,7 +3708,7 @@
         <v>5</v>
       </c>
       <c r="AF19" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
@@ -4895,7 +4898,7 @@
         <v>5</v>
       </c>
       <c r="AF26" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
@@ -6129,7 +6132,7 @@
         <v>5</v>
       </c>
       <c r="AF34" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAFEE0BD-494E-4BC6-8002-92B0AF024FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7C14594-6FF6-4B28-8BED-C224D0C4B617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="45">
   <si>
     <t>TER</t>
   </si>
@@ -969,6 +969,9 @@
       <c r="AF3" t="s">
         <v>5</v>
       </c>
+      <c r="AG3" t="s">
+        <v>5</v>
+      </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2"/>
       <c r="AW3" s="2"/>
@@ -1142,6 +1145,9 @@
       <c r="AF4" t="s">
         <v>5</v>
       </c>
+      <c r="AG4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1315,6 +1321,9 @@
       <c r="AF5" t="s">
         <v>5</v>
       </c>
+      <c r="AG5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1488,6 +1497,9 @@
       <c r="AF6" t="s">
         <v>5</v>
       </c>
+      <c r="AG6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1643,6 +1655,9 @@
       <c r="AF7" t="s">
         <v>5</v>
       </c>
+      <c r="AG7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1816,6 +1831,9 @@
       <c r="AF8" t="s">
         <v>5</v>
       </c>
+      <c r="AG8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1989,6 +2007,9 @@
       <c r="AF9" t="s">
         <v>7</v>
       </c>
+      <c r="AG9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2162,6 +2183,9 @@
       <c r="AF10" t="s">
         <v>5</v>
       </c>
+      <c r="AG10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2335,6 +2359,9 @@
       <c r="AF11" t="s">
         <v>5</v>
       </c>
+      <c r="AG11" t="s">
+        <v>5</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2508,6 +2535,9 @@
       <c r="AF12" t="s">
         <v>5</v>
       </c>
+      <c r="AG12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2672,6 +2702,9 @@
       <c r="AF13" t="s">
         <v>5</v>
       </c>
+      <c r="AG13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2845,6 +2878,9 @@
       <c r="AF14" t="s">
         <v>5</v>
       </c>
+      <c r="AG14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -3018,6 +3054,9 @@
       <c r="AF15" t="s">
         <v>5</v>
       </c>
+      <c r="AG15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3191,6 +3230,9 @@
       <c r="AF16" s="9" t="s">
         <v>7</v>
       </c>
+      <c r="AG16" t="s">
+        <v>5</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3364,6 +3406,9 @@
       <c r="AF17" t="s">
         <v>5</v>
       </c>
+      <c r="AG17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3537,6 +3582,9 @@
       <c r="AF18" t="s">
         <v>5</v>
       </c>
+      <c r="AG18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3710,6 +3758,9 @@
       <c r="AF19" t="s">
         <v>44</v>
       </c>
+      <c r="AG19" t="s">
+        <v>5</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3883,6 +3934,9 @@
       <c r="AF20" t="s">
         <v>5</v>
       </c>
+      <c r="AG20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -4056,6 +4110,9 @@
       <c r="AF21" t="s">
         <v>5</v>
       </c>
+      <c r="AG21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -4229,6 +4286,9 @@
       <c r="AF22" t="s">
         <v>5</v>
       </c>
+      <c r="AG22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -4402,6 +4462,9 @@
       <c r="AF23" t="s">
         <v>5</v>
       </c>
+      <c r="AG23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -4554,6 +4617,9 @@
       <c r="AF24" t="s">
         <v>5</v>
       </c>
+      <c r="AG24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4727,6 +4793,9 @@
       <c r="AF25" t="s">
         <v>5</v>
       </c>
+      <c r="AG25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4900,6 +4969,9 @@
       <c r="AF26" t="s">
         <v>44</v>
       </c>
+      <c r="AG26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -5073,6 +5145,9 @@
       <c r="AF27" t="s">
         <v>5</v>
       </c>
+      <c r="AG27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -5246,6 +5321,9 @@
       <c r="AF28" t="s">
         <v>5</v>
       </c>
+      <c r="AG28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -5419,6 +5497,9 @@
       <c r="AF29" t="s">
         <v>5</v>
       </c>
+      <c r="AG29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -5592,6 +5673,9 @@
       <c r="AF30" t="s">
         <v>5</v>
       </c>
+      <c r="AG30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -5765,6 +5849,9 @@
       <c r="AF31" t="s">
         <v>5</v>
       </c>
+      <c r="AG31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -5938,8 +6025,11 @@
       <c r="AF32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -6036,8 +6126,11 @@
       <c r="AF33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -6133,6 +6226,9 @@
       </c>
       <c r="AF34" t="s">
         <v>44</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6140,7 +6236,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 P3:AZ3 BE3:DG3 BB3:BB22 O3:O34 AC4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P4:AB34 AC11:BA22 BC11:BJ22 AC23:BJ31 G32:I32 AC32:AF34">
+  <conditionalFormatting sqref="D3:N3 P3:AZ3 BE3:DG3 BB3:BB22 O3:O34 AC4:AZ4 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P4:AB34 BC11:BJ22 G32:I32 AH23:BJ31 AH11:BA22 AH5:AZ10 AC5:AG34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7C14594-6FF6-4B28-8BED-C224D0C4B617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BD49D0-FD26-49DA-A3CF-D4FEC218D2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3231,7 +3231,7 @@
         <v>7</v>
       </c>
       <c r="AG16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
@@ -6236,7 +6236,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 P3:AZ3 BE3:DG3 BB3:BB22 O3:O34 AC4:AZ4 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P4:AB34 BC11:BJ22 G32:I32 AH23:BJ31 AH11:BA22 AH5:AZ10 AC5:AG34">
+  <conditionalFormatting sqref="D3:N3 P3:AZ3 BE3:DG3 BB3:BB22 O3:O34 AC4:AZ4 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P4:AB34 AH5:AZ10 AC5:AG34 AH11:BA22 BC11:BJ22 AH23:BJ31 G32:I32">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BD49D0-FD26-49DA-A3CF-D4FEC218D2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A461E86F-DAE6-4E68-82E8-A9D62934C756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="45">
   <si>
     <t>TER</t>
   </si>
@@ -557,27 +557,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -668,8 +668,12 @@
       <c r="AG1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
+      <c r="AH1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
@@ -727,7 +731,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -827,6 +831,12 @@
       </c>
       <c r="AG2" s="1">
         <v>46149</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>46154</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>46156</v>
       </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
@@ -872,7 +882,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -970,6 +980,12 @@
         <v>5</v>
       </c>
       <c r="AG3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1048,7 +1064,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1146,6 +1162,12 @@
         <v>5</v>
       </c>
       <c r="AG4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI4" t="s">
         <v>5</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1224,7 +1246,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1322,6 +1344,12 @@
         <v>5</v>
       </c>
       <c r="AG5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI5" t="s">
         <v>5</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1400,7 +1428,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -1498,6 +1526,12 @@
         <v>5</v>
       </c>
       <c r="AG6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI6" t="s">
         <v>5</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1576,7 +1610,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -1656,6 +1690,12 @@
         <v>5</v>
       </c>
       <c r="AG7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI7" t="s">
         <v>5</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1734,7 +1774,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -1832,6 +1872,12 @@
         <v>5</v>
       </c>
       <c r="AG8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI8" t="s">
         <v>5</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1910,7 +1956,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2008,6 +2054,12 @@
         <v>7</v>
       </c>
       <c r="AG9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI9" t="s">
         <v>5</v>
       </c>
       <c r="AU9" s="2"/>
@@ -2086,7 +2138,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -2184,6 +2236,12 @@
         <v>5</v>
       </c>
       <c r="AG10" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI10" t="s">
         <v>5</v>
       </c>
       <c r="AU10" s="2"/>
@@ -2262,7 +2320,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -2360,6 +2418,12 @@
         <v>5</v>
       </c>
       <c r="AG11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI11" t="s">
         <v>5</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2438,7 +2502,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -2536,6 +2600,12 @@
         <v>5</v>
       </c>
       <c r="AG12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI12" t="s">
         <v>5</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2614,7 +2684,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -2703,6 +2773,12 @@
         <v>5</v>
       </c>
       <c r="AG13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI13" t="s">
         <v>5</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2781,7 +2857,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -2879,6 +2955,12 @@
         <v>5</v>
       </c>
       <c r="AG14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI14" t="s">
         <v>5</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2957,7 +3039,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -3055,6 +3137,12 @@
         <v>5</v>
       </c>
       <c r="AG15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI15" t="s">
         <v>5</v>
       </c>
       <c r="AU15" s="2"/>
@@ -3133,7 +3221,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -3231,6 +3319,12 @@
         <v>7</v>
       </c>
       <c r="AG16" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI16" t="s">
         <v>7</v>
       </c>
       <c r="AU16" s="2"/>
@@ -3309,7 +3403,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -3407,6 +3501,12 @@
         <v>5</v>
       </c>
       <c r="AG17" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI17" t="s">
         <v>5</v>
       </c>
       <c r="AU17" s="2"/>
@@ -3485,7 +3585,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -3583,6 +3683,12 @@
         <v>5</v>
       </c>
       <c r="AG18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI18" t="s">
         <v>5</v>
       </c>
       <c r="AU18" s="2"/>
@@ -3661,7 +3767,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -3759,6 +3865,12 @@
         <v>44</v>
       </c>
       <c r="AG19" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI19" t="s">
         <v>5</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3837,7 +3949,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -3935,6 +4047,12 @@
         <v>5</v>
       </c>
       <c r="AG20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI20" t="s">
         <v>5</v>
       </c>
       <c r="AU20" s="2"/>
@@ -4013,7 +4131,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -4111,6 +4229,12 @@
         <v>5</v>
       </c>
       <c r="AG21" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI21" t="s">
         <v>5</v>
       </c>
       <c r="AU21" s="2"/>
@@ -4189,7 +4313,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -4287,6 +4411,12 @@
         <v>5</v>
       </c>
       <c r="AG22" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI22" t="s">
         <v>5</v>
       </c>
       <c r="AU22" s="2"/>
@@ -4365,7 +4495,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -4463,6 +4593,12 @@
         <v>5</v>
       </c>
       <c r="AG23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI23" t="s">
         <v>5</v>
       </c>
       <c r="AU23" s="2"/>
@@ -4541,7 +4677,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -4618,6 +4754,12 @@
         <v>5</v>
       </c>
       <c r="AG24" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI24" t="s">
         <v>5</v>
       </c>
       <c r="AU24" s="2"/>
@@ -4696,7 +4838,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -4794,6 +4936,12 @@
         <v>5</v>
       </c>
       <c r="AG25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI25" t="s">
         <v>5</v>
       </c>
       <c r="AU25" s="2"/>
@@ -4872,7 +5020,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -4970,6 +5118,12 @@
         <v>44</v>
       </c>
       <c r="AG26" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI26" t="s">
         <v>5</v>
       </c>
       <c r="AU26" s="2"/>
@@ -5048,7 +5202,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -5146,6 +5300,12 @@
         <v>5</v>
       </c>
       <c r="AG27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI27" t="s">
         <v>5</v>
       </c>
       <c r="AU27" s="2"/>
@@ -5224,7 +5384,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -5322,6 +5482,12 @@
         <v>5</v>
       </c>
       <c r="AG28" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI28" t="s">
         <v>5</v>
       </c>
       <c r="AU28" s="2"/>
@@ -5400,7 +5566,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -5498,6 +5664,12 @@
         <v>5</v>
       </c>
       <c r="AG29" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI29" t="s">
         <v>5</v>
       </c>
       <c r="AU29" s="2"/>
@@ -5576,7 +5748,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -5674,6 +5846,12 @@
         <v>5</v>
       </c>
       <c r="AG30" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI30" t="s">
         <v>5</v>
       </c>
       <c r="AU30" s="2"/>
@@ -5752,7 +5930,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -5850,6 +6028,12 @@
         <v>5</v>
       </c>
       <c r="AG31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI31" t="s">
         <v>5</v>
       </c>
       <c r="AU31" s="2"/>
@@ -5928,7 +6112,7 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -6028,8 +6212,14 @@
       <c r="AG32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH32" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -6129,8 +6319,14 @@
       <c r="AG33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH33" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -6228,6 +6424,12 @@
         <v>44</v>
       </c>
       <c r="AG34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6236,7 +6438,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 P3:AZ3 BE3:DG3 BB3:BB22 O3:O34 AC4:AZ4 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 P4:AB34 AH5:AZ10 AC5:AG34 AH11:BA22 BC11:BJ22 AH23:BJ31 G32:I32">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 BB3:BB22 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ11:BA22 BC11:BJ22 AJ23:BJ31 G32:I32 AJ3:AZ10 O3:AI34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -6249,14 +6451,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6264,7 +6466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -6272,7 +6474,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -6280,7 +6482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -6288,7 +6490,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -6296,7 +6498,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -6304,7 +6506,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -6312,7 +6514,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -6320,7 +6522,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -6328,7 +6530,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -6336,7 +6538,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -6344,7 +6546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -6352,7 +6554,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -6360,7 +6562,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -6368,7 +6570,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -6376,7 +6578,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -6384,7 +6586,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -6392,7 +6594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -6400,7 +6602,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -6408,7 +6610,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -6416,7 +6618,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -6424,7 +6626,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -6432,7 +6634,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -6440,7 +6642,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -6448,7 +6650,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -6456,7 +6658,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -6464,7 +6666,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -6472,7 +6674,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -6480,7 +6682,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -6488,7 +6690,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -6496,7 +6698,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -6504,7 +6706,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -6512,7 +6714,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132234</v>
       </c>
@@ -6529,185 +6731,185 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E8BA54-AA53-4AE8-B8DA-79238D2ECDF5}">
   <dimension ref="A2:A31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Alicia Coelho Gomes de Oliveira</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Ana Klara do Carmo</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Franco de Lima</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Bruno Vascon</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B7</f>
         <v>Davi Parreira Cardeal</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B8</f>
         <v>Eloísa Macedo da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B9</f>
         <v>Enzo Casadei Macedo</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B10</f>
         <v>Felipe Martins</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B11</f>
         <v>Gabriel Pereira de Oliveira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B13</f>
         <v>Giovana Luísa Cezar</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B14</f>
         <v>Guilherme Enrico Barichello</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B15</f>
         <v>Isabele Hilary Reis Silva</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B16</f>
         <v>Isabelle Moreira Cezar Barichello</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B17</f>
         <v>Jéssica Guedes Vaz</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B18</f>
         <v>Joana Fernandes Fabrin</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B19</f>
         <v>João Henrique Leme da Silva</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B20</f>
         <v>João Victor Moraes Lopes</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B21</f>
         <v>Kamilly Vitória Ferreira Silvério</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B22</f>
         <v>Leonardo Canina Marchiori</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B24</f>
         <v>Lívia Fernandes Morais</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B25</f>
         <v>Maria Eduarda Betim Gomes de Moraes</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B26</f>
         <v>Mariana Correia Santos</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B27</f>
         <v>Miguel Cardoso Pignata</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B28</f>
         <v>Mirella Camilotti Perez</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B29</f>
         <v>Pietro Cardoso Broleze</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B30</f>
         <v>Samuel Gomes Silva</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B31</f>
         <v>Thiago Lima Amaral</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B32</f>
         <v>Vitor Rafael Parisato</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B33</f>
         <v>Yasmin Drudi</v>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A461E86F-DAE6-4E68-82E8-A9D62934C756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC69468B-75F4-46FB-AB25-B36C4FF9D97B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -809,7 +809,7 @@
         <v>46121</v>
       </c>
       <c r="Z2" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="AA2" s="1">
         <v>46128</v>
@@ -6438,7 +6438,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 BB3:BB22 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ11:BA22 BC11:BJ22 AJ23:BJ31 G32:I32 AJ3:AZ10 O3:AI34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 AJ3:AZ10 BB3:BB22 O3:AI34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ11:BA22 BC11:BJ22 AJ23:BJ31 G32:I32">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC69468B-75F4-46FB-AB25-B36C4FF9D97B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC2AFA1-B48F-4E48-B115-01B50AF90FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="45">
   <si>
     <t>TER</t>
   </si>
@@ -557,27 +557,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -674,8 +674,12 @@
       <c r="AI1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
+      <c r="AJ1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
       <c r="AN1" s="1"/>
@@ -731,7 +735,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -837,6 +841,12 @@
       </c>
       <c r="AI2" s="1">
         <v>46156</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>46161</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>46163</v>
       </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
@@ -882,7 +892,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -986,6 +996,12 @@
         <v>5</v>
       </c>
       <c r="AI3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1064,7 +1080,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1168,6 +1184,12 @@
         <v>5</v>
       </c>
       <c r="AI4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK4" t="s">
         <v>5</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1246,7 +1268,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1350,6 +1372,12 @@
         <v>5</v>
       </c>
       <c r="AI5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK5" t="s">
         <v>5</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1428,7 +1456,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -1532,6 +1560,12 @@
         <v>5</v>
       </c>
       <c r="AI6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK6" t="s">
         <v>5</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1610,7 +1644,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -1696,6 +1730,12 @@
         <v>5</v>
       </c>
       <c r="AI7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK7" t="s">
         <v>5</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1774,7 +1814,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -1878,6 +1918,12 @@
         <v>5</v>
       </c>
       <c r="AI8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK8" t="s">
         <v>5</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1956,7 +2002,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2060,6 +2106,12 @@
         <v>5</v>
       </c>
       <c r="AI9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK9" t="s">
         <v>5</v>
       </c>
       <c r="AU9" s="2"/>
@@ -2138,7 +2190,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -2242,6 +2294,12 @@
         <v>5</v>
       </c>
       <c r="AI10" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK10" t="s">
         <v>5</v>
       </c>
       <c r="AU10" s="2"/>
@@ -2320,7 +2378,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -2424,6 +2482,12 @@
         <v>5</v>
       </c>
       <c r="AI11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK11" t="s">
         <v>5</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2502,7 +2566,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -2606,6 +2670,12 @@
         <v>5</v>
       </c>
       <c r="AI12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK12" t="s">
         <v>5</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2684,7 +2754,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -2779,6 +2849,12 @@
         <v>5</v>
       </c>
       <c r="AI13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK13" t="s">
         <v>5</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2857,7 +2933,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -2961,6 +3037,12 @@
         <v>5</v>
       </c>
       <c r="AI14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK14" t="s">
         <v>5</v>
       </c>
       <c r="AU14" s="2"/>
@@ -3039,7 +3121,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -3143,6 +3225,12 @@
         <v>5</v>
       </c>
       <c r="AI15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK15" t="s">
         <v>5</v>
       </c>
       <c r="AU15" s="2"/>
@@ -3221,7 +3309,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -3325,6 +3413,12 @@
         <v>7</v>
       </c>
       <c r="AI16" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK16" t="s">
         <v>7</v>
       </c>
       <c r="AU16" s="2"/>
@@ -3403,7 +3497,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -3507,6 +3601,12 @@
         <v>5</v>
       </c>
       <c r="AI17" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK17" t="s">
         <v>5</v>
       </c>
       <c r="AU17" s="2"/>
@@ -3585,7 +3685,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -3689,6 +3789,12 @@
         <v>5</v>
       </c>
       <c r="AI18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK18" t="s">
         <v>5</v>
       </c>
       <c r="AU18" s="2"/>
@@ -3767,7 +3873,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -3872,6 +3978,12 @@
       </c>
       <c r="AI19" t="s">
         <v>5</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>7</v>
       </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
@@ -3949,7 +4061,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -4053,6 +4165,12 @@
         <v>5</v>
       </c>
       <c r="AI20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK20" t="s">
         <v>5</v>
       </c>
       <c r="AU20" s="2"/>
@@ -4131,7 +4249,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -4235,6 +4353,12 @@
         <v>5</v>
       </c>
       <c r="AI21" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK21" t="s">
         <v>5</v>
       </c>
       <c r="AU21" s="2"/>
@@ -4313,7 +4437,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -4417,6 +4541,12 @@
         <v>5</v>
       </c>
       <c r="AI22" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK22" t="s">
         <v>5</v>
       </c>
       <c r="AU22" s="2"/>
@@ -4495,7 +4625,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -4599,6 +4729,12 @@
         <v>5</v>
       </c>
       <c r="AI23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK23" t="s">
         <v>5</v>
       </c>
       <c r="AU23" s="2"/>
@@ -4677,7 +4813,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -4760,6 +4896,12 @@
         <v>5</v>
       </c>
       <c r="AI24" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK24" t="s">
         <v>5</v>
       </c>
       <c r="AU24" s="2"/>
@@ -4838,7 +4980,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -4942,6 +5084,12 @@
         <v>5</v>
       </c>
       <c r="AI25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK25" t="s">
         <v>5</v>
       </c>
       <c r="AU25" s="2"/>
@@ -5020,7 +5168,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -5124,6 +5272,12 @@
         <v>5</v>
       </c>
       <c r="AI26" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK26" t="s">
         <v>5</v>
       </c>
       <c r="AU26" s="2"/>
@@ -5202,7 +5356,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -5306,6 +5460,12 @@
         <v>5</v>
       </c>
       <c r="AI27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK27" t="s">
         <v>5</v>
       </c>
       <c r="AU27" s="2"/>
@@ -5384,7 +5544,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -5488,6 +5648,12 @@
         <v>5</v>
       </c>
       <c r="AI28" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK28" t="s">
         <v>5</v>
       </c>
       <c r="AU28" s="2"/>
@@ -5566,7 +5732,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -5670,6 +5836,12 @@
         <v>5</v>
       </c>
       <c r="AI29" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK29" t="s">
         <v>5</v>
       </c>
       <c r="AU29" s="2"/>
@@ -5748,7 +5920,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -5852,6 +6024,12 @@
         <v>5</v>
       </c>
       <c r="AI30" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK30" t="s">
         <v>5</v>
       </c>
       <c r="AU30" s="2"/>
@@ -5930,7 +6108,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -6035,6 +6213,12 @@
       </c>
       <c r="AI31" t="s">
         <v>5</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>7</v>
       </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
@@ -6112,7 +6296,7 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -6218,8 +6402,14 @@
       <c r="AI32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ32" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -6325,8 +6515,14 @@
       <c r="AI33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ33" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -6430,6 +6626,12 @@
         <v>5</v>
       </c>
       <c r="AI34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6438,7 +6640,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 AJ3:AZ10 BB3:BB22 O3:AI34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ11:BA22 BC11:BJ22 AJ23:BJ31 G32:I32">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 AJ3:AZ10 BB3:BB22 O3:AI34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ11:BA22 BC11:BJ22 AJ23:BJ31 G32:I32 AJ32:AK34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -6451,14 +6653,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6466,7 +6668,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -6474,7 +6676,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -6482,7 +6684,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -6490,7 +6692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -6498,7 +6700,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -6506,7 +6708,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -6514,7 +6716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -6522,7 +6724,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -6530,7 +6732,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -6538,7 +6740,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -6546,7 +6748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -6554,7 +6756,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -6562,7 +6764,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -6570,7 +6772,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -6578,7 +6780,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -6586,7 +6788,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -6594,7 +6796,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -6602,7 +6804,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -6610,7 +6812,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -6618,7 +6820,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -6626,7 +6828,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -6634,7 +6836,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -6642,7 +6844,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -6650,7 +6852,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -6658,7 +6860,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -6666,7 +6868,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -6674,7 +6876,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -6682,7 +6884,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -6690,7 +6892,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -6698,7 +6900,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -6706,7 +6908,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -6714,7 +6916,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132234</v>
       </c>
@@ -6731,185 +6933,185 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E8BA54-AA53-4AE8-B8DA-79238D2ECDF5}">
   <dimension ref="A2:A31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Alicia Coelho Gomes de Oliveira</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Ana Klara do Carmo</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Franco de Lima</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Bruno Vascon</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B7</f>
         <v>Davi Parreira Cardeal</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B8</f>
         <v>Eloísa Macedo da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B9</f>
         <v>Enzo Casadei Macedo</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B10</f>
         <v>Felipe Martins</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B11</f>
         <v>Gabriel Pereira de Oliveira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B13</f>
         <v>Giovana Luísa Cezar</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B14</f>
         <v>Guilherme Enrico Barichello</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B15</f>
         <v>Isabele Hilary Reis Silva</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B16</f>
         <v>Isabelle Moreira Cezar Barichello</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B17</f>
         <v>Jéssica Guedes Vaz</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B18</f>
         <v>Joana Fernandes Fabrin</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B19</f>
         <v>João Henrique Leme da Silva</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B20</f>
         <v>João Victor Moraes Lopes</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B21</f>
         <v>Kamilly Vitória Ferreira Silvério</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B22</f>
         <v>Leonardo Canina Marchiori</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B24</f>
         <v>Lívia Fernandes Morais</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B25</f>
         <v>Maria Eduarda Betim Gomes de Moraes</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B26</f>
         <v>Mariana Correia Santos</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B27</f>
         <v>Miguel Cardoso Pignata</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B28</f>
         <v>Mirella Camilotti Perez</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B29</f>
         <v>Pietro Cardoso Broleze</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B30</f>
         <v>Samuel Gomes Silva</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B31</f>
         <v>Thiago Lima Amaral</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B32</f>
         <v>Vitor Rafael Parisato</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B33</f>
         <v>Yasmin Drudi</v>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC2AFA1-B48F-4E48-B115-01B50AF90FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8802235B-9F9E-4C0C-A1DD-10C507E54406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
     <sheet name="alunos" sheetId="2" r:id="rId2"/>
-    <sheet name="vistos" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="45">
   <si>
     <t>TER</t>
   </si>
@@ -6657,7 +6656,6 @@
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6928,196 +6926,4 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E8BA54-AA53-4AE8-B8DA-79238D2ECDF5}">
-  <dimension ref="A2:A31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
-        <f>alunos!B2</f>
-        <v>Alicia Coelho Gomes de Oliveira</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="str">
-        <f>alunos!B3</f>
-        <v>Ana Klara do Carmo</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="str">
-        <f>alunos!B4</f>
-        <v>Breno Franco de Lima</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="str">
-        <f>alunos!B5</f>
-        <v>Bruno Vascon</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="str">
-        <f>alunos!B7</f>
-        <v>Davi Parreira Cardeal</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="str">
-        <f>alunos!B8</f>
-        <v>Eloísa Macedo da Silva</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="str">
-        <f>alunos!B9</f>
-        <v>Enzo Casadei Macedo</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="str">
-        <f>alunos!B10</f>
-        <v>Felipe Martins</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
-        <f>alunos!B11</f>
-        <v>Gabriel Pereira de Oliveira</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="str">
-        <f>alunos!B13</f>
-        <v>Giovana Luísa Cezar</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="str">
-        <f>alunos!B14</f>
-        <v>Guilherme Enrico Barichello</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="str">
-        <f>alunos!B15</f>
-        <v>Isabele Hilary Reis Silva</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="str">
-        <f>alunos!B16</f>
-        <v>Isabelle Moreira Cezar Barichello</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="str">
-        <f>alunos!B17</f>
-        <v>Jéssica Guedes Vaz</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="str">
-        <f>alunos!B18</f>
-        <v>Joana Fernandes Fabrin</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="str">
-        <f>alunos!B19</f>
-        <v>João Henrique Leme da Silva</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="str">
-        <f>alunos!B20</f>
-        <v>João Victor Moraes Lopes</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="str">
-        <f>alunos!B21</f>
-        <v>Kamilly Vitória Ferreira Silvério</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="str">
-        <f>alunos!B22</f>
-        <v>Leonardo Canina Marchiori</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="str">
-        <f>alunos!B24</f>
-        <v>Lívia Fernandes Morais</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="str">
-        <f>alunos!B25</f>
-        <v>Maria Eduarda Betim Gomes de Moraes</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="str">
-        <f>alunos!B26</f>
-        <v>Mariana Correia Santos</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="str">
-        <f>alunos!B27</f>
-        <v>Miguel Cardoso Pignata</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="str">
-        <f>alunos!B28</f>
-        <v>Mirella Camilotti Perez</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="str">
-        <f>alunos!B29</f>
-        <v>Pietro Cardoso Broleze</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="str">
-        <f>alunos!B30</f>
-        <v>Samuel Gomes Silva</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="str">
-        <f>alunos!B31</f>
-        <v>Thiago Lima Amaral</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="str">
-        <f>alunos!B32</f>
-        <v>Vitor Rafael Parisato</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="str">
-        <f>alunos!B33</f>
-        <v>Yasmin Drudi</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
 </file>
--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8802235B-9F9E-4C0C-A1DD-10C507E54406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A45118-09F3-4ED3-A1A1-157AA3C1B87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="45">
   <si>
     <t>TER</t>
   </si>
@@ -679,8 +679,12 @@
       <c r="AK1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
+      <c r="AL1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="AN1" s="1"/>
       <c r="AO1" s="1"/>
       <c r="AP1" s="1"/>
@@ -847,6 +851,19 @@
       <c r="AK2" s="1">
         <v>46163</v>
       </c>
+      <c r="AL2" s="1">
+        <v>46168</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>46170</v>
+      </c>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -1001,6 +1018,9 @@
         <v>5</v>
       </c>
       <c r="AK3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1191,6 +1211,9 @@
       <c r="AK4" t="s">
         <v>5</v>
       </c>
+      <c r="AL4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1379,6 +1402,9 @@
       <c r="AK5" t="s">
         <v>5</v>
       </c>
+      <c r="AL5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1567,6 +1593,9 @@
       <c r="AK6" t="s">
         <v>5</v>
       </c>
+      <c r="AL6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1737,6 +1766,9 @@
       <c r="AK7" t="s">
         <v>5</v>
       </c>
+      <c r="AL7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1925,6 +1957,9 @@
       <c r="AK8" t="s">
         <v>5</v>
       </c>
+      <c r="AL8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -2113,6 +2148,9 @@
       <c r="AK9" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2301,6 +2339,9 @@
       <c r="AK10" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2489,6 +2530,9 @@
       <c r="AK11" t="s">
         <v>5</v>
       </c>
+      <c r="AL11" t="s">
+        <v>7</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2677,6 +2721,9 @@
       <c r="AK12" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2856,6 +2903,9 @@
       <c r="AK13" t="s">
         <v>5</v>
       </c>
+      <c r="AL13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -3044,6 +3094,9 @@
       <c r="AK14" t="s">
         <v>5</v>
       </c>
+      <c r="AL14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -3232,6 +3285,9 @@
       <c r="AK15" t="s">
         <v>5</v>
       </c>
+      <c r="AL15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3420,6 +3476,9 @@
       <c r="AK16" t="s">
         <v>7</v>
       </c>
+      <c r="AL16" t="s">
+        <v>7</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3608,6 +3667,9 @@
       <c r="AK17" t="s">
         <v>5</v>
       </c>
+      <c r="AL17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3796,6 +3858,9 @@
       <c r="AK18" t="s">
         <v>5</v>
       </c>
+      <c r="AL18" t="s">
+        <v>7</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3984,6 +4049,9 @@
       <c r="AK19" t="s">
         <v>7</v>
       </c>
+      <c r="AL19" t="s">
+        <v>7</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -4172,6 +4240,9 @@
       <c r="AK20" t="s">
         <v>5</v>
       </c>
+      <c r="AL20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -4360,6 +4431,9 @@
       <c r="AK21" t="s">
         <v>5</v>
       </c>
+      <c r="AL21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -4548,6 +4622,9 @@
       <c r="AK22" t="s">
         <v>5</v>
       </c>
+      <c r="AL22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -4736,6 +4813,9 @@
       <c r="AK23" t="s">
         <v>5</v>
       </c>
+      <c r="AL23" t="s">
+        <v>7</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -4903,6 +4983,9 @@
       <c r="AK24" t="s">
         <v>5</v>
       </c>
+      <c r="AL24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -5091,6 +5174,9 @@
       <c r="AK25" t="s">
         <v>5</v>
       </c>
+      <c r="AL25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -5279,6 +5365,9 @@
       <c r="AK26" t="s">
         <v>5</v>
       </c>
+      <c r="AL26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -5467,6 +5556,9 @@
       <c r="AK27" t="s">
         <v>5</v>
       </c>
+      <c r="AL27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -5655,6 +5747,9 @@
       <c r="AK28" t="s">
         <v>5</v>
       </c>
+      <c r="AL28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -5843,6 +5938,9 @@
       <c r="AK29" t="s">
         <v>5</v>
       </c>
+      <c r="AL29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -6031,6 +6129,9 @@
       <c r="AK30" t="s">
         <v>5</v>
       </c>
+      <c r="AL30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -6219,6 +6320,9 @@
       <c r="AK31" t="s">
         <v>7</v>
       </c>
+      <c r="AL31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -6407,8 +6511,11 @@
       <c r="AK32" t="s">
         <v>5</v>
       </c>
+      <c r="AL32" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -6520,8 +6627,11 @@
       <c r="AK33" t="s">
         <v>5</v>
       </c>
+      <c r="AL33" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -6631,6 +6741,9 @@
         <v>5</v>
       </c>
       <c r="AK34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6639,7 +6752,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 AJ3:AZ10 BB3:BB22 O3:AI34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ11:BA22 BC11:BJ22 AJ23:BJ31 G32:I32 AJ32:AK34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 AJ3:AZ10 BB3:BB22 O3:AI34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ11:BA22 BC11:BJ22 AJ23:BJ31 G32:I32 AJ32:AL34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8802235B-9F9E-4C0C-A1DD-10C507E54406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726609FC-E53D-443A-8871-DB4ECF22B733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="45">
   <si>
     <t>TER</t>
   </si>
@@ -178,7 +178,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +219,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -247,7 +255,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -263,6 +271,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -679,7 +688,9 @@
       <c r="AK1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AL1" s="1"/>
+      <c r="AL1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="AM1" s="1"/>
       <c r="AN1" s="1"/>
       <c r="AO1" s="1"/>
@@ -847,6 +858,9 @@
       <c r="AK2" s="1">
         <v>46163</v>
       </c>
+      <c r="AL2" s="11">
+        <v>46168</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -1001,6 +1015,9 @@
         <v>5</v>
       </c>
       <c r="AK3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1191,6 +1208,9 @@
       <c r="AK4" t="s">
         <v>5</v>
       </c>
+      <c r="AL4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1379,6 +1399,9 @@
       <c r="AK5" t="s">
         <v>5</v>
       </c>
+      <c r="AL5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1567,6 +1590,9 @@
       <c r="AK6" t="s">
         <v>5</v>
       </c>
+      <c r="AL6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1737,6 +1763,9 @@
       <c r="AK7" t="s">
         <v>5</v>
       </c>
+      <c r="AL7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1925,6 +1954,9 @@
       <c r="AK8" t="s">
         <v>5</v>
       </c>
+      <c r="AL8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -2113,6 +2145,9 @@
       <c r="AK9" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2301,6 +2336,9 @@
       <c r="AK10" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2489,6 +2527,9 @@
       <c r="AK11" t="s">
         <v>5</v>
       </c>
+      <c r="AL11" t="s">
+        <v>7</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2677,6 +2718,9 @@
       <c r="AK12" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2854,6 +2898,9 @@
         <v>5</v>
       </c>
       <c r="AK13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL13" t="s">
         <v>5</v>
       </c>
       <c r="AU13" s="2"/>
@@ -3044,6 +3091,9 @@
       <c r="AK14" t="s">
         <v>5</v>
       </c>
+      <c r="AL14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -3232,6 +3282,9 @@
       <c r="AK15" t="s">
         <v>5</v>
       </c>
+      <c r="AL15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3420,6 +3473,9 @@
       <c r="AK16" t="s">
         <v>7</v>
       </c>
+      <c r="AL16" t="s">
+        <v>7</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3608,6 +3664,9 @@
       <c r="AK17" t="s">
         <v>5</v>
       </c>
+      <c r="AL17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3796,6 +3855,9 @@
       <c r="AK18" t="s">
         <v>5</v>
       </c>
+      <c r="AL18" t="s">
+        <v>7</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3984,6 +4046,9 @@
       <c r="AK19" t="s">
         <v>7</v>
       </c>
+      <c r="AL19" t="s">
+        <v>5</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -4172,6 +4237,9 @@
       <c r="AK20" t="s">
         <v>5</v>
       </c>
+      <c r="AL20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -4360,6 +4428,9 @@
       <c r="AK21" t="s">
         <v>5</v>
       </c>
+      <c r="AL21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -4548,6 +4619,9 @@
       <c r="AK22" t="s">
         <v>5</v>
       </c>
+      <c r="AL22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -4736,6 +4810,9 @@
       <c r="AK23" t="s">
         <v>5</v>
       </c>
+      <c r="AL23" t="s">
+        <v>7</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -4903,6 +4980,9 @@
       <c r="AK24" t="s">
         <v>5</v>
       </c>
+      <c r="AL24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -5091,6 +5171,9 @@
       <c r="AK25" t="s">
         <v>5</v>
       </c>
+      <c r="AL25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -5279,6 +5362,9 @@
       <c r="AK26" t="s">
         <v>5</v>
       </c>
+      <c r="AL26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -5467,6 +5553,9 @@
       <c r="AK27" t="s">
         <v>5</v>
       </c>
+      <c r="AL27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -5655,6 +5744,9 @@
       <c r="AK28" t="s">
         <v>5</v>
       </c>
+      <c r="AL28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -5843,6 +5935,9 @@
       <c r="AK29" t="s">
         <v>5</v>
       </c>
+      <c r="AL29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -6031,6 +6126,9 @@
       <c r="AK30" t="s">
         <v>5</v>
       </c>
+      <c r="AL30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -6219,6 +6317,9 @@
       <c r="AK31" t="s">
         <v>7</v>
       </c>
+      <c r="AL31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -6407,8 +6508,11 @@
       <c r="AK32" t="s">
         <v>5</v>
       </c>
+      <c r="AL32" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -6520,8 +6624,11 @@
       <c r="AK33" t="s">
         <v>5</v>
       </c>
+      <c r="AL33" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -6631,6 +6738,9 @@
         <v>5</v>
       </c>
       <c r="AK34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6639,7 +6749,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 AJ3:AZ10 BB3:BB22 O3:AI34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ11:BA22 BC11:BJ22 AJ23:BJ31 G32:I32 AJ32:AK34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 BB3:BB22 O3:AI34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 BC11:BJ22 G32:I32 AJ3:AZ3 AM4:AZ10 AM23:BJ31 AM11:BA22 AJ4:AL34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726609FC-E53D-443A-8871-DB4ECF22B733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332807CE-35D4-4EC5-86A1-ECD7C461291E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="45">
   <si>
     <t>TER</t>
   </si>
@@ -178,7 +178,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,14 +214,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -271,7 +263,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -691,11 +683,21 @@
       <c r="AL1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1"/>
-      <c r="AP1" s="1"/>
-      <c r="AQ1" s="1"/>
+      <c r="AM1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
@@ -861,6 +863,21 @@
       <c r="AL2" s="11">
         <v>46168</v>
       </c>
+      <c r="AM2" s="1">
+        <v>46170</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>46175</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>46177</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>46186</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>46188</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -1019,6 +1036,15 @@
       </c>
       <c r="AL3" t="s">
         <v>5</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>43</v>
       </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2"/>
@@ -1211,6 +1237,15 @@
       <c r="AL4" t="s">
         <v>5</v>
       </c>
+      <c r="AM4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>43</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1402,6 +1437,15 @@
       <c r="AL5" t="s">
         <v>5</v>
       </c>
+      <c r="AM5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>43</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1593,6 +1637,15 @@
       <c r="AL6" t="s">
         <v>5</v>
       </c>
+      <c r="AM6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>43</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1766,6 +1819,15 @@
       <c r="AL7" t="s">
         <v>5</v>
       </c>
+      <c r="AM7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>43</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1957,6 +2019,15 @@
       <c r="AL8" t="s">
         <v>5</v>
       </c>
+      <c r="AM8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>43</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -2148,6 +2219,15 @@
       <c r="AL9" t="s">
         <v>5</v>
       </c>
+      <c r="AM9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>43</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2339,6 +2419,15 @@
       <c r="AL10" t="s">
         <v>5</v>
       </c>
+      <c r="AM10" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>43</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2530,6 +2619,15 @@
       <c r="AL11" t="s">
         <v>7</v>
       </c>
+      <c r="AM11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>43</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2721,6 +2819,15 @@
       <c r="AL12" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>43</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2903,6 +3010,15 @@
       <c r="AL13" t="s">
         <v>5</v>
       </c>
+      <c r="AM13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>43</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -3094,6 +3210,15 @@
       <c r="AL14" t="s">
         <v>5</v>
       </c>
+      <c r="AM14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>43</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -3285,6 +3410,15 @@
       <c r="AL15" t="s">
         <v>5</v>
       </c>
+      <c r="AM15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>43</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3476,6 +3610,15 @@
       <c r="AL16" t="s">
         <v>7</v>
       </c>
+      <c r="AM16" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>43</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3667,6 +3810,15 @@
       <c r="AL17" t="s">
         <v>5</v>
       </c>
+      <c r="AM17" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>43</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3858,6 +4010,15 @@
       <c r="AL18" t="s">
         <v>7</v>
       </c>
+      <c r="AM18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>43</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -4047,7 +4208,16 @@
         <v>7</v>
       </c>
       <c r="AL19" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>43</v>
       </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
@@ -4240,6 +4410,15 @@
       <c r="AL20" t="s">
         <v>5</v>
       </c>
+      <c r="AM20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>43</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -4431,6 +4610,15 @@
       <c r="AL21" t="s">
         <v>5</v>
       </c>
+      <c r="AM21" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>43</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -4622,6 +4810,15 @@
       <c r="AL22" t="s">
         <v>5</v>
       </c>
+      <c r="AM22" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO22" t="s">
+        <v>43</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -4813,6 +5010,15 @@
       <c r="AL23" t="s">
         <v>7</v>
       </c>
+      <c r="AM23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>43</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -4983,6 +5189,15 @@
       <c r="AL24" t="s">
         <v>5</v>
       </c>
+      <c r="AM24" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>43</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -5174,6 +5389,15 @@
       <c r="AL25" t="s">
         <v>5</v>
       </c>
+      <c r="AM25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO25" t="s">
+        <v>43</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -5365,6 +5589,15 @@
       <c r="AL26" t="s">
         <v>5</v>
       </c>
+      <c r="AM26" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO26" t="s">
+        <v>43</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -5556,6 +5789,15 @@
       <c r="AL27" t="s">
         <v>5</v>
       </c>
+      <c r="AM27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO27" t="s">
+        <v>43</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -5747,6 +5989,15 @@
       <c r="AL28" t="s">
         <v>5</v>
       </c>
+      <c r="AM28" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO28" t="s">
+        <v>43</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -5938,6 +6189,15 @@
       <c r="AL29" t="s">
         <v>5</v>
       </c>
+      <c r="AM29" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO29" t="s">
+        <v>43</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -6129,6 +6389,15 @@
       <c r="AL30" t="s">
         <v>5</v>
       </c>
+      <c r="AM30" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO30" t="s">
+        <v>43</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -6320,6 +6589,15 @@
       <c r="AL31" t="s">
         <v>5</v>
       </c>
+      <c r="AM31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO31" t="s">
+        <v>43</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -6511,8 +6789,17 @@
       <c r="AL32" t="s">
         <v>5</v>
       </c>
+      <c r="AM32" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO32" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -6627,8 +6914,17 @@
       <c r="AL33" t="s">
         <v>5</v>
       </c>
+      <c r="AM33" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO33" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -6742,6 +7038,15 @@
       </c>
       <c r="AL34" t="s">
         <v>5</v>
+      </c>
+      <c r="AM34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO34" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -6749,7 +7054,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 BB3:BB22 O3:AI34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 BC11:BJ22 G32:I32 AJ3:AZ3 AM4:AZ10 AM23:BJ31 AM11:BA22 AJ4:AL34">
+  <conditionalFormatting sqref="D3:N3 AJ3:AZ3 BE3:DG3 BB3:BB22 O3:AI34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 BC11:BJ22 G32:I32 AP23:BJ31 AP11:BA22 AP4:AZ10 AJ4:AO34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332807CE-35D4-4EC5-86A1-ECD7C461291E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230D51D5-B051-477D-B9C9-92FE9EE32965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -247,7 +247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -263,7 +263,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,27 +556,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -747,7 +746,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -860,7 +859,7 @@
       <c r="AK2" s="1">
         <v>46163</v>
       </c>
-      <c r="AL2" s="11">
+      <c r="AL2" s="1">
         <v>46168</v>
       </c>
       <c r="AM2" s="1">
@@ -873,10 +872,10 @@
         <v>46177</v>
       </c>
       <c r="AP2" s="1">
-        <v>46186</v>
+        <v>46182</v>
       </c>
       <c r="AQ2" s="1">
-        <v>46188</v>
+        <v>46184</v>
       </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
@@ -922,7 +921,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1122,7 +1121,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1322,7 +1321,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1522,7 +1521,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -1722,7 +1721,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -1904,7 +1903,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2104,7 +2103,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2304,7 +2303,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -2504,7 +2503,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -2704,7 +2703,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -2904,7 +2903,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3095,7 +3094,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -3295,7 +3294,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -3495,7 +3494,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -3695,7 +3694,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -3895,7 +3894,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -4095,7 +4094,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -4295,7 +4294,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -4495,7 +4494,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -4695,7 +4694,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -4895,7 +4894,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -5095,7 +5094,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -5274,7 +5273,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -5474,7 +5473,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -5674,7 +5673,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -5874,7 +5873,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -6074,7 +6073,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -6274,7 +6273,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -6474,7 +6473,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -6674,7 +6673,7 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -6799,7 +6798,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -6924,7 +6923,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -7054,7 +7053,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 AJ3:AZ3 BE3:DG3 BB3:BB22 O3:AI34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 BC11:BJ22 G32:I32 AP23:BJ31 AP11:BA22 AP4:AZ10 AJ4:AO34">
+  <conditionalFormatting sqref="D3:N3 AJ3:AZ3 BE3:DG3 BB3:BB22 O3:AI34 AP4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ4:AO34 AP11:BA22 BC11:BJ22 AP23:BJ31 G32:I32">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -7067,13 +7066,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7081,7 +7080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -7089,7 +7088,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -7097,7 +7096,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -7105,7 +7104,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -7113,7 +7112,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -7121,7 +7120,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -7129,7 +7128,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -7137,7 +7136,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -7145,7 +7144,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -7153,7 +7152,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -7161,7 +7160,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -7169,7 +7168,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -7177,7 +7176,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -7185,7 +7184,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -7193,7 +7192,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -7201,7 +7200,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -7209,7 +7208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -7217,7 +7216,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -7225,7 +7224,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -7233,7 +7232,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -7241,7 +7240,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -7249,7 +7248,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -7257,7 +7256,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -7265,7 +7264,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -7273,7 +7272,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -7281,7 +7280,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -7289,7 +7288,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -7297,7 +7296,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -7305,7 +7304,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -7313,7 +7312,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -7321,7 +7320,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -7329,7 +7328,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230D51D5-B051-477D-B9C9-92FE9EE32965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A68D6B-7A2E-467F-9141-A12ACDB98374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="45">
   <si>
     <t>TER</t>
   </si>
@@ -1045,6 +1045,9 @@
       <c r="AO3" t="s">
         <v>43</v>
       </c>
+      <c r="AP3" t="s">
+        <v>5</v>
+      </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2"/>
       <c r="AW3" s="2"/>
@@ -1245,6 +1248,9 @@
       <c r="AO4" t="s">
         <v>43</v>
       </c>
+      <c r="AP4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1445,6 +1451,9 @@
       <c r="AO5" t="s">
         <v>43</v>
       </c>
+      <c r="AP5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1645,6 +1654,9 @@
       <c r="AO6" t="s">
         <v>43</v>
       </c>
+      <c r="AP6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1827,6 +1839,9 @@
       <c r="AO7" t="s">
         <v>43</v>
       </c>
+      <c r="AP7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -2027,6 +2042,9 @@
       <c r="AO8" t="s">
         <v>43</v>
       </c>
+      <c r="AP8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -2227,6 +2245,9 @@
       <c r="AO9" t="s">
         <v>43</v>
       </c>
+      <c r="AP9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2427,6 +2448,9 @@
       <c r="AO10" t="s">
         <v>43</v>
       </c>
+      <c r="AP10" t="s">
+        <v>7</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2627,6 +2651,9 @@
       <c r="AO11" t="s">
         <v>43</v>
       </c>
+      <c r="AP11" t="s">
+        <v>5</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2827,6 +2854,9 @@
       <c r="AO12" t="s">
         <v>43</v>
       </c>
+      <c r="AP12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -3018,6 +3048,9 @@
       <c r="AO13" t="s">
         <v>43</v>
       </c>
+      <c r="AP13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -3218,6 +3251,9 @@
       <c r="AO14" t="s">
         <v>43</v>
       </c>
+      <c r="AP14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -3418,6 +3454,9 @@
       <c r="AO15" t="s">
         <v>43</v>
       </c>
+      <c r="AP15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3618,6 +3657,9 @@
       <c r="AO16" t="s">
         <v>43</v>
       </c>
+      <c r="AP16" t="s">
+        <v>5</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3818,6 +3860,9 @@
       <c r="AO17" t="s">
         <v>43</v>
       </c>
+      <c r="AP17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -4018,6 +4063,9 @@
       <c r="AO18" t="s">
         <v>43</v>
       </c>
+      <c r="AP18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -4218,6 +4266,9 @@
       <c r="AO19" t="s">
         <v>43</v>
       </c>
+      <c r="AP19" t="s">
+        <v>7</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -4418,6 +4469,9 @@
       <c r="AO20" t="s">
         <v>43</v>
       </c>
+      <c r="AP20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -4618,6 +4672,9 @@
       <c r="AO21" t="s">
         <v>43</v>
       </c>
+      <c r="AP21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -4818,6 +4875,9 @@
       <c r="AO22" t="s">
         <v>43</v>
       </c>
+      <c r="AP22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -5018,6 +5078,9 @@
       <c r="AO23" t="s">
         <v>43</v>
       </c>
+      <c r="AP23" t="s">
+        <v>7</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -5197,6 +5260,9 @@
       <c r="AO24" t="s">
         <v>43</v>
       </c>
+      <c r="AP24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -5397,6 +5463,9 @@
       <c r="AO25" t="s">
         <v>43</v>
       </c>
+      <c r="AP25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -5597,6 +5666,9 @@
       <c r="AO26" t="s">
         <v>43</v>
       </c>
+      <c r="AP26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -5797,6 +5869,9 @@
       <c r="AO27" t="s">
         <v>43</v>
       </c>
+      <c r="AP27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -5997,6 +6072,9 @@
       <c r="AO28" t="s">
         <v>43</v>
       </c>
+      <c r="AP28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -6197,6 +6275,9 @@
       <c r="AO29" t="s">
         <v>43</v>
       </c>
+      <c r="AP29" t="s">
+        <v>7</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -6397,6 +6478,9 @@
       <c r="AO30" t="s">
         <v>43</v>
       </c>
+      <c r="AP30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -6597,6 +6681,9 @@
       <c r="AO31" t="s">
         <v>43</v>
       </c>
+      <c r="AP31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -6797,8 +6884,11 @@
       <c r="AO32" t="s">
         <v>43</v>
       </c>
+      <c r="AP32" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -6922,8 +7012,11 @@
       <c r="AO33" t="s">
         <v>43</v>
       </c>
+      <c r="AP33" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -7046,6 +7139,9 @@
       </c>
       <c r="AO34" t="s">
         <v>43</v>
+      </c>
+      <c r="AP34" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7053,7 +7149,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 AJ3:AZ3 BE3:DG3 BB3:BB22 O3:AI34 AP4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ4:AO34 AP11:BA22 BC11:BJ22 AP23:BJ31 G32:I32">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 BB3:BB22 O3:AI34 AQ4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AQ11:BA22 BC11:BJ22 AQ23:BJ31 G32:I32 AJ3:AZ3 AJ4:AP34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A68D6B-7A2E-467F-9141-A12ACDB98374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8809CBF-594C-4D0E-8D09-104FC30413B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="47">
   <si>
     <t>TER</t>
   </si>
@@ -172,6 +172,12 @@
   </si>
   <si>
     <t>4P/4F</t>
+  </si>
+  <si>
+    <t>P - F Tarde</t>
+  </si>
+  <si>
+    <t>1F - P</t>
   </si>
 </sst>
 </file>
@@ -556,27 +562,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="41" width="7.7109375" customWidth="1"/>
+    <col min="42" max="42" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="43" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -746,7 +754,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -921,7 +929,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1124,7 +1132,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1327,7 +1335,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1530,7 +1538,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -1733,7 +1741,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -1840,7 +1848,7 @@
         <v>43</v>
       </c>
       <c r="AP7" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
@@ -1918,7 +1926,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2121,7 +2129,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2324,7 +2332,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -2527,7 +2535,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -2730,7 +2738,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -2933,7 +2941,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3127,7 +3135,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -3330,7 +3338,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -3533,7 +3541,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -3658,7 +3666,7 @@
         <v>43</v>
       </c>
       <c r="AP16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
@@ -3736,7 +3744,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -3939,7 +3947,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -4142,7 +4150,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -4345,7 +4353,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -4548,7 +4556,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -4751,7 +4759,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -4954,7 +4962,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -5157,7 +5165,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -5339,7 +5347,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -5542,7 +5550,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -5745,7 +5753,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -5948,7 +5956,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -6151,7 +6159,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -6276,7 +6284,7 @@
         <v>43</v>
       </c>
       <c r="AP29" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
@@ -6354,7 +6362,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -6557,7 +6565,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -6760,7 +6768,7 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -6888,7 +6896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -7016,7 +7024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -7149,7 +7157,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 BB3:BB22 O3:AI34 AQ4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AQ11:BA22 BC11:BJ22 AQ23:BJ31 G32:I32 AJ3:AZ3 AJ4:AP34">
+  <conditionalFormatting sqref="D3:N3 AJ3:AZ3 BE3:DG3 BB3:BB22 O3:AI34 AQ4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ4:AP34 AQ11:BA22 BC11:BJ22 AQ23:BJ31 G32:I32">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -7162,13 +7170,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7176,7 +7184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -7184,7 +7192,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -7192,7 +7200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -7200,7 +7208,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -7208,7 +7216,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -7216,7 +7224,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -7224,7 +7232,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -7232,7 +7240,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -7240,7 +7248,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -7248,7 +7256,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -7256,7 +7264,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -7264,7 +7272,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -7272,7 +7280,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -7280,7 +7288,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -7288,7 +7296,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -7296,7 +7304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -7304,7 +7312,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -7312,7 +7320,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -7320,7 +7328,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -7328,7 +7336,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -7336,7 +7344,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -7344,7 +7352,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -7352,7 +7360,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -7360,7 +7368,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -7368,7 +7376,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -7376,7 +7384,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -7384,7 +7392,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -7392,7 +7400,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -7400,7 +7408,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -7408,7 +7416,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -7416,7 +7424,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -7424,7 +7432,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\SENAI\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8809CBF-594C-4D0E-8D09-104FC30413B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC13603-3BEA-4D73-B995-029F96E36537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="47">
   <si>
     <t>TER</t>
   </si>
@@ -1056,6 +1056,9 @@
       <c r="AP3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ3" t="s">
+        <v>5</v>
+      </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2"/>
       <c r="AW3" s="2"/>
@@ -1259,6 +1262,9 @@
       <c r="AP4" t="s">
         <v>5</v>
       </c>
+      <c r="AQ4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1462,6 +1468,9 @@
       <c r="AP5" t="s">
         <v>5</v>
       </c>
+      <c r="AQ5" t="s">
+        <v>5</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1665,6 +1674,9 @@
       <c r="AP6" t="s">
         <v>5</v>
       </c>
+      <c r="AQ6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1850,6 +1862,9 @@
       <c r="AP7" t="s">
         <v>45</v>
       </c>
+      <c r="AQ7" t="s">
+        <v>7</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -2053,6 +2068,9 @@
       <c r="AP8" t="s">
         <v>5</v>
       </c>
+      <c r="AQ8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -2256,6 +2274,9 @@
       <c r="AP9" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2459,6 +2480,9 @@
       <c r="AP10" t="s">
         <v>7</v>
       </c>
+      <c r="AQ10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2662,6 +2686,9 @@
       <c r="AP11" t="s">
         <v>5</v>
       </c>
+      <c r="AQ11" t="s">
+        <v>5</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2865,6 +2892,9 @@
       <c r="AP12" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -3059,6 +3089,9 @@
       <c r="AP13" t="s">
         <v>5</v>
       </c>
+      <c r="AQ13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -3262,6 +3295,9 @@
       <c r="AP14" t="s">
         <v>5</v>
       </c>
+      <c r="AQ14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -3465,6 +3501,9 @@
       <c r="AP15" t="s">
         <v>5</v>
       </c>
+      <c r="AQ15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3668,6 +3707,9 @@
       <c r="AP16" t="s">
         <v>7</v>
       </c>
+      <c r="AQ16" t="s">
+        <v>7</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3871,6 +3913,9 @@
       <c r="AP17" t="s">
         <v>5</v>
       </c>
+      <c r="AQ17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -4074,6 +4119,9 @@
       <c r="AP18" t="s">
         <v>5</v>
       </c>
+      <c r="AQ18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -4277,6 +4325,9 @@
       <c r="AP19" t="s">
         <v>7</v>
       </c>
+      <c r="AQ19" t="s">
+        <v>7</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -4480,6 +4531,9 @@
       <c r="AP20" t="s">
         <v>5</v>
       </c>
+      <c r="AQ20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -4683,6 +4737,9 @@
       <c r="AP21" t="s">
         <v>5</v>
       </c>
+      <c r="AQ21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -4886,6 +4943,9 @@
       <c r="AP22" t="s">
         <v>5</v>
       </c>
+      <c r="AQ22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -5089,6 +5149,9 @@
       <c r="AP23" t="s">
         <v>7</v>
       </c>
+      <c r="AQ23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -5271,6 +5334,9 @@
       <c r="AP24" t="s">
         <v>5</v>
       </c>
+      <c r="AQ24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -5474,6 +5540,9 @@
       <c r="AP25" t="s">
         <v>5</v>
       </c>
+      <c r="AQ25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -5677,6 +5746,9 @@
       <c r="AP26" t="s">
         <v>5</v>
       </c>
+      <c r="AQ26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -5880,6 +5952,9 @@
       <c r="AP27" t="s">
         <v>5</v>
       </c>
+      <c r="AQ27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -6083,6 +6158,9 @@
       <c r="AP28" t="s">
         <v>5</v>
       </c>
+      <c r="AQ28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -6286,6 +6364,9 @@
       <c r="AP29" t="s">
         <v>46</v>
       </c>
+      <c r="AQ29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -6489,6 +6570,9 @@
       <c r="AP30" t="s">
         <v>5</v>
       </c>
+      <c r="AQ30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -6692,6 +6776,9 @@
       <c r="AP31" t="s">
         <v>5</v>
       </c>
+      <c r="AQ31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -6895,8 +6982,11 @@
       <c r="AP32" t="s">
         <v>5</v>
       </c>
+      <c r="AQ32" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -7023,8 +7113,11 @@
       <c r="AP33" t="s">
         <v>5</v>
       </c>
+      <c r="AQ33" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -7149,6 +7242,9 @@
         <v>43</v>
       </c>
       <c r="AP34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -7157,7 +7253,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 AJ3:AZ3 BE3:DG3 BB3:BB22 O3:AI34 AQ4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ4:AP34 AQ11:BA22 BC11:BJ22 AQ23:BJ31 G32:I32">
+  <conditionalFormatting sqref="D3:N3 AJ3:AZ3 BE3:DG3 BB3:BB22 O3:AI34 AQ4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ4:AP34 AQ11:BA22 BC11:BJ22 AQ23:BJ31 G32:I32 AQ32:AQ34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\SENAI\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC13603-3BEA-4D73-B995-029F96E36537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F493C82F-5C0D-471B-B1E8-1F98A9D6B85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="46">
   <si>
     <t>TER</t>
   </si>
@@ -174,10 +174,7 @@
     <t>4P/4F</t>
   </si>
   <si>
-    <t>P - F Tarde</t>
-  </si>
-  <si>
-    <t>1F - P</t>
+    <t>1/P</t>
   </si>
 </sst>
 </file>
@@ -562,29 +559,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="41" width="7.7109375" customWidth="1"/>
-    <col min="42" max="42" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="43" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="41" width="7.6640625" customWidth="1"/>
+    <col min="42" max="42" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="43" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -754,7 +751,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -929,7 +926,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1135,7 +1132,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1341,7 +1338,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1547,7 +1544,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -1753,7 +1750,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -1860,7 +1857,7 @@
         <v>43</v>
       </c>
       <c r="AP7" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="AQ7" t="s">
         <v>7</v>
@@ -1941,7 +1938,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2147,7 +2144,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2353,7 +2350,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -2559,7 +2556,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -2765,7 +2762,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -2971,7 +2968,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3168,7 +3165,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -3374,7 +3371,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -3580,7 +3577,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -3786,7 +3783,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -3992,7 +3989,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -4198,7 +4195,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -4404,7 +4401,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -4610,7 +4607,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -4816,7 +4813,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -5022,7 +5019,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -5228,7 +5225,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -5413,7 +5410,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -5619,7 +5616,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -5825,7 +5822,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -6031,7 +6028,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -6237,7 +6234,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -6362,7 +6359,7 @@
         <v>43</v>
       </c>
       <c r="AP29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AQ29" t="s">
         <v>5</v>
@@ -6443,7 +6440,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -6649,7 +6646,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -6855,7 +6852,7 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -6986,7 +6983,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -7117,7 +7114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -7266,13 +7263,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7280,7 +7277,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -7288,7 +7285,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -7296,7 +7293,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -7304,7 +7301,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -7312,7 +7309,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -7320,7 +7317,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -7328,7 +7325,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -7336,7 +7333,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -7344,7 +7341,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -7352,7 +7349,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -7360,7 +7357,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -7368,7 +7365,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -7376,7 +7373,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -7384,7 +7381,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -7392,7 +7389,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -7400,7 +7397,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -7408,7 +7405,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -7416,7 +7413,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -7424,7 +7421,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -7432,7 +7429,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -7440,7 +7437,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -7448,7 +7445,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -7456,7 +7453,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -7464,7 +7461,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -7472,7 +7469,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -7480,7 +7477,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -7488,7 +7485,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -7496,7 +7493,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -7504,7 +7501,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -7512,7 +7509,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -7520,7 +7517,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -7528,7 +7525,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F493C82F-5C0D-471B-B1E8-1F98A9D6B85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F840235B-8AAE-4D1C-A1D3-CF7835E9DDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="46">
   <si>
     <t>TER</t>
   </si>
@@ -702,8 +702,12 @@
       <c r="AQ1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AR1" s="1"/>
-      <c r="AS1" s="1"/>
+      <c r="AR1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="AT1" s="1"/>
       <c r="AU1" s="3"/>
       <c r="AV1" s="3"/>
@@ -882,6 +886,12 @@
       <c r="AQ2" s="1">
         <v>46184</v>
       </c>
+      <c r="AR2" s="1">
+        <v>46189</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>46191</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -1054,6 +1064,9 @@
         <v>5</v>
       </c>
       <c r="AQ3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1262,6 +1275,9 @@
       <c r="AQ4" t="s">
         <v>5</v>
       </c>
+      <c r="AR4" t="s">
+        <v>5</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1468,6 +1484,9 @@
       <c r="AQ5" t="s">
         <v>5</v>
       </c>
+      <c r="AR5" t="s">
+        <v>7</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1674,6 +1693,9 @@
       <c r="AQ6" t="s">
         <v>5</v>
       </c>
+      <c r="AR6" t="s">
+        <v>5</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1862,6 +1884,9 @@
       <c r="AQ7" t="s">
         <v>7</v>
       </c>
+      <c r="AR7" t="s">
+        <v>5</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -2068,6 +2093,9 @@
       <c r="AQ8" t="s">
         <v>5</v>
       </c>
+      <c r="AR8" t="s">
+        <v>5</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -2274,6 +2302,9 @@
       <c r="AQ9" t="s">
         <v>5</v>
       </c>
+      <c r="AR9" t="s">
+        <v>5</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2480,6 +2511,9 @@
       <c r="AQ10" t="s">
         <v>5</v>
       </c>
+      <c r="AR10" t="s">
+        <v>5</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2686,6 +2720,9 @@
       <c r="AQ11" t="s">
         <v>5</v>
       </c>
+      <c r="AR11" t="s">
+        <v>5</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2892,6 +2929,9 @@
       <c r="AQ12" t="s">
         <v>5</v>
       </c>
+      <c r="AR12" t="s">
+        <v>5</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -3089,6 +3129,9 @@
       <c r="AQ13" t="s">
         <v>5</v>
       </c>
+      <c r="AR13" t="s">
+        <v>5</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -3295,6 +3338,9 @@
       <c r="AQ14" t="s">
         <v>5</v>
       </c>
+      <c r="AR14" t="s">
+        <v>5</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -3501,6 +3547,9 @@
       <c r="AQ15" t="s">
         <v>5</v>
       </c>
+      <c r="AR15" t="s">
+        <v>5</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3707,6 +3756,9 @@
       <c r="AQ16" t="s">
         <v>7</v>
       </c>
+      <c r="AR16" t="s">
+        <v>7</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3913,6 +3965,9 @@
       <c r="AQ17" t="s">
         <v>5</v>
       </c>
+      <c r="AR17" t="s">
+        <v>5</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -4119,6 +4174,9 @@
       <c r="AQ18" t="s">
         <v>5</v>
       </c>
+      <c r="AR18" t="s">
+        <v>5</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -4325,6 +4383,9 @@
       <c r="AQ19" t="s">
         <v>7</v>
       </c>
+      <c r="AR19" t="s">
+        <v>7</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -4531,6 +4592,9 @@
       <c r="AQ20" t="s">
         <v>5</v>
       </c>
+      <c r="AR20" t="s">
+        <v>5</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -4737,6 +4801,9 @@
       <c r="AQ21" t="s">
         <v>5</v>
       </c>
+      <c r="AR21" t="s">
+        <v>5</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -4943,6 +5010,9 @@
       <c r="AQ22" t="s">
         <v>5</v>
       </c>
+      <c r="AR22" t="s">
+        <v>5</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -5149,6 +5219,9 @@
       <c r="AQ23" t="s">
         <v>5</v>
       </c>
+      <c r="AR23" t="s">
+        <v>5</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -5334,6 +5407,9 @@
       <c r="AQ24" t="s">
         <v>5</v>
       </c>
+      <c r="AR24" t="s">
+        <v>5</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -5540,6 +5616,9 @@
       <c r="AQ25" t="s">
         <v>5</v>
       </c>
+      <c r="AR25" t="s">
+        <v>5</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -5746,6 +5825,9 @@
       <c r="AQ26" t="s">
         <v>5</v>
       </c>
+      <c r="AR26" t="s">
+        <v>5</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -5952,6 +6034,9 @@
       <c r="AQ27" t="s">
         <v>5</v>
       </c>
+      <c r="AR27" t="s">
+        <v>5</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -6158,6 +6243,9 @@
       <c r="AQ28" t="s">
         <v>5</v>
       </c>
+      <c r="AR28" t="s">
+        <v>5</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -6364,6 +6452,9 @@
       <c r="AQ29" t="s">
         <v>5</v>
       </c>
+      <c r="AR29" t="s">
+        <v>5</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -6570,6 +6661,9 @@
       <c r="AQ30" t="s">
         <v>5</v>
       </c>
+      <c r="AR30" t="s">
+        <v>5</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -6776,6 +6870,9 @@
       <c r="AQ31" t="s">
         <v>5</v>
       </c>
+      <c r="AR31" t="s">
+        <v>5</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -6982,8 +7079,11 @@
       <c r="AQ32" t="s">
         <v>5</v>
       </c>
+      <c r="AR32" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -7113,8 +7213,11 @@
       <c r="AQ33" t="s">
         <v>5</v>
       </c>
+      <c r="AR33" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -7242,6 +7345,9 @@
         <v>5</v>
       </c>
       <c r="AQ34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -7250,7 +7356,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 AJ3:AZ3 BE3:DG3 BB3:BB22 O3:AI34 AQ4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ4:AP34 AQ11:BA22 BC11:BJ22 AQ23:BJ31 G32:I32 AQ32:AQ34">
+  <conditionalFormatting sqref="D3:N3 AJ3:AZ3 BE3:DG3 BB3:BB22 O3:AI34 AQ4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ4:AP34 AQ11:BA22 BC11:BJ22 AQ23:BJ31 G32:I32 AQ32:AR34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F840235B-8AAE-4D1C-A1D3-CF7835E9DDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73068D61-58B1-4384-A779-E7CB6F283797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -559,29 +559,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="41" width="7.6640625" customWidth="1"/>
-    <col min="42" max="42" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="43" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="41" width="7.7109375" customWidth="1"/>
+    <col min="42" max="42" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -755,7 +755,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -936,7 +936,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1145,7 +1145,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1354,7 +1354,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1563,7 +1563,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -1772,7 +1772,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -1963,7 +1963,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2172,7 +2172,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2381,7 +2381,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -2590,7 +2590,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -2799,7 +2799,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -3008,7 +3008,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3208,7 +3208,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -3417,7 +3417,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -3626,7 +3626,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -3835,7 +3835,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -4044,7 +4044,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -4253,7 +4253,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -4462,7 +4462,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -4671,7 +4671,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -4880,7 +4880,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -5089,7 +5089,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -5298,7 +5298,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -5486,7 +5486,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -5695,7 +5695,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -5904,7 +5904,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -6113,7 +6113,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -6322,7 +6322,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -6531,7 +6531,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -6740,7 +6740,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -6949,7 +6949,7 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -7217,7 +7217,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -7369,13 +7369,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7383,7 +7383,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -7391,7 +7391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -7407,7 +7407,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -7415,7 +7415,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -7423,7 +7423,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -7439,7 +7439,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -7447,7 +7447,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -7479,7 +7479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -7487,7 +7487,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -7495,7 +7495,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -7511,7 +7511,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -7527,7 +7527,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -7543,7 +7543,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -7559,7 +7559,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -7567,7 +7567,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -7591,7 +7591,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -7599,7 +7599,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -7607,7 +7607,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -7623,7 +7623,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -7631,7 +7631,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73068D61-58B1-4384-A779-E7CB6F283797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E360A8FF-94A4-4F81-BD7A-26BE8A4C120A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="46">
   <si>
     <t>TER</t>
   </si>
@@ -559,29 +559,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="41" width="7.7109375" customWidth="1"/>
-    <col min="42" max="42" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="43" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="41" width="7.6640625" customWidth="1"/>
+    <col min="42" max="42" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,9 @@
       <c r="AS1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AT1" s="1"/>
+      <c r="AT1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="AU1" s="3"/>
       <c r="AV1" s="3"/>
       <c r="AW1" s="3"/>
@@ -755,7 +757,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -891,6 +893,9 @@
       </c>
       <c r="AS2" s="1">
         <v>46191</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>46196</v>
       </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
@@ -936,7 +941,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1067,6 +1072,12 @@
         <v>5</v>
       </c>
       <c r="AR3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT3" t="s">
         <v>5</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1145,7 +1156,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1276,6 +1287,12 @@
         <v>5</v>
       </c>
       <c r="AR4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT4" t="s">
         <v>5</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1354,7 +1371,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1486,6 +1503,12 @@
       </c>
       <c r="AR5" t="s">
         <v>7</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>5</v>
       </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
@@ -1563,7 +1586,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -1694,6 +1717,12 @@
         <v>5</v>
       </c>
       <c r="AR6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT6" t="s">
         <v>5</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1772,7 +1801,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -1885,6 +1914,12 @@
         <v>7</v>
       </c>
       <c r="AR7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT7" t="s">
         <v>5</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1963,7 +1998,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2094,6 +2129,12 @@
         <v>5</v>
       </c>
       <c r="AR8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT8" t="s">
         <v>5</v>
       </c>
       <c r="AU8" s="2"/>
@@ -2172,7 +2213,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2303,6 +2344,12 @@
         <v>5</v>
       </c>
       <c r="AR9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT9" t="s">
         <v>5</v>
       </c>
       <c r="AU9" s="2"/>
@@ -2381,7 +2428,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -2512,6 +2559,12 @@
         <v>5</v>
       </c>
       <c r="AR10" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT10" t="s">
         <v>5</v>
       </c>
       <c r="AU10" s="2"/>
@@ -2590,7 +2643,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -2721,6 +2774,12 @@
         <v>5</v>
       </c>
       <c r="AR11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT11" t="s">
         <v>5</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2799,7 +2858,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -2930,6 +2989,12 @@
         <v>5</v>
       </c>
       <c r="AR12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT12" t="s">
         <v>5</v>
       </c>
       <c r="AU12" s="2"/>
@@ -3008,7 +3073,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3130,6 +3195,12 @@
         <v>5</v>
       </c>
       <c r="AR13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT13" t="s">
         <v>5</v>
       </c>
       <c r="AU13" s="2"/>
@@ -3208,7 +3279,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -3339,6 +3410,12 @@
         <v>5</v>
       </c>
       <c r="AR14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT14" t="s">
         <v>5</v>
       </c>
       <c r="AU14" s="2"/>
@@ -3417,7 +3494,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -3548,6 +3625,12 @@
         <v>5</v>
       </c>
       <c r="AR15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT15" t="s">
         <v>5</v>
       </c>
       <c r="AU15" s="2"/>
@@ -3626,7 +3709,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -3757,6 +3840,12 @@
         <v>7</v>
       </c>
       <c r="AR16" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT16" t="s">
         <v>7</v>
       </c>
       <c r="AU16" s="2"/>
@@ -3835,7 +3924,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -3966,6 +4055,12 @@
         <v>5</v>
       </c>
       <c r="AR17" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT17" t="s">
         <v>5</v>
       </c>
       <c r="AU17" s="2"/>
@@ -4044,7 +4139,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -4175,6 +4270,12 @@
         <v>5</v>
       </c>
       <c r="AR18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT18" t="s">
         <v>5</v>
       </c>
       <c r="AU18" s="2"/>
@@ -4253,7 +4354,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -4384,6 +4485,12 @@
         <v>7</v>
       </c>
       <c r="AR19" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS19" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT19" t="s">
         <v>7</v>
       </c>
       <c r="AU19" s="2"/>
@@ -4462,7 +4569,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -4593,6 +4700,12 @@
         <v>5</v>
       </c>
       <c r="AR20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT20" t="s">
         <v>5</v>
       </c>
       <c r="AU20" s="2"/>
@@ -4671,7 +4784,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -4802,6 +4915,12 @@
         <v>5</v>
       </c>
       <c r="AR21" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS21" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT21" t="s">
         <v>5</v>
       </c>
       <c r="AU21" s="2"/>
@@ -4880,7 +4999,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -5011,6 +5130,12 @@
         <v>5</v>
       </c>
       <c r="AR22" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS22" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT22" t="s">
         <v>5</v>
       </c>
       <c r="AU22" s="2"/>
@@ -5089,7 +5214,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -5220,6 +5345,12 @@
         <v>5</v>
       </c>
       <c r="AR23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT23" t="s">
         <v>5</v>
       </c>
       <c r="AU23" s="2"/>
@@ -5298,7 +5429,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -5408,6 +5539,12 @@
         <v>5</v>
       </c>
       <c r="AR24" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS24" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT24" t="s">
         <v>5</v>
       </c>
       <c r="AU24" s="2"/>
@@ -5486,7 +5623,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -5617,6 +5754,12 @@
         <v>5</v>
       </c>
       <c r="AR25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT25" t="s">
         <v>5</v>
       </c>
       <c r="AU25" s="2"/>
@@ -5695,7 +5838,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -5826,6 +5969,12 @@
         <v>5</v>
       </c>
       <c r="AR26" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS26" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT26" t="s">
         <v>5</v>
       </c>
       <c r="AU26" s="2"/>
@@ -5904,7 +6053,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -6035,6 +6184,12 @@
         <v>5</v>
       </c>
       <c r="AR27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT27" t="s">
         <v>5</v>
       </c>
       <c r="AU27" s="2"/>
@@ -6113,7 +6268,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -6244,6 +6399,12 @@
         <v>5</v>
       </c>
       <c r="AR28" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS28" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT28" t="s">
         <v>5</v>
       </c>
       <c r="AU28" s="2"/>
@@ -6322,7 +6483,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -6453,6 +6614,12 @@
         <v>5</v>
       </c>
       <c r="AR29" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS29" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT29" t="s">
         <v>5</v>
       </c>
       <c r="AU29" s="2"/>
@@ -6531,7 +6698,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -6662,6 +6829,12 @@
         <v>5</v>
       </c>
       <c r="AR30" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS30" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT30" t="s">
         <v>5</v>
       </c>
       <c r="AU30" s="2"/>
@@ -6740,7 +6913,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -6871,6 +7044,12 @@
         <v>5</v>
       </c>
       <c r="AR31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT31" t="s">
         <v>5</v>
       </c>
       <c r="AU31" s="2"/>
@@ -6949,7 +7128,7 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -7082,8 +7261,14 @@
       <c r="AR32" t="s">
         <v>5</v>
       </c>
+      <c r="AS32" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT32" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -7216,8 +7401,14 @@
       <c r="AR33" t="s">
         <v>5</v>
       </c>
+      <c r="AS33" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT33" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="34" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -7348,6 +7539,12 @@
         <v>5</v>
       </c>
       <c r="AR34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -7356,7 +7553,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 AJ3:AZ3 BE3:DG3 BB3:BB22 O3:AI34 AQ4:AZ10 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AJ4:AP34 AQ11:BA22 BC11:BJ22 AQ23:BJ31 G32:I32 AQ32:AR34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 BB3:BB22 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 BC11:BJ22 G32:I32 AU23:BJ31 AU11:BA22 AU3:AZ10 O3:AT34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -7369,13 +7566,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7383,7 +7580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -7391,7 +7588,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -7399,7 +7596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -7407,7 +7604,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -7415,7 +7612,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -7423,7 +7620,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -7431,7 +7628,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -7439,7 +7636,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -7447,7 +7644,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -7455,7 +7652,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -7463,7 +7660,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -7471,7 +7668,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -7479,7 +7676,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -7487,7 +7684,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -7495,7 +7692,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -7503,7 +7700,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -7511,7 +7708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -7519,7 +7716,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -7527,7 +7724,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -7535,7 +7732,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -7543,7 +7740,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -7551,7 +7748,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -7559,7 +7756,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -7567,7 +7764,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -7575,7 +7772,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -7583,7 +7780,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -7591,7 +7788,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -7599,7 +7796,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -7607,7 +7804,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -7615,7 +7812,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -7623,7 +7820,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -7631,7 +7828,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E360A8FF-94A4-4F81-BD7A-26BE8A4C120A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A108078D-CD4A-48E6-95F3-596BA6A36552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="47">
   <si>
     <t>TER</t>
   </si>
@@ -176,6 +176,9 @@
   <si>
     <t>1/P</t>
   </si>
+  <si>
+    <t>FÉRIAS</t>
+  </si>
 </sst>
 </file>
 
@@ -250,10 +253,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -559,29 +561,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="41" width="7.6640625" customWidth="1"/>
-    <col min="42" max="42" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="43" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="41" width="7.7109375" customWidth="1"/>
+    <col min="42" max="42" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="47" width="7.7109375" customWidth="1"/>
+    <col min="48" max="48" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="49" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="4" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -711,53 +715,57 @@
       <c r="AT1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AU1" s="3"/>
-      <c r="AV1" s="3"/>
-      <c r="AW1" s="3"/>
+      <c r="AU1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW1" s="1"/>
       <c r="AX1" s="1"/>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4"/>
-      <c r="BA1" s="4"/>
-      <c r="BB1" s="4"/>
-      <c r="BC1" s="4"/>
-      <c r="BD1" s="4"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="4"/>
-      <c r="BG1" s="4"/>
-      <c r="BH1" s="4"/>
-      <c r="BI1" s="4"/>
-      <c r="BJ1" s="4"/>
-      <c r="BK1" s="4"/>
-      <c r="BL1" s="4"/>
-      <c r="BM1" s="4"/>
-      <c r="BN1" s="4"/>
-      <c r="BO1" s="4"/>
-      <c r="BP1" s="4"/>
-      <c r="BQ1" s="4"/>
-      <c r="BR1" s="4"/>
-      <c r="BS1" s="4"/>
-      <c r="BT1" s="4"/>
-      <c r="BU1" s="4"/>
-      <c r="BV1" s="4"/>
-      <c r="BW1" s="4"/>
-      <c r="BX1" s="4"/>
-      <c r="BY1" s="4"/>
-      <c r="BZ1" s="4"/>
-      <c r="CA1" s="4"/>
-      <c r="CB1" s="4"/>
-      <c r="CC1" s="4"/>
-      <c r="CD1" s="4"/>
-      <c r="CE1" s="4"/>
-      <c r="CF1" s="4"/>
-      <c r="CG1" s="4"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="3"/>
+      <c r="BO1" s="3"/>
+      <c r="BP1" s="3"/>
+      <c r="BQ1" s="3"/>
+      <c r="BR1" s="3"/>
+      <c r="BS1" s="3"/>
+      <c r="BT1" s="3"/>
+      <c r="BU1" s="3"/>
+      <c r="BV1" s="3"/>
+      <c r="BW1" s="3"/>
+      <c r="BX1" s="3"/>
+      <c r="BY1" s="3"/>
+      <c r="BZ1" s="3"/>
+      <c r="CA1" s="3"/>
+      <c r="CB1" s="3"/>
+      <c r="CC1" s="3"/>
+      <c r="CD1" s="3"/>
+      <c r="CE1" s="3"/>
+      <c r="CF1" s="3"/>
+      <c r="CG1" s="3"/>
       <c r="CH1" s="1"/>
-      <c r="CI1" s="4"/>
-      <c r="CJ1" s="4"/>
-      <c r="CK1" s="4"/>
-      <c r="CL1" s="4"/>
-      <c r="CM1" s="4"/>
+      <c r="CI1" s="3"/>
+      <c r="CJ1" s="3"/>
+      <c r="CK1" s="3"/>
+      <c r="CL1" s="3"/>
+      <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -897,51 +905,57 @@
       <c r="AT2" s="1">
         <v>46196</v>
       </c>
-      <c r="AU2" s="2"/>
-      <c r="AV2" s="2"/>
-      <c r="AW2" s="2"/>
-      <c r="AZ2" s="5"/>
-      <c r="BA2" s="5"/>
-      <c r="BB2" s="5"/>
-      <c r="BC2" s="5"/>
-      <c r="BD2" s="5"/>
-      <c r="BE2" s="5"/>
-      <c r="BF2" s="5"/>
-      <c r="BG2" s="5"/>
-      <c r="BH2" s="5"/>
-      <c r="BI2" s="5"/>
-      <c r="BJ2" s="5"/>
-      <c r="BK2" s="5"/>
-      <c r="BL2" s="5"/>
-      <c r="BM2" s="5"/>
-      <c r="BN2" s="5"/>
-      <c r="BO2" s="5"/>
-      <c r="BP2" s="5"/>
-      <c r="BQ2" s="5"/>
-      <c r="BR2" s="5"/>
-      <c r="BS2" s="5"/>
-      <c r="BT2" s="5"/>
-      <c r="BU2" s="5"/>
-      <c r="BV2" s="5"/>
-      <c r="BW2" s="5"/>
-      <c r="BX2" s="5"/>
-      <c r="BY2" s="5"/>
-      <c r="BZ2" s="5"/>
-      <c r="CA2" s="5"/>
-      <c r="CB2" s="5"/>
-      <c r="CC2" s="5"/>
-      <c r="CD2" s="5"/>
-      <c r="CE2" s="5"/>
-      <c r="CF2" s="5"/>
-      <c r="CG2" s="5"/>
-      <c r="CH2" s="5"/>
-      <c r="CI2" s="5"/>
-      <c r="CJ2" s="5"/>
-      <c r="CK2" s="5"/>
-      <c r="CL2" s="5"/>
-      <c r="CM2" s="5"/>
+      <c r="AU2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>46231</v>
+      </c>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="4"/>
+      <c r="BO2" s="4"/>
+      <c r="BP2" s="4"/>
+      <c r="BQ2" s="4"/>
+      <c r="BR2" s="4"/>
+      <c r="BS2" s="4"/>
+      <c r="BT2" s="4"/>
+      <c r="BU2" s="4"/>
+      <c r="BV2" s="4"/>
+      <c r="BW2" s="4"/>
+      <c r="BX2" s="4"/>
+      <c r="BY2" s="4"/>
+      <c r="BZ2" s="4"/>
+      <c r="CA2" s="4"/>
+      <c r="CB2" s="4"/>
+      <c r="CC2" s="4"/>
+      <c r="CD2" s="4"/>
+      <c r="CE2" s="4"/>
+      <c r="CF2" s="4"/>
+      <c r="CG2" s="4"/>
+      <c r="CH2" s="4"/>
+      <c r="CI2" s="4"/>
+      <c r="CJ2" s="4"/>
+      <c r="CK2" s="4"/>
+      <c r="CL2" s="4"/>
+      <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -969,7 +983,7 @@
       <c r="I3" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K3" t="s">
@@ -1080,83 +1094,88 @@
       <c r="AT3" t="s">
         <v>5</v>
       </c>
-      <c r="AU3" s="2"/>
-      <c r="AV3" s="2"/>
-      <c r="AW3" s="2"/>
-      <c r="AZ3" s="5"/>
-      <c r="BA3" s="5"/>
-      <c r="BB3" s="5"/>
-      <c r="BC3" s="5"/>
-      <c r="BD3" s="5"/>
-      <c r="BE3" s="5"/>
-      <c r="BF3" s="5"/>
-      <c r="BG3" s="5"/>
-      <c r="BH3" s="5"/>
-      <c r="BI3" s="5"/>
-      <c r="BJ3" s="5"/>
-      <c r="BK3" s="5"/>
-      <c r="BL3" s="5"/>
-      <c r="BM3" s="5"/>
-      <c r="BN3" s="5"/>
-      <c r="BO3" s="5"/>
-      <c r="BP3" s="5"/>
-      <c r="BQ3" s="5"/>
-      <c r="BR3" s="5"/>
-      <c r="BS3" s="5"/>
-      <c r="BT3" s="5"/>
-      <c r="BU3" s="5"/>
-      <c r="BV3" s="5"/>
-      <c r="BW3" s="5"/>
-      <c r="BX3" s="5"/>
-      <c r="BY3" s="5"/>
-      <c r="BZ3" s="5"/>
-      <c r="CA3" s="5"/>
-      <c r="CB3" s="5"/>
-      <c r="CC3" s="5"/>
-      <c r="CD3" s="5"/>
-      <c r="CE3" s="5"/>
-      <c r="CF3" s="5"/>
-      <c r="CG3" s="5"/>
-      <c r="CH3" s="5"/>
-      <c r="CI3" s="5"/>
-      <c r="CJ3" s="5"/>
-      <c r="CK3" s="5"/>
-      <c r="CL3" s="5"/>
-      <c r="CM3" s="5"/>
-      <c r="CN3" s="5"/>
-      <c r="CO3" s="5"/>
-      <c r="CP3" s="5"/>
-      <c r="CQ3" s="5"/>
-      <c r="CR3" s="5"/>
-      <c r="CS3" s="5"/>
-      <c r="CT3" s="5"/>
-      <c r="CU3" s="5"/>
-      <c r="CV3" s="5"/>
-      <c r="CW3" s="5"/>
-      <c r="CX3" s="5"/>
-      <c r="CY3" s="5"/>
-      <c r="CZ3" s="5"/>
-      <c r="DA3" s="5"/>
-      <c r="DB3" s="5"/>
-      <c r="DC3" s="5"/>
-      <c r="DD3" s="5"/>
-      <c r="DE3" s="5"/>
-      <c r="DF3" s="5"/>
-      <c r="DG3" s="5"/>
-      <c r="DH3" s="5"/>
-      <c r="DI3" s="5"/>
-      <c r="DJ3" s="5"/>
-      <c r="DK3" s="5"/>
-      <c r="DL3" s="5"/>
-      <c r="DM3" s="5"/>
-      <c r="DN3" s="5"/>
-      <c r="DO3" s="5"/>
-      <c r="DP3" s="5"/>
-      <c r="DQ3" s="5"/>
-      <c r="DR3" s="5"/>
-      <c r="DS3" s="5"/>
+      <c r="AU3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW3" s="4"/>
+      <c r="AX3" s="4"/>
+      <c r="AZ3" s="4"/>
+      <c r="BA3" s="4"/>
+      <c r="BB3" s="4"/>
+      <c r="BC3" s="4"/>
+      <c r="BD3" s="4"/>
+      <c r="BE3" s="4"/>
+      <c r="BF3" s="4"/>
+      <c r="BG3" s="4"/>
+      <c r="BH3" s="4"/>
+      <c r="BI3" s="4"/>
+      <c r="BJ3" s="4"/>
+      <c r="BK3" s="4"/>
+      <c r="BL3" s="4"/>
+      <c r="BM3" s="4"/>
+      <c r="BN3" s="4"/>
+      <c r="BO3" s="4"/>
+      <c r="BP3" s="4"/>
+      <c r="BQ3" s="4"/>
+      <c r="BR3" s="4"/>
+      <c r="BS3" s="4"/>
+      <c r="BT3" s="4"/>
+      <c r="BU3" s="4"/>
+      <c r="BV3" s="4"/>
+      <c r="BW3" s="4"/>
+      <c r="BX3" s="4"/>
+      <c r="BY3" s="4"/>
+      <c r="BZ3" s="4"/>
+      <c r="CA3" s="4"/>
+      <c r="CB3" s="4"/>
+      <c r="CC3" s="4"/>
+      <c r="CD3" s="4"/>
+      <c r="CE3" s="4"/>
+      <c r="CF3" s="4"/>
+      <c r="CG3" s="4"/>
+      <c r="CH3" s="4"/>
+      <c r="CI3" s="4"/>
+      <c r="CJ3" s="4"/>
+      <c r="CK3" s="4"/>
+      <c r="CL3" s="4"/>
+      <c r="CM3" s="4"/>
+      <c r="CN3" s="4"/>
+      <c r="CO3" s="4"/>
+      <c r="CP3" s="4"/>
+      <c r="CQ3" s="4"/>
+      <c r="CR3" s="4"/>
+      <c r="CS3" s="4"/>
+      <c r="CT3" s="4"/>
+      <c r="CU3" s="4"/>
+      <c r="CV3" s="4"/>
+      <c r="CW3" s="4"/>
+      <c r="CX3" s="4"/>
+      <c r="CY3" s="4"/>
+      <c r="CZ3" s="4"/>
+      <c r="DA3" s="4"/>
+      <c r="DB3" s="4"/>
+      <c r="DC3" s="4"/>
+      <c r="DD3" s="4"/>
+      <c r="DE3" s="4"/>
+      <c r="DF3" s="4"/>
+      <c r="DG3" s="4"/>
+      <c r="DH3" s="4"/>
+      <c r="DI3" s="4"/>
+      <c r="DJ3" s="4"/>
+      <c r="DK3" s="4"/>
+      <c r="DL3" s="4"/>
+      <c r="DM3" s="4"/>
+      <c r="DN3" s="4"/>
+      <c r="DO3" s="4"/>
+      <c r="DP3" s="4"/>
+      <c r="DQ3" s="4"/>
+      <c r="DR3" s="4"/>
+      <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1184,7 +1203,7 @@
       <c r="I4" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K4" t="s">
@@ -1295,83 +1314,88 @@
       <c r="AT4" t="s">
         <v>5</v>
       </c>
-      <c r="AU4" s="2"/>
-      <c r="AV4" s="2"/>
-      <c r="AW4" s="2"/>
-      <c r="AZ4" s="5"/>
-      <c r="BA4" s="5"/>
-      <c r="BB4" s="5"/>
-      <c r="BC4" s="5"/>
-      <c r="BD4" s="5"/>
-      <c r="BE4" s="5"/>
-      <c r="BF4" s="5"/>
-      <c r="BG4" s="5"/>
-      <c r="BH4" s="5"/>
-      <c r="BI4" s="5"/>
-      <c r="BJ4" s="5"/>
-      <c r="BK4" s="5"/>
-      <c r="BL4" s="5"/>
-      <c r="BM4" s="5"/>
-      <c r="BN4" s="5"/>
-      <c r="BO4" s="5"/>
-      <c r="BP4" s="5"/>
-      <c r="BQ4" s="5"/>
-      <c r="BR4" s="5"/>
-      <c r="BS4" s="5"/>
-      <c r="BT4" s="5"/>
-      <c r="BU4" s="5"/>
-      <c r="BV4" s="5"/>
-      <c r="BW4" s="5"/>
-      <c r="BX4" s="5"/>
-      <c r="BY4" s="5"/>
-      <c r="BZ4" s="5"/>
-      <c r="CA4" s="5"/>
-      <c r="CB4" s="5"/>
-      <c r="CC4" s="5"/>
-      <c r="CD4" s="5"/>
-      <c r="CE4" s="5"/>
-      <c r="CF4" s="5"/>
-      <c r="CG4" s="5"/>
-      <c r="CH4" s="5"/>
-      <c r="CI4" s="5"/>
-      <c r="CJ4" s="5"/>
-      <c r="CK4" s="5"/>
-      <c r="CL4" s="5"/>
-      <c r="CM4" s="5"/>
-      <c r="CN4" s="5"/>
-      <c r="CO4" s="5"/>
-      <c r="CP4" s="5"/>
-      <c r="CQ4" s="5"/>
-      <c r="CR4" s="5"/>
-      <c r="CS4" s="5"/>
-      <c r="CT4" s="5"/>
-      <c r="CU4" s="5"/>
-      <c r="CV4" s="5"/>
-      <c r="CW4" s="5"/>
-      <c r="CX4" s="5"/>
-      <c r="CY4" s="5"/>
-      <c r="CZ4" s="5"/>
-      <c r="DA4" s="5"/>
-      <c r="DB4" s="5"/>
-      <c r="DC4" s="5"/>
-      <c r="DD4" s="5"/>
-      <c r="DE4" s="5"/>
-      <c r="DF4" s="5"/>
-      <c r="DG4" s="5"/>
-      <c r="DH4" s="5"/>
-      <c r="DI4" s="5"/>
-      <c r="DJ4" s="5"/>
-      <c r="DK4" s="5"/>
-      <c r="DL4" s="5"/>
-      <c r="DM4" s="5"/>
-      <c r="DN4" s="5"/>
-      <c r="DO4" s="5"/>
-      <c r="DP4" s="5"/>
-      <c r="DQ4" s="5"/>
-      <c r="DR4" s="5"/>
-      <c r="DS4" s="5"/>
+      <c r="AU4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW4" s="4"/>
+      <c r="AX4" s="4"/>
+      <c r="AZ4" s="4"/>
+      <c r="BA4" s="4"/>
+      <c r="BB4" s="4"/>
+      <c r="BC4" s="4"/>
+      <c r="BD4" s="4"/>
+      <c r="BE4" s="4"/>
+      <c r="BF4" s="4"/>
+      <c r="BG4" s="4"/>
+      <c r="BH4" s="4"/>
+      <c r="BI4" s="4"/>
+      <c r="BJ4" s="4"/>
+      <c r="BK4" s="4"/>
+      <c r="BL4" s="4"/>
+      <c r="BM4" s="4"/>
+      <c r="BN4" s="4"/>
+      <c r="BO4" s="4"/>
+      <c r="BP4" s="4"/>
+      <c r="BQ4" s="4"/>
+      <c r="BR4" s="4"/>
+      <c r="BS4" s="4"/>
+      <c r="BT4" s="4"/>
+      <c r="BU4" s="4"/>
+      <c r="BV4" s="4"/>
+      <c r="BW4" s="4"/>
+      <c r="BX4" s="4"/>
+      <c r="BY4" s="4"/>
+      <c r="BZ4" s="4"/>
+      <c r="CA4" s="4"/>
+      <c r="CB4" s="4"/>
+      <c r="CC4" s="4"/>
+      <c r="CD4" s="4"/>
+      <c r="CE4" s="4"/>
+      <c r="CF4" s="4"/>
+      <c r="CG4" s="4"/>
+      <c r="CH4" s="4"/>
+      <c r="CI4" s="4"/>
+      <c r="CJ4" s="4"/>
+      <c r="CK4" s="4"/>
+      <c r="CL4" s="4"/>
+      <c r="CM4" s="4"/>
+      <c r="CN4" s="4"/>
+      <c r="CO4" s="4"/>
+      <c r="CP4" s="4"/>
+      <c r="CQ4" s="4"/>
+      <c r="CR4" s="4"/>
+      <c r="CS4" s="4"/>
+      <c r="CT4" s="4"/>
+      <c r="CU4" s="4"/>
+      <c r="CV4" s="4"/>
+      <c r="CW4" s="4"/>
+      <c r="CX4" s="4"/>
+      <c r="CY4" s="4"/>
+      <c r="CZ4" s="4"/>
+      <c r="DA4" s="4"/>
+      <c r="DB4" s="4"/>
+      <c r="DC4" s="4"/>
+      <c r="DD4" s="4"/>
+      <c r="DE4" s="4"/>
+      <c r="DF4" s="4"/>
+      <c r="DG4" s="4"/>
+      <c r="DH4" s="4"/>
+      <c r="DI4" s="4"/>
+      <c r="DJ4" s="4"/>
+      <c r="DK4" s="4"/>
+      <c r="DL4" s="4"/>
+      <c r="DM4" s="4"/>
+      <c r="DN4" s="4"/>
+      <c r="DO4" s="4"/>
+      <c r="DP4" s="4"/>
+      <c r="DQ4" s="4"/>
+      <c r="DR4" s="4"/>
+      <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1399,7 +1423,7 @@
       <c r="I5" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K5" t="s">
@@ -1510,83 +1534,88 @@
       <c r="AT5" t="s">
         <v>5</v>
       </c>
-      <c r="AU5" s="2"/>
-      <c r="AV5" s="2"/>
-      <c r="AW5" s="2"/>
-      <c r="AZ5" s="5"/>
-      <c r="BA5" s="5"/>
-      <c r="BB5" s="5"/>
-      <c r="BC5" s="5"/>
-      <c r="BD5" s="5"/>
-      <c r="BE5" s="5"/>
-      <c r="BF5" s="5"/>
-      <c r="BG5" s="5"/>
-      <c r="BH5" s="5"/>
-      <c r="BI5" s="5"/>
-      <c r="BJ5" s="5"/>
-      <c r="BK5" s="5"/>
-      <c r="BL5" s="5"/>
-      <c r="BM5" s="5"/>
-      <c r="BN5" s="5"/>
-      <c r="BO5" s="5"/>
-      <c r="BP5" s="5"/>
-      <c r="BQ5" s="5"/>
-      <c r="BR5" s="5"/>
-      <c r="BS5" s="5"/>
-      <c r="BT5" s="5"/>
-      <c r="BU5" s="5"/>
-      <c r="BV5" s="5"/>
-      <c r="BW5" s="5"/>
-      <c r="BX5" s="5"/>
-      <c r="BY5" s="5"/>
-      <c r="BZ5" s="5"/>
-      <c r="CA5" s="5"/>
-      <c r="CB5" s="5"/>
-      <c r="CC5" s="5"/>
-      <c r="CD5" s="5"/>
-      <c r="CE5" s="5"/>
-      <c r="CF5" s="5"/>
-      <c r="CG5" s="5"/>
-      <c r="CH5" s="5"/>
-      <c r="CI5" s="5"/>
-      <c r="CJ5" s="5"/>
-      <c r="CK5" s="5"/>
-      <c r="CL5" s="5"/>
-      <c r="CM5" s="5"/>
-      <c r="CN5" s="5"/>
-      <c r="CO5" s="5"/>
-      <c r="CP5" s="5"/>
-      <c r="CQ5" s="5"/>
-      <c r="CR5" s="5"/>
-      <c r="CS5" s="5"/>
-      <c r="CT5" s="5"/>
-      <c r="CU5" s="5"/>
-      <c r="CV5" s="5"/>
-      <c r="CW5" s="5"/>
-      <c r="CX5" s="5"/>
-      <c r="CY5" s="5"/>
-      <c r="CZ5" s="5"/>
-      <c r="DA5" s="5"/>
-      <c r="DB5" s="5"/>
-      <c r="DC5" s="5"/>
-      <c r="DD5" s="5"/>
-      <c r="DE5" s="5"/>
-      <c r="DF5" s="5"/>
-      <c r="DG5" s="5"/>
-      <c r="DH5" s="5"/>
-      <c r="DI5" s="5"/>
-      <c r="DJ5" s="5"/>
-      <c r="DK5" s="5"/>
-      <c r="DL5" s="5"/>
-      <c r="DM5" s="5"/>
-      <c r="DN5" s="5"/>
-      <c r="DO5" s="5"/>
-      <c r="DP5" s="5"/>
-      <c r="DQ5" s="5"/>
-      <c r="DR5" s="5"/>
-      <c r="DS5" s="5"/>
+      <c r="AU5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW5" s="4"/>
+      <c r="AX5" s="4"/>
+      <c r="AZ5" s="4"/>
+      <c r="BA5" s="4"/>
+      <c r="BB5" s="4"/>
+      <c r="BC5" s="4"/>
+      <c r="BD5" s="4"/>
+      <c r="BE5" s="4"/>
+      <c r="BF5" s="4"/>
+      <c r="BG5" s="4"/>
+      <c r="BH5" s="4"/>
+      <c r="BI5" s="4"/>
+      <c r="BJ5" s="4"/>
+      <c r="BK5" s="4"/>
+      <c r="BL5" s="4"/>
+      <c r="BM5" s="4"/>
+      <c r="BN5" s="4"/>
+      <c r="BO5" s="4"/>
+      <c r="BP5" s="4"/>
+      <c r="BQ5" s="4"/>
+      <c r="BR5" s="4"/>
+      <c r="BS5" s="4"/>
+      <c r="BT5" s="4"/>
+      <c r="BU5" s="4"/>
+      <c r="BV5" s="4"/>
+      <c r="BW5" s="4"/>
+      <c r="BX5" s="4"/>
+      <c r="BY5" s="4"/>
+      <c r="BZ5" s="4"/>
+      <c r="CA5" s="4"/>
+      <c r="CB5" s="4"/>
+      <c r="CC5" s="4"/>
+      <c r="CD5" s="4"/>
+      <c r="CE5" s="4"/>
+      <c r="CF5" s="4"/>
+      <c r="CG5" s="4"/>
+      <c r="CH5" s="4"/>
+      <c r="CI5" s="4"/>
+      <c r="CJ5" s="4"/>
+      <c r="CK5" s="4"/>
+      <c r="CL5" s="4"/>
+      <c r="CM5" s="4"/>
+      <c r="CN5" s="4"/>
+      <c r="CO5" s="4"/>
+      <c r="CP5" s="4"/>
+      <c r="CQ5" s="4"/>
+      <c r="CR5" s="4"/>
+      <c r="CS5" s="4"/>
+      <c r="CT5" s="4"/>
+      <c r="CU5" s="4"/>
+      <c r="CV5" s="4"/>
+      <c r="CW5" s="4"/>
+      <c r="CX5" s="4"/>
+      <c r="CY5" s="4"/>
+      <c r="CZ5" s="4"/>
+      <c r="DA5" s="4"/>
+      <c r="DB5" s="4"/>
+      <c r="DC5" s="4"/>
+      <c r="DD5" s="4"/>
+      <c r="DE5" s="4"/>
+      <c r="DF5" s="4"/>
+      <c r="DG5" s="4"/>
+      <c r="DH5" s="4"/>
+      <c r="DI5" s="4"/>
+      <c r="DJ5" s="4"/>
+      <c r="DK5" s="4"/>
+      <c r="DL5" s="4"/>
+      <c r="DM5" s="4"/>
+      <c r="DN5" s="4"/>
+      <c r="DO5" s="4"/>
+      <c r="DP5" s="4"/>
+      <c r="DQ5" s="4"/>
+      <c r="DR5" s="4"/>
+      <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -1614,7 +1643,7 @@
       <c r="I6" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K6" t="s">
@@ -1725,83 +1754,88 @@
       <c r="AT6" t="s">
         <v>5</v>
       </c>
-      <c r="AU6" s="2"/>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2"/>
-      <c r="AZ6" s="5"/>
-      <c r="BA6" s="5"/>
-      <c r="BB6" s="5"/>
-      <c r="BC6" s="5"/>
-      <c r="BD6" s="5"/>
-      <c r="BE6" s="5"/>
-      <c r="BF6" s="5"/>
-      <c r="BG6" s="5"/>
-      <c r="BH6" s="5"/>
-      <c r="BI6" s="5"/>
-      <c r="BJ6" s="5"/>
-      <c r="BK6" s="5"/>
-      <c r="BL6" s="5"/>
-      <c r="BM6" s="5"/>
-      <c r="BN6" s="5"/>
-      <c r="BO6" s="5"/>
-      <c r="BP6" s="5"/>
-      <c r="BQ6" s="5"/>
-      <c r="BR6" s="5"/>
-      <c r="BS6" s="5"/>
-      <c r="BT6" s="5"/>
-      <c r="BU6" s="5"/>
-      <c r="BV6" s="5"/>
-      <c r="BW6" s="5"/>
-      <c r="BX6" s="5"/>
-      <c r="BY6" s="5"/>
-      <c r="BZ6" s="5"/>
-      <c r="CA6" s="5"/>
-      <c r="CB6" s="5"/>
-      <c r="CC6" s="5"/>
-      <c r="CD6" s="5"/>
-      <c r="CE6" s="5"/>
-      <c r="CF6" s="5"/>
-      <c r="CG6" s="5"/>
-      <c r="CH6" s="5"/>
-      <c r="CI6" s="7"/>
-      <c r="CJ6" s="5"/>
-      <c r="CK6" s="5"/>
-      <c r="CL6" s="5"/>
-      <c r="CM6" s="5"/>
-      <c r="CN6" s="5"/>
-      <c r="CO6" s="5"/>
-      <c r="CP6" s="5"/>
-      <c r="CQ6" s="5"/>
-      <c r="CR6" s="5"/>
-      <c r="CS6" s="5"/>
-      <c r="CT6" s="5"/>
-      <c r="CU6" s="5"/>
-      <c r="CV6" s="5"/>
-      <c r="CW6" s="5"/>
-      <c r="CX6" s="5"/>
-      <c r="CY6" s="5"/>
-      <c r="CZ6" s="5"/>
-      <c r="DA6" s="5"/>
-      <c r="DB6" s="5"/>
-      <c r="DC6" s="5"/>
-      <c r="DD6" s="5"/>
-      <c r="DE6" s="5"/>
-      <c r="DF6" s="5"/>
-      <c r="DG6" s="5"/>
-      <c r="DH6" s="5"/>
-      <c r="DI6" s="5"/>
-      <c r="DJ6" s="5"/>
-      <c r="DK6" s="5"/>
-      <c r="DL6" s="5"/>
-      <c r="DM6" s="5"/>
-      <c r="DN6" s="5"/>
-      <c r="DO6" s="5"/>
-      <c r="DP6" s="5"/>
-      <c r="DQ6" s="5"/>
-      <c r="DR6" s="5"/>
-      <c r="DS6" s="5"/>
+      <c r="AU6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW6" s="4"/>
+      <c r="AX6" s="4"/>
+      <c r="AZ6" s="4"/>
+      <c r="BA6" s="4"/>
+      <c r="BB6" s="4"/>
+      <c r="BC6" s="4"/>
+      <c r="BD6" s="4"/>
+      <c r="BE6" s="4"/>
+      <c r="BF6" s="4"/>
+      <c r="BG6" s="4"/>
+      <c r="BH6" s="4"/>
+      <c r="BI6" s="4"/>
+      <c r="BJ6" s="4"/>
+      <c r="BK6" s="4"/>
+      <c r="BL6" s="4"/>
+      <c r="BM6" s="4"/>
+      <c r="BN6" s="4"/>
+      <c r="BO6" s="4"/>
+      <c r="BP6" s="4"/>
+      <c r="BQ6" s="4"/>
+      <c r="BR6" s="4"/>
+      <c r="BS6" s="4"/>
+      <c r="BT6" s="4"/>
+      <c r="BU6" s="4"/>
+      <c r="BV6" s="4"/>
+      <c r="BW6" s="4"/>
+      <c r="BX6" s="4"/>
+      <c r="BY6" s="4"/>
+      <c r="BZ6" s="4"/>
+      <c r="CA6" s="4"/>
+      <c r="CB6" s="4"/>
+      <c r="CC6" s="4"/>
+      <c r="CD6" s="4"/>
+      <c r="CE6" s="4"/>
+      <c r="CF6" s="4"/>
+      <c r="CG6" s="4"/>
+      <c r="CH6" s="4"/>
+      <c r="CI6" s="6"/>
+      <c r="CJ6" s="4"/>
+      <c r="CK6" s="4"/>
+      <c r="CL6" s="4"/>
+      <c r="CM6" s="4"/>
+      <c r="CN6" s="4"/>
+      <c r="CO6" s="4"/>
+      <c r="CP6" s="4"/>
+      <c r="CQ6" s="4"/>
+      <c r="CR6" s="4"/>
+      <c r="CS6" s="4"/>
+      <c r="CT6" s="4"/>
+      <c r="CU6" s="4"/>
+      <c r="CV6" s="4"/>
+      <c r="CW6" s="4"/>
+      <c r="CX6" s="4"/>
+      <c r="CY6" s="4"/>
+      <c r="CZ6" s="4"/>
+      <c r="DA6" s="4"/>
+      <c r="DB6" s="4"/>
+      <c r="DC6" s="4"/>
+      <c r="DD6" s="4"/>
+      <c r="DE6" s="4"/>
+      <c r="DF6" s="4"/>
+      <c r="DG6" s="4"/>
+      <c r="DH6" s="4"/>
+      <c r="DI6" s="4"/>
+      <c r="DJ6" s="4"/>
+      <c r="DK6" s="4"/>
+      <c r="DL6" s="4"/>
+      <c r="DM6" s="4"/>
+      <c r="DN6" s="4"/>
+      <c r="DO6" s="4"/>
+      <c r="DP6" s="4"/>
+      <c r="DQ6" s="4"/>
+      <c r="DR6" s="4"/>
+      <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -1811,7 +1845,7 @@
       <c r="C7">
         <v>5</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K7" t="s">
@@ -1922,83 +1956,88 @@
       <c r="AT7" t="s">
         <v>5</v>
       </c>
-      <c r="AU7" s="2"/>
-      <c r="AV7" s="2"/>
-      <c r="AW7" s="2"/>
-      <c r="AZ7" s="5"/>
-      <c r="BA7" s="5"/>
-      <c r="BB7" s="5"/>
-      <c r="BC7" s="5"/>
-      <c r="BD7" s="5"/>
-      <c r="BE7" s="5"/>
-      <c r="BF7" s="5"/>
-      <c r="BG7" s="5"/>
-      <c r="BH7" s="5"/>
-      <c r="BI7" s="5"/>
-      <c r="BJ7" s="5"/>
-      <c r="BK7" s="5"/>
-      <c r="BL7" s="5"/>
-      <c r="BM7" s="5"/>
-      <c r="BN7" s="5"/>
-      <c r="BO7" s="5"/>
-      <c r="BP7" s="5"/>
-      <c r="BQ7" s="5"/>
-      <c r="BR7" s="5"/>
-      <c r="BS7" s="5"/>
-      <c r="BT7" s="5"/>
-      <c r="BU7" s="5"/>
-      <c r="BV7" s="5"/>
-      <c r="BW7" s="5"/>
-      <c r="BX7" s="5"/>
-      <c r="BY7" s="5"/>
-      <c r="BZ7" s="5"/>
-      <c r="CA7" s="5"/>
-      <c r="CB7" s="5"/>
-      <c r="CC7" s="5"/>
-      <c r="CD7" s="5"/>
-      <c r="CE7" s="5"/>
-      <c r="CF7" s="5"/>
-      <c r="CG7" s="5"/>
-      <c r="CH7" s="5"/>
-      <c r="CI7" s="6"/>
-      <c r="CJ7" s="5"/>
-      <c r="CK7" s="5"/>
-      <c r="CL7" s="5"/>
-      <c r="CM7" s="5"/>
-      <c r="CN7" s="5"/>
-      <c r="CO7" s="5"/>
-      <c r="CP7" s="5"/>
-      <c r="CQ7" s="5"/>
-      <c r="CR7" s="5"/>
-      <c r="CS7" s="5"/>
-      <c r="CT7" s="5"/>
-      <c r="CU7" s="5"/>
-      <c r="CV7" s="5"/>
-      <c r="CW7" s="5"/>
-      <c r="CX7" s="5"/>
-      <c r="CY7" s="5"/>
-      <c r="CZ7" s="5"/>
-      <c r="DA7" s="5"/>
-      <c r="DB7" s="5"/>
-      <c r="DC7" s="5"/>
-      <c r="DD7" s="5"/>
-      <c r="DE7" s="5"/>
-      <c r="DF7" s="5"/>
-      <c r="DG7" s="5"/>
-      <c r="DH7" s="5"/>
-      <c r="DI7" s="5"/>
-      <c r="DJ7" s="5"/>
-      <c r="DK7" s="5"/>
-      <c r="DL7" s="5"/>
-      <c r="DM7" s="5"/>
-      <c r="DN7" s="5"/>
-      <c r="DO7" s="5"/>
-      <c r="DP7" s="5"/>
-      <c r="DQ7" s="5"/>
-      <c r="DR7" s="5"/>
-      <c r="DS7" s="5"/>
+      <c r="AU7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW7" s="4"/>
+      <c r="AX7" s="4"/>
+      <c r="AZ7" s="4"/>
+      <c r="BA7" s="4"/>
+      <c r="BB7" s="4"/>
+      <c r="BC7" s="4"/>
+      <c r="BD7" s="4"/>
+      <c r="BE7" s="4"/>
+      <c r="BF7" s="4"/>
+      <c r="BG7" s="4"/>
+      <c r="BH7" s="4"/>
+      <c r="BI7" s="4"/>
+      <c r="BJ7" s="4"/>
+      <c r="BK7" s="4"/>
+      <c r="BL7" s="4"/>
+      <c r="BM7" s="4"/>
+      <c r="BN7" s="4"/>
+      <c r="BO7" s="4"/>
+      <c r="BP7" s="4"/>
+      <c r="BQ7" s="4"/>
+      <c r="BR7" s="4"/>
+      <c r="BS7" s="4"/>
+      <c r="BT7" s="4"/>
+      <c r="BU7" s="4"/>
+      <c r="BV7" s="4"/>
+      <c r="BW7" s="4"/>
+      <c r="BX7" s="4"/>
+      <c r="BY7" s="4"/>
+      <c r="BZ7" s="4"/>
+      <c r="CA7" s="4"/>
+      <c r="CB7" s="4"/>
+      <c r="CC7" s="4"/>
+      <c r="CD7" s="4"/>
+      <c r="CE7" s="4"/>
+      <c r="CF7" s="4"/>
+      <c r="CG7" s="4"/>
+      <c r="CH7" s="4"/>
+      <c r="CI7" s="5"/>
+      <c r="CJ7" s="4"/>
+      <c r="CK7" s="4"/>
+      <c r="CL7" s="4"/>
+      <c r="CM7" s="4"/>
+      <c r="CN7" s="4"/>
+      <c r="CO7" s="4"/>
+      <c r="CP7" s="4"/>
+      <c r="CQ7" s="4"/>
+      <c r="CR7" s="4"/>
+      <c r="CS7" s="4"/>
+      <c r="CT7" s="4"/>
+      <c r="CU7" s="4"/>
+      <c r="CV7" s="4"/>
+      <c r="CW7" s="4"/>
+      <c r="CX7" s="4"/>
+      <c r="CY7" s="4"/>
+      <c r="CZ7" s="4"/>
+      <c r="DA7" s="4"/>
+      <c r="DB7" s="4"/>
+      <c r="DC7" s="4"/>
+      <c r="DD7" s="4"/>
+      <c r="DE7" s="4"/>
+      <c r="DF7" s="4"/>
+      <c r="DG7" s="4"/>
+      <c r="DH7" s="4"/>
+      <c r="DI7" s="4"/>
+      <c r="DJ7" s="4"/>
+      <c r="DK7" s="4"/>
+      <c r="DL7" s="4"/>
+      <c r="DM7" s="4"/>
+      <c r="DN7" s="4"/>
+      <c r="DO7" s="4"/>
+      <c r="DP7" s="4"/>
+      <c r="DQ7" s="4"/>
+      <c r="DR7" s="4"/>
+      <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2026,7 +2065,7 @@
       <c r="I8" t="s">
         <v>5</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K8" t="s">
@@ -2137,83 +2176,88 @@
       <c r="AT8" t="s">
         <v>5</v>
       </c>
-      <c r="AU8" s="2"/>
-      <c r="AV8" s="2"/>
-      <c r="AW8" s="2"/>
-      <c r="AZ8" s="5"/>
-      <c r="BA8" s="5"/>
-      <c r="BB8" s="5"/>
-      <c r="BC8" s="5"/>
-      <c r="BD8" s="5"/>
-      <c r="BE8" s="5"/>
-      <c r="BF8" s="5"/>
-      <c r="BG8" s="5"/>
-      <c r="BH8" s="5"/>
-      <c r="BI8" s="5"/>
-      <c r="BJ8" s="5"/>
-      <c r="BK8" s="5"/>
-      <c r="BL8" s="5"/>
-      <c r="BM8" s="5"/>
-      <c r="BN8" s="5"/>
-      <c r="BO8" s="5"/>
-      <c r="BP8" s="5"/>
-      <c r="BQ8" s="5"/>
-      <c r="BR8" s="5"/>
-      <c r="BS8" s="5"/>
-      <c r="BT8" s="5"/>
-      <c r="BU8" s="5"/>
-      <c r="BV8" s="5"/>
-      <c r="BW8" s="5"/>
-      <c r="BX8" s="5"/>
-      <c r="BY8" s="5"/>
-      <c r="BZ8" s="5"/>
-      <c r="CA8" s="5"/>
-      <c r="CB8" s="5"/>
-      <c r="CC8" s="5"/>
-      <c r="CD8" s="5"/>
-      <c r="CE8" s="5"/>
-      <c r="CF8" s="5"/>
-      <c r="CG8" s="5"/>
-      <c r="CH8" s="5"/>
-      <c r="CI8" s="5"/>
-      <c r="CJ8" s="5"/>
-      <c r="CK8" s="5"/>
-      <c r="CL8" s="5"/>
-      <c r="CM8" s="5"/>
-      <c r="CN8" s="5"/>
-      <c r="CO8" s="5"/>
-      <c r="CP8" s="5"/>
-      <c r="CQ8" s="5"/>
-      <c r="CR8" s="5"/>
-      <c r="CS8" s="5"/>
-      <c r="CT8" s="5"/>
-      <c r="CU8" s="5"/>
-      <c r="CV8" s="5"/>
-      <c r="CW8" s="5"/>
-      <c r="CX8" s="5"/>
-      <c r="CY8" s="5"/>
-      <c r="CZ8" s="5"/>
-      <c r="DA8" s="5"/>
-      <c r="DB8" s="5"/>
-      <c r="DC8" s="5"/>
-      <c r="DD8" s="5"/>
-      <c r="DE8" s="5"/>
-      <c r="DF8" s="5"/>
-      <c r="DG8" s="5"/>
-      <c r="DH8" s="5"/>
-      <c r="DI8" s="5"/>
-      <c r="DJ8" s="5"/>
-      <c r="DK8" s="5"/>
-      <c r="DL8" s="5"/>
-      <c r="DM8" s="5"/>
-      <c r="DN8" s="5"/>
-      <c r="DO8" s="5"/>
-      <c r="DP8" s="5"/>
-      <c r="DQ8" s="5"/>
-      <c r="DR8" s="5"/>
-      <c r="DS8" s="5"/>
+      <c r="AU8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW8" s="4"/>
+      <c r="AX8" s="4"/>
+      <c r="AZ8" s="4"/>
+      <c r="BA8" s="4"/>
+      <c r="BB8" s="4"/>
+      <c r="BC8" s="4"/>
+      <c r="BD8" s="4"/>
+      <c r="BE8" s="4"/>
+      <c r="BF8" s="4"/>
+      <c r="BG8" s="4"/>
+      <c r="BH8" s="4"/>
+      <c r="BI8" s="4"/>
+      <c r="BJ8" s="4"/>
+      <c r="BK8" s="4"/>
+      <c r="BL8" s="4"/>
+      <c r="BM8" s="4"/>
+      <c r="BN8" s="4"/>
+      <c r="BO8" s="4"/>
+      <c r="BP8" s="4"/>
+      <c r="BQ8" s="4"/>
+      <c r="BR8" s="4"/>
+      <c r="BS8" s="4"/>
+      <c r="BT8" s="4"/>
+      <c r="BU8" s="4"/>
+      <c r="BV8" s="4"/>
+      <c r="BW8" s="4"/>
+      <c r="BX8" s="4"/>
+      <c r="BY8" s="4"/>
+      <c r="BZ8" s="4"/>
+      <c r="CA8" s="4"/>
+      <c r="CB8" s="4"/>
+      <c r="CC8" s="4"/>
+      <c r="CD8" s="4"/>
+      <c r="CE8" s="4"/>
+      <c r="CF8" s="4"/>
+      <c r="CG8" s="4"/>
+      <c r="CH8" s="4"/>
+      <c r="CI8" s="4"/>
+      <c r="CJ8" s="4"/>
+      <c r="CK8" s="4"/>
+      <c r="CL8" s="4"/>
+      <c r="CM8" s="4"/>
+      <c r="CN8" s="4"/>
+      <c r="CO8" s="4"/>
+      <c r="CP8" s="4"/>
+      <c r="CQ8" s="4"/>
+      <c r="CR8" s="4"/>
+      <c r="CS8" s="4"/>
+      <c r="CT8" s="4"/>
+      <c r="CU8" s="4"/>
+      <c r="CV8" s="4"/>
+      <c r="CW8" s="4"/>
+      <c r="CX8" s="4"/>
+      <c r="CY8" s="4"/>
+      <c r="CZ8" s="4"/>
+      <c r="DA8" s="4"/>
+      <c r="DB8" s="4"/>
+      <c r="DC8" s="4"/>
+      <c r="DD8" s="4"/>
+      <c r="DE8" s="4"/>
+      <c r="DF8" s="4"/>
+      <c r="DG8" s="4"/>
+      <c r="DH8" s="4"/>
+      <c r="DI8" s="4"/>
+      <c r="DJ8" s="4"/>
+      <c r="DK8" s="4"/>
+      <c r="DL8" s="4"/>
+      <c r="DM8" s="4"/>
+      <c r="DN8" s="4"/>
+      <c r="DO8" s="4"/>
+      <c r="DP8" s="4"/>
+      <c r="DQ8" s="4"/>
+      <c r="DR8" s="4"/>
+      <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2241,7 +2285,7 @@
       <c r="I9" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K9" t="s">
@@ -2352,83 +2396,88 @@
       <c r="AT9" t="s">
         <v>5</v>
       </c>
-      <c r="AU9" s="2"/>
-      <c r="AV9" s="2"/>
-      <c r="AW9" s="2"/>
-      <c r="AZ9" s="5"/>
-      <c r="BA9" s="5"/>
-      <c r="BB9" s="5"/>
-      <c r="BC9" s="5"/>
-      <c r="BD9" s="5"/>
-      <c r="BE9" s="5"/>
-      <c r="BF9" s="5"/>
-      <c r="BG9" s="5"/>
-      <c r="BH9" s="5"/>
-      <c r="BI9" s="5"/>
-      <c r="BJ9" s="5"/>
-      <c r="BK9" s="5"/>
-      <c r="BL9" s="5"/>
-      <c r="BM9" s="5"/>
-      <c r="BN9" s="5"/>
-      <c r="BO9" s="5"/>
-      <c r="BP9" s="5"/>
-      <c r="BQ9" s="5"/>
-      <c r="BR9" s="5"/>
-      <c r="BS9" s="5"/>
-      <c r="BT9" s="5"/>
-      <c r="BU9" s="5"/>
-      <c r="BV9" s="5"/>
-      <c r="BW9" s="5"/>
-      <c r="BX9" s="5"/>
-      <c r="BY9" s="5"/>
-      <c r="BZ9" s="5"/>
-      <c r="CA9" s="5"/>
-      <c r="CB9" s="5"/>
-      <c r="CC9" s="5"/>
-      <c r="CD9" s="5"/>
-      <c r="CE9" s="5"/>
-      <c r="CF9" s="5"/>
-      <c r="CG9" s="5"/>
-      <c r="CH9" s="5"/>
-      <c r="CI9" s="5"/>
-      <c r="CJ9" s="5"/>
-      <c r="CK9" s="5"/>
-      <c r="CL9" s="5"/>
-      <c r="CM9" s="5"/>
-      <c r="CN9" s="5"/>
-      <c r="CO9" s="5"/>
-      <c r="CP9" s="5"/>
-      <c r="CQ9" s="5"/>
-      <c r="CR9" s="5"/>
-      <c r="CS9" s="5"/>
-      <c r="CT9" s="5"/>
-      <c r="CU9" s="5"/>
-      <c r="CV9" s="5"/>
-      <c r="CW9" s="5"/>
-      <c r="CX9" s="5"/>
-      <c r="CY9" s="5"/>
-      <c r="CZ9" s="5"/>
-      <c r="DA9" s="5"/>
-      <c r="DB9" s="5"/>
-      <c r="DC9" s="5"/>
-      <c r="DD9" s="5"/>
-      <c r="DE9" s="5"/>
-      <c r="DF9" s="5"/>
-      <c r="DG9" s="5"/>
-      <c r="DH9" s="5"/>
-      <c r="DI9" s="5"/>
-      <c r="DJ9" s="5"/>
-      <c r="DK9" s="5"/>
-      <c r="DL9" s="5"/>
-      <c r="DM9" s="5"/>
-      <c r="DN9" s="5"/>
-      <c r="DO9" s="5"/>
-      <c r="DP9" s="5"/>
-      <c r="DQ9" s="5"/>
-      <c r="DR9" s="5"/>
-      <c r="DS9" s="5"/>
+      <c r="AU9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW9" s="4"/>
+      <c r="AX9" s="4"/>
+      <c r="AZ9" s="4"/>
+      <c r="BA9" s="4"/>
+      <c r="BB9" s="4"/>
+      <c r="BC9" s="4"/>
+      <c r="BD9" s="4"/>
+      <c r="BE9" s="4"/>
+      <c r="BF9" s="4"/>
+      <c r="BG9" s="4"/>
+      <c r="BH9" s="4"/>
+      <c r="BI9" s="4"/>
+      <c r="BJ9" s="4"/>
+      <c r="BK9" s="4"/>
+      <c r="BL9" s="4"/>
+      <c r="BM9" s="4"/>
+      <c r="BN9" s="4"/>
+      <c r="BO9" s="4"/>
+      <c r="BP9" s="4"/>
+      <c r="BQ9" s="4"/>
+      <c r="BR9" s="4"/>
+      <c r="BS9" s="4"/>
+      <c r="BT9" s="4"/>
+      <c r="BU9" s="4"/>
+      <c r="BV9" s="4"/>
+      <c r="BW9" s="4"/>
+      <c r="BX9" s="4"/>
+      <c r="BY9" s="4"/>
+      <c r="BZ9" s="4"/>
+      <c r="CA9" s="4"/>
+      <c r="CB9" s="4"/>
+      <c r="CC9" s="4"/>
+      <c r="CD9" s="4"/>
+      <c r="CE9" s="4"/>
+      <c r="CF9" s="4"/>
+      <c r="CG9" s="4"/>
+      <c r="CH9" s="4"/>
+      <c r="CI9" s="4"/>
+      <c r="CJ9" s="4"/>
+      <c r="CK9" s="4"/>
+      <c r="CL9" s="4"/>
+      <c r="CM9" s="4"/>
+      <c r="CN9" s="4"/>
+      <c r="CO9" s="4"/>
+      <c r="CP9" s="4"/>
+      <c r="CQ9" s="4"/>
+      <c r="CR9" s="4"/>
+      <c r="CS9" s="4"/>
+      <c r="CT9" s="4"/>
+      <c r="CU9" s="4"/>
+      <c r="CV9" s="4"/>
+      <c r="CW9" s="4"/>
+      <c r="CX9" s="4"/>
+      <c r="CY9" s="4"/>
+      <c r="CZ9" s="4"/>
+      <c r="DA9" s="4"/>
+      <c r="DB9" s="4"/>
+      <c r="DC9" s="4"/>
+      <c r="DD9" s="4"/>
+      <c r="DE9" s="4"/>
+      <c r="DF9" s="4"/>
+      <c r="DG9" s="4"/>
+      <c r="DH9" s="4"/>
+      <c r="DI9" s="4"/>
+      <c r="DJ9" s="4"/>
+      <c r="DK9" s="4"/>
+      <c r="DL9" s="4"/>
+      <c r="DM9" s="4"/>
+      <c r="DN9" s="4"/>
+      <c r="DO9" s="4"/>
+      <c r="DP9" s="4"/>
+      <c r="DQ9" s="4"/>
+      <c r="DR9" s="4"/>
+      <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -2456,7 +2505,7 @@
       <c r="I10" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K10" t="s">
@@ -2567,83 +2616,88 @@
       <c r="AT10" t="s">
         <v>5</v>
       </c>
-      <c r="AU10" s="2"/>
-      <c r="AV10" s="2"/>
-      <c r="AW10" s="2"/>
-      <c r="AZ10" s="5"/>
-      <c r="BA10" s="5"/>
-      <c r="BB10" s="5"/>
-      <c r="BC10" s="5"/>
-      <c r="BD10" s="5"/>
-      <c r="BE10" s="5"/>
-      <c r="BF10" s="5"/>
-      <c r="BG10" s="5"/>
-      <c r="BH10" s="5"/>
-      <c r="BI10" s="5"/>
-      <c r="BJ10" s="5"/>
-      <c r="BK10" s="5"/>
-      <c r="BL10" s="5"/>
-      <c r="BM10" s="5"/>
-      <c r="BN10" s="5"/>
-      <c r="BO10" s="5"/>
-      <c r="BP10" s="5"/>
-      <c r="BQ10" s="5"/>
-      <c r="BR10" s="5"/>
-      <c r="BS10" s="5"/>
-      <c r="BT10" s="5"/>
-      <c r="BU10" s="5"/>
-      <c r="BV10" s="5"/>
-      <c r="BW10" s="5"/>
-      <c r="BX10" s="5"/>
-      <c r="BY10" s="5"/>
-      <c r="BZ10" s="5"/>
-      <c r="CA10" s="5"/>
-      <c r="CB10" s="5"/>
-      <c r="CC10" s="5"/>
-      <c r="CD10" s="5"/>
-      <c r="CE10" s="5"/>
-      <c r="CF10" s="5"/>
-      <c r="CG10" s="5"/>
-      <c r="CH10" s="5"/>
-      <c r="CI10" s="5"/>
-      <c r="CJ10" s="5"/>
-      <c r="CK10" s="5"/>
-      <c r="CL10" s="5"/>
-      <c r="CM10" s="5"/>
-      <c r="CN10" s="5"/>
-      <c r="CO10" s="5"/>
-      <c r="CP10" s="5"/>
-      <c r="CQ10" s="5"/>
-      <c r="CR10" s="5"/>
-      <c r="CS10" s="5"/>
-      <c r="CT10" s="5"/>
-      <c r="CU10" s="5"/>
-      <c r="CV10" s="5"/>
-      <c r="CW10" s="5"/>
-      <c r="CX10" s="5"/>
-      <c r="CY10" s="5"/>
-      <c r="CZ10" s="5"/>
-      <c r="DA10" s="5"/>
-      <c r="DB10" s="5"/>
-      <c r="DC10" s="5"/>
-      <c r="DD10" s="5"/>
-      <c r="DE10" s="5"/>
-      <c r="DF10" s="5"/>
-      <c r="DG10" s="5"/>
-      <c r="DH10" s="5"/>
-      <c r="DI10" s="5"/>
-      <c r="DJ10" s="5"/>
-      <c r="DK10" s="5"/>
-      <c r="DL10" s="5"/>
-      <c r="DM10" s="5"/>
-      <c r="DN10" s="5"/>
-      <c r="DO10" s="5"/>
-      <c r="DP10" s="5"/>
-      <c r="DQ10" s="5"/>
-      <c r="DR10" s="5"/>
-      <c r="DS10" s="5"/>
+      <c r="AU10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW10" s="4"/>
+      <c r="AX10" s="4"/>
+      <c r="AZ10" s="4"/>
+      <c r="BA10" s="4"/>
+      <c r="BB10" s="4"/>
+      <c r="BC10" s="4"/>
+      <c r="BD10" s="4"/>
+      <c r="BE10" s="4"/>
+      <c r="BF10" s="4"/>
+      <c r="BG10" s="4"/>
+      <c r="BH10" s="4"/>
+      <c r="BI10" s="4"/>
+      <c r="BJ10" s="4"/>
+      <c r="BK10" s="4"/>
+      <c r="BL10" s="4"/>
+      <c r="BM10" s="4"/>
+      <c r="BN10" s="4"/>
+      <c r="BO10" s="4"/>
+      <c r="BP10" s="4"/>
+      <c r="BQ10" s="4"/>
+      <c r="BR10" s="4"/>
+      <c r="BS10" s="4"/>
+      <c r="BT10" s="4"/>
+      <c r="BU10" s="4"/>
+      <c r="BV10" s="4"/>
+      <c r="BW10" s="4"/>
+      <c r="BX10" s="4"/>
+      <c r="BY10" s="4"/>
+      <c r="BZ10" s="4"/>
+      <c r="CA10" s="4"/>
+      <c r="CB10" s="4"/>
+      <c r="CC10" s="4"/>
+      <c r="CD10" s="4"/>
+      <c r="CE10" s="4"/>
+      <c r="CF10" s="4"/>
+      <c r="CG10" s="4"/>
+      <c r="CH10" s="4"/>
+      <c r="CI10" s="4"/>
+      <c r="CJ10" s="4"/>
+      <c r="CK10" s="4"/>
+      <c r="CL10" s="4"/>
+      <c r="CM10" s="4"/>
+      <c r="CN10" s="4"/>
+      <c r="CO10" s="4"/>
+      <c r="CP10" s="4"/>
+      <c r="CQ10" s="4"/>
+      <c r="CR10" s="4"/>
+      <c r="CS10" s="4"/>
+      <c r="CT10" s="4"/>
+      <c r="CU10" s="4"/>
+      <c r="CV10" s="4"/>
+      <c r="CW10" s="4"/>
+      <c r="CX10" s="4"/>
+      <c r="CY10" s="4"/>
+      <c r="CZ10" s="4"/>
+      <c r="DA10" s="4"/>
+      <c r="DB10" s="4"/>
+      <c r="DC10" s="4"/>
+      <c r="DD10" s="4"/>
+      <c r="DE10" s="4"/>
+      <c r="DF10" s="4"/>
+      <c r="DG10" s="4"/>
+      <c r="DH10" s="4"/>
+      <c r="DI10" s="4"/>
+      <c r="DJ10" s="4"/>
+      <c r="DK10" s="4"/>
+      <c r="DL10" s="4"/>
+      <c r="DM10" s="4"/>
+      <c r="DN10" s="4"/>
+      <c r="DO10" s="4"/>
+      <c r="DP10" s="4"/>
+      <c r="DQ10" s="4"/>
+      <c r="DR10" s="4"/>
+      <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -2671,7 +2725,7 @@
       <c r="I11" t="s">
         <v>5</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K11" t="s">
@@ -2782,83 +2836,88 @@
       <c r="AT11" t="s">
         <v>5</v>
       </c>
-      <c r="AU11" s="2"/>
-      <c r="AV11" s="2"/>
-      <c r="AW11" s="2"/>
-      <c r="AZ11" s="5"/>
-      <c r="BA11" s="5"/>
-      <c r="BB11" s="5"/>
-      <c r="BC11" s="5"/>
-      <c r="BD11" s="5"/>
-      <c r="BE11" s="5"/>
-      <c r="BF11" s="5"/>
-      <c r="BG11" s="5"/>
-      <c r="BH11" s="5"/>
-      <c r="BI11" s="5"/>
-      <c r="BJ11" s="5"/>
-      <c r="BK11" s="5"/>
-      <c r="BL11" s="5"/>
-      <c r="BM11" s="5"/>
-      <c r="BN11" s="5"/>
-      <c r="BO11" s="5"/>
-      <c r="BP11" s="5"/>
-      <c r="BQ11" s="5"/>
-      <c r="BR11" s="5"/>
-      <c r="BS11" s="5"/>
-      <c r="BT11" s="5"/>
-      <c r="BU11" s="5"/>
-      <c r="BV11" s="5"/>
-      <c r="BW11" s="5"/>
-      <c r="BX11" s="5"/>
-      <c r="BY11" s="5"/>
-      <c r="BZ11" s="5"/>
-      <c r="CA11" s="5"/>
-      <c r="CB11" s="5"/>
-      <c r="CC11" s="5"/>
-      <c r="CD11" s="5"/>
-      <c r="CE11" s="5"/>
-      <c r="CF11" s="5"/>
-      <c r="CG11" s="5"/>
-      <c r="CH11" s="5"/>
-      <c r="CI11" s="5"/>
-      <c r="CJ11" s="5"/>
-      <c r="CK11" s="5"/>
-      <c r="CL11" s="5"/>
-      <c r="CM11" s="5"/>
-      <c r="CN11" s="5"/>
-      <c r="CO11" s="5"/>
-      <c r="CP11" s="5"/>
-      <c r="CQ11" s="5"/>
-      <c r="CR11" s="5"/>
-      <c r="CS11" s="5"/>
-      <c r="CT11" s="5"/>
-      <c r="CU11" s="5"/>
-      <c r="CV11" s="5"/>
-      <c r="CW11" s="5"/>
-      <c r="CX11" s="5"/>
-      <c r="CY11" s="5"/>
-      <c r="CZ11" s="5"/>
-      <c r="DA11" s="5"/>
-      <c r="DB11" s="5"/>
-      <c r="DC11" s="5"/>
-      <c r="DD11" s="5"/>
-      <c r="DE11" s="5"/>
-      <c r="DF11" s="5"/>
-      <c r="DG11" s="5"/>
-      <c r="DH11" s="5"/>
-      <c r="DI11" s="5"/>
-      <c r="DJ11" s="5"/>
-      <c r="DK11" s="5"/>
-      <c r="DL11" s="5"/>
-      <c r="DM11" s="5"/>
-      <c r="DN11" s="5"/>
-      <c r="DO11" s="5"/>
-      <c r="DP11" s="5"/>
-      <c r="DQ11" s="5"/>
-      <c r="DR11" s="5"/>
-      <c r="DS11" s="5"/>
+      <c r="AU11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW11" s="4"/>
+      <c r="AX11" s="4"/>
+      <c r="AZ11" s="4"/>
+      <c r="BA11" s="4"/>
+      <c r="BB11" s="4"/>
+      <c r="BC11" s="4"/>
+      <c r="BD11" s="4"/>
+      <c r="BE11" s="4"/>
+      <c r="BF11" s="4"/>
+      <c r="BG11" s="4"/>
+      <c r="BH11" s="4"/>
+      <c r="BI11" s="4"/>
+      <c r="BJ11" s="4"/>
+      <c r="BK11" s="4"/>
+      <c r="BL11" s="4"/>
+      <c r="BM11" s="4"/>
+      <c r="BN11" s="4"/>
+      <c r="BO11" s="4"/>
+      <c r="BP11" s="4"/>
+      <c r="BQ11" s="4"/>
+      <c r="BR11" s="4"/>
+      <c r="BS11" s="4"/>
+      <c r="BT11" s="4"/>
+      <c r="BU11" s="4"/>
+      <c r="BV11" s="4"/>
+      <c r="BW11" s="4"/>
+      <c r="BX11" s="4"/>
+      <c r="BY11" s="4"/>
+      <c r="BZ11" s="4"/>
+      <c r="CA11" s="4"/>
+      <c r="CB11" s="4"/>
+      <c r="CC11" s="4"/>
+      <c r="CD11" s="4"/>
+      <c r="CE11" s="4"/>
+      <c r="CF11" s="4"/>
+      <c r="CG11" s="4"/>
+      <c r="CH11" s="4"/>
+      <c r="CI11" s="4"/>
+      <c r="CJ11" s="4"/>
+      <c r="CK11" s="4"/>
+      <c r="CL11" s="4"/>
+      <c r="CM11" s="4"/>
+      <c r="CN11" s="4"/>
+      <c r="CO11" s="4"/>
+      <c r="CP11" s="4"/>
+      <c r="CQ11" s="4"/>
+      <c r="CR11" s="4"/>
+      <c r="CS11" s="4"/>
+      <c r="CT11" s="4"/>
+      <c r="CU11" s="4"/>
+      <c r="CV11" s="4"/>
+      <c r="CW11" s="4"/>
+      <c r="CX11" s="4"/>
+      <c r="CY11" s="4"/>
+      <c r="CZ11" s="4"/>
+      <c r="DA11" s="4"/>
+      <c r="DB11" s="4"/>
+      <c r="DC11" s="4"/>
+      <c r="DD11" s="4"/>
+      <c r="DE11" s="4"/>
+      <c r="DF11" s="4"/>
+      <c r="DG11" s="4"/>
+      <c r="DH11" s="4"/>
+      <c r="DI11" s="4"/>
+      <c r="DJ11" s="4"/>
+      <c r="DK11" s="4"/>
+      <c r="DL11" s="4"/>
+      <c r="DM11" s="4"/>
+      <c r="DN11" s="4"/>
+      <c r="DO11" s="4"/>
+      <c r="DP11" s="4"/>
+      <c r="DQ11" s="4"/>
+      <c r="DR11" s="4"/>
+      <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -2886,7 +2945,7 @@
       <c r="I12" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K12" t="s">
@@ -2997,83 +3056,88 @@
       <c r="AT12" t="s">
         <v>5</v>
       </c>
-      <c r="AU12" s="2"/>
-      <c r="AV12" s="2"/>
-      <c r="AW12" s="2"/>
-      <c r="AZ12" s="5"/>
-      <c r="BA12" s="5"/>
-      <c r="BB12" s="5"/>
-      <c r="BC12" s="5"/>
-      <c r="BD12" s="5"/>
-      <c r="BE12" s="5"/>
-      <c r="BF12" s="5"/>
-      <c r="BG12" s="5"/>
-      <c r="BH12" s="5"/>
-      <c r="BI12" s="5"/>
-      <c r="BJ12" s="5"/>
-      <c r="BK12" s="5"/>
-      <c r="BL12" s="5"/>
-      <c r="BM12" s="5"/>
-      <c r="BN12" s="5"/>
-      <c r="BO12" s="5"/>
-      <c r="BP12" s="5"/>
-      <c r="BQ12" s="5"/>
-      <c r="BR12" s="5"/>
-      <c r="BS12" s="5"/>
-      <c r="BT12" s="5"/>
-      <c r="BU12" s="5"/>
-      <c r="BV12" s="5"/>
-      <c r="BW12" s="5"/>
-      <c r="BX12" s="5"/>
-      <c r="BY12" s="5"/>
-      <c r="BZ12" s="5"/>
-      <c r="CA12" s="5"/>
-      <c r="CB12" s="5"/>
-      <c r="CC12" s="5"/>
-      <c r="CD12" s="5"/>
-      <c r="CE12" s="5"/>
-      <c r="CF12" s="5"/>
-      <c r="CG12" s="5"/>
-      <c r="CH12" s="5"/>
-      <c r="CI12" s="5"/>
-      <c r="CJ12" s="5"/>
-      <c r="CK12" s="5"/>
-      <c r="CL12" s="5"/>
-      <c r="CM12" s="5"/>
-      <c r="CN12" s="5"/>
-      <c r="CO12" s="5"/>
-      <c r="CP12" s="5"/>
-      <c r="CQ12" s="5"/>
-      <c r="CR12" s="5"/>
-      <c r="CS12" s="5"/>
-      <c r="CT12" s="5"/>
-      <c r="CU12" s="5"/>
-      <c r="CV12" s="5"/>
-      <c r="CW12" s="5"/>
-      <c r="CX12" s="5"/>
-      <c r="CY12" s="5"/>
-      <c r="CZ12" s="5"/>
-      <c r="DA12" s="5"/>
-      <c r="DB12" s="5"/>
-      <c r="DC12" s="5"/>
-      <c r="DD12" s="5"/>
-      <c r="DE12" s="5"/>
-      <c r="DF12" s="5"/>
-      <c r="DG12" s="5"/>
-      <c r="DH12" s="5"/>
-      <c r="DI12" s="5"/>
-      <c r="DJ12" s="5"/>
-      <c r="DK12" s="5"/>
-      <c r="DL12" s="5"/>
-      <c r="DM12" s="5"/>
-      <c r="DN12" s="5"/>
-      <c r="DO12" s="5"/>
-      <c r="DP12" s="5"/>
-      <c r="DQ12" s="5"/>
-      <c r="DR12" s="5"/>
-      <c r="DS12" s="5"/>
+      <c r="AU12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW12" s="4"/>
+      <c r="AX12" s="4"/>
+      <c r="AZ12" s="4"/>
+      <c r="BA12" s="4"/>
+      <c r="BB12" s="4"/>
+      <c r="BC12" s="4"/>
+      <c r="BD12" s="4"/>
+      <c r="BE12" s="4"/>
+      <c r="BF12" s="4"/>
+      <c r="BG12" s="4"/>
+      <c r="BH12" s="4"/>
+      <c r="BI12" s="4"/>
+      <c r="BJ12" s="4"/>
+      <c r="BK12" s="4"/>
+      <c r="BL12" s="4"/>
+      <c r="BM12" s="4"/>
+      <c r="BN12" s="4"/>
+      <c r="BO12" s="4"/>
+      <c r="BP12" s="4"/>
+      <c r="BQ12" s="4"/>
+      <c r="BR12" s="4"/>
+      <c r="BS12" s="4"/>
+      <c r="BT12" s="4"/>
+      <c r="BU12" s="4"/>
+      <c r="BV12" s="4"/>
+      <c r="BW12" s="4"/>
+      <c r="BX12" s="4"/>
+      <c r="BY12" s="4"/>
+      <c r="BZ12" s="4"/>
+      <c r="CA12" s="4"/>
+      <c r="CB12" s="4"/>
+      <c r="CC12" s="4"/>
+      <c r="CD12" s="4"/>
+      <c r="CE12" s="4"/>
+      <c r="CF12" s="4"/>
+      <c r="CG12" s="4"/>
+      <c r="CH12" s="4"/>
+      <c r="CI12" s="4"/>
+      <c r="CJ12" s="4"/>
+      <c r="CK12" s="4"/>
+      <c r="CL12" s="4"/>
+      <c r="CM12" s="4"/>
+      <c r="CN12" s="4"/>
+      <c r="CO12" s="4"/>
+      <c r="CP12" s="4"/>
+      <c r="CQ12" s="4"/>
+      <c r="CR12" s="4"/>
+      <c r="CS12" s="4"/>
+      <c r="CT12" s="4"/>
+      <c r="CU12" s="4"/>
+      <c r="CV12" s="4"/>
+      <c r="CW12" s="4"/>
+      <c r="CX12" s="4"/>
+      <c r="CY12" s="4"/>
+      <c r="CZ12" s="4"/>
+      <c r="DA12" s="4"/>
+      <c r="DB12" s="4"/>
+      <c r="DC12" s="4"/>
+      <c r="DD12" s="4"/>
+      <c r="DE12" s="4"/>
+      <c r="DF12" s="4"/>
+      <c r="DG12" s="4"/>
+      <c r="DH12" s="4"/>
+      <c r="DI12" s="4"/>
+      <c r="DJ12" s="4"/>
+      <c r="DK12" s="4"/>
+      <c r="DL12" s="4"/>
+      <c r="DM12" s="4"/>
+      <c r="DN12" s="4"/>
+      <c r="DO12" s="4"/>
+      <c r="DP12" s="4"/>
+      <c r="DQ12" s="4"/>
+      <c r="DR12" s="4"/>
+      <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3092,7 +3156,7 @@
       <c r="I13" t="s">
         <v>5</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K13" t="s">
@@ -3203,83 +3267,88 @@
       <c r="AT13" t="s">
         <v>5</v>
       </c>
-      <c r="AU13" s="2"/>
-      <c r="AV13" s="2"/>
-      <c r="AW13" s="2"/>
-      <c r="AZ13" s="5"/>
-      <c r="BA13" s="5"/>
-      <c r="BB13" s="5"/>
-      <c r="BC13" s="5"/>
-      <c r="BD13" s="5"/>
-      <c r="BE13" s="5"/>
-      <c r="BF13" s="5"/>
-      <c r="BG13" s="5"/>
-      <c r="BH13" s="5"/>
-      <c r="BI13" s="5"/>
-      <c r="BJ13" s="5"/>
-      <c r="BK13" s="5"/>
-      <c r="BL13" s="5"/>
-      <c r="BM13" s="5"/>
-      <c r="BN13" s="5"/>
-      <c r="BO13" s="5"/>
-      <c r="BP13" s="5"/>
-      <c r="BQ13" s="5"/>
-      <c r="BR13" s="5"/>
-      <c r="BS13" s="5"/>
-      <c r="BT13" s="5"/>
-      <c r="BU13" s="5"/>
-      <c r="BV13" s="5"/>
-      <c r="BW13" s="5"/>
-      <c r="BX13" s="5"/>
-      <c r="BY13" s="5"/>
-      <c r="BZ13" s="5"/>
-      <c r="CA13" s="5"/>
-      <c r="CB13" s="5"/>
-      <c r="CC13" s="5"/>
-      <c r="CD13" s="5"/>
-      <c r="CE13" s="5"/>
-      <c r="CF13" s="5"/>
-      <c r="CG13" s="5"/>
-      <c r="CH13" s="5"/>
-      <c r="CI13" s="5"/>
-      <c r="CJ13" s="5"/>
-      <c r="CK13" s="5"/>
-      <c r="CL13" s="5"/>
-      <c r="CM13" s="5"/>
-      <c r="CN13" s="5"/>
-      <c r="CO13" s="5"/>
-      <c r="CP13" s="5"/>
-      <c r="CQ13" s="5"/>
-      <c r="CR13" s="5"/>
-      <c r="CS13" s="5"/>
-      <c r="CT13" s="5"/>
-      <c r="CU13" s="5"/>
-      <c r="CV13" s="5"/>
-      <c r="CW13" s="5"/>
-      <c r="CX13" s="5"/>
-      <c r="CY13" s="5"/>
-      <c r="CZ13" s="5"/>
-      <c r="DA13" s="5"/>
-      <c r="DB13" s="5"/>
-      <c r="DC13" s="5"/>
-      <c r="DD13" s="5"/>
-      <c r="DE13" s="5"/>
-      <c r="DF13" s="5"/>
-      <c r="DG13" s="5"/>
-      <c r="DH13" s="5"/>
-      <c r="DI13" s="5"/>
-      <c r="DJ13" s="5"/>
-      <c r="DK13" s="5"/>
-      <c r="DL13" s="5"/>
-      <c r="DM13" s="5"/>
-      <c r="DN13" s="5"/>
-      <c r="DO13" s="5"/>
-      <c r="DP13" s="5"/>
-      <c r="DQ13" s="5"/>
-      <c r="DR13" s="5"/>
-      <c r="DS13" s="5"/>
+      <c r="AU13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW13" s="4"/>
+      <c r="AX13" s="4"/>
+      <c r="AZ13" s="4"/>
+      <c r="BA13" s="4"/>
+      <c r="BB13" s="4"/>
+      <c r="BC13" s="4"/>
+      <c r="BD13" s="4"/>
+      <c r="BE13" s="4"/>
+      <c r="BF13" s="4"/>
+      <c r="BG13" s="4"/>
+      <c r="BH13" s="4"/>
+      <c r="BI13" s="4"/>
+      <c r="BJ13" s="4"/>
+      <c r="BK13" s="4"/>
+      <c r="BL13" s="4"/>
+      <c r="BM13" s="4"/>
+      <c r="BN13" s="4"/>
+      <c r="BO13" s="4"/>
+      <c r="BP13" s="4"/>
+      <c r="BQ13" s="4"/>
+      <c r="BR13" s="4"/>
+      <c r="BS13" s="4"/>
+      <c r="BT13" s="4"/>
+      <c r="BU13" s="4"/>
+      <c r="BV13" s="4"/>
+      <c r="BW13" s="4"/>
+      <c r="BX13" s="4"/>
+      <c r="BY13" s="4"/>
+      <c r="BZ13" s="4"/>
+      <c r="CA13" s="4"/>
+      <c r="CB13" s="4"/>
+      <c r="CC13" s="4"/>
+      <c r="CD13" s="4"/>
+      <c r="CE13" s="4"/>
+      <c r="CF13" s="4"/>
+      <c r="CG13" s="4"/>
+      <c r="CH13" s="4"/>
+      <c r="CI13" s="4"/>
+      <c r="CJ13" s="4"/>
+      <c r="CK13" s="4"/>
+      <c r="CL13" s="4"/>
+      <c r="CM13" s="4"/>
+      <c r="CN13" s="4"/>
+      <c r="CO13" s="4"/>
+      <c r="CP13" s="4"/>
+      <c r="CQ13" s="4"/>
+      <c r="CR13" s="4"/>
+      <c r="CS13" s="4"/>
+      <c r="CT13" s="4"/>
+      <c r="CU13" s="4"/>
+      <c r="CV13" s="4"/>
+      <c r="CW13" s="4"/>
+      <c r="CX13" s="4"/>
+      <c r="CY13" s="4"/>
+      <c r="CZ13" s="4"/>
+      <c r="DA13" s="4"/>
+      <c r="DB13" s="4"/>
+      <c r="DC13" s="4"/>
+      <c r="DD13" s="4"/>
+      <c r="DE13" s="4"/>
+      <c r="DF13" s="4"/>
+      <c r="DG13" s="4"/>
+      <c r="DH13" s="4"/>
+      <c r="DI13" s="4"/>
+      <c r="DJ13" s="4"/>
+      <c r="DK13" s="4"/>
+      <c r="DL13" s="4"/>
+      <c r="DM13" s="4"/>
+      <c r="DN13" s="4"/>
+      <c r="DO13" s="4"/>
+      <c r="DP13" s="4"/>
+      <c r="DQ13" s="4"/>
+      <c r="DR13" s="4"/>
+      <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -3307,7 +3376,7 @@
       <c r="I14" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K14" t="s">
@@ -3418,83 +3487,88 @@
       <c r="AT14" t="s">
         <v>5</v>
       </c>
-      <c r="AU14" s="2"/>
-      <c r="AV14" s="2"/>
-      <c r="AW14" s="2"/>
-      <c r="AZ14" s="5"/>
-      <c r="BA14" s="5"/>
-      <c r="BB14" s="5"/>
-      <c r="BC14" s="5"/>
-      <c r="BD14" s="5"/>
-      <c r="BE14" s="5"/>
-      <c r="BF14" s="5"/>
-      <c r="BG14" s="5"/>
-      <c r="BH14" s="5"/>
-      <c r="BI14" s="5"/>
-      <c r="BJ14" s="5"/>
-      <c r="BK14" s="5"/>
-      <c r="BL14" s="5"/>
-      <c r="BM14" s="5"/>
-      <c r="BN14" s="5"/>
-      <c r="BO14" s="5"/>
-      <c r="BP14" s="5"/>
-      <c r="BQ14" s="5"/>
-      <c r="BR14" s="5"/>
-      <c r="BS14" s="5"/>
-      <c r="BT14" s="5"/>
-      <c r="BU14" s="5"/>
-      <c r="BV14" s="5"/>
-      <c r="BW14" s="5"/>
-      <c r="BX14" s="5"/>
-      <c r="BY14" s="5"/>
-      <c r="BZ14" s="5"/>
-      <c r="CA14" s="5"/>
-      <c r="CB14" s="5"/>
-      <c r="CC14" s="5"/>
-      <c r="CD14" s="5"/>
-      <c r="CE14" s="5"/>
-      <c r="CF14" s="5"/>
-      <c r="CG14" s="5"/>
-      <c r="CH14" s="5"/>
-      <c r="CI14" s="5"/>
-      <c r="CJ14" s="5"/>
-      <c r="CK14" s="5"/>
-      <c r="CL14" s="5"/>
-      <c r="CM14" s="5"/>
-      <c r="CN14" s="5"/>
-      <c r="CO14" s="5"/>
-      <c r="CP14" s="5"/>
-      <c r="CQ14" s="5"/>
-      <c r="CR14" s="5"/>
-      <c r="CS14" s="5"/>
-      <c r="CT14" s="5"/>
-      <c r="CU14" s="5"/>
-      <c r="CV14" s="5"/>
-      <c r="CW14" s="5"/>
-      <c r="CX14" s="5"/>
-      <c r="CY14" s="5"/>
-      <c r="CZ14" s="5"/>
-      <c r="DA14" s="5"/>
-      <c r="DB14" s="5"/>
-      <c r="DC14" s="5"/>
-      <c r="DD14" s="5"/>
-      <c r="DE14" s="5"/>
-      <c r="DF14" s="5"/>
-      <c r="DG14" s="5"/>
-      <c r="DH14" s="5"/>
-      <c r="DI14" s="5"/>
-      <c r="DJ14" s="5"/>
-      <c r="DK14" s="5"/>
-      <c r="DL14" s="5"/>
-      <c r="DM14" s="5"/>
-      <c r="DN14" s="5"/>
-      <c r="DO14" s="5"/>
-      <c r="DP14" s="5"/>
-      <c r="DQ14" s="5"/>
-      <c r="DR14" s="5"/>
-      <c r="DS14" s="5"/>
+      <c r="AU14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW14" s="4"/>
+      <c r="AX14" s="4"/>
+      <c r="AZ14" s="4"/>
+      <c r="BA14" s="4"/>
+      <c r="BB14" s="4"/>
+      <c r="BC14" s="4"/>
+      <c r="BD14" s="4"/>
+      <c r="BE14" s="4"/>
+      <c r="BF14" s="4"/>
+      <c r="BG14" s="4"/>
+      <c r="BH14" s="4"/>
+      <c r="BI14" s="4"/>
+      <c r="BJ14" s="4"/>
+      <c r="BK14" s="4"/>
+      <c r="BL14" s="4"/>
+      <c r="BM14" s="4"/>
+      <c r="BN14" s="4"/>
+      <c r="BO14" s="4"/>
+      <c r="BP14" s="4"/>
+      <c r="BQ14" s="4"/>
+      <c r="BR14" s="4"/>
+      <c r="BS14" s="4"/>
+      <c r="BT14" s="4"/>
+      <c r="BU14" s="4"/>
+      <c r="BV14" s="4"/>
+      <c r="BW14" s="4"/>
+      <c r="BX14" s="4"/>
+      <c r="BY14" s="4"/>
+      <c r="BZ14" s="4"/>
+      <c r="CA14" s="4"/>
+      <c r="CB14" s="4"/>
+      <c r="CC14" s="4"/>
+      <c r="CD14" s="4"/>
+      <c r="CE14" s="4"/>
+      <c r="CF14" s="4"/>
+      <c r="CG14" s="4"/>
+      <c r="CH14" s="4"/>
+      <c r="CI14" s="4"/>
+      <c r="CJ14" s="4"/>
+      <c r="CK14" s="4"/>
+      <c r="CL14" s="4"/>
+      <c r="CM14" s="4"/>
+      <c r="CN14" s="4"/>
+      <c r="CO14" s="4"/>
+      <c r="CP14" s="4"/>
+      <c r="CQ14" s="4"/>
+      <c r="CR14" s="4"/>
+      <c r="CS14" s="4"/>
+      <c r="CT14" s="4"/>
+      <c r="CU14" s="4"/>
+      <c r="CV14" s="4"/>
+      <c r="CW14" s="4"/>
+      <c r="CX14" s="4"/>
+      <c r="CY14" s="4"/>
+      <c r="CZ14" s="4"/>
+      <c r="DA14" s="4"/>
+      <c r="DB14" s="4"/>
+      <c r="DC14" s="4"/>
+      <c r="DD14" s="4"/>
+      <c r="DE14" s="4"/>
+      <c r="DF14" s="4"/>
+      <c r="DG14" s="4"/>
+      <c r="DH14" s="4"/>
+      <c r="DI14" s="4"/>
+      <c r="DJ14" s="4"/>
+      <c r="DK14" s="4"/>
+      <c r="DL14" s="4"/>
+      <c r="DM14" s="4"/>
+      <c r="DN14" s="4"/>
+      <c r="DO14" s="4"/>
+      <c r="DP14" s="4"/>
+      <c r="DQ14" s="4"/>
+      <c r="DR14" s="4"/>
+      <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -3522,7 +3596,7 @@
       <c r="I15" t="s">
         <v>5</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K15" t="s">
@@ -3633,83 +3707,88 @@
       <c r="AT15" t="s">
         <v>5</v>
       </c>
-      <c r="AU15" s="2"/>
-      <c r="AV15" s="2"/>
-      <c r="AW15" s="2"/>
-      <c r="AZ15" s="5"/>
-      <c r="BA15" s="5"/>
-      <c r="BB15" s="5"/>
-      <c r="BC15" s="5"/>
-      <c r="BD15" s="5"/>
-      <c r="BE15" s="5"/>
-      <c r="BF15" s="5"/>
-      <c r="BG15" s="5"/>
-      <c r="BH15" s="5"/>
-      <c r="BI15" s="5"/>
-      <c r="BJ15" s="5"/>
-      <c r="BK15" s="5"/>
-      <c r="BL15" s="5"/>
-      <c r="BM15" s="5"/>
-      <c r="BN15" s="5"/>
-      <c r="BO15" s="5"/>
-      <c r="BP15" s="5"/>
-      <c r="BQ15" s="5"/>
-      <c r="BR15" s="5"/>
-      <c r="BS15" s="5"/>
-      <c r="BT15" s="5"/>
-      <c r="BU15" s="5"/>
-      <c r="BV15" s="5"/>
-      <c r="BW15" s="5"/>
-      <c r="BX15" s="5"/>
-      <c r="BY15" s="5"/>
-      <c r="BZ15" s="5"/>
-      <c r="CA15" s="5"/>
-      <c r="CB15" s="5"/>
-      <c r="CC15" s="5"/>
-      <c r="CD15" s="5"/>
-      <c r="CE15" s="5"/>
-      <c r="CF15" s="5"/>
-      <c r="CG15" s="5"/>
-      <c r="CH15" s="5"/>
-      <c r="CI15" s="5"/>
-      <c r="CJ15" s="5"/>
-      <c r="CK15" s="5"/>
-      <c r="CL15" s="5"/>
-      <c r="CM15" s="5"/>
-      <c r="CN15" s="5"/>
-      <c r="CO15" s="5"/>
-      <c r="CP15" s="5"/>
-      <c r="CQ15" s="5"/>
-      <c r="CR15" s="5"/>
-      <c r="CS15" s="5"/>
-      <c r="CT15" s="5"/>
-      <c r="CU15" s="5"/>
-      <c r="CV15" s="5"/>
-      <c r="CW15" s="5"/>
-      <c r="CX15" s="5"/>
-      <c r="CY15" s="5"/>
-      <c r="CZ15" s="5"/>
-      <c r="DA15" s="5"/>
-      <c r="DB15" s="5"/>
-      <c r="DC15" s="5"/>
-      <c r="DD15" s="5"/>
-      <c r="DE15" s="5"/>
-      <c r="DF15" s="5"/>
-      <c r="DG15" s="5"/>
-      <c r="DH15" s="5"/>
-      <c r="DI15" s="5"/>
-      <c r="DJ15" s="5"/>
-      <c r="DK15" s="5"/>
-      <c r="DL15" s="5"/>
-      <c r="DM15" s="5"/>
-      <c r="DN15" s="5"/>
-      <c r="DO15" s="5"/>
-      <c r="DP15" s="5"/>
-      <c r="DQ15" s="5"/>
-      <c r="DR15" s="5"/>
-      <c r="DS15" s="5"/>
+      <c r="AU15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW15" s="4"/>
+      <c r="AX15" s="4"/>
+      <c r="AZ15" s="4"/>
+      <c r="BA15" s="4"/>
+      <c r="BB15" s="4"/>
+      <c r="BC15" s="4"/>
+      <c r="BD15" s="4"/>
+      <c r="BE15" s="4"/>
+      <c r="BF15" s="4"/>
+      <c r="BG15" s="4"/>
+      <c r="BH15" s="4"/>
+      <c r="BI15" s="4"/>
+      <c r="BJ15" s="4"/>
+      <c r="BK15" s="4"/>
+      <c r="BL15" s="4"/>
+      <c r="BM15" s="4"/>
+      <c r="BN15" s="4"/>
+      <c r="BO15" s="4"/>
+      <c r="BP15" s="4"/>
+      <c r="BQ15" s="4"/>
+      <c r="BR15" s="4"/>
+      <c r="BS15" s="4"/>
+      <c r="BT15" s="4"/>
+      <c r="BU15" s="4"/>
+      <c r="BV15" s="4"/>
+      <c r="BW15" s="4"/>
+      <c r="BX15" s="4"/>
+      <c r="BY15" s="4"/>
+      <c r="BZ15" s="4"/>
+      <c r="CA15" s="4"/>
+      <c r="CB15" s="4"/>
+      <c r="CC15" s="4"/>
+      <c r="CD15" s="4"/>
+      <c r="CE15" s="4"/>
+      <c r="CF15" s="4"/>
+      <c r="CG15" s="4"/>
+      <c r="CH15" s="4"/>
+      <c r="CI15" s="4"/>
+      <c r="CJ15" s="4"/>
+      <c r="CK15" s="4"/>
+      <c r="CL15" s="4"/>
+      <c r="CM15" s="4"/>
+      <c r="CN15" s="4"/>
+      <c r="CO15" s="4"/>
+      <c r="CP15" s="4"/>
+      <c r="CQ15" s="4"/>
+      <c r="CR15" s="4"/>
+      <c r="CS15" s="4"/>
+      <c r="CT15" s="4"/>
+      <c r="CU15" s="4"/>
+      <c r="CV15" s="4"/>
+      <c r="CW15" s="4"/>
+      <c r="CX15" s="4"/>
+      <c r="CY15" s="4"/>
+      <c r="CZ15" s="4"/>
+      <c r="DA15" s="4"/>
+      <c r="DB15" s="4"/>
+      <c r="DC15" s="4"/>
+      <c r="DD15" s="4"/>
+      <c r="DE15" s="4"/>
+      <c r="DF15" s="4"/>
+      <c r="DG15" s="4"/>
+      <c r="DH15" s="4"/>
+      <c r="DI15" s="4"/>
+      <c r="DJ15" s="4"/>
+      <c r="DK15" s="4"/>
+      <c r="DL15" s="4"/>
+      <c r="DM15" s="4"/>
+      <c r="DN15" s="4"/>
+      <c r="DO15" s="4"/>
+      <c r="DP15" s="4"/>
+      <c r="DQ15" s="4"/>
+      <c r="DR15" s="4"/>
+      <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -3719,91 +3798,91 @@
       <c r="C16">
         <v>14</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="J16" s="10" t="s">
+      <c r="D16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="M16" s="9" t="s">
+      <c r="K16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="M16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="P16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q16" s="9" t="s">
+      <c r="N16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="R16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="S16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="T16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="U16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="X16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y16" s="9" t="s">
+      <c r="R16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="S16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="T16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="V16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="W16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="X16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Z16" s="9" t="s">
+      <c r="Z16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="AA16" s="9" t="s">
+      <c r="AA16" s="8" t="s">
         <v>7</v>
       </c>
       <c r="AB16" t="s">
         <v>43</v>
       </c>
-      <c r="AC16" s="9" t="s">
+      <c r="AC16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="AD16" s="9" t="s">
+      <c r="AD16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="AE16" s="9" t="s">
+      <c r="AE16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="AF16" s="9" t="s">
+      <c r="AF16" s="8" t="s">
         <v>7</v>
       </c>
       <c r="AG16" t="s">
@@ -3848,83 +3927,88 @@
       <c r="AT16" t="s">
         <v>7</v>
       </c>
-      <c r="AU16" s="2"/>
-      <c r="AV16" s="2"/>
-      <c r="AW16" s="2"/>
-      <c r="AZ16" s="5"/>
-      <c r="BA16" s="5"/>
-      <c r="BB16" s="5"/>
-      <c r="BC16" s="5"/>
-      <c r="BD16" s="5"/>
-      <c r="BE16" s="5"/>
-      <c r="BF16" s="5"/>
-      <c r="BG16" s="5"/>
-      <c r="BH16" s="5"/>
-      <c r="BI16" s="5"/>
-      <c r="BJ16" s="5"/>
-      <c r="BK16" s="5"/>
-      <c r="BL16" s="5"/>
-      <c r="BM16" s="5"/>
-      <c r="BN16" s="5"/>
-      <c r="BO16" s="5"/>
-      <c r="BP16" s="5"/>
-      <c r="BQ16" s="5"/>
-      <c r="BR16" s="5"/>
-      <c r="BS16" s="5"/>
-      <c r="BT16" s="5"/>
-      <c r="BU16" s="5"/>
-      <c r="BV16" s="5"/>
-      <c r="BW16" s="5"/>
-      <c r="BX16" s="5"/>
-      <c r="BY16" s="5"/>
-      <c r="BZ16" s="5"/>
-      <c r="CA16" s="5"/>
-      <c r="CB16" s="5"/>
-      <c r="CC16" s="5"/>
-      <c r="CD16" s="5"/>
-      <c r="CE16" s="5"/>
-      <c r="CF16" s="5"/>
-      <c r="CG16" s="5"/>
-      <c r="CH16" s="5"/>
-      <c r="CI16" s="5"/>
-      <c r="CJ16" s="5"/>
-      <c r="CK16" s="5"/>
-      <c r="CL16" s="5"/>
-      <c r="CM16" s="5"/>
-      <c r="CN16" s="5"/>
-      <c r="CO16" s="5"/>
-      <c r="CP16" s="5"/>
-      <c r="CQ16" s="5"/>
-      <c r="CR16" s="5"/>
-      <c r="CS16" s="5"/>
-      <c r="CT16" s="5"/>
-      <c r="CU16" s="5"/>
-      <c r="CV16" s="5"/>
-      <c r="CW16" s="5"/>
-      <c r="CX16" s="5"/>
-      <c r="CY16" s="5"/>
-      <c r="CZ16" s="5"/>
-      <c r="DA16" s="5"/>
-      <c r="DB16" s="5"/>
-      <c r="DC16" s="5"/>
-      <c r="DD16" s="5"/>
-      <c r="DE16" s="5"/>
-      <c r="DF16" s="5"/>
-      <c r="DG16" s="5"/>
-      <c r="DH16" s="5"/>
-      <c r="DI16" s="5"/>
-      <c r="DJ16" s="5"/>
-      <c r="DK16" s="5"/>
-      <c r="DL16" s="5"/>
-      <c r="DM16" s="5"/>
-      <c r="DN16" s="5"/>
-      <c r="DO16" s="5"/>
-      <c r="DP16" s="5"/>
-      <c r="DQ16" s="5"/>
-      <c r="DR16" s="5"/>
-      <c r="DS16" s="5"/>
+      <c r="AU16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW16" s="4"/>
+      <c r="AX16" s="4"/>
+      <c r="AZ16" s="4"/>
+      <c r="BA16" s="4"/>
+      <c r="BB16" s="4"/>
+      <c r="BC16" s="4"/>
+      <c r="BD16" s="4"/>
+      <c r="BE16" s="4"/>
+      <c r="BF16" s="4"/>
+      <c r="BG16" s="4"/>
+      <c r="BH16" s="4"/>
+      <c r="BI16" s="4"/>
+      <c r="BJ16" s="4"/>
+      <c r="BK16" s="4"/>
+      <c r="BL16" s="4"/>
+      <c r="BM16" s="4"/>
+      <c r="BN16" s="4"/>
+      <c r="BO16" s="4"/>
+      <c r="BP16" s="4"/>
+      <c r="BQ16" s="4"/>
+      <c r="BR16" s="4"/>
+      <c r="BS16" s="4"/>
+      <c r="BT16" s="4"/>
+      <c r="BU16" s="4"/>
+      <c r="BV16" s="4"/>
+      <c r="BW16" s="4"/>
+      <c r="BX16" s="4"/>
+      <c r="BY16" s="4"/>
+      <c r="BZ16" s="4"/>
+      <c r="CA16" s="4"/>
+      <c r="CB16" s="4"/>
+      <c r="CC16" s="4"/>
+      <c r="CD16" s="4"/>
+      <c r="CE16" s="4"/>
+      <c r="CF16" s="4"/>
+      <c r="CG16" s="4"/>
+      <c r="CH16" s="4"/>
+      <c r="CI16" s="4"/>
+      <c r="CJ16" s="4"/>
+      <c r="CK16" s="4"/>
+      <c r="CL16" s="4"/>
+      <c r="CM16" s="4"/>
+      <c r="CN16" s="4"/>
+      <c r="CO16" s="4"/>
+      <c r="CP16" s="4"/>
+      <c r="CQ16" s="4"/>
+      <c r="CR16" s="4"/>
+      <c r="CS16" s="4"/>
+      <c r="CT16" s="4"/>
+      <c r="CU16" s="4"/>
+      <c r="CV16" s="4"/>
+      <c r="CW16" s="4"/>
+      <c r="CX16" s="4"/>
+      <c r="CY16" s="4"/>
+      <c r="CZ16" s="4"/>
+      <c r="DA16" s="4"/>
+      <c r="DB16" s="4"/>
+      <c r="DC16" s="4"/>
+      <c r="DD16" s="4"/>
+      <c r="DE16" s="4"/>
+      <c r="DF16" s="4"/>
+      <c r="DG16" s="4"/>
+      <c r="DH16" s="4"/>
+      <c r="DI16" s="4"/>
+      <c r="DJ16" s="4"/>
+      <c r="DK16" s="4"/>
+      <c r="DL16" s="4"/>
+      <c r="DM16" s="4"/>
+      <c r="DN16" s="4"/>
+      <c r="DO16" s="4"/>
+      <c r="DP16" s="4"/>
+      <c r="DQ16" s="4"/>
+      <c r="DR16" s="4"/>
+      <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -3952,7 +4036,7 @@
       <c r="I17" t="s">
         <v>5</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K17" t="s">
@@ -4063,83 +4147,88 @@
       <c r="AT17" t="s">
         <v>5</v>
       </c>
-      <c r="AU17" s="2"/>
-      <c r="AV17" s="2"/>
-      <c r="AW17" s="2"/>
-      <c r="AZ17" s="5"/>
-      <c r="BA17" s="5"/>
-      <c r="BB17" s="5"/>
-      <c r="BC17" s="5"/>
-      <c r="BD17" s="5"/>
-      <c r="BE17" s="5"/>
-      <c r="BF17" s="5"/>
-      <c r="BG17" s="5"/>
-      <c r="BH17" s="5"/>
-      <c r="BI17" s="5"/>
-      <c r="BJ17" s="5"/>
-      <c r="BK17" s="5"/>
-      <c r="BL17" s="5"/>
-      <c r="BM17" s="5"/>
-      <c r="BN17" s="5"/>
-      <c r="BO17" s="5"/>
-      <c r="BP17" s="5"/>
-      <c r="BQ17" s="5"/>
-      <c r="BR17" s="5"/>
-      <c r="BS17" s="5"/>
-      <c r="BT17" s="5"/>
-      <c r="BU17" s="5"/>
-      <c r="BV17" s="5"/>
-      <c r="BW17" s="5"/>
-      <c r="BX17" s="5"/>
-      <c r="BY17" s="5"/>
-      <c r="BZ17" s="5"/>
-      <c r="CA17" s="5"/>
-      <c r="CB17" s="5"/>
-      <c r="CC17" s="5"/>
-      <c r="CD17" s="5"/>
-      <c r="CE17" s="5"/>
-      <c r="CF17" s="5"/>
-      <c r="CG17" s="5"/>
-      <c r="CH17" s="5"/>
-      <c r="CI17" s="5"/>
-      <c r="CJ17" s="5"/>
-      <c r="CK17" s="5"/>
-      <c r="CL17" s="5"/>
-      <c r="CM17" s="5"/>
-      <c r="CN17" s="5"/>
-      <c r="CO17" s="5"/>
-      <c r="CP17" s="5"/>
-      <c r="CQ17" s="5"/>
-      <c r="CR17" s="5"/>
-      <c r="CS17" s="5"/>
-      <c r="CT17" s="5"/>
-      <c r="CU17" s="5"/>
-      <c r="CV17" s="5"/>
-      <c r="CW17" s="5"/>
-      <c r="CX17" s="5"/>
-      <c r="CY17" s="5"/>
-      <c r="CZ17" s="5"/>
-      <c r="DA17" s="5"/>
-      <c r="DB17" s="5"/>
-      <c r="DC17" s="5"/>
-      <c r="DD17" s="5"/>
-      <c r="DE17" s="5"/>
-      <c r="DF17" s="5"/>
-      <c r="DG17" s="5"/>
-      <c r="DH17" s="5"/>
-      <c r="DI17" s="5"/>
-      <c r="DJ17" s="5"/>
-      <c r="DK17" s="5"/>
-      <c r="DL17" s="5"/>
-      <c r="DM17" s="5"/>
-      <c r="DN17" s="5"/>
-      <c r="DO17" s="5"/>
-      <c r="DP17" s="5"/>
-      <c r="DQ17" s="5"/>
-      <c r="DR17" s="5"/>
-      <c r="DS17" s="5"/>
+      <c r="AU17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW17" s="4"/>
+      <c r="AX17" s="4"/>
+      <c r="AZ17" s="4"/>
+      <c r="BA17" s="4"/>
+      <c r="BB17" s="4"/>
+      <c r="BC17" s="4"/>
+      <c r="BD17" s="4"/>
+      <c r="BE17" s="4"/>
+      <c r="BF17" s="4"/>
+      <c r="BG17" s="4"/>
+      <c r="BH17" s="4"/>
+      <c r="BI17" s="4"/>
+      <c r="BJ17" s="4"/>
+      <c r="BK17" s="4"/>
+      <c r="BL17" s="4"/>
+      <c r="BM17" s="4"/>
+      <c r="BN17" s="4"/>
+      <c r="BO17" s="4"/>
+      <c r="BP17" s="4"/>
+      <c r="BQ17" s="4"/>
+      <c r="BR17" s="4"/>
+      <c r="BS17" s="4"/>
+      <c r="BT17" s="4"/>
+      <c r="BU17" s="4"/>
+      <c r="BV17" s="4"/>
+      <c r="BW17" s="4"/>
+      <c r="BX17" s="4"/>
+      <c r="BY17" s="4"/>
+      <c r="BZ17" s="4"/>
+      <c r="CA17" s="4"/>
+      <c r="CB17" s="4"/>
+      <c r="CC17" s="4"/>
+      <c r="CD17" s="4"/>
+      <c r="CE17" s="4"/>
+      <c r="CF17" s="4"/>
+      <c r="CG17" s="4"/>
+      <c r="CH17" s="4"/>
+      <c r="CI17" s="4"/>
+      <c r="CJ17" s="4"/>
+      <c r="CK17" s="4"/>
+      <c r="CL17" s="4"/>
+      <c r="CM17" s="4"/>
+      <c r="CN17" s="4"/>
+      <c r="CO17" s="4"/>
+      <c r="CP17" s="4"/>
+      <c r="CQ17" s="4"/>
+      <c r="CR17" s="4"/>
+      <c r="CS17" s="4"/>
+      <c r="CT17" s="4"/>
+      <c r="CU17" s="4"/>
+      <c r="CV17" s="4"/>
+      <c r="CW17" s="4"/>
+      <c r="CX17" s="4"/>
+      <c r="CY17" s="4"/>
+      <c r="CZ17" s="4"/>
+      <c r="DA17" s="4"/>
+      <c r="DB17" s="4"/>
+      <c r="DC17" s="4"/>
+      <c r="DD17" s="4"/>
+      <c r="DE17" s="4"/>
+      <c r="DF17" s="4"/>
+      <c r="DG17" s="4"/>
+      <c r="DH17" s="4"/>
+      <c r="DI17" s="4"/>
+      <c r="DJ17" s="4"/>
+      <c r="DK17" s="4"/>
+      <c r="DL17" s="4"/>
+      <c r="DM17" s="4"/>
+      <c r="DN17" s="4"/>
+      <c r="DO17" s="4"/>
+      <c r="DP17" s="4"/>
+      <c r="DQ17" s="4"/>
+      <c r="DR17" s="4"/>
+      <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -4167,7 +4256,7 @@
       <c r="I18" t="s">
         <v>5</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K18" t="s">
@@ -4278,83 +4367,88 @@
       <c r="AT18" t="s">
         <v>5</v>
       </c>
-      <c r="AU18" s="2"/>
-      <c r="AV18" s="2"/>
-      <c r="AW18" s="2"/>
-      <c r="AZ18" s="5"/>
-      <c r="BA18" s="5"/>
-      <c r="BB18" s="5"/>
-      <c r="BC18" s="5"/>
-      <c r="BD18" s="5"/>
-      <c r="BE18" s="5"/>
-      <c r="BF18" s="5"/>
-      <c r="BG18" s="5"/>
-      <c r="BH18" s="5"/>
-      <c r="BI18" s="5"/>
-      <c r="BJ18" s="5"/>
-      <c r="BK18" s="5"/>
-      <c r="BL18" s="5"/>
-      <c r="BM18" s="5"/>
-      <c r="BN18" s="5"/>
-      <c r="BO18" s="5"/>
-      <c r="BP18" s="5"/>
-      <c r="BQ18" s="5"/>
-      <c r="BR18" s="5"/>
-      <c r="BS18" s="5"/>
-      <c r="BT18" s="5"/>
-      <c r="BU18" s="5"/>
-      <c r="BV18" s="5"/>
-      <c r="BW18" s="5"/>
-      <c r="BX18" s="5"/>
-      <c r="BY18" s="5"/>
-      <c r="BZ18" s="5"/>
-      <c r="CA18" s="5"/>
-      <c r="CB18" s="5"/>
-      <c r="CC18" s="5"/>
-      <c r="CD18" s="5"/>
-      <c r="CE18" s="5"/>
-      <c r="CF18" s="5"/>
-      <c r="CG18" s="5"/>
-      <c r="CH18" s="5"/>
-      <c r="CI18" s="5"/>
-      <c r="CJ18" s="5"/>
-      <c r="CK18" s="5"/>
-      <c r="CL18" s="5"/>
-      <c r="CM18" s="5"/>
-      <c r="CN18" s="5"/>
-      <c r="CO18" s="5"/>
-      <c r="CP18" s="5"/>
-      <c r="CQ18" s="5"/>
-      <c r="CR18" s="5"/>
-      <c r="CS18" s="5"/>
-      <c r="CT18" s="5"/>
-      <c r="CU18" s="5"/>
-      <c r="CV18" s="5"/>
-      <c r="CW18" s="5"/>
-      <c r="CX18" s="5"/>
-      <c r="CY18" s="5"/>
-      <c r="CZ18" s="5"/>
-      <c r="DA18" s="5"/>
-      <c r="DB18" s="5"/>
-      <c r="DC18" s="5"/>
-      <c r="DD18" s="5"/>
-      <c r="DE18" s="5"/>
-      <c r="DF18" s="5"/>
-      <c r="DG18" s="5"/>
-      <c r="DH18" s="5"/>
-      <c r="DI18" s="5"/>
-      <c r="DJ18" s="5"/>
-      <c r="DK18" s="5"/>
-      <c r="DL18" s="5"/>
-      <c r="DM18" s="5"/>
-      <c r="DN18" s="5"/>
-      <c r="DO18" s="5"/>
-      <c r="DP18" s="5"/>
-      <c r="DQ18" s="5"/>
-      <c r="DR18" s="5"/>
-      <c r="DS18" s="5"/>
+      <c r="AU18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW18" s="4"/>
+      <c r="AX18" s="4"/>
+      <c r="AZ18" s="4"/>
+      <c r="BA18" s="4"/>
+      <c r="BB18" s="4"/>
+      <c r="BC18" s="4"/>
+      <c r="BD18" s="4"/>
+      <c r="BE18" s="4"/>
+      <c r="BF18" s="4"/>
+      <c r="BG18" s="4"/>
+      <c r="BH18" s="4"/>
+      <c r="BI18" s="4"/>
+      <c r="BJ18" s="4"/>
+      <c r="BK18" s="4"/>
+      <c r="BL18" s="4"/>
+      <c r="BM18" s="4"/>
+      <c r="BN18" s="4"/>
+      <c r="BO18" s="4"/>
+      <c r="BP18" s="4"/>
+      <c r="BQ18" s="4"/>
+      <c r="BR18" s="4"/>
+      <c r="BS18" s="4"/>
+      <c r="BT18" s="4"/>
+      <c r="BU18" s="4"/>
+      <c r="BV18" s="4"/>
+      <c r="BW18" s="4"/>
+      <c r="BX18" s="4"/>
+      <c r="BY18" s="4"/>
+      <c r="BZ18" s="4"/>
+      <c r="CA18" s="4"/>
+      <c r="CB18" s="4"/>
+      <c r="CC18" s="4"/>
+      <c r="CD18" s="4"/>
+      <c r="CE18" s="4"/>
+      <c r="CF18" s="4"/>
+      <c r="CG18" s="4"/>
+      <c r="CH18" s="4"/>
+      <c r="CI18" s="4"/>
+      <c r="CJ18" s="4"/>
+      <c r="CK18" s="4"/>
+      <c r="CL18" s="4"/>
+      <c r="CM18" s="4"/>
+      <c r="CN18" s="4"/>
+      <c r="CO18" s="4"/>
+      <c r="CP18" s="4"/>
+      <c r="CQ18" s="4"/>
+      <c r="CR18" s="4"/>
+      <c r="CS18" s="4"/>
+      <c r="CT18" s="4"/>
+      <c r="CU18" s="4"/>
+      <c r="CV18" s="4"/>
+      <c r="CW18" s="4"/>
+      <c r="CX18" s="4"/>
+      <c r="CY18" s="4"/>
+      <c r="CZ18" s="4"/>
+      <c r="DA18" s="4"/>
+      <c r="DB18" s="4"/>
+      <c r="DC18" s="4"/>
+      <c r="DD18" s="4"/>
+      <c r="DE18" s="4"/>
+      <c r="DF18" s="4"/>
+      <c r="DG18" s="4"/>
+      <c r="DH18" s="4"/>
+      <c r="DI18" s="4"/>
+      <c r="DJ18" s="4"/>
+      <c r="DK18" s="4"/>
+      <c r="DL18" s="4"/>
+      <c r="DM18" s="4"/>
+      <c r="DN18" s="4"/>
+      <c r="DO18" s="4"/>
+      <c r="DP18" s="4"/>
+      <c r="DQ18" s="4"/>
+      <c r="DR18" s="4"/>
+      <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -4382,7 +4476,7 @@
       <c r="I19" t="s">
         <v>5</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K19" t="s">
@@ -4493,83 +4587,88 @@
       <c r="AT19" t="s">
         <v>7</v>
       </c>
-      <c r="AU19" s="2"/>
-      <c r="AV19" s="2"/>
-      <c r="AW19" s="2"/>
-      <c r="AZ19" s="5"/>
-      <c r="BA19" s="5"/>
-      <c r="BB19" s="5"/>
-      <c r="BC19" s="5"/>
-      <c r="BD19" s="5"/>
-      <c r="BE19" s="5"/>
-      <c r="BF19" s="5"/>
-      <c r="BG19" s="5"/>
-      <c r="BH19" s="5"/>
-      <c r="BI19" s="5"/>
-      <c r="BJ19" s="5"/>
-      <c r="BK19" s="5"/>
-      <c r="BL19" s="5"/>
-      <c r="BM19" s="5"/>
-      <c r="BN19" s="5"/>
-      <c r="BO19" s="5"/>
-      <c r="BP19" s="5"/>
-      <c r="BQ19" s="5"/>
-      <c r="BR19" s="5"/>
-      <c r="BS19" s="5"/>
-      <c r="BT19" s="5"/>
-      <c r="BU19" s="5"/>
-      <c r="BV19" s="5"/>
-      <c r="BW19" s="5"/>
-      <c r="BX19" s="5"/>
-      <c r="BY19" s="5"/>
-      <c r="BZ19" s="5"/>
-      <c r="CA19" s="5"/>
-      <c r="CB19" s="5"/>
-      <c r="CC19" s="5"/>
-      <c r="CD19" s="5"/>
-      <c r="CE19" s="5"/>
-      <c r="CF19" s="5"/>
-      <c r="CG19" s="5"/>
-      <c r="CH19" s="5"/>
-      <c r="CI19" s="5"/>
-      <c r="CJ19" s="5"/>
-      <c r="CK19" s="5"/>
-      <c r="CL19" s="5"/>
-      <c r="CM19" s="5"/>
-      <c r="CN19" s="5"/>
-      <c r="CO19" s="5"/>
-      <c r="CP19" s="5"/>
-      <c r="CQ19" s="5"/>
-      <c r="CR19" s="5"/>
-      <c r="CS19" s="5"/>
-      <c r="CT19" s="5"/>
-      <c r="CU19" s="5"/>
-      <c r="CV19" s="5"/>
-      <c r="CW19" s="5"/>
-      <c r="CX19" s="5"/>
-      <c r="CY19" s="5"/>
-      <c r="CZ19" s="5"/>
-      <c r="DA19" s="5"/>
-      <c r="DB19" s="5"/>
-      <c r="DC19" s="5"/>
-      <c r="DD19" s="5"/>
-      <c r="DE19" s="5"/>
-      <c r="DF19" s="5"/>
-      <c r="DG19" s="5"/>
-      <c r="DH19" s="5"/>
-      <c r="DI19" s="5"/>
-      <c r="DJ19" s="5"/>
-      <c r="DK19" s="5"/>
-      <c r="DL19" s="5"/>
-      <c r="DM19" s="5"/>
-      <c r="DN19" s="5"/>
-      <c r="DO19" s="5"/>
-      <c r="DP19" s="5"/>
-      <c r="DQ19" s="5"/>
-      <c r="DR19" s="5"/>
-      <c r="DS19" s="5"/>
+      <c r="AU19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW19" s="4"/>
+      <c r="AX19" s="4"/>
+      <c r="AZ19" s="4"/>
+      <c r="BA19" s="4"/>
+      <c r="BB19" s="4"/>
+      <c r="BC19" s="4"/>
+      <c r="BD19" s="4"/>
+      <c r="BE19" s="4"/>
+      <c r="BF19" s="4"/>
+      <c r="BG19" s="4"/>
+      <c r="BH19" s="4"/>
+      <c r="BI19" s="4"/>
+      <c r="BJ19" s="4"/>
+      <c r="BK19" s="4"/>
+      <c r="BL19" s="4"/>
+      <c r="BM19" s="4"/>
+      <c r="BN19" s="4"/>
+      <c r="BO19" s="4"/>
+      <c r="BP19" s="4"/>
+      <c r="BQ19" s="4"/>
+      <c r="BR19" s="4"/>
+      <c r="BS19" s="4"/>
+      <c r="BT19" s="4"/>
+      <c r="BU19" s="4"/>
+      <c r="BV19" s="4"/>
+      <c r="BW19" s="4"/>
+      <c r="BX19" s="4"/>
+      <c r="BY19" s="4"/>
+      <c r="BZ19" s="4"/>
+      <c r="CA19" s="4"/>
+      <c r="CB19" s="4"/>
+      <c r="CC19" s="4"/>
+      <c r="CD19" s="4"/>
+      <c r="CE19" s="4"/>
+      <c r="CF19" s="4"/>
+      <c r="CG19" s="4"/>
+      <c r="CH19" s="4"/>
+      <c r="CI19" s="4"/>
+      <c r="CJ19" s="4"/>
+      <c r="CK19" s="4"/>
+      <c r="CL19" s="4"/>
+      <c r="CM19" s="4"/>
+      <c r="CN19" s="4"/>
+      <c r="CO19" s="4"/>
+      <c r="CP19" s="4"/>
+      <c r="CQ19" s="4"/>
+      <c r="CR19" s="4"/>
+      <c r="CS19" s="4"/>
+      <c r="CT19" s="4"/>
+      <c r="CU19" s="4"/>
+      <c r="CV19" s="4"/>
+      <c r="CW19" s="4"/>
+      <c r="CX19" s="4"/>
+      <c r="CY19" s="4"/>
+      <c r="CZ19" s="4"/>
+      <c r="DA19" s="4"/>
+      <c r="DB19" s="4"/>
+      <c r="DC19" s="4"/>
+      <c r="DD19" s="4"/>
+      <c r="DE19" s="4"/>
+      <c r="DF19" s="4"/>
+      <c r="DG19" s="4"/>
+      <c r="DH19" s="4"/>
+      <c r="DI19" s="4"/>
+      <c r="DJ19" s="4"/>
+      <c r="DK19" s="4"/>
+      <c r="DL19" s="4"/>
+      <c r="DM19" s="4"/>
+      <c r="DN19" s="4"/>
+      <c r="DO19" s="4"/>
+      <c r="DP19" s="4"/>
+      <c r="DQ19" s="4"/>
+      <c r="DR19" s="4"/>
+      <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -4597,7 +4696,7 @@
       <c r="I20" t="s">
         <v>5</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J20" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K20" t="s">
@@ -4708,83 +4807,88 @@
       <c r="AT20" t="s">
         <v>5</v>
       </c>
-      <c r="AU20" s="2"/>
-      <c r="AV20" s="2"/>
-      <c r="AW20" s="2"/>
-      <c r="AZ20" s="5"/>
-      <c r="BA20" s="5"/>
-      <c r="BB20" s="5"/>
-      <c r="BC20" s="5"/>
-      <c r="BD20" s="5"/>
-      <c r="BE20" s="5"/>
-      <c r="BF20" s="5"/>
-      <c r="BG20" s="5"/>
-      <c r="BH20" s="5"/>
-      <c r="BI20" s="5"/>
-      <c r="BJ20" s="5"/>
-      <c r="BK20" s="5"/>
-      <c r="BL20" s="5"/>
-      <c r="BM20" s="5"/>
-      <c r="BN20" s="5"/>
-      <c r="BO20" s="5"/>
-      <c r="BP20" s="5"/>
-      <c r="BQ20" s="5"/>
-      <c r="BR20" s="5"/>
-      <c r="BS20" s="5"/>
-      <c r="BT20" s="5"/>
-      <c r="BU20" s="5"/>
-      <c r="BV20" s="5"/>
-      <c r="BW20" s="5"/>
-      <c r="BX20" s="5"/>
-      <c r="BY20" s="5"/>
-      <c r="BZ20" s="5"/>
-      <c r="CA20" s="5"/>
-      <c r="CB20" s="5"/>
-      <c r="CC20" s="5"/>
-      <c r="CD20" s="5"/>
-      <c r="CE20" s="5"/>
-      <c r="CF20" s="5"/>
-      <c r="CG20" s="5"/>
-      <c r="CH20" s="5"/>
-      <c r="CI20" s="5"/>
-      <c r="CJ20" s="5"/>
-      <c r="CK20" s="5"/>
-      <c r="CL20" s="5"/>
-      <c r="CM20" s="5"/>
-      <c r="CN20" s="5"/>
-      <c r="CO20" s="5"/>
-      <c r="CP20" s="5"/>
-      <c r="CQ20" s="5"/>
-      <c r="CR20" s="5"/>
-      <c r="CS20" s="5"/>
-      <c r="CT20" s="5"/>
-      <c r="CU20" s="5"/>
-      <c r="CV20" s="5"/>
-      <c r="CW20" s="5"/>
-      <c r="CX20" s="5"/>
-      <c r="CY20" s="5"/>
-      <c r="CZ20" s="5"/>
-      <c r="DA20" s="5"/>
-      <c r="DB20" s="5"/>
-      <c r="DC20" s="5"/>
-      <c r="DD20" s="5"/>
-      <c r="DE20" s="5"/>
-      <c r="DF20" s="5"/>
-      <c r="DG20" s="5"/>
-      <c r="DH20" s="5"/>
-      <c r="DI20" s="5"/>
-      <c r="DJ20" s="5"/>
-      <c r="DK20" s="5"/>
-      <c r="DL20" s="5"/>
-      <c r="DM20" s="5"/>
-      <c r="DN20" s="5"/>
-      <c r="DO20" s="5"/>
-      <c r="DP20" s="5"/>
-      <c r="DQ20" s="5"/>
-      <c r="DR20" s="5"/>
-      <c r="DS20" s="5"/>
+      <c r="AU20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW20" s="4"/>
+      <c r="AX20" s="4"/>
+      <c r="AZ20" s="4"/>
+      <c r="BA20" s="4"/>
+      <c r="BB20" s="4"/>
+      <c r="BC20" s="4"/>
+      <c r="BD20" s="4"/>
+      <c r="BE20" s="4"/>
+      <c r="BF20" s="4"/>
+      <c r="BG20" s="4"/>
+      <c r="BH20" s="4"/>
+      <c r="BI20" s="4"/>
+      <c r="BJ20" s="4"/>
+      <c r="BK20" s="4"/>
+      <c r="BL20" s="4"/>
+      <c r="BM20" s="4"/>
+      <c r="BN20" s="4"/>
+      <c r="BO20" s="4"/>
+      <c r="BP20" s="4"/>
+      <c r="BQ20" s="4"/>
+      <c r="BR20" s="4"/>
+      <c r="BS20" s="4"/>
+      <c r="BT20" s="4"/>
+      <c r="BU20" s="4"/>
+      <c r="BV20" s="4"/>
+      <c r="BW20" s="4"/>
+      <c r="BX20" s="4"/>
+      <c r="BY20" s="4"/>
+      <c r="BZ20" s="4"/>
+      <c r="CA20" s="4"/>
+      <c r="CB20" s="4"/>
+      <c r="CC20" s="4"/>
+      <c r="CD20" s="4"/>
+      <c r="CE20" s="4"/>
+      <c r="CF20" s="4"/>
+      <c r="CG20" s="4"/>
+      <c r="CH20" s="4"/>
+      <c r="CI20" s="4"/>
+      <c r="CJ20" s="4"/>
+      <c r="CK20" s="4"/>
+      <c r="CL20" s="4"/>
+      <c r="CM20" s="4"/>
+      <c r="CN20" s="4"/>
+      <c r="CO20" s="4"/>
+      <c r="CP20" s="4"/>
+      <c r="CQ20" s="4"/>
+      <c r="CR20" s="4"/>
+      <c r="CS20" s="4"/>
+      <c r="CT20" s="4"/>
+      <c r="CU20" s="4"/>
+      <c r="CV20" s="4"/>
+      <c r="CW20" s="4"/>
+      <c r="CX20" s="4"/>
+      <c r="CY20" s="4"/>
+      <c r="CZ20" s="4"/>
+      <c r="DA20" s="4"/>
+      <c r="DB20" s="4"/>
+      <c r="DC20" s="4"/>
+      <c r="DD20" s="4"/>
+      <c r="DE20" s="4"/>
+      <c r="DF20" s="4"/>
+      <c r="DG20" s="4"/>
+      <c r="DH20" s="4"/>
+      <c r="DI20" s="4"/>
+      <c r="DJ20" s="4"/>
+      <c r="DK20" s="4"/>
+      <c r="DL20" s="4"/>
+      <c r="DM20" s="4"/>
+      <c r="DN20" s="4"/>
+      <c r="DO20" s="4"/>
+      <c r="DP20" s="4"/>
+      <c r="DQ20" s="4"/>
+      <c r="DR20" s="4"/>
+      <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -4812,7 +4916,7 @@
       <c r="I21" t="s">
         <v>5</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K21" t="s">
@@ -4923,83 +5027,88 @@
       <c r="AT21" t="s">
         <v>5</v>
       </c>
-      <c r="AU21" s="2"/>
-      <c r="AV21" s="2"/>
-      <c r="AW21" s="2"/>
-      <c r="AZ21" s="5"/>
-      <c r="BA21" s="5"/>
-      <c r="BB21" s="5"/>
-      <c r="BC21" s="5"/>
-      <c r="BD21" s="5"/>
-      <c r="BE21" s="5"/>
-      <c r="BF21" s="5"/>
-      <c r="BG21" s="5"/>
-      <c r="BH21" s="5"/>
-      <c r="BI21" s="5"/>
-      <c r="BJ21" s="5"/>
-      <c r="BK21" s="5"/>
-      <c r="BL21" s="5"/>
-      <c r="BM21" s="5"/>
-      <c r="BN21" s="5"/>
-      <c r="BO21" s="5"/>
-      <c r="BP21" s="5"/>
-      <c r="BQ21" s="5"/>
-      <c r="BR21" s="5"/>
-      <c r="BS21" s="5"/>
-      <c r="BT21" s="5"/>
-      <c r="BU21" s="5"/>
-      <c r="BV21" s="5"/>
-      <c r="BW21" s="5"/>
-      <c r="BX21" s="5"/>
-      <c r="BY21" s="5"/>
-      <c r="BZ21" s="5"/>
-      <c r="CA21" s="5"/>
-      <c r="CB21" s="5"/>
-      <c r="CC21" s="5"/>
-      <c r="CD21" s="5"/>
-      <c r="CE21" s="5"/>
-      <c r="CF21" s="5"/>
-      <c r="CG21" s="5"/>
-      <c r="CH21" s="5"/>
-      <c r="CI21" s="5"/>
-      <c r="CJ21" s="5"/>
-      <c r="CK21" s="5"/>
-      <c r="CL21" s="5"/>
-      <c r="CM21" s="5"/>
-      <c r="CN21" s="5"/>
-      <c r="CO21" s="5"/>
-      <c r="CP21" s="5"/>
-      <c r="CQ21" s="5"/>
-      <c r="CR21" s="5"/>
-      <c r="CS21" s="5"/>
-      <c r="CT21" s="5"/>
-      <c r="CU21" s="5"/>
-      <c r="CV21" s="5"/>
-      <c r="CW21" s="5"/>
-      <c r="CX21" s="5"/>
-      <c r="CY21" s="5"/>
-      <c r="CZ21" s="5"/>
-      <c r="DA21" s="5"/>
-      <c r="DB21" s="5"/>
-      <c r="DC21" s="5"/>
-      <c r="DD21" s="5"/>
-      <c r="DE21" s="5"/>
-      <c r="DF21" s="5"/>
-      <c r="DG21" s="5"/>
-      <c r="DH21" s="5"/>
-      <c r="DI21" s="5"/>
-      <c r="DJ21" s="5"/>
-      <c r="DK21" s="5"/>
-      <c r="DL21" s="5"/>
-      <c r="DM21" s="5"/>
-      <c r="DN21" s="5"/>
-      <c r="DO21" s="5"/>
-      <c r="DP21" s="5"/>
-      <c r="DQ21" s="5"/>
-      <c r="DR21" s="5"/>
-      <c r="DS21" s="5"/>
+      <c r="AU21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV21" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW21" s="4"/>
+      <c r="AX21" s="4"/>
+      <c r="AZ21" s="4"/>
+      <c r="BA21" s="4"/>
+      <c r="BB21" s="4"/>
+      <c r="BC21" s="4"/>
+      <c r="BD21" s="4"/>
+      <c r="BE21" s="4"/>
+      <c r="BF21" s="4"/>
+      <c r="BG21" s="4"/>
+      <c r="BH21" s="4"/>
+      <c r="BI21" s="4"/>
+      <c r="BJ21" s="4"/>
+      <c r="BK21" s="4"/>
+      <c r="BL21" s="4"/>
+      <c r="BM21" s="4"/>
+      <c r="BN21" s="4"/>
+      <c r="BO21" s="4"/>
+      <c r="BP21" s="4"/>
+      <c r="BQ21" s="4"/>
+      <c r="BR21" s="4"/>
+      <c r="BS21" s="4"/>
+      <c r="BT21" s="4"/>
+      <c r="BU21" s="4"/>
+      <c r="BV21" s="4"/>
+      <c r="BW21" s="4"/>
+      <c r="BX21" s="4"/>
+      <c r="BY21" s="4"/>
+      <c r="BZ21" s="4"/>
+      <c r="CA21" s="4"/>
+      <c r="CB21" s="4"/>
+      <c r="CC21" s="4"/>
+      <c r="CD21" s="4"/>
+      <c r="CE21" s="4"/>
+      <c r="CF21" s="4"/>
+      <c r="CG21" s="4"/>
+      <c r="CH21" s="4"/>
+      <c r="CI21" s="4"/>
+      <c r="CJ21" s="4"/>
+      <c r="CK21" s="4"/>
+      <c r="CL21" s="4"/>
+      <c r="CM21" s="4"/>
+      <c r="CN21" s="4"/>
+      <c r="CO21" s="4"/>
+      <c r="CP21" s="4"/>
+      <c r="CQ21" s="4"/>
+      <c r="CR21" s="4"/>
+      <c r="CS21" s="4"/>
+      <c r="CT21" s="4"/>
+      <c r="CU21" s="4"/>
+      <c r="CV21" s="4"/>
+      <c r="CW21" s="4"/>
+      <c r="CX21" s="4"/>
+      <c r="CY21" s="4"/>
+      <c r="CZ21" s="4"/>
+      <c r="DA21" s="4"/>
+      <c r="DB21" s="4"/>
+      <c r="DC21" s="4"/>
+      <c r="DD21" s="4"/>
+      <c r="DE21" s="4"/>
+      <c r="DF21" s="4"/>
+      <c r="DG21" s="4"/>
+      <c r="DH21" s="4"/>
+      <c r="DI21" s="4"/>
+      <c r="DJ21" s="4"/>
+      <c r="DK21" s="4"/>
+      <c r="DL21" s="4"/>
+      <c r="DM21" s="4"/>
+      <c r="DN21" s="4"/>
+      <c r="DO21" s="4"/>
+      <c r="DP21" s="4"/>
+      <c r="DQ21" s="4"/>
+      <c r="DR21" s="4"/>
+      <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -5027,7 +5136,7 @@
       <c r="I22" t="s">
         <v>5</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J22" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K22" t="s">
@@ -5138,83 +5247,88 @@
       <c r="AT22" t="s">
         <v>5</v>
       </c>
-      <c r="AU22" s="2"/>
-      <c r="AV22" s="2"/>
-      <c r="AW22" s="2"/>
-      <c r="AZ22" s="5"/>
-      <c r="BA22" s="5"/>
-      <c r="BB22" s="5"/>
-      <c r="BC22" s="5"/>
-      <c r="BD22" s="5"/>
-      <c r="BE22" s="5"/>
-      <c r="BF22" s="5"/>
-      <c r="BG22" s="5"/>
-      <c r="BH22" s="5"/>
-      <c r="BI22" s="5"/>
-      <c r="BJ22" s="5"/>
-      <c r="BK22" s="5"/>
-      <c r="BL22" s="5"/>
-      <c r="BM22" s="5"/>
-      <c r="BN22" s="5"/>
-      <c r="BO22" s="5"/>
-      <c r="BP22" s="5"/>
-      <c r="BQ22" s="5"/>
-      <c r="BR22" s="5"/>
-      <c r="BS22" s="5"/>
-      <c r="BT22" s="5"/>
-      <c r="BU22" s="5"/>
-      <c r="BV22" s="5"/>
-      <c r="BW22" s="5"/>
-      <c r="BX22" s="5"/>
-      <c r="BY22" s="5"/>
-      <c r="BZ22" s="5"/>
-      <c r="CA22" s="5"/>
-      <c r="CB22" s="5"/>
-      <c r="CC22" s="5"/>
-      <c r="CD22" s="5"/>
-      <c r="CE22" s="5"/>
-      <c r="CF22" s="5"/>
-      <c r="CG22" s="5"/>
-      <c r="CH22" s="5"/>
-      <c r="CI22" s="5"/>
-      <c r="CJ22" s="5"/>
-      <c r="CK22" s="5"/>
-      <c r="CL22" s="5"/>
-      <c r="CM22" s="5"/>
-      <c r="CN22" s="5"/>
-      <c r="CO22" s="5"/>
-      <c r="CP22" s="5"/>
-      <c r="CQ22" s="5"/>
-      <c r="CR22" s="5"/>
-      <c r="CS22" s="5"/>
-      <c r="CT22" s="5"/>
-      <c r="CU22" s="5"/>
-      <c r="CV22" s="5"/>
-      <c r="CW22" s="5"/>
-      <c r="CX22" s="5"/>
-      <c r="CY22" s="5"/>
-      <c r="CZ22" s="5"/>
-      <c r="DA22" s="5"/>
-      <c r="DB22" s="5"/>
-      <c r="DC22" s="5"/>
-      <c r="DD22" s="5"/>
-      <c r="DE22" s="5"/>
-      <c r="DF22" s="5"/>
-      <c r="DG22" s="5"/>
-      <c r="DH22" s="5"/>
-      <c r="DI22" s="5"/>
-      <c r="DJ22" s="5"/>
-      <c r="DK22" s="5"/>
-      <c r="DL22" s="5"/>
-      <c r="DM22" s="5"/>
-      <c r="DN22" s="5"/>
-      <c r="DO22" s="5"/>
-      <c r="DP22" s="5"/>
-      <c r="DQ22" s="5"/>
-      <c r="DR22" s="5"/>
-      <c r="DS22" s="5"/>
+      <c r="AU22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW22" s="4"/>
+      <c r="AX22" s="4"/>
+      <c r="AZ22" s="4"/>
+      <c r="BA22" s="4"/>
+      <c r="BB22" s="4"/>
+      <c r="BC22" s="4"/>
+      <c r="BD22" s="4"/>
+      <c r="BE22" s="4"/>
+      <c r="BF22" s="4"/>
+      <c r="BG22" s="4"/>
+      <c r="BH22" s="4"/>
+      <c r="BI22" s="4"/>
+      <c r="BJ22" s="4"/>
+      <c r="BK22" s="4"/>
+      <c r="BL22" s="4"/>
+      <c r="BM22" s="4"/>
+      <c r="BN22" s="4"/>
+      <c r="BO22" s="4"/>
+      <c r="BP22" s="4"/>
+      <c r="BQ22" s="4"/>
+      <c r="BR22" s="4"/>
+      <c r="BS22" s="4"/>
+      <c r="BT22" s="4"/>
+      <c r="BU22" s="4"/>
+      <c r="BV22" s="4"/>
+      <c r="BW22" s="4"/>
+      <c r="BX22" s="4"/>
+      <c r="BY22" s="4"/>
+      <c r="BZ22" s="4"/>
+      <c r="CA22" s="4"/>
+      <c r="CB22" s="4"/>
+      <c r="CC22" s="4"/>
+      <c r="CD22" s="4"/>
+      <c r="CE22" s="4"/>
+      <c r="CF22" s="4"/>
+      <c r="CG22" s="4"/>
+      <c r="CH22" s="4"/>
+      <c r="CI22" s="4"/>
+      <c r="CJ22" s="4"/>
+      <c r="CK22" s="4"/>
+      <c r="CL22" s="4"/>
+      <c r="CM22" s="4"/>
+      <c r="CN22" s="4"/>
+      <c r="CO22" s="4"/>
+      <c r="CP22" s="4"/>
+      <c r="CQ22" s="4"/>
+      <c r="CR22" s="4"/>
+      <c r="CS22" s="4"/>
+      <c r="CT22" s="4"/>
+      <c r="CU22" s="4"/>
+      <c r="CV22" s="4"/>
+      <c r="CW22" s="4"/>
+      <c r="CX22" s="4"/>
+      <c r="CY22" s="4"/>
+      <c r="CZ22" s="4"/>
+      <c r="DA22" s="4"/>
+      <c r="DB22" s="4"/>
+      <c r="DC22" s="4"/>
+      <c r="DD22" s="4"/>
+      <c r="DE22" s="4"/>
+      <c r="DF22" s="4"/>
+      <c r="DG22" s="4"/>
+      <c r="DH22" s="4"/>
+      <c r="DI22" s="4"/>
+      <c r="DJ22" s="4"/>
+      <c r="DK22" s="4"/>
+      <c r="DL22" s="4"/>
+      <c r="DM22" s="4"/>
+      <c r="DN22" s="4"/>
+      <c r="DO22" s="4"/>
+      <c r="DP22" s="4"/>
+      <c r="DQ22" s="4"/>
+      <c r="DR22" s="4"/>
+      <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -5242,7 +5356,7 @@
       <c r="I23" t="s">
         <v>5</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="J23" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K23" t="s">
@@ -5353,83 +5467,88 @@
       <c r="AT23" t="s">
         <v>5</v>
       </c>
-      <c r="AU23" s="2"/>
-      <c r="AV23" s="2"/>
-      <c r="AW23" s="2"/>
-      <c r="AZ23" s="5"/>
-      <c r="BA23" s="5"/>
-      <c r="BB23" s="5"/>
-      <c r="BC23" s="5"/>
-      <c r="BD23" s="5"/>
-      <c r="BE23" s="5"/>
-      <c r="BF23" s="5"/>
-      <c r="BG23" s="5"/>
-      <c r="BH23" s="5"/>
-      <c r="BI23" s="5"/>
-      <c r="BJ23" s="5"/>
-      <c r="BK23" s="5"/>
-      <c r="BL23" s="5"/>
-      <c r="BM23" s="5"/>
-      <c r="BN23" s="5"/>
-      <c r="BO23" s="5"/>
-      <c r="BP23" s="5"/>
-      <c r="BQ23" s="5"/>
-      <c r="BR23" s="5"/>
-      <c r="BS23" s="5"/>
-      <c r="BT23" s="5"/>
-      <c r="BU23" s="5"/>
-      <c r="BV23" s="5"/>
-      <c r="BW23" s="5"/>
-      <c r="BX23" s="5"/>
-      <c r="BY23" s="5"/>
-      <c r="BZ23" s="5"/>
-      <c r="CA23" s="5"/>
-      <c r="CB23" s="5"/>
-      <c r="CC23" s="5"/>
-      <c r="CD23" s="5"/>
-      <c r="CE23" s="5"/>
-      <c r="CF23" s="5"/>
-      <c r="CG23" s="5"/>
-      <c r="CH23" s="5"/>
-      <c r="CI23" s="5"/>
-      <c r="CJ23" s="5"/>
-      <c r="CK23" s="5"/>
-      <c r="CL23" s="5"/>
-      <c r="CM23" s="5"/>
-      <c r="CN23" s="5"/>
-      <c r="CO23" s="5"/>
-      <c r="CP23" s="5"/>
-      <c r="CQ23" s="5"/>
-      <c r="CR23" s="5"/>
-      <c r="CS23" s="5"/>
-      <c r="CT23" s="5"/>
-      <c r="CU23" s="5"/>
-      <c r="CV23" s="5"/>
-      <c r="CW23" s="5"/>
-      <c r="CX23" s="5"/>
-      <c r="CY23" s="5"/>
-      <c r="CZ23" s="5"/>
-      <c r="DA23" s="5"/>
-      <c r="DB23" s="5"/>
-      <c r="DC23" s="5"/>
-      <c r="DD23" s="5"/>
-      <c r="DE23" s="5"/>
-      <c r="DF23" s="5"/>
-      <c r="DG23" s="5"/>
-      <c r="DH23" s="5"/>
-      <c r="DI23" s="5"/>
-      <c r="DJ23" s="5"/>
-      <c r="DK23" s="5"/>
-      <c r="DL23" s="5"/>
-      <c r="DM23" s="5"/>
-      <c r="DN23" s="5"/>
-      <c r="DO23" s="5"/>
-      <c r="DP23" s="5"/>
-      <c r="DQ23" s="5"/>
-      <c r="DR23" s="5"/>
-      <c r="DS23" s="5"/>
+      <c r="AU23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW23" s="4"/>
+      <c r="AX23" s="4"/>
+      <c r="AZ23" s="4"/>
+      <c r="BA23" s="4"/>
+      <c r="BB23" s="4"/>
+      <c r="BC23" s="4"/>
+      <c r="BD23" s="4"/>
+      <c r="BE23" s="4"/>
+      <c r="BF23" s="4"/>
+      <c r="BG23" s="4"/>
+      <c r="BH23" s="4"/>
+      <c r="BI23" s="4"/>
+      <c r="BJ23" s="4"/>
+      <c r="BK23" s="4"/>
+      <c r="BL23" s="4"/>
+      <c r="BM23" s="4"/>
+      <c r="BN23" s="4"/>
+      <c r="BO23" s="4"/>
+      <c r="BP23" s="4"/>
+      <c r="BQ23" s="4"/>
+      <c r="BR23" s="4"/>
+      <c r="BS23" s="4"/>
+      <c r="BT23" s="4"/>
+      <c r="BU23" s="4"/>
+      <c r="BV23" s="4"/>
+      <c r="BW23" s="4"/>
+      <c r="BX23" s="4"/>
+      <c r="BY23" s="4"/>
+      <c r="BZ23" s="4"/>
+      <c r="CA23" s="4"/>
+      <c r="CB23" s="4"/>
+      <c r="CC23" s="4"/>
+      <c r="CD23" s="4"/>
+      <c r="CE23" s="4"/>
+      <c r="CF23" s="4"/>
+      <c r="CG23" s="4"/>
+      <c r="CH23" s="4"/>
+      <c r="CI23" s="4"/>
+      <c r="CJ23" s="4"/>
+      <c r="CK23" s="4"/>
+      <c r="CL23" s="4"/>
+      <c r="CM23" s="4"/>
+      <c r="CN23" s="4"/>
+      <c r="CO23" s="4"/>
+      <c r="CP23" s="4"/>
+      <c r="CQ23" s="4"/>
+      <c r="CR23" s="4"/>
+      <c r="CS23" s="4"/>
+      <c r="CT23" s="4"/>
+      <c r="CU23" s="4"/>
+      <c r="CV23" s="4"/>
+      <c r="CW23" s="4"/>
+      <c r="CX23" s="4"/>
+      <c r="CY23" s="4"/>
+      <c r="CZ23" s="4"/>
+      <c r="DA23" s="4"/>
+      <c r="DB23" s="4"/>
+      <c r="DC23" s="4"/>
+      <c r="DD23" s="4"/>
+      <c r="DE23" s="4"/>
+      <c r="DF23" s="4"/>
+      <c r="DG23" s="4"/>
+      <c r="DH23" s="4"/>
+      <c r="DI23" s="4"/>
+      <c r="DJ23" s="4"/>
+      <c r="DK23" s="4"/>
+      <c r="DL23" s="4"/>
+      <c r="DM23" s="4"/>
+      <c r="DN23" s="4"/>
+      <c r="DO23" s="4"/>
+      <c r="DP23" s="4"/>
+      <c r="DQ23" s="4"/>
+      <c r="DR23" s="4"/>
+      <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -5439,7 +5558,7 @@
       <c r="C24">
         <v>22</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="7" t="s">
         <v>40</v>
       </c>
       <c r="L24" t="s">
@@ -5547,83 +5666,88 @@
       <c r="AT24" t="s">
         <v>5</v>
       </c>
-      <c r="AU24" s="2"/>
-      <c r="AV24" s="2"/>
-      <c r="AW24" s="2"/>
-      <c r="AZ24" s="5"/>
-      <c r="BA24" s="5"/>
-      <c r="BB24" s="5"/>
-      <c r="BC24" s="5"/>
-      <c r="BD24" s="5"/>
-      <c r="BE24" s="5"/>
-      <c r="BF24" s="5"/>
-      <c r="BG24" s="5"/>
-      <c r="BH24" s="5"/>
-      <c r="BI24" s="5"/>
-      <c r="BJ24" s="5"/>
-      <c r="BK24" s="5"/>
-      <c r="BL24" s="5"/>
-      <c r="BM24" s="5"/>
-      <c r="BN24" s="5"/>
-      <c r="BO24" s="5"/>
-      <c r="BP24" s="5"/>
-      <c r="BQ24" s="5"/>
-      <c r="BR24" s="5"/>
-      <c r="BS24" s="5"/>
-      <c r="BT24" s="5"/>
-      <c r="BU24" s="5"/>
-      <c r="BV24" s="5"/>
-      <c r="BW24" s="5"/>
-      <c r="BX24" s="5"/>
-      <c r="BY24" s="5"/>
-      <c r="BZ24" s="5"/>
-      <c r="CA24" s="5"/>
-      <c r="CB24" s="5"/>
-      <c r="CC24" s="5"/>
-      <c r="CD24" s="5"/>
-      <c r="CE24" s="5"/>
-      <c r="CF24" s="5"/>
-      <c r="CG24" s="5"/>
-      <c r="CH24" s="5"/>
-      <c r="CI24" s="5"/>
-      <c r="CJ24" s="5"/>
-      <c r="CK24" s="5"/>
-      <c r="CL24" s="5"/>
-      <c r="CM24" s="5"/>
-      <c r="CN24" s="5"/>
-      <c r="CO24" s="5"/>
-      <c r="CP24" s="5"/>
-      <c r="CQ24" s="5"/>
-      <c r="CR24" s="5"/>
-      <c r="CS24" s="5"/>
-      <c r="CT24" s="5"/>
-      <c r="CU24" s="5"/>
-      <c r="CV24" s="5"/>
-      <c r="CW24" s="5"/>
-      <c r="CX24" s="5"/>
-      <c r="CY24" s="5"/>
-      <c r="CZ24" s="5"/>
-      <c r="DA24" s="5"/>
-      <c r="DB24" s="5"/>
-      <c r="DC24" s="5"/>
-      <c r="DD24" s="5"/>
-      <c r="DE24" s="5"/>
-      <c r="DF24" s="5"/>
-      <c r="DG24" s="5"/>
-      <c r="DH24" s="5"/>
-      <c r="DI24" s="5"/>
-      <c r="DJ24" s="5"/>
-      <c r="DK24" s="5"/>
-      <c r="DL24" s="5"/>
-      <c r="DM24" s="5"/>
-      <c r="DN24" s="5"/>
-      <c r="DO24" s="5"/>
-      <c r="DP24" s="5"/>
-      <c r="DQ24" s="5"/>
-      <c r="DR24" s="5"/>
-      <c r="DS24" s="5"/>
+      <c r="AU24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW24" s="4"/>
+      <c r="AX24" s="4"/>
+      <c r="AZ24" s="4"/>
+      <c r="BA24" s="4"/>
+      <c r="BB24" s="4"/>
+      <c r="BC24" s="4"/>
+      <c r="BD24" s="4"/>
+      <c r="BE24" s="4"/>
+      <c r="BF24" s="4"/>
+      <c r="BG24" s="4"/>
+      <c r="BH24" s="4"/>
+      <c r="BI24" s="4"/>
+      <c r="BJ24" s="4"/>
+      <c r="BK24" s="4"/>
+      <c r="BL24" s="4"/>
+      <c r="BM24" s="4"/>
+      <c r="BN24" s="4"/>
+      <c r="BO24" s="4"/>
+      <c r="BP24" s="4"/>
+      <c r="BQ24" s="4"/>
+      <c r="BR24" s="4"/>
+      <c r="BS24" s="4"/>
+      <c r="BT24" s="4"/>
+      <c r="BU24" s="4"/>
+      <c r="BV24" s="4"/>
+      <c r="BW24" s="4"/>
+      <c r="BX24" s="4"/>
+      <c r="BY24" s="4"/>
+      <c r="BZ24" s="4"/>
+      <c r="CA24" s="4"/>
+      <c r="CB24" s="4"/>
+      <c r="CC24" s="4"/>
+      <c r="CD24" s="4"/>
+      <c r="CE24" s="4"/>
+      <c r="CF24" s="4"/>
+      <c r="CG24" s="4"/>
+      <c r="CH24" s="4"/>
+      <c r="CI24" s="4"/>
+      <c r="CJ24" s="4"/>
+      <c r="CK24" s="4"/>
+      <c r="CL24" s="4"/>
+      <c r="CM24" s="4"/>
+      <c r="CN24" s="4"/>
+      <c r="CO24" s="4"/>
+      <c r="CP24" s="4"/>
+      <c r="CQ24" s="4"/>
+      <c r="CR24" s="4"/>
+      <c r="CS24" s="4"/>
+      <c r="CT24" s="4"/>
+      <c r="CU24" s="4"/>
+      <c r="CV24" s="4"/>
+      <c r="CW24" s="4"/>
+      <c r="CX24" s="4"/>
+      <c r="CY24" s="4"/>
+      <c r="CZ24" s="4"/>
+      <c r="DA24" s="4"/>
+      <c r="DB24" s="4"/>
+      <c r="DC24" s="4"/>
+      <c r="DD24" s="4"/>
+      <c r="DE24" s="4"/>
+      <c r="DF24" s="4"/>
+      <c r="DG24" s="4"/>
+      <c r="DH24" s="4"/>
+      <c r="DI24" s="4"/>
+      <c r="DJ24" s="4"/>
+      <c r="DK24" s="4"/>
+      <c r="DL24" s="4"/>
+      <c r="DM24" s="4"/>
+      <c r="DN24" s="4"/>
+      <c r="DO24" s="4"/>
+      <c r="DP24" s="4"/>
+      <c r="DQ24" s="4"/>
+      <c r="DR24" s="4"/>
+      <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -5651,7 +5775,7 @@
       <c r="I25" t="s">
         <v>5</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="J25" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K25" t="s">
@@ -5762,83 +5886,88 @@
       <c r="AT25" t="s">
         <v>5</v>
       </c>
-      <c r="AU25" s="2"/>
-      <c r="AV25" s="2"/>
-      <c r="AW25" s="2"/>
-      <c r="AZ25" s="5"/>
-      <c r="BA25" s="5"/>
-      <c r="BB25" s="5"/>
-      <c r="BC25" s="5"/>
-      <c r="BD25" s="5"/>
-      <c r="BE25" s="5"/>
-      <c r="BF25" s="5"/>
-      <c r="BG25" s="5"/>
-      <c r="BH25" s="5"/>
-      <c r="BI25" s="5"/>
-      <c r="BJ25" s="5"/>
-      <c r="BK25" s="5"/>
-      <c r="BL25" s="5"/>
-      <c r="BM25" s="5"/>
-      <c r="BN25" s="5"/>
-      <c r="BO25" s="5"/>
-      <c r="BP25" s="5"/>
-      <c r="BQ25" s="5"/>
-      <c r="BR25" s="5"/>
-      <c r="BS25" s="5"/>
-      <c r="BT25" s="5"/>
-      <c r="BU25" s="5"/>
-      <c r="BV25" s="5"/>
-      <c r="BW25" s="5"/>
-      <c r="BX25" s="5"/>
-      <c r="BY25" s="5"/>
-      <c r="BZ25" s="5"/>
-      <c r="CA25" s="5"/>
-      <c r="CB25" s="5"/>
-      <c r="CC25" s="5"/>
-      <c r="CD25" s="5"/>
-      <c r="CE25" s="5"/>
-      <c r="CF25" s="5"/>
-      <c r="CG25" s="5"/>
-      <c r="CH25" s="5"/>
-      <c r="CI25" s="5"/>
-      <c r="CJ25" s="5"/>
-      <c r="CK25" s="5"/>
-      <c r="CL25" s="5"/>
-      <c r="CM25" s="5"/>
-      <c r="CN25" s="5"/>
-      <c r="CO25" s="5"/>
-      <c r="CP25" s="5"/>
-      <c r="CQ25" s="5"/>
-      <c r="CR25" s="5"/>
-      <c r="CS25" s="5"/>
-      <c r="CT25" s="5"/>
-      <c r="CU25" s="5"/>
-      <c r="CV25" s="5"/>
-      <c r="CW25" s="5"/>
-      <c r="CX25" s="5"/>
-      <c r="CY25" s="5"/>
-      <c r="CZ25" s="5"/>
-      <c r="DA25" s="5"/>
-      <c r="DB25" s="5"/>
-      <c r="DC25" s="5"/>
-      <c r="DD25" s="5"/>
-      <c r="DE25" s="5"/>
-      <c r="DF25" s="5"/>
-      <c r="DG25" s="5"/>
-      <c r="DH25" s="5"/>
-      <c r="DI25" s="5"/>
-      <c r="DJ25" s="5"/>
-      <c r="DK25" s="5"/>
-      <c r="DL25" s="5"/>
-      <c r="DM25" s="5"/>
-      <c r="DN25" s="5"/>
-      <c r="DO25" s="5"/>
-      <c r="DP25" s="5"/>
-      <c r="DQ25" s="5"/>
-      <c r="DR25" s="5"/>
-      <c r="DS25" s="5"/>
+      <c r="AU25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW25" s="4"/>
+      <c r="AX25" s="4"/>
+      <c r="AZ25" s="4"/>
+      <c r="BA25" s="4"/>
+      <c r="BB25" s="4"/>
+      <c r="BC25" s="4"/>
+      <c r="BD25" s="4"/>
+      <c r="BE25" s="4"/>
+      <c r="BF25" s="4"/>
+      <c r="BG25" s="4"/>
+      <c r="BH25" s="4"/>
+      <c r="BI25" s="4"/>
+      <c r="BJ25" s="4"/>
+      <c r="BK25" s="4"/>
+      <c r="BL25" s="4"/>
+      <c r="BM25" s="4"/>
+      <c r="BN25" s="4"/>
+      <c r="BO25" s="4"/>
+      <c r="BP25" s="4"/>
+      <c r="BQ25" s="4"/>
+      <c r="BR25" s="4"/>
+      <c r="BS25" s="4"/>
+      <c r="BT25" s="4"/>
+      <c r="BU25" s="4"/>
+      <c r="BV25" s="4"/>
+      <c r="BW25" s="4"/>
+      <c r="BX25" s="4"/>
+      <c r="BY25" s="4"/>
+      <c r="BZ25" s="4"/>
+      <c r="CA25" s="4"/>
+      <c r="CB25" s="4"/>
+      <c r="CC25" s="4"/>
+      <c r="CD25" s="4"/>
+      <c r="CE25" s="4"/>
+      <c r="CF25" s="4"/>
+      <c r="CG25" s="4"/>
+      <c r="CH25" s="4"/>
+      <c r="CI25" s="4"/>
+      <c r="CJ25" s="4"/>
+      <c r="CK25" s="4"/>
+      <c r="CL25" s="4"/>
+      <c r="CM25" s="4"/>
+      <c r="CN25" s="4"/>
+      <c r="CO25" s="4"/>
+      <c r="CP25" s="4"/>
+      <c r="CQ25" s="4"/>
+      <c r="CR25" s="4"/>
+      <c r="CS25" s="4"/>
+      <c r="CT25" s="4"/>
+      <c r="CU25" s="4"/>
+      <c r="CV25" s="4"/>
+      <c r="CW25" s="4"/>
+      <c r="CX25" s="4"/>
+      <c r="CY25" s="4"/>
+      <c r="CZ25" s="4"/>
+      <c r="DA25" s="4"/>
+      <c r="DB25" s="4"/>
+      <c r="DC25" s="4"/>
+      <c r="DD25" s="4"/>
+      <c r="DE25" s="4"/>
+      <c r="DF25" s="4"/>
+      <c r="DG25" s="4"/>
+      <c r="DH25" s="4"/>
+      <c r="DI25" s="4"/>
+      <c r="DJ25" s="4"/>
+      <c r="DK25" s="4"/>
+      <c r="DL25" s="4"/>
+      <c r="DM25" s="4"/>
+      <c r="DN25" s="4"/>
+      <c r="DO25" s="4"/>
+      <c r="DP25" s="4"/>
+      <c r="DQ25" s="4"/>
+      <c r="DR25" s="4"/>
+      <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -5866,7 +5995,7 @@
       <c r="I26" t="s">
         <v>5</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="J26" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K26" t="s">
@@ -5977,83 +6106,88 @@
       <c r="AT26" t="s">
         <v>5</v>
       </c>
-      <c r="AU26" s="2"/>
-      <c r="AV26" s="2"/>
-      <c r="AW26" s="2"/>
-      <c r="AZ26" s="5"/>
-      <c r="BA26" s="5"/>
-      <c r="BB26" s="5"/>
-      <c r="BC26" s="5"/>
-      <c r="BD26" s="5"/>
-      <c r="BE26" s="5"/>
-      <c r="BF26" s="5"/>
-      <c r="BG26" s="5"/>
-      <c r="BH26" s="5"/>
-      <c r="BI26" s="5"/>
-      <c r="BJ26" s="5"/>
-      <c r="BK26" s="5"/>
-      <c r="BL26" s="5"/>
-      <c r="BM26" s="5"/>
-      <c r="BN26" s="5"/>
-      <c r="BO26" s="5"/>
-      <c r="BP26" s="5"/>
-      <c r="BQ26" s="5"/>
-      <c r="BR26" s="5"/>
-      <c r="BS26" s="5"/>
-      <c r="BT26" s="5"/>
-      <c r="BU26" s="5"/>
-      <c r="BV26" s="5"/>
-      <c r="BW26" s="5"/>
-      <c r="BX26" s="5"/>
-      <c r="BY26" s="5"/>
-      <c r="BZ26" s="5"/>
-      <c r="CA26" s="5"/>
-      <c r="CB26" s="5"/>
-      <c r="CC26" s="5"/>
-      <c r="CD26" s="5"/>
-      <c r="CE26" s="5"/>
-      <c r="CF26" s="5"/>
-      <c r="CG26" s="5"/>
-      <c r="CH26" s="5"/>
-      <c r="CI26" s="5"/>
-      <c r="CJ26" s="5"/>
-      <c r="CK26" s="5"/>
-      <c r="CL26" s="5"/>
-      <c r="CM26" s="5"/>
-      <c r="CN26" s="5"/>
-      <c r="CO26" s="5"/>
-      <c r="CP26" s="5"/>
-      <c r="CQ26" s="5"/>
-      <c r="CR26" s="5"/>
-      <c r="CS26" s="5"/>
-      <c r="CT26" s="5"/>
-      <c r="CU26" s="5"/>
-      <c r="CV26" s="5"/>
-      <c r="CW26" s="5"/>
-      <c r="CX26" s="5"/>
-      <c r="CY26" s="5"/>
-      <c r="CZ26" s="5"/>
-      <c r="DA26" s="5"/>
-      <c r="DB26" s="5"/>
-      <c r="DC26" s="5"/>
-      <c r="DD26" s="5"/>
-      <c r="DE26" s="5"/>
-      <c r="DF26" s="5"/>
-      <c r="DG26" s="5"/>
-      <c r="DH26" s="5"/>
-      <c r="DI26" s="5"/>
-      <c r="DJ26" s="5"/>
-      <c r="DK26" s="5"/>
-      <c r="DL26" s="5"/>
-      <c r="DM26" s="5"/>
-      <c r="DN26" s="5"/>
-      <c r="DO26" s="5"/>
-      <c r="DP26" s="5"/>
-      <c r="DQ26" s="5"/>
-      <c r="DR26" s="5"/>
-      <c r="DS26" s="5"/>
+      <c r="AU26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW26" s="4"/>
+      <c r="AX26" s="4"/>
+      <c r="AZ26" s="4"/>
+      <c r="BA26" s="4"/>
+      <c r="BB26" s="4"/>
+      <c r="BC26" s="4"/>
+      <c r="BD26" s="4"/>
+      <c r="BE26" s="4"/>
+      <c r="BF26" s="4"/>
+      <c r="BG26" s="4"/>
+      <c r="BH26" s="4"/>
+      <c r="BI26" s="4"/>
+      <c r="BJ26" s="4"/>
+      <c r="BK26" s="4"/>
+      <c r="BL26" s="4"/>
+      <c r="BM26" s="4"/>
+      <c r="BN26" s="4"/>
+      <c r="BO26" s="4"/>
+      <c r="BP26" s="4"/>
+      <c r="BQ26" s="4"/>
+      <c r="BR26" s="4"/>
+      <c r="BS26" s="4"/>
+      <c r="BT26" s="4"/>
+      <c r="BU26" s="4"/>
+      <c r="BV26" s="4"/>
+      <c r="BW26" s="4"/>
+      <c r="BX26" s="4"/>
+      <c r="BY26" s="4"/>
+      <c r="BZ26" s="4"/>
+      <c r="CA26" s="4"/>
+      <c r="CB26" s="4"/>
+      <c r="CC26" s="4"/>
+      <c r="CD26" s="4"/>
+      <c r="CE26" s="4"/>
+      <c r="CF26" s="4"/>
+      <c r="CG26" s="4"/>
+      <c r="CH26" s="4"/>
+      <c r="CI26" s="4"/>
+      <c r="CJ26" s="4"/>
+      <c r="CK26" s="4"/>
+      <c r="CL26" s="4"/>
+      <c r="CM26" s="4"/>
+      <c r="CN26" s="4"/>
+      <c r="CO26" s="4"/>
+      <c r="CP26" s="4"/>
+      <c r="CQ26" s="4"/>
+      <c r="CR26" s="4"/>
+      <c r="CS26" s="4"/>
+      <c r="CT26" s="4"/>
+      <c r="CU26" s="4"/>
+      <c r="CV26" s="4"/>
+      <c r="CW26" s="4"/>
+      <c r="CX26" s="4"/>
+      <c r="CY26" s="4"/>
+      <c r="CZ26" s="4"/>
+      <c r="DA26" s="4"/>
+      <c r="DB26" s="4"/>
+      <c r="DC26" s="4"/>
+      <c r="DD26" s="4"/>
+      <c r="DE26" s="4"/>
+      <c r="DF26" s="4"/>
+      <c r="DG26" s="4"/>
+      <c r="DH26" s="4"/>
+      <c r="DI26" s="4"/>
+      <c r="DJ26" s="4"/>
+      <c r="DK26" s="4"/>
+      <c r="DL26" s="4"/>
+      <c r="DM26" s="4"/>
+      <c r="DN26" s="4"/>
+      <c r="DO26" s="4"/>
+      <c r="DP26" s="4"/>
+      <c r="DQ26" s="4"/>
+      <c r="DR26" s="4"/>
+      <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -6081,7 +6215,7 @@
       <c r="I27" t="s">
         <v>5</v>
       </c>
-      <c r="J27" s="8" t="s">
+      <c r="J27" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K27" t="s">
@@ -6192,83 +6326,88 @@
       <c r="AT27" t="s">
         <v>5</v>
       </c>
-      <c r="AU27" s="2"/>
-      <c r="AV27" s="2"/>
-      <c r="AW27" s="2"/>
-      <c r="AZ27" s="5"/>
-      <c r="BA27" s="5"/>
-      <c r="BB27" s="5"/>
-      <c r="BC27" s="5"/>
-      <c r="BD27" s="5"/>
-      <c r="BE27" s="5"/>
-      <c r="BF27" s="5"/>
-      <c r="BG27" s="5"/>
-      <c r="BH27" s="5"/>
-      <c r="BI27" s="5"/>
-      <c r="BJ27" s="5"/>
-      <c r="BK27" s="5"/>
-      <c r="BL27" s="5"/>
-      <c r="BM27" s="5"/>
-      <c r="BN27" s="5"/>
-      <c r="BO27" s="5"/>
-      <c r="BP27" s="5"/>
-      <c r="BQ27" s="5"/>
-      <c r="BR27" s="5"/>
-      <c r="BS27" s="5"/>
-      <c r="BT27" s="5"/>
-      <c r="BU27" s="5"/>
-      <c r="BV27" s="5"/>
-      <c r="BW27" s="5"/>
-      <c r="BX27" s="5"/>
-      <c r="BY27" s="5"/>
-      <c r="BZ27" s="5"/>
-      <c r="CA27" s="5"/>
-      <c r="CB27" s="5"/>
-      <c r="CC27" s="5"/>
-      <c r="CD27" s="5"/>
-      <c r="CE27" s="5"/>
-      <c r="CF27" s="5"/>
-      <c r="CG27" s="5"/>
-      <c r="CH27" s="5"/>
-      <c r="CI27" s="5"/>
-      <c r="CJ27" s="5"/>
-      <c r="CK27" s="5"/>
-      <c r="CL27" s="5"/>
-      <c r="CM27" s="5"/>
-      <c r="CN27" s="5"/>
-      <c r="CO27" s="5"/>
-      <c r="CP27" s="5"/>
-      <c r="CQ27" s="5"/>
-      <c r="CR27" s="5"/>
-      <c r="CS27" s="5"/>
-      <c r="CT27" s="5"/>
-      <c r="CU27" s="5"/>
-      <c r="CV27" s="5"/>
-      <c r="CW27" s="5"/>
-      <c r="CX27" s="5"/>
-      <c r="CY27" s="5"/>
-      <c r="CZ27" s="5"/>
-      <c r="DA27" s="5"/>
-      <c r="DB27" s="5"/>
-      <c r="DC27" s="5"/>
-      <c r="DD27" s="5"/>
-      <c r="DE27" s="5"/>
-      <c r="DF27" s="5"/>
-      <c r="DG27" s="5"/>
-      <c r="DH27" s="5"/>
-      <c r="DI27" s="5"/>
-      <c r="DJ27" s="5"/>
-      <c r="DK27" s="5"/>
-      <c r="DL27" s="5"/>
-      <c r="DM27" s="5"/>
-      <c r="DN27" s="5"/>
-      <c r="DO27" s="5"/>
-      <c r="DP27" s="5"/>
-      <c r="DQ27" s="5"/>
-      <c r="DR27" s="5"/>
-      <c r="DS27" s="5"/>
+      <c r="AU27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW27" s="4"/>
+      <c r="AX27" s="4"/>
+      <c r="AZ27" s="4"/>
+      <c r="BA27" s="4"/>
+      <c r="BB27" s="4"/>
+      <c r="BC27" s="4"/>
+      <c r="BD27" s="4"/>
+      <c r="BE27" s="4"/>
+      <c r="BF27" s="4"/>
+      <c r="BG27" s="4"/>
+      <c r="BH27" s="4"/>
+      <c r="BI27" s="4"/>
+      <c r="BJ27" s="4"/>
+      <c r="BK27" s="4"/>
+      <c r="BL27" s="4"/>
+      <c r="BM27" s="4"/>
+      <c r="BN27" s="4"/>
+      <c r="BO27" s="4"/>
+      <c r="BP27" s="4"/>
+      <c r="BQ27" s="4"/>
+      <c r="BR27" s="4"/>
+      <c r="BS27" s="4"/>
+      <c r="BT27" s="4"/>
+      <c r="BU27" s="4"/>
+      <c r="BV27" s="4"/>
+      <c r="BW27" s="4"/>
+      <c r="BX27" s="4"/>
+      <c r="BY27" s="4"/>
+      <c r="BZ27" s="4"/>
+      <c r="CA27" s="4"/>
+      <c r="CB27" s="4"/>
+      <c r="CC27" s="4"/>
+      <c r="CD27" s="4"/>
+      <c r="CE27" s="4"/>
+      <c r="CF27" s="4"/>
+      <c r="CG27" s="4"/>
+      <c r="CH27" s="4"/>
+      <c r="CI27" s="4"/>
+      <c r="CJ27" s="4"/>
+      <c r="CK27" s="4"/>
+      <c r="CL27" s="4"/>
+      <c r="CM27" s="4"/>
+      <c r="CN27" s="4"/>
+      <c r="CO27" s="4"/>
+      <c r="CP27" s="4"/>
+      <c r="CQ27" s="4"/>
+      <c r="CR27" s="4"/>
+      <c r="CS27" s="4"/>
+      <c r="CT27" s="4"/>
+      <c r="CU27" s="4"/>
+      <c r="CV27" s="4"/>
+      <c r="CW27" s="4"/>
+      <c r="CX27" s="4"/>
+      <c r="CY27" s="4"/>
+      <c r="CZ27" s="4"/>
+      <c r="DA27" s="4"/>
+      <c r="DB27" s="4"/>
+      <c r="DC27" s="4"/>
+      <c r="DD27" s="4"/>
+      <c r="DE27" s="4"/>
+      <c r="DF27" s="4"/>
+      <c r="DG27" s="4"/>
+      <c r="DH27" s="4"/>
+      <c r="DI27" s="4"/>
+      <c r="DJ27" s="4"/>
+      <c r="DK27" s="4"/>
+      <c r="DL27" s="4"/>
+      <c r="DM27" s="4"/>
+      <c r="DN27" s="4"/>
+      <c r="DO27" s="4"/>
+      <c r="DP27" s="4"/>
+      <c r="DQ27" s="4"/>
+      <c r="DR27" s="4"/>
+      <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -6296,7 +6435,7 @@
       <c r="I28" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="J28" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K28" t="s">
@@ -6407,83 +6546,88 @@
       <c r="AT28" t="s">
         <v>5</v>
       </c>
-      <c r="AU28" s="2"/>
-      <c r="AV28" s="2"/>
-      <c r="AW28" s="2"/>
-      <c r="AZ28" s="5"/>
-      <c r="BA28" s="5"/>
-      <c r="BB28" s="5"/>
-      <c r="BC28" s="5"/>
-      <c r="BD28" s="5"/>
-      <c r="BE28" s="5"/>
-      <c r="BF28" s="5"/>
-      <c r="BG28" s="5"/>
-      <c r="BH28" s="5"/>
-      <c r="BI28" s="5"/>
-      <c r="BJ28" s="5"/>
-      <c r="BK28" s="5"/>
-      <c r="BL28" s="5"/>
-      <c r="BM28" s="5"/>
-      <c r="BN28" s="5"/>
-      <c r="BO28" s="5"/>
-      <c r="BP28" s="5"/>
-      <c r="BQ28" s="5"/>
-      <c r="BR28" s="5"/>
-      <c r="BS28" s="5"/>
-      <c r="BT28" s="5"/>
-      <c r="BU28" s="5"/>
-      <c r="BV28" s="5"/>
-      <c r="BW28" s="5"/>
-      <c r="BX28" s="5"/>
-      <c r="BY28" s="5"/>
-      <c r="BZ28" s="5"/>
-      <c r="CA28" s="5"/>
-      <c r="CB28" s="5"/>
-      <c r="CC28" s="5"/>
-      <c r="CD28" s="5"/>
-      <c r="CE28" s="5"/>
-      <c r="CF28" s="5"/>
-      <c r="CG28" s="5"/>
-      <c r="CH28" s="5"/>
-      <c r="CI28" s="5"/>
-      <c r="CJ28" s="5"/>
-      <c r="CK28" s="5"/>
-      <c r="CL28" s="5"/>
-      <c r="CM28" s="5"/>
-      <c r="CN28" s="5"/>
-      <c r="CO28" s="5"/>
-      <c r="CP28" s="5"/>
-      <c r="CQ28" s="5"/>
-      <c r="CR28" s="5"/>
-      <c r="CS28" s="5"/>
-      <c r="CT28" s="5"/>
-      <c r="CU28" s="5"/>
-      <c r="CV28" s="5"/>
-      <c r="CW28" s="5"/>
-      <c r="CX28" s="5"/>
-      <c r="CY28" s="5"/>
-      <c r="CZ28" s="5"/>
-      <c r="DA28" s="5"/>
-      <c r="DB28" s="5"/>
-      <c r="DC28" s="5"/>
-      <c r="DD28" s="5"/>
-      <c r="DE28" s="5"/>
-      <c r="DF28" s="5"/>
-      <c r="DG28" s="5"/>
-      <c r="DH28" s="5"/>
-      <c r="DI28" s="5"/>
-      <c r="DJ28" s="5"/>
-      <c r="DK28" s="5"/>
-      <c r="DL28" s="5"/>
-      <c r="DM28" s="5"/>
-      <c r="DN28" s="5"/>
-      <c r="DO28" s="5"/>
-      <c r="DP28" s="5"/>
-      <c r="DQ28" s="5"/>
-      <c r="DR28" s="5"/>
-      <c r="DS28" s="5"/>
+      <c r="AU28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV28" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW28" s="4"/>
+      <c r="AX28" s="4"/>
+      <c r="AZ28" s="4"/>
+      <c r="BA28" s="4"/>
+      <c r="BB28" s="4"/>
+      <c r="BC28" s="4"/>
+      <c r="BD28" s="4"/>
+      <c r="BE28" s="4"/>
+      <c r="BF28" s="4"/>
+      <c r="BG28" s="4"/>
+      <c r="BH28" s="4"/>
+      <c r="BI28" s="4"/>
+      <c r="BJ28" s="4"/>
+      <c r="BK28" s="4"/>
+      <c r="BL28" s="4"/>
+      <c r="BM28" s="4"/>
+      <c r="BN28" s="4"/>
+      <c r="BO28" s="4"/>
+      <c r="BP28" s="4"/>
+      <c r="BQ28" s="4"/>
+      <c r="BR28" s="4"/>
+      <c r="BS28" s="4"/>
+      <c r="BT28" s="4"/>
+      <c r="BU28" s="4"/>
+      <c r="BV28" s="4"/>
+      <c r="BW28" s="4"/>
+      <c r="BX28" s="4"/>
+      <c r="BY28" s="4"/>
+      <c r="BZ28" s="4"/>
+      <c r="CA28" s="4"/>
+      <c r="CB28" s="4"/>
+      <c r="CC28" s="4"/>
+      <c r="CD28" s="4"/>
+      <c r="CE28" s="4"/>
+      <c r="CF28" s="4"/>
+      <c r="CG28" s="4"/>
+      <c r="CH28" s="4"/>
+      <c r="CI28" s="4"/>
+      <c r="CJ28" s="4"/>
+      <c r="CK28" s="4"/>
+      <c r="CL28" s="4"/>
+      <c r="CM28" s="4"/>
+      <c r="CN28" s="4"/>
+      <c r="CO28" s="4"/>
+      <c r="CP28" s="4"/>
+      <c r="CQ28" s="4"/>
+      <c r="CR28" s="4"/>
+      <c r="CS28" s="4"/>
+      <c r="CT28" s="4"/>
+      <c r="CU28" s="4"/>
+      <c r="CV28" s="4"/>
+      <c r="CW28" s="4"/>
+      <c r="CX28" s="4"/>
+      <c r="CY28" s="4"/>
+      <c r="CZ28" s="4"/>
+      <c r="DA28" s="4"/>
+      <c r="DB28" s="4"/>
+      <c r="DC28" s="4"/>
+      <c r="DD28" s="4"/>
+      <c r="DE28" s="4"/>
+      <c r="DF28" s="4"/>
+      <c r="DG28" s="4"/>
+      <c r="DH28" s="4"/>
+      <c r="DI28" s="4"/>
+      <c r="DJ28" s="4"/>
+      <c r="DK28" s="4"/>
+      <c r="DL28" s="4"/>
+      <c r="DM28" s="4"/>
+      <c r="DN28" s="4"/>
+      <c r="DO28" s="4"/>
+      <c r="DP28" s="4"/>
+      <c r="DQ28" s="4"/>
+      <c r="DR28" s="4"/>
+      <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -6511,7 +6655,7 @@
       <c r="I29" t="s">
         <v>5</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="J29" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K29" t="s">
@@ -6622,83 +6766,88 @@
       <c r="AT29" t="s">
         <v>5</v>
       </c>
-      <c r="AU29" s="2"/>
-      <c r="AV29" s="2"/>
-      <c r="AW29" s="2"/>
-      <c r="AZ29" s="5"/>
-      <c r="BA29" s="5"/>
-      <c r="BB29" s="5"/>
-      <c r="BC29" s="5"/>
-      <c r="BD29" s="5"/>
-      <c r="BE29" s="5"/>
-      <c r="BF29" s="5"/>
-      <c r="BG29" s="5"/>
-      <c r="BH29" s="5"/>
-      <c r="BI29" s="5"/>
-      <c r="BJ29" s="5"/>
-      <c r="BK29" s="5"/>
-      <c r="BL29" s="5"/>
-      <c r="BM29" s="5"/>
-      <c r="BN29" s="5"/>
-      <c r="BO29" s="5"/>
-      <c r="BP29" s="5"/>
-      <c r="BQ29" s="5"/>
-      <c r="BR29" s="5"/>
-      <c r="BS29" s="5"/>
-      <c r="BT29" s="5"/>
-      <c r="BU29" s="5"/>
-      <c r="BV29" s="5"/>
-      <c r="BW29" s="5"/>
-      <c r="BX29" s="5"/>
-      <c r="BY29" s="5"/>
-      <c r="BZ29" s="5"/>
-      <c r="CA29" s="5"/>
-      <c r="CB29" s="5"/>
-      <c r="CC29" s="5"/>
-      <c r="CD29" s="5"/>
-      <c r="CE29" s="5"/>
-      <c r="CF29" s="5"/>
-      <c r="CG29" s="5"/>
-      <c r="CH29" s="5"/>
-      <c r="CI29" s="5"/>
-      <c r="CJ29" s="5"/>
-      <c r="CK29" s="5"/>
-      <c r="CL29" s="5"/>
-      <c r="CM29" s="5"/>
-      <c r="CN29" s="5"/>
-      <c r="CO29" s="5"/>
-      <c r="CP29" s="5"/>
-      <c r="CQ29" s="5"/>
-      <c r="CR29" s="5"/>
-      <c r="CS29" s="5"/>
-      <c r="CT29" s="5"/>
-      <c r="CU29" s="5"/>
-      <c r="CV29" s="5"/>
-      <c r="CW29" s="5"/>
-      <c r="CX29" s="5"/>
-      <c r="CY29" s="5"/>
-      <c r="CZ29" s="5"/>
-      <c r="DA29" s="5"/>
-      <c r="DB29" s="5"/>
-      <c r="DC29" s="5"/>
-      <c r="DD29" s="5"/>
-      <c r="DE29" s="5"/>
-      <c r="DF29" s="5"/>
-      <c r="DG29" s="5"/>
-      <c r="DH29" s="5"/>
-      <c r="DI29" s="5"/>
-      <c r="DJ29" s="5"/>
-      <c r="DK29" s="5"/>
-      <c r="DL29" s="5"/>
-      <c r="DM29" s="5"/>
-      <c r="DN29" s="5"/>
-      <c r="DO29" s="5"/>
-      <c r="DP29" s="5"/>
-      <c r="DQ29" s="5"/>
-      <c r="DR29" s="5"/>
-      <c r="DS29" s="5"/>
+      <c r="AU29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW29" s="4"/>
+      <c r="AX29" s="4"/>
+      <c r="AZ29" s="4"/>
+      <c r="BA29" s="4"/>
+      <c r="BB29" s="4"/>
+      <c r="BC29" s="4"/>
+      <c r="BD29" s="4"/>
+      <c r="BE29" s="4"/>
+      <c r="BF29" s="4"/>
+      <c r="BG29" s="4"/>
+      <c r="BH29" s="4"/>
+      <c r="BI29" s="4"/>
+      <c r="BJ29" s="4"/>
+      <c r="BK29" s="4"/>
+      <c r="BL29" s="4"/>
+      <c r="BM29" s="4"/>
+      <c r="BN29" s="4"/>
+      <c r="BO29" s="4"/>
+      <c r="BP29" s="4"/>
+      <c r="BQ29" s="4"/>
+      <c r="BR29" s="4"/>
+      <c r="BS29" s="4"/>
+      <c r="BT29" s="4"/>
+      <c r="BU29" s="4"/>
+      <c r="BV29" s="4"/>
+      <c r="BW29" s="4"/>
+      <c r="BX29" s="4"/>
+      <c r="BY29" s="4"/>
+      <c r="BZ29" s="4"/>
+      <c r="CA29" s="4"/>
+      <c r="CB29" s="4"/>
+      <c r="CC29" s="4"/>
+      <c r="CD29" s="4"/>
+      <c r="CE29" s="4"/>
+      <c r="CF29" s="4"/>
+      <c r="CG29" s="4"/>
+      <c r="CH29" s="4"/>
+      <c r="CI29" s="4"/>
+      <c r="CJ29" s="4"/>
+      <c r="CK29" s="4"/>
+      <c r="CL29" s="4"/>
+      <c r="CM29" s="4"/>
+      <c r="CN29" s="4"/>
+      <c r="CO29" s="4"/>
+      <c r="CP29" s="4"/>
+      <c r="CQ29" s="4"/>
+      <c r="CR29" s="4"/>
+      <c r="CS29" s="4"/>
+      <c r="CT29" s="4"/>
+      <c r="CU29" s="4"/>
+      <c r="CV29" s="4"/>
+      <c r="CW29" s="4"/>
+      <c r="CX29" s="4"/>
+      <c r="CY29" s="4"/>
+      <c r="CZ29" s="4"/>
+      <c r="DA29" s="4"/>
+      <c r="DB29" s="4"/>
+      <c r="DC29" s="4"/>
+      <c r="DD29" s="4"/>
+      <c r="DE29" s="4"/>
+      <c r="DF29" s="4"/>
+      <c r="DG29" s="4"/>
+      <c r="DH29" s="4"/>
+      <c r="DI29" s="4"/>
+      <c r="DJ29" s="4"/>
+      <c r="DK29" s="4"/>
+      <c r="DL29" s="4"/>
+      <c r="DM29" s="4"/>
+      <c r="DN29" s="4"/>
+      <c r="DO29" s="4"/>
+      <c r="DP29" s="4"/>
+      <c r="DQ29" s="4"/>
+      <c r="DR29" s="4"/>
+      <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -6726,7 +6875,7 @@
       <c r="I30" t="s">
         <v>5</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="J30" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K30" t="s">
@@ -6837,83 +6986,88 @@
       <c r="AT30" t="s">
         <v>5</v>
       </c>
-      <c r="AU30" s="2"/>
-      <c r="AV30" s="2"/>
-      <c r="AW30" s="2"/>
-      <c r="AZ30" s="5"/>
-      <c r="BA30" s="5"/>
-      <c r="BB30" s="5"/>
-      <c r="BC30" s="5"/>
-      <c r="BD30" s="5"/>
-      <c r="BE30" s="5"/>
-      <c r="BF30" s="5"/>
-      <c r="BG30" s="5"/>
-      <c r="BH30" s="5"/>
-      <c r="BI30" s="5"/>
-      <c r="BJ30" s="5"/>
-      <c r="BK30" s="5"/>
-      <c r="BL30" s="5"/>
-      <c r="BM30" s="5"/>
-      <c r="BN30" s="5"/>
-      <c r="BO30" s="5"/>
-      <c r="BP30" s="5"/>
-      <c r="BQ30" s="5"/>
-      <c r="BR30" s="5"/>
-      <c r="BS30" s="5"/>
-      <c r="BT30" s="5"/>
-      <c r="BU30" s="5"/>
-      <c r="BV30" s="5"/>
-      <c r="BW30" s="5"/>
-      <c r="BX30" s="5"/>
-      <c r="BY30" s="5"/>
-      <c r="BZ30" s="5"/>
-      <c r="CA30" s="5"/>
-      <c r="CB30" s="5"/>
-      <c r="CC30" s="5"/>
-      <c r="CD30" s="5"/>
-      <c r="CE30" s="5"/>
-      <c r="CF30" s="5"/>
-      <c r="CG30" s="5"/>
-      <c r="CH30" s="5"/>
-      <c r="CI30" s="5"/>
-      <c r="CJ30" s="5"/>
-      <c r="CK30" s="5"/>
-      <c r="CL30" s="5"/>
-      <c r="CM30" s="5"/>
-      <c r="CN30" s="5"/>
-      <c r="CO30" s="5"/>
-      <c r="CP30" s="5"/>
-      <c r="CQ30" s="5"/>
-      <c r="CR30" s="5"/>
-      <c r="CS30" s="5"/>
-      <c r="CT30" s="5"/>
-      <c r="CU30" s="5"/>
-      <c r="CV30" s="5"/>
-      <c r="CW30" s="5"/>
-      <c r="CX30" s="5"/>
-      <c r="CY30" s="5"/>
-      <c r="CZ30" s="5"/>
-      <c r="DA30" s="5"/>
-      <c r="DB30" s="5"/>
-      <c r="DC30" s="5"/>
-      <c r="DD30" s="5"/>
-      <c r="DE30" s="5"/>
-      <c r="DF30" s="5"/>
-      <c r="DG30" s="5"/>
-      <c r="DH30" s="5"/>
-      <c r="DI30" s="5"/>
-      <c r="DJ30" s="5"/>
-      <c r="DK30" s="5"/>
-      <c r="DL30" s="5"/>
-      <c r="DM30" s="5"/>
-      <c r="DN30" s="5"/>
-      <c r="DO30" s="5"/>
-      <c r="DP30" s="5"/>
-      <c r="DQ30" s="5"/>
-      <c r="DR30" s="5"/>
-      <c r="DS30" s="5"/>
+      <c r="AU30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV30" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW30" s="4"/>
+      <c r="AX30" s="4"/>
+      <c r="AZ30" s="4"/>
+      <c r="BA30" s="4"/>
+      <c r="BB30" s="4"/>
+      <c r="BC30" s="4"/>
+      <c r="BD30" s="4"/>
+      <c r="BE30" s="4"/>
+      <c r="BF30" s="4"/>
+      <c r="BG30" s="4"/>
+      <c r="BH30" s="4"/>
+      <c r="BI30" s="4"/>
+      <c r="BJ30" s="4"/>
+      <c r="BK30" s="4"/>
+      <c r="BL30" s="4"/>
+      <c r="BM30" s="4"/>
+      <c r="BN30" s="4"/>
+      <c r="BO30" s="4"/>
+      <c r="BP30" s="4"/>
+      <c r="BQ30" s="4"/>
+      <c r="BR30" s="4"/>
+      <c r="BS30" s="4"/>
+      <c r="BT30" s="4"/>
+      <c r="BU30" s="4"/>
+      <c r="BV30" s="4"/>
+      <c r="BW30" s="4"/>
+      <c r="BX30" s="4"/>
+      <c r="BY30" s="4"/>
+      <c r="BZ30" s="4"/>
+      <c r="CA30" s="4"/>
+      <c r="CB30" s="4"/>
+      <c r="CC30" s="4"/>
+      <c r="CD30" s="4"/>
+      <c r="CE30" s="4"/>
+      <c r="CF30" s="4"/>
+      <c r="CG30" s="4"/>
+      <c r="CH30" s="4"/>
+      <c r="CI30" s="4"/>
+      <c r="CJ30" s="4"/>
+      <c r="CK30" s="4"/>
+      <c r="CL30" s="4"/>
+      <c r="CM30" s="4"/>
+      <c r="CN30" s="4"/>
+      <c r="CO30" s="4"/>
+      <c r="CP30" s="4"/>
+      <c r="CQ30" s="4"/>
+      <c r="CR30" s="4"/>
+      <c r="CS30" s="4"/>
+      <c r="CT30" s="4"/>
+      <c r="CU30" s="4"/>
+      <c r="CV30" s="4"/>
+      <c r="CW30" s="4"/>
+      <c r="CX30" s="4"/>
+      <c r="CY30" s="4"/>
+      <c r="CZ30" s="4"/>
+      <c r="DA30" s="4"/>
+      <c r="DB30" s="4"/>
+      <c r="DC30" s="4"/>
+      <c r="DD30" s="4"/>
+      <c r="DE30" s="4"/>
+      <c r="DF30" s="4"/>
+      <c r="DG30" s="4"/>
+      <c r="DH30" s="4"/>
+      <c r="DI30" s="4"/>
+      <c r="DJ30" s="4"/>
+      <c r="DK30" s="4"/>
+      <c r="DL30" s="4"/>
+      <c r="DM30" s="4"/>
+      <c r="DN30" s="4"/>
+      <c r="DO30" s="4"/>
+      <c r="DP30" s="4"/>
+      <c r="DQ30" s="4"/>
+      <c r="DR30" s="4"/>
+      <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -6941,7 +7095,7 @@
       <c r="I31" t="s">
         <v>5</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="J31" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K31" t="s">
@@ -7052,83 +7206,88 @@
       <c r="AT31" t="s">
         <v>5</v>
       </c>
-      <c r="AU31" s="2"/>
-      <c r="AV31" s="2"/>
-      <c r="AW31" s="2"/>
-      <c r="AZ31" s="5"/>
-      <c r="BA31" s="5"/>
-      <c r="BB31" s="5"/>
-      <c r="BC31" s="5"/>
-      <c r="BD31" s="5"/>
-      <c r="BE31" s="5"/>
-      <c r="BF31" s="5"/>
-      <c r="BG31" s="5"/>
-      <c r="BH31" s="5"/>
-      <c r="BI31" s="5"/>
-      <c r="BJ31" s="5"/>
-      <c r="BK31" s="5"/>
-      <c r="BL31" s="5"/>
-      <c r="BM31" s="5"/>
-      <c r="BN31" s="5"/>
-      <c r="BO31" s="5"/>
-      <c r="BP31" s="5"/>
-      <c r="BQ31" s="5"/>
-      <c r="BR31" s="5"/>
-      <c r="BS31" s="5"/>
-      <c r="BT31" s="5"/>
-      <c r="BU31" s="5"/>
-      <c r="BV31" s="5"/>
-      <c r="BW31" s="5"/>
-      <c r="BX31" s="5"/>
-      <c r="BY31" s="5"/>
-      <c r="BZ31" s="5"/>
-      <c r="CA31" s="5"/>
-      <c r="CB31" s="5"/>
-      <c r="CC31" s="5"/>
-      <c r="CD31" s="5"/>
-      <c r="CE31" s="5"/>
-      <c r="CF31" s="5"/>
-      <c r="CG31" s="5"/>
-      <c r="CH31" s="5"/>
-      <c r="CI31" s="5"/>
-      <c r="CJ31" s="5"/>
-      <c r="CK31" s="5"/>
-      <c r="CL31" s="5"/>
-      <c r="CM31" s="5"/>
-      <c r="CN31" s="5"/>
-      <c r="CO31" s="5"/>
-      <c r="CP31" s="5"/>
-      <c r="CQ31" s="5"/>
-      <c r="CR31" s="5"/>
-      <c r="CS31" s="5"/>
-      <c r="CT31" s="5"/>
-      <c r="CU31" s="5"/>
-      <c r="CV31" s="5"/>
-      <c r="CW31" s="5"/>
-      <c r="CX31" s="5"/>
-      <c r="CY31" s="5"/>
-      <c r="CZ31" s="5"/>
-      <c r="DA31" s="5"/>
-      <c r="DB31" s="5"/>
-      <c r="DC31" s="5"/>
-      <c r="DD31" s="5"/>
-      <c r="DE31" s="5"/>
-      <c r="DF31" s="5"/>
-      <c r="DG31" s="5"/>
-      <c r="DH31" s="5"/>
-      <c r="DI31" s="5"/>
-      <c r="DJ31" s="5"/>
-      <c r="DK31" s="5"/>
-      <c r="DL31" s="5"/>
-      <c r="DM31" s="5"/>
-      <c r="DN31" s="5"/>
-      <c r="DO31" s="5"/>
-      <c r="DP31" s="5"/>
-      <c r="DQ31" s="5"/>
-      <c r="DR31" s="5"/>
-      <c r="DS31" s="5"/>
+      <c r="AU31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW31" s="4"/>
+      <c r="AX31" s="4"/>
+      <c r="AZ31" s="4"/>
+      <c r="BA31" s="4"/>
+      <c r="BB31" s="4"/>
+      <c r="BC31" s="4"/>
+      <c r="BD31" s="4"/>
+      <c r="BE31" s="4"/>
+      <c r="BF31" s="4"/>
+      <c r="BG31" s="4"/>
+      <c r="BH31" s="4"/>
+      <c r="BI31" s="4"/>
+      <c r="BJ31" s="4"/>
+      <c r="BK31" s="4"/>
+      <c r="BL31" s="4"/>
+      <c r="BM31" s="4"/>
+      <c r="BN31" s="4"/>
+      <c r="BO31" s="4"/>
+      <c r="BP31" s="4"/>
+      <c r="BQ31" s="4"/>
+      <c r="BR31" s="4"/>
+      <c r="BS31" s="4"/>
+      <c r="BT31" s="4"/>
+      <c r="BU31" s="4"/>
+      <c r="BV31" s="4"/>
+      <c r="BW31" s="4"/>
+      <c r="BX31" s="4"/>
+      <c r="BY31" s="4"/>
+      <c r="BZ31" s="4"/>
+      <c r="CA31" s="4"/>
+      <c r="CB31" s="4"/>
+      <c r="CC31" s="4"/>
+      <c r="CD31" s="4"/>
+      <c r="CE31" s="4"/>
+      <c r="CF31" s="4"/>
+      <c r="CG31" s="4"/>
+      <c r="CH31" s="4"/>
+      <c r="CI31" s="4"/>
+      <c r="CJ31" s="4"/>
+      <c r="CK31" s="4"/>
+      <c r="CL31" s="4"/>
+      <c r="CM31" s="4"/>
+      <c r="CN31" s="4"/>
+      <c r="CO31" s="4"/>
+      <c r="CP31" s="4"/>
+      <c r="CQ31" s="4"/>
+      <c r="CR31" s="4"/>
+      <c r="CS31" s="4"/>
+      <c r="CT31" s="4"/>
+      <c r="CU31" s="4"/>
+      <c r="CV31" s="4"/>
+      <c r="CW31" s="4"/>
+      <c r="CX31" s="4"/>
+      <c r="CY31" s="4"/>
+      <c r="CZ31" s="4"/>
+      <c r="DA31" s="4"/>
+      <c r="DB31" s="4"/>
+      <c r="DC31" s="4"/>
+      <c r="DD31" s="4"/>
+      <c r="DE31" s="4"/>
+      <c r="DF31" s="4"/>
+      <c r="DG31" s="4"/>
+      <c r="DH31" s="4"/>
+      <c r="DI31" s="4"/>
+      <c r="DJ31" s="4"/>
+      <c r="DK31" s="4"/>
+      <c r="DL31" s="4"/>
+      <c r="DM31" s="4"/>
+      <c r="DN31" s="4"/>
+      <c r="DO31" s="4"/>
+      <c r="DP31" s="4"/>
+      <c r="DQ31" s="4"/>
+      <c r="DR31" s="4"/>
+      <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -7156,7 +7315,7 @@
       <c r="I32" t="s">
         <v>5</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="J32" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K32" t="s">
@@ -7267,8 +7426,31 @@
       <c r="AT32" t="s">
         <v>5</v>
       </c>
+      <c r="AU32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV32" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW32" s="4"/>
+      <c r="AX32" s="4"/>
+      <c r="AZ32" s="4"/>
+      <c r="BA32" s="4"/>
+      <c r="BB32" s="4"/>
+      <c r="BC32" s="4"/>
+      <c r="BD32" s="4"/>
+      <c r="BE32" s="4"/>
+      <c r="BF32" s="4"/>
+      <c r="BG32" s="4"/>
+      <c r="BH32" s="4"/>
+      <c r="BI32" s="4"/>
+      <c r="BJ32" s="4"/>
+      <c r="BK32" s="4"/>
+      <c r="BL32" s="4"/>
+      <c r="BM32" s="4"/>
+      <c r="BN32" s="4"/>
     </row>
-    <row r="33" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -7296,7 +7478,7 @@
       <c r="I33" t="s">
         <v>5</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="J33" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K33" t="s">
@@ -7407,8 +7589,31 @@
       <c r="AT33" t="s">
         <v>5</v>
       </c>
+      <c r="AU33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV33" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW33" s="4"/>
+      <c r="AX33" s="4"/>
+      <c r="AZ33" s="4"/>
+      <c r="BA33" s="4"/>
+      <c r="BB33" s="4"/>
+      <c r="BC33" s="4"/>
+      <c r="BD33" s="4"/>
+      <c r="BE33" s="4"/>
+      <c r="BF33" s="4"/>
+      <c r="BG33" s="4"/>
+      <c r="BH33" s="4"/>
+      <c r="BI33" s="4"/>
+      <c r="BJ33" s="4"/>
+      <c r="BK33" s="4"/>
+      <c r="BL33" s="4"/>
+      <c r="BM33" s="4"/>
+      <c r="BN33" s="4"/>
     </row>
-    <row r="34" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -7436,7 +7641,7 @@
       <c r="I34" t="s">
         <v>5</v>
       </c>
-      <c r="J34" s="8" t="s">
+      <c r="J34" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K34" t="s">
@@ -7547,13 +7752,36 @@
       <c r="AT34" t="s">
         <v>5</v>
       </c>
+      <c r="AU34" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW34" s="4"/>
+      <c r="AX34" s="4"/>
+      <c r="AZ34" s="4"/>
+      <c r="BA34" s="4"/>
+      <c r="BB34" s="4"/>
+      <c r="BC34" s="4"/>
+      <c r="BD34" s="4"/>
+      <c r="BE34" s="4"/>
+      <c r="BF34" s="4"/>
+      <c r="BG34" s="4"/>
+      <c r="BH34" s="4"/>
+      <c r="BI34" s="4"/>
+      <c r="BJ34" s="4"/>
+      <c r="BK34" s="4"/>
+      <c r="BL34" s="4"/>
+      <c r="BM34" s="4"/>
+      <c r="BN34" s="4"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:N34">
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 BB3:BB22 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 BC11:BJ22 G32:I32 AU23:BJ31 AU11:BA22 AU3:AZ10 O3:AT34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 AV3:AZ10 BB3:BB22 O3:AT34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AV11:BA22 BC11:BJ22 AV23:BJ31 G32:I32 AV32:AV34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -7566,13 +7794,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7580,7 +7808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -7588,7 +7816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -7596,7 +7824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -7604,7 +7832,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -7612,7 +7840,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -7620,7 +7848,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -7628,7 +7856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -7636,7 +7864,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -7644,7 +7872,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -7652,7 +7880,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -7660,7 +7888,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -7668,7 +7896,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -7676,7 +7904,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -7684,7 +7912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -7692,7 +7920,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -7700,7 +7928,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -7708,7 +7936,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -7716,7 +7944,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -7724,7 +7952,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -7732,7 +7960,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -7740,7 +7968,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -7748,7 +7976,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -7756,7 +7984,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -7764,7 +7992,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -7772,7 +8000,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -7780,7 +8008,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -7788,7 +8016,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -7796,7 +8024,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -7804,7 +8032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -7812,7 +8040,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -7820,7 +8048,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -7828,7 +8056,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A108078D-CD4A-48E6-95F3-596BA6A36552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9B790B-79B5-455E-A8FB-AD156B5745E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="48">
   <si>
     <t>TER</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>FÉRIAS</t>
+  </si>
+  <si>
+    <t>QUA</t>
   </si>
 </sst>
 </file>
@@ -721,7 +724,9 @@
       <c r="AV1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AW1" s="1"/>
+      <c r="AW1" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="AX1" s="1"/>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
@@ -911,7 +916,9 @@
       <c r="AV2" s="1">
         <v>46231</v>
       </c>
-      <c r="AW2" s="1"/>
+      <c r="AW2" s="1">
+        <v>46233</v>
+      </c>
       <c r="AX2" s="1"/>
       <c r="AY2" s="1"/>
       <c r="AZ2" s="1"/>
@@ -1100,7 +1107,9 @@
       <c r="AV3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW3" s="4"/>
+      <c r="AW3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX3" s="4"/>
       <c r="AZ3" s="4"/>
       <c r="BA3" s="4"/>
@@ -1320,7 +1329,9 @@
       <c r="AV4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW4" s="4"/>
+      <c r="AW4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX4" s="4"/>
       <c r="AZ4" s="4"/>
       <c r="BA4" s="4"/>
@@ -1540,7 +1551,9 @@
       <c r="AV5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW5" s="4"/>
+      <c r="AW5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX5" s="4"/>
       <c r="AZ5" s="4"/>
       <c r="BA5" s="4"/>
@@ -1760,7 +1773,9 @@
       <c r="AV6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW6" s="4"/>
+      <c r="AW6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX6" s="4"/>
       <c r="AZ6" s="4"/>
       <c r="BA6" s="4"/>
@@ -1962,7 +1977,9 @@
       <c r="AV7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW7" s="4"/>
+      <c r="AW7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX7" s="4"/>
       <c r="AZ7" s="4"/>
       <c r="BA7" s="4"/>
@@ -2182,7 +2199,9 @@
       <c r="AV8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW8" s="4"/>
+      <c r="AW8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX8" s="4"/>
       <c r="AZ8" s="4"/>
       <c r="BA8" s="4"/>
@@ -2402,7 +2421,9 @@
       <c r="AV9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW9" s="4"/>
+      <c r="AW9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX9" s="4"/>
       <c r="AZ9" s="4"/>
       <c r="BA9" s="4"/>
@@ -2622,7 +2643,9 @@
       <c r="AV10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW10" s="4"/>
+      <c r="AW10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX10" s="4"/>
       <c r="AZ10" s="4"/>
       <c r="BA10" s="4"/>
@@ -2842,7 +2865,9 @@
       <c r="AV11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW11" s="4"/>
+      <c r="AW11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX11" s="4"/>
       <c r="AZ11" s="4"/>
       <c r="BA11" s="4"/>
@@ -3062,7 +3087,9 @@
       <c r="AV12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW12" s="4"/>
+      <c r="AW12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX12" s="4"/>
       <c r="AZ12" s="4"/>
       <c r="BA12" s="4"/>
@@ -3273,7 +3300,9 @@
       <c r="AV13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW13" s="4"/>
+      <c r="AW13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX13" s="4"/>
       <c r="AZ13" s="4"/>
       <c r="BA13" s="4"/>
@@ -3493,7 +3522,9 @@
       <c r="AV14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW14" s="4"/>
+      <c r="AW14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX14" s="4"/>
       <c r="AZ14" s="4"/>
       <c r="BA14" s="4"/>
@@ -3713,7 +3744,9 @@
       <c r="AV15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW15" s="4"/>
+      <c r="AW15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX15" s="4"/>
       <c r="AZ15" s="4"/>
       <c r="BA15" s="4"/>
@@ -3933,7 +3966,9 @@
       <c r="AV16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AW16" s="4"/>
+      <c r="AW16" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="AX16" s="4"/>
       <c r="AZ16" s="4"/>
       <c r="BA16" s="4"/>
@@ -4153,7 +4188,9 @@
       <c r="AV17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW17" s="4"/>
+      <c r="AW17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX17" s="4"/>
       <c r="AZ17" s="4"/>
       <c r="BA17" s="4"/>
@@ -4373,7 +4410,9 @@
       <c r="AV18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW18" s="4"/>
+      <c r="AW18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX18" s="4"/>
       <c r="AZ18" s="4"/>
       <c r="BA18" s="4"/>
@@ -4593,7 +4632,9 @@
       <c r="AV19" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AW19" s="4"/>
+      <c r="AW19" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="AX19" s="4"/>
       <c r="AZ19" s="4"/>
       <c r="BA19" s="4"/>
@@ -4813,7 +4854,9 @@
       <c r="AV20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW20" s="4"/>
+      <c r="AW20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX20" s="4"/>
       <c r="AZ20" s="4"/>
       <c r="BA20" s="4"/>
@@ -5033,7 +5076,9 @@
       <c r="AV21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW21" s="4"/>
+      <c r="AW21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX21" s="4"/>
       <c r="AZ21" s="4"/>
       <c r="BA21" s="4"/>
@@ -5253,7 +5298,9 @@
       <c r="AV22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW22" s="4"/>
+      <c r="AW22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX22" s="4"/>
       <c r="AZ22" s="4"/>
       <c r="BA22" s="4"/>
@@ -5473,7 +5520,9 @@
       <c r="AV23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW23" s="4"/>
+      <c r="AW23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX23" s="4"/>
       <c r="AZ23" s="4"/>
       <c r="BA23" s="4"/>
@@ -5672,7 +5721,9 @@
       <c r="AV24" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AW24" s="4"/>
+      <c r="AW24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX24" s="4"/>
       <c r="AZ24" s="4"/>
       <c r="BA24" s="4"/>
@@ -5892,7 +5943,9 @@
       <c r="AV25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW25" s="4"/>
+      <c r="AW25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX25" s="4"/>
       <c r="AZ25" s="4"/>
       <c r="BA25" s="4"/>
@@ -6112,7 +6165,9 @@
       <c r="AV26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW26" s="4"/>
+      <c r="AW26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX26" s="4"/>
       <c r="AZ26" s="4"/>
       <c r="BA26" s="4"/>
@@ -6332,7 +6387,9 @@
       <c r="AV27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW27" s="4"/>
+      <c r="AW27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX27" s="4"/>
       <c r="AZ27" s="4"/>
       <c r="BA27" s="4"/>
@@ -6552,7 +6609,9 @@
       <c r="AV28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW28" s="4"/>
+      <c r="AW28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX28" s="4"/>
       <c r="AZ28" s="4"/>
       <c r="BA28" s="4"/>
@@ -6772,7 +6831,9 @@
       <c r="AV29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW29" s="4"/>
+      <c r="AW29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX29" s="4"/>
       <c r="AZ29" s="4"/>
       <c r="BA29" s="4"/>
@@ -6992,7 +7053,9 @@
       <c r="AV30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW30" s="4"/>
+      <c r="AW30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX30" s="4"/>
       <c r="AZ30" s="4"/>
       <c r="BA30" s="4"/>
@@ -7212,7 +7275,9 @@
       <c r="AV31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW31" s="4"/>
+      <c r="AW31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX31" s="4"/>
       <c r="AZ31" s="4"/>
       <c r="BA31" s="4"/>
@@ -7432,7 +7497,9 @@
       <c r="AV32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW32" s="4"/>
+      <c r="AW32" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX32" s="4"/>
       <c r="AZ32" s="4"/>
       <c r="BA32" s="4"/>
@@ -7595,7 +7662,9 @@
       <c r="AV33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW33" s="4"/>
+      <c r="AW33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX33" s="4"/>
       <c r="AZ33" s="4"/>
       <c r="BA33" s="4"/>
@@ -7758,7 +7827,9 @@
       <c r="AV34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AW34" s="4"/>
+      <c r="AW34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AX34" s="4"/>
       <c r="AZ34" s="4"/>
       <c r="BA34" s="4"/>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9B790B-79B5-455E-A8FB-AD156B5745E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBAB892-E82B-41D2-9D12-93168759329C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="48">
   <si>
     <t>TER</t>
   </si>
@@ -727,7 +727,9 @@
       <c r="AW1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="1"/>
+      <c r="AX1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
       <c r="BA1" s="1"/>
@@ -919,7 +921,9 @@
       <c r="AW2" s="1">
         <v>46233</v>
       </c>
-      <c r="AX2" s="1"/>
+      <c r="AX2" s="1">
+        <v>46238</v>
+      </c>
       <c r="AY2" s="1"/>
       <c r="AZ2" s="1"/>
       <c r="BA2" s="1"/>
@@ -1110,7 +1114,9 @@
       <c r="AW3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX3" s="4"/>
+      <c r="AX3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ3" s="4"/>
       <c r="BA3" s="4"/>
       <c r="BB3" s="4"/>
@@ -1332,7 +1338,9 @@
       <c r="AW4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX4" s="4"/>
+      <c r="AX4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ4" s="4"/>
       <c r="BA4" s="4"/>
       <c r="BB4" s="4"/>
@@ -1554,7 +1562,9 @@
       <c r="AW5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX5" s="4"/>
+      <c r="AX5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ5" s="4"/>
       <c r="BA5" s="4"/>
       <c r="BB5" s="4"/>
@@ -1776,7 +1786,9 @@
       <c r="AW6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX6" s="4"/>
+      <c r="AX6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ6" s="4"/>
       <c r="BA6" s="4"/>
       <c r="BB6" s="4"/>
@@ -1980,7 +1992,9 @@
       <c r="AW7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX7" s="4"/>
+      <c r="AX7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ7" s="4"/>
       <c r="BA7" s="4"/>
       <c r="BB7" s="4"/>
@@ -2202,7 +2216,9 @@
       <c r="AW8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX8" s="4"/>
+      <c r="AX8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ8" s="4"/>
       <c r="BA8" s="4"/>
       <c r="BB8" s="4"/>
@@ -2424,7 +2440,9 @@
       <c r="AW9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX9" s="4"/>
+      <c r="AX9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ9" s="4"/>
       <c r="BA9" s="4"/>
       <c r="BB9" s="4"/>
@@ -2646,7 +2664,9 @@
       <c r="AW10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX10" s="4"/>
+      <c r="AX10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ10" s="4"/>
       <c r="BA10" s="4"/>
       <c r="BB10" s="4"/>
@@ -2868,7 +2888,9 @@
       <c r="AW11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX11" s="4"/>
+      <c r="AX11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ11" s="4"/>
       <c r="BA11" s="4"/>
       <c r="BB11" s="4"/>
@@ -3090,7 +3112,9 @@
       <c r="AW12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX12" s="4"/>
+      <c r="AX12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ12" s="4"/>
       <c r="BA12" s="4"/>
       <c r="BB12" s="4"/>
@@ -3303,7 +3327,9 @@
       <c r="AW13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX13" s="4"/>
+      <c r="AX13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ13" s="4"/>
       <c r="BA13" s="4"/>
       <c r="BB13" s="4"/>
@@ -3525,7 +3551,9 @@
       <c r="AW14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX14" s="4"/>
+      <c r="AX14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ14" s="4"/>
       <c r="BA14" s="4"/>
       <c r="BB14" s="4"/>
@@ -3747,7 +3775,9 @@
       <c r="AW15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX15" s="4"/>
+      <c r="AX15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ15" s="4"/>
       <c r="BA15" s="4"/>
       <c r="BB15" s="4"/>
@@ -3969,7 +3999,9 @@
       <c r="AW16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AX16" s="4"/>
+      <c r="AX16" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="AZ16" s="4"/>
       <c r="BA16" s="4"/>
       <c r="BB16" s="4"/>
@@ -4191,7 +4223,9 @@
       <c r="AW17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX17" s="4"/>
+      <c r="AX17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ17" s="4"/>
       <c r="BA17" s="4"/>
       <c r="BB17" s="4"/>
@@ -4413,7 +4447,9 @@
       <c r="AW18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX18" s="4"/>
+      <c r="AX18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ18" s="4"/>
       <c r="BA18" s="4"/>
       <c r="BB18" s="4"/>
@@ -4635,7 +4671,9 @@
       <c r="AW19" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AX19" s="4"/>
+      <c r="AX19" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="AZ19" s="4"/>
       <c r="BA19" s="4"/>
       <c r="BB19" s="4"/>
@@ -4857,7 +4895,9 @@
       <c r="AW20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX20" s="4"/>
+      <c r="AX20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ20" s="4"/>
       <c r="BA20" s="4"/>
       <c r="BB20" s="4"/>
@@ -5079,7 +5119,9 @@
       <c r="AW21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX21" s="4"/>
+      <c r="AX21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ21" s="4"/>
       <c r="BA21" s="4"/>
       <c r="BB21" s="4"/>
@@ -5301,7 +5343,9 @@
       <c r="AW22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX22" s="4"/>
+      <c r="AX22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ22" s="4"/>
       <c r="BA22" s="4"/>
       <c r="BB22" s="4"/>
@@ -5523,7 +5567,9 @@
       <c r="AW23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX23" s="4"/>
+      <c r="AX23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ23" s="4"/>
       <c r="BA23" s="4"/>
       <c r="BB23" s="4"/>
@@ -5724,7 +5770,9 @@
       <c r="AW24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX24" s="4"/>
+      <c r="AX24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ24" s="4"/>
       <c r="BA24" s="4"/>
       <c r="BB24" s="4"/>
@@ -5946,7 +5994,9 @@
       <c r="AW25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX25" s="4"/>
+      <c r="AX25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ25" s="4"/>
       <c r="BA25" s="4"/>
       <c r="BB25" s="4"/>
@@ -6168,7 +6218,9 @@
       <c r="AW26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX26" s="4"/>
+      <c r="AX26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ26" s="4"/>
       <c r="BA26" s="4"/>
       <c r="BB26" s="4"/>
@@ -6390,7 +6442,9 @@
       <c r="AW27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX27" s="4"/>
+      <c r="AX27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ27" s="4"/>
       <c r="BA27" s="4"/>
       <c r="BB27" s="4"/>
@@ -6612,7 +6666,9 @@
       <c r="AW28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX28" s="4"/>
+      <c r="AX28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ28" s="4"/>
       <c r="BA28" s="4"/>
       <c r="BB28" s="4"/>
@@ -6834,7 +6890,9 @@
       <c r="AW29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX29" s="4"/>
+      <c r="AX29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ29" s="4"/>
       <c r="BA29" s="4"/>
       <c r="BB29" s="4"/>
@@ -7056,7 +7114,9 @@
       <c r="AW30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX30" s="4"/>
+      <c r="AX30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ30" s="4"/>
       <c r="BA30" s="4"/>
       <c r="BB30" s="4"/>
@@ -7278,7 +7338,9 @@
       <c r="AW31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX31" s="4"/>
+      <c r="AX31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ31" s="4"/>
       <c r="BA31" s="4"/>
       <c r="BB31" s="4"/>
@@ -7500,7 +7562,9 @@
       <c r="AW32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX32" s="4"/>
+      <c r="AX32" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ32" s="4"/>
       <c r="BA32" s="4"/>
       <c r="BB32" s="4"/>
@@ -7665,7 +7729,9 @@
       <c r="AW33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX33" s="4"/>
+      <c r="AX33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ33" s="4"/>
       <c r="BA33" s="4"/>
       <c r="BB33" s="4"/>
@@ -7830,7 +7896,9 @@
       <c r="AW34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AX34" s="4"/>
+      <c r="AX34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ34" s="4"/>
       <c r="BA34" s="4"/>
       <c r="BB34" s="4"/>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBAB892-E82B-41D2-9D12-93168759329C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24093740-35AA-4F9F-9800-CF8EC9D768B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="48">
   <si>
     <t>TER</t>
   </si>
@@ -730,7 +730,9 @@
       <c r="AX1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AY1" s="1"/>
+      <c r="AY1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="AZ1" s="1"/>
       <c r="BA1" s="1"/>
       <c r="BB1" s="1"/>
@@ -924,7 +926,9 @@
       <c r="AX2" s="1">
         <v>46238</v>
       </c>
-      <c r="AY2" s="1"/>
+      <c r="AY2" s="1">
+        <v>46240</v>
+      </c>
       <c r="AZ2" s="1"/>
       <c r="BA2" s="1"/>
       <c r="BB2" s="1"/>
@@ -1115,6 +1119,9 @@
         <v>5</v>
       </c>
       <c r="AX3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="AZ3" s="4"/>
@@ -1341,6 +1348,9 @@
       <c r="AX4" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ4" s="4"/>
       <c r="BA4" s="4"/>
       <c r="BB4" s="4"/>
@@ -1565,6 +1575,9 @@
       <c r="AX5" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ5" s="4"/>
       <c r="BA5" s="4"/>
       <c r="BB5" s="4"/>
@@ -1789,6 +1802,9 @@
       <c r="AX6" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ6" s="4"/>
       <c r="BA6" s="4"/>
       <c r="BB6" s="4"/>
@@ -1995,6 +2011,9 @@
       <c r="AX7" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ7" s="4"/>
       <c r="BA7" s="4"/>
       <c r="BB7" s="4"/>
@@ -2219,6 +2238,9 @@
       <c r="AX8" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ8" s="4"/>
       <c r="BA8" s="4"/>
       <c r="BB8" s="4"/>
@@ -2443,6 +2465,9 @@
       <c r="AX9" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ9" s="4"/>
       <c r="BA9" s="4"/>
       <c r="BB9" s="4"/>
@@ -2667,6 +2692,9 @@
       <c r="AX10" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ10" s="4"/>
       <c r="BA10" s="4"/>
       <c r="BB10" s="4"/>
@@ -2891,6 +2919,9 @@
       <c r="AX11" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ11" s="4"/>
       <c r="BA11" s="4"/>
       <c r="BB11" s="4"/>
@@ -3115,6 +3146,9 @@
       <c r="AX12" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ12" s="4"/>
       <c r="BA12" s="4"/>
       <c r="BB12" s="4"/>
@@ -3330,6 +3364,9 @@
       <c r="AX13" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ13" s="4"/>
       <c r="BA13" s="4"/>
       <c r="BB13" s="4"/>
@@ -3554,6 +3591,9 @@
       <c r="AX14" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ14" s="4"/>
       <c r="BA14" s="4"/>
       <c r="BB14" s="4"/>
@@ -3778,6 +3818,9 @@
       <c r="AX15" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ15" s="4"/>
       <c r="BA15" s="4"/>
       <c r="BB15" s="4"/>
@@ -3851,7 +3894,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -4001,6 +4044,9 @@
       </c>
       <c r="AX16" s="4" t="s">
         <v>7</v>
+      </c>
+      <c r="AY16" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="AZ16" s="4"/>
       <c r="BA16" s="4"/>
@@ -4226,6 +4272,9 @@
       <c r="AX17" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ17" s="4"/>
       <c r="BA17" s="4"/>
       <c r="BB17" s="4"/>
@@ -4450,6 +4499,9 @@
       <c r="AX18" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ18" s="4"/>
       <c r="BA18" s="4"/>
       <c r="BB18" s="4"/>
@@ -4523,7 +4575,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -4673,6 +4725,9 @@
       </c>
       <c r="AX19" s="4" t="s">
         <v>7</v>
+      </c>
+      <c r="AY19" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="AZ19" s="4"/>
       <c r="BA19" s="4"/>
@@ -4898,6 +4953,9 @@
       <c r="AX20" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ20" s="4"/>
       <c r="BA20" s="4"/>
       <c r="BB20" s="4"/>
@@ -5122,6 +5180,9 @@
       <c r="AX21" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ21" s="4"/>
       <c r="BA21" s="4"/>
       <c r="BB21" s="4"/>
@@ -5346,6 +5407,9 @@
       <c r="AX22" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ22" s="4"/>
       <c r="BA22" s="4"/>
       <c r="BB22" s="4"/>
@@ -5570,6 +5634,9 @@
       <c r="AX23" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ23" s="4"/>
       <c r="BA23" s="4"/>
       <c r="BB23" s="4"/>
@@ -5773,6 +5840,9 @@
       <c r="AX24" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ24" s="4"/>
       <c r="BA24" s="4"/>
       <c r="BB24" s="4"/>
@@ -5997,6 +6067,9 @@
       <c r="AX25" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ25" s="4"/>
       <c r="BA25" s="4"/>
       <c r="BB25" s="4"/>
@@ -6221,6 +6294,9 @@
       <c r="AX26" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ26" s="4"/>
       <c r="BA26" s="4"/>
       <c r="BB26" s="4"/>
@@ -6445,6 +6521,9 @@
       <c r="AX27" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ27" s="4"/>
       <c r="BA27" s="4"/>
       <c r="BB27" s="4"/>
@@ -6669,6 +6748,9 @@
       <c r="AX28" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ28" s="4"/>
       <c r="BA28" s="4"/>
       <c r="BB28" s="4"/>
@@ -6893,6 +6975,9 @@
       <c r="AX29" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ29" s="4"/>
       <c r="BA29" s="4"/>
       <c r="BB29" s="4"/>
@@ -7117,6 +7202,9 @@
       <c r="AX30" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ30" s="4"/>
       <c r="BA30" s="4"/>
       <c r="BB30" s="4"/>
@@ -7341,6 +7429,9 @@
       <c r="AX31" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY31" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="AZ31" s="4"/>
       <c r="BA31" s="4"/>
       <c r="BB31" s="4"/>
@@ -7565,6 +7656,9 @@
       <c r="AX32" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY32" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ32" s="4"/>
       <c r="BA32" s="4"/>
       <c r="BB32" s="4"/>
@@ -7732,6 +7826,9 @@
       <c r="AX33" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="AY33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ33" s="4"/>
       <c r="BA33" s="4"/>
       <c r="BB33" s="4"/>
@@ -7897,6 +7994,9 @@
         <v>5</v>
       </c>
       <c r="AX34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY34" s="4" t="s">
         <v>5</v>
       </c>
       <c r="AZ34" s="4"/>
@@ -7920,7 +8020,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 AV3:AZ10 BB3:BB22 O3:AT34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AV11:BA22 BC11:BJ22 AV23:BJ31 G32:I32 AV32:AV34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 BB3:BB22 O3:AT34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 BC11:BJ22 G32:I32 AV32:AV34 AV3:AZ4 AV5:AX31 AZ5:AZ10 AZ23:BJ31 AZ11:BA22 AY5:AY34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24093740-35AA-4F9F-9800-CF8EC9D768B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5525F40-CF96-4EE8-B3D5-5DFA5D520B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="48">
   <si>
     <t>TER</t>
   </si>
@@ -733,7 +733,9 @@
       <c r="AY1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AZ1" s="1"/>
+      <c r="AZ1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="BA1" s="1"/>
       <c r="BB1" s="1"/>
       <c r="BC1" s="1"/>
@@ -929,7 +931,9 @@
       <c r="AY2" s="1">
         <v>46240</v>
       </c>
-      <c r="AZ2" s="1"/>
+      <c r="AZ2" s="1">
+        <v>46245</v>
+      </c>
       <c r="BA2" s="1"/>
       <c r="BB2" s="1"/>
       <c r="BC2" s="1"/>
@@ -1124,7 +1128,9 @@
       <c r="AY3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ3" s="4"/>
+      <c r="AZ3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA3" s="4"/>
       <c r="BB3" s="4"/>
       <c r="BC3" s="4"/>
@@ -1351,7 +1357,9 @@
       <c r="AY4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ4" s="4"/>
+      <c r="AZ4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA4" s="4"/>
       <c r="BB4" s="4"/>
       <c r="BC4" s="4"/>
@@ -1578,7 +1586,9 @@
       <c r="AY5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ5" s="4"/>
+      <c r="AZ5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA5" s="4"/>
       <c r="BB5" s="4"/>
       <c r="BC5" s="4"/>
@@ -1805,7 +1815,9 @@
       <c r="AY6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ6" s="4"/>
+      <c r="AZ6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA6" s="4"/>
       <c r="BB6" s="4"/>
       <c r="BC6" s="4"/>
@@ -2014,7 +2026,9 @@
       <c r="AY7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ7" s="4"/>
+      <c r="AZ7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA7" s="4"/>
       <c r="BB7" s="4"/>
       <c r="BC7" s="4"/>
@@ -2241,7 +2255,9 @@
       <c r="AY8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ8" s="4"/>
+      <c r="AZ8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA8" s="4"/>
       <c r="BB8" s="4"/>
       <c r="BC8" s="4"/>
@@ -2468,7 +2484,9 @@
       <c r="AY9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ9" s="4"/>
+      <c r="AZ9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA9" s="4"/>
       <c r="BB9" s="4"/>
       <c r="BC9" s="4"/>
@@ -2695,7 +2713,9 @@
       <c r="AY10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ10" s="4"/>
+      <c r="AZ10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA10" s="4"/>
       <c r="BB10" s="4"/>
       <c r="BC10" s="4"/>
@@ -2922,7 +2942,9 @@
       <c r="AY11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ11" s="4"/>
+      <c r="AZ11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA11" s="4"/>
       <c r="BB11" s="4"/>
       <c r="BC11" s="4"/>
@@ -3149,7 +3171,9 @@
       <c r="AY12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ12" s="4"/>
+      <c r="AZ12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA12" s="4"/>
       <c r="BB12" s="4"/>
       <c r="BC12" s="4"/>
@@ -3367,7 +3391,9 @@
       <c r="AY13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ13" s="4"/>
+      <c r="AZ13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA13" s="4"/>
       <c r="BB13" s="4"/>
       <c r="BC13" s="4"/>
@@ -3594,7 +3620,9 @@
       <c r="AY14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ14" s="4"/>
+      <c r="AZ14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA14" s="4"/>
       <c r="BB14" s="4"/>
       <c r="BC14" s="4"/>
@@ -3821,7 +3849,9 @@
       <c r="AY15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ15" s="4"/>
+      <c r="AZ15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA15" s="4"/>
       <c r="BB15" s="4"/>
       <c r="BC15" s="4"/>
@@ -4275,7 +4305,9 @@
       <c r="AY17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ17" s="4"/>
+      <c r="AZ17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA17" s="4"/>
       <c r="BB17" s="4"/>
       <c r="BC17" s="4"/>
@@ -4502,7 +4534,9 @@
       <c r="AY18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ18" s="4"/>
+      <c r="AZ18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA18" s="4"/>
       <c r="BB18" s="4"/>
       <c r="BC18" s="4"/>
@@ -4956,7 +4990,9 @@
       <c r="AY20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ20" s="4"/>
+      <c r="AZ20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA20" s="4"/>
       <c r="BB20" s="4"/>
       <c r="BC20" s="4"/>
@@ -5183,7 +5219,9 @@
       <c r="AY21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ21" s="4"/>
+      <c r="AZ21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA21" s="4"/>
       <c r="BB21" s="4"/>
       <c r="BC21" s="4"/>
@@ -5410,7 +5448,9 @@
       <c r="AY22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ22" s="4"/>
+      <c r="AZ22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA22" s="4"/>
       <c r="BB22" s="4"/>
       <c r="BC22" s="4"/>
@@ -5637,7 +5677,9 @@
       <c r="AY23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ23" s="4"/>
+      <c r="AZ23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA23" s="4"/>
       <c r="BB23" s="4"/>
       <c r="BC23" s="4"/>
@@ -5843,7 +5885,9 @@
       <c r="AY24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ24" s="4"/>
+      <c r="AZ24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA24" s="4"/>
       <c r="BB24" s="4"/>
       <c r="BC24" s="4"/>
@@ -6070,7 +6114,9 @@
       <c r="AY25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ25" s="4"/>
+      <c r="AZ25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA25" s="4"/>
       <c r="BB25" s="4"/>
       <c r="BC25" s="4"/>
@@ -6297,7 +6343,9 @@
       <c r="AY26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ26" s="4"/>
+      <c r="AZ26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA26" s="4"/>
       <c r="BB26" s="4"/>
       <c r="BC26" s="4"/>
@@ -6524,7 +6572,9 @@
       <c r="AY27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ27" s="4"/>
+      <c r="AZ27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA27" s="4"/>
       <c r="BB27" s="4"/>
       <c r="BC27" s="4"/>
@@ -6751,7 +6801,9 @@
       <c r="AY28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ28" s="4"/>
+      <c r="AZ28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA28" s="4"/>
       <c r="BB28" s="4"/>
       <c r="BC28" s="4"/>
@@ -6978,7 +7030,9 @@
       <c r="AY29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ29" s="4"/>
+      <c r="AZ29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA29" s="4"/>
       <c r="BB29" s="4"/>
       <c r="BC29" s="4"/>
@@ -7205,7 +7259,9 @@
       <c r="AY30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ30" s="4"/>
+      <c r="AZ30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA30" s="4"/>
       <c r="BB30" s="4"/>
       <c r="BC30" s="4"/>
@@ -7432,7 +7488,9 @@
       <c r="AY31" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AZ31" s="4"/>
+      <c r="AZ31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA31" s="4"/>
       <c r="BB31" s="4"/>
       <c r="BC31" s="4"/>
@@ -7659,7 +7717,9 @@
       <c r="AY32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ32" s="4"/>
+      <c r="AZ32" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA32" s="4"/>
       <c r="BB32" s="4"/>
       <c r="BC32" s="4"/>
@@ -7829,7 +7889,9 @@
       <c r="AY33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ33" s="4"/>
+      <c r="AZ33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA33" s="4"/>
       <c r="BB33" s="4"/>
       <c r="BC33" s="4"/>
@@ -7999,7 +8061,9 @@
       <c r="AY34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AZ34" s="4"/>
+      <c r="AZ34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BA34" s="4"/>
       <c r="BB34" s="4"/>
       <c r="BC34" s="4"/>
@@ -8020,7 +8084,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 BB3:BB22 O3:AT34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 BC11:BJ22 G32:I32 AV32:AV34 AV3:AZ4 AV5:AX31 AZ5:AZ10 AZ23:BJ31 AZ11:BA22 AY5:AY34">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 AV3:AZ4 BB3:BB22 O3:AT34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BC11:BJ22 AZ23:BJ31 G32:I32 AV32:AV34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5525F40-CF96-4EE8-B3D5-5DFA5D520B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314489D4-74B0-4E22-9CF4-076CE1868722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="48">
   <si>
     <t>TER</t>
   </si>
@@ -736,7 +736,9 @@
       <c r="AZ1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BA1" s="1"/>
+      <c r="BA1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="BB1" s="1"/>
       <c r="BC1" s="1"/>
       <c r="BD1" s="1"/>
@@ -934,7 +936,9 @@
       <c r="AZ2" s="1">
         <v>46245</v>
       </c>
-      <c r="BA2" s="1"/>
+      <c r="BA2" s="1">
+        <v>46247</v>
+      </c>
       <c r="BB2" s="1"/>
       <c r="BC2" s="1"/>
       <c r="BD2" s="1"/>
@@ -1131,7 +1135,9 @@
       <c r="AZ3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA3" s="4"/>
+      <c r="BA3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB3" s="4"/>
       <c r="BC3" s="4"/>
       <c r="BD3" s="4"/>
@@ -1360,7 +1366,9 @@
       <c r="AZ4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA4" s="4"/>
+      <c r="BA4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB4" s="4"/>
       <c r="BC4" s="4"/>
       <c r="BD4" s="4"/>
@@ -1589,7 +1597,9 @@
       <c r="AZ5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA5" s="4"/>
+      <c r="BA5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB5" s="4"/>
       <c r="BC5" s="4"/>
       <c r="BD5" s="4"/>
@@ -1818,7 +1828,9 @@
       <c r="AZ6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA6" s="4"/>
+      <c r="BA6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB6" s="4"/>
       <c r="BC6" s="4"/>
       <c r="BD6" s="4"/>
@@ -2029,7 +2041,9 @@
       <c r="AZ7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA7" s="4"/>
+      <c r="BA7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB7" s="4"/>
       <c r="BC7" s="4"/>
       <c r="BD7" s="4"/>
@@ -2258,7 +2272,9 @@
       <c r="AZ8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA8" s="4"/>
+      <c r="BA8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB8" s="4"/>
       <c r="BC8" s="4"/>
       <c r="BD8" s="4"/>
@@ -2487,7 +2503,9 @@
       <c r="AZ9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA9" s="4"/>
+      <c r="BA9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB9" s="4"/>
       <c r="BC9" s="4"/>
       <c r="BD9" s="4"/>
@@ -2716,7 +2734,9 @@
       <c r="AZ10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA10" s="4"/>
+      <c r="BA10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB10" s="4"/>
       <c r="BC10" s="4"/>
       <c r="BD10" s="4"/>
@@ -2945,7 +2965,9 @@
       <c r="AZ11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA11" s="4"/>
+      <c r="BA11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB11" s="4"/>
       <c r="BC11" s="4"/>
       <c r="BD11" s="4"/>
@@ -3174,7 +3196,9 @@
       <c r="AZ12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA12" s="4"/>
+      <c r="BA12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB12" s="4"/>
       <c r="BC12" s="4"/>
       <c r="BD12" s="4"/>
@@ -3394,7 +3418,9 @@
       <c r="AZ13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA13" s="4"/>
+      <c r="BA13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB13" s="4"/>
       <c r="BC13" s="4"/>
       <c r="BD13" s="4"/>
@@ -3623,7 +3649,9 @@
       <c r="AZ14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA14" s="4"/>
+      <c r="BA14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB14" s="4"/>
       <c r="BC14" s="4"/>
       <c r="BD14" s="4"/>
@@ -3852,7 +3880,9 @@
       <c r="AZ15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA15" s="4"/>
+      <c r="BA15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB15" s="4"/>
       <c r="BC15" s="4"/>
       <c r="BD15" s="4"/>
@@ -4308,7 +4338,9 @@
       <c r="AZ17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA17" s="4"/>
+      <c r="BA17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB17" s="4"/>
       <c r="BC17" s="4"/>
       <c r="BD17" s="4"/>
@@ -4537,7 +4569,9 @@
       <c r="AZ18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA18" s="4"/>
+      <c r="BA18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB18" s="4"/>
       <c r="BC18" s="4"/>
       <c r="BD18" s="4"/>
@@ -4993,7 +5027,9 @@
       <c r="AZ20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA20" s="4"/>
+      <c r="BA20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB20" s="4"/>
       <c r="BC20" s="4"/>
       <c r="BD20" s="4"/>
@@ -5222,7 +5258,9 @@
       <c r="AZ21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA21" s="4"/>
+      <c r="BA21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB21" s="4"/>
       <c r="BC21" s="4"/>
       <c r="BD21" s="4"/>
@@ -5451,7 +5489,9 @@
       <c r="AZ22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA22" s="4"/>
+      <c r="BA22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB22" s="4"/>
       <c r="BC22" s="4"/>
       <c r="BD22" s="4"/>
@@ -5680,7 +5720,9 @@
       <c r="AZ23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA23" s="4"/>
+      <c r="BA23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB23" s="4"/>
       <c r="BC23" s="4"/>
       <c r="BD23" s="4"/>
@@ -5888,7 +5930,9 @@
       <c r="AZ24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA24" s="4"/>
+      <c r="BA24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB24" s="4"/>
       <c r="BC24" s="4"/>
       <c r="BD24" s="4"/>
@@ -6117,7 +6161,9 @@
       <c r="AZ25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA25" s="4"/>
+      <c r="BA25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB25" s="4"/>
       <c r="BC25" s="4"/>
       <c r="BD25" s="4"/>
@@ -6346,7 +6392,9 @@
       <c r="AZ26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA26" s="4"/>
+      <c r="BA26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB26" s="4"/>
       <c r="BC26" s="4"/>
       <c r="BD26" s="4"/>
@@ -6575,7 +6623,9 @@
       <c r="AZ27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA27" s="4"/>
+      <c r="BA27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB27" s="4"/>
       <c r="BC27" s="4"/>
       <c r="BD27" s="4"/>
@@ -6804,7 +6854,9 @@
       <c r="AZ28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA28" s="4"/>
+      <c r="BA28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB28" s="4"/>
       <c r="BC28" s="4"/>
       <c r="BD28" s="4"/>
@@ -7033,7 +7085,9 @@
       <c r="AZ29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA29" s="4"/>
+      <c r="BA29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB29" s="4"/>
       <c r="BC29" s="4"/>
       <c r="BD29" s="4"/>
@@ -7262,7 +7316,9 @@
       <c r="AZ30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA30" s="4"/>
+      <c r="BA30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB30" s="4"/>
       <c r="BC30" s="4"/>
       <c r="BD30" s="4"/>
@@ -7491,7 +7547,9 @@
       <c r="AZ31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA31" s="4"/>
+      <c r="BA31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB31" s="4"/>
       <c r="BC31" s="4"/>
       <c r="BD31" s="4"/>
@@ -7720,7 +7778,9 @@
       <c r="AZ32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA32" s="4"/>
+      <c r="BA32" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB32" s="4"/>
       <c r="BC32" s="4"/>
       <c r="BD32" s="4"/>
@@ -7892,7 +7952,9 @@
       <c r="AZ33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA33" s="4"/>
+      <c r="BA33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB33" s="4"/>
       <c r="BC33" s="4"/>
       <c r="BD33" s="4"/>
@@ -8064,7 +8126,9 @@
       <c r="AZ34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BA34" s="4"/>
+      <c r="BA34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BB34" s="4"/>
       <c r="BC34" s="4"/>
       <c r="BD34" s="4"/>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314489D4-74B0-4E22-9CF4-076CE1868722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD82673-0F38-41C9-87ED-1BD0C34B4AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="48">
   <si>
     <t>TER</t>
   </si>
@@ -276,7 +276,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -578,14 +588,17 @@
     <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="41" width="7.7109375" customWidth="1"/>
-    <col min="42" max="42" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="43" max="47" width="7.7109375" customWidth="1"/>
-    <col min="48" max="48" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="49" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="4" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="29" max="31" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="39" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.7109375" customWidth="1"/>
+    <col min="42" max="46" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="7" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="7" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="7" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="54" width="7" bestFit="1" customWidth="1"/>
+    <col min="55" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:123" x14ac:dyDescent="0.25">
@@ -739,7 +752,9 @@
       <c r="BA1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="BB1" s="1"/>
+      <c r="BB1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="BC1" s="1"/>
       <c r="BD1" s="1"/>
       <c r="BE1" s="1"/>
@@ -939,7 +954,9 @@
       <c r="BA2" s="1">
         <v>46247</v>
       </c>
-      <c r="BB2" s="1"/>
+      <c r="BB2" s="1">
+        <v>46252</v>
+      </c>
       <c r="BC2" s="1"/>
       <c r="BD2" s="1"/>
       <c r="BE2" s="1"/>
@@ -1138,7 +1155,9 @@
       <c r="BA3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB3" s="4"/>
+      <c r="BB3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC3" s="4"/>
       <c r="BD3" s="4"/>
       <c r="BE3" s="4"/>
@@ -1369,7 +1388,9 @@
       <c r="BA4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB4" s="4"/>
+      <c r="BB4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC4" s="4"/>
       <c r="BD4" s="4"/>
       <c r="BE4" s="4"/>
@@ -1600,7 +1621,9 @@
       <c r="BA5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB5" s="4"/>
+      <c r="BB5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC5" s="4"/>
       <c r="BD5" s="4"/>
       <c r="BE5" s="4"/>
@@ -1831,7 +1854,9 @@
       <c r="BA6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB6" s="4"/>
+      <c r="BB6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC6" s="4"/>
       <c r="BD6" s="4"/>
       <c r="BE6" s="4"/>
@@ -2044,7 +2069,9 @@
       <c r="BA7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB7" s="4"/>
+      <c r="BB7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC7" s="4"/>
       <c r="BD7" s="4"/>
       <c r="BE7" s="4"/>
@@ -2275,7 +2302,9 @@
       <c r="BA8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB8" s="4"/>
+      <c r="BB8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC8" s="4"/>
       <c r="BD8" s="4"/>
       <c r="BE8" s="4"/>
@@ -2506,7 +2535,9 @@
       <c r="BA9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB9" s="4"/>
+      <c r="BB9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC9" s="4"/>
       <c r="BD9" s="4"/>
       <c r="BE9" s="4"/>
@@ -2737,7 +2768,9 @@
       <c r="BA10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB10" s="4"/>
+      <c r="BB10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC10" s="4"/>
       <c r="BD10" s="4"/>
       <c r="BE10" s="4"/>
@@ -2968,7 +3001,9 @@
       <c r="BA11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB11" s="4"/>
+      <c r="BB11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC11" s="4"/>
       <c r="BD11" s="4"/>
       <c r="BE11" s="4"/>
@@ -3199,7 +3234,9 @@
       <c r="BA12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB12" s="4"/>
+      <c r="BB12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC12" s="4"/>
       <c r="BD12" s="4"/>
       <c r="BE12" s="4"/>
@@ -3421,7 +3458,9 @@
       <c r="BA13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB13" s="4"/>
+      <c r="BB13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC13" s="4"/>
       <c r="BD13" s="4"/>
       <c r="BE13" s="4"/>
@@ -3652,7 +3691,9 @@
       <c r="BA14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB14" s="4"/>
+      <c r="BB14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC14" s="4"/>
       <c r="BD14" s="4"/>
       <c r="BE14" s="4"/>
@@ -3883,7 +3924,9 @@
       <c r="BA15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB15" s="4"/>
+      <c r="BB15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC15" s="4"/>
       <c r="BD15" s="4"/>
       <c r="BE15" s="4"/>
@@ -4341,7 +4384,9 @@
       <c r="BA17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB17" s="4"/>
+      <c r="BB17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC17" s="4"/>
       <c r="BD17" s="4"/>
       <c r="BE17" s="4"/>
@@ -4572,7 +4617,9 @@
       <c r="BA18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB18" s="4"/>
+      <c r="BB18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC18" s="4"/>
       <c r="BD18" s="4"/>
       <c r="BE18" s="4"/>
@@ -5030,7 +5077,9 @@
       <c r="BA20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB20" s="4"/>
+      <c r="BB20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC20" s="4"/>
       <c r="BD20" s="4"/>
       <c r="BE20" s="4"/>
@@ -5261,7 +5310,9 @@
       <c r="BA21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB21" s="4"/>
+      <c r="BB21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC21" s="4"/>
       <c r="BD21" s="4"/>
       <c r="BE21" s="4"/>
@@ -5492,7 +5543,9 @@
       <c r="BA22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB22" s="4"/>
+      <c r="BB22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC22" s="4"/>
       <c r="BD22" s="4"/>
       <c r="BE22" s="4"/>
@@ -5723,7 +5776,9 @@
       <c r="BA23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB23" s="4"/>
+      <c r="BB23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC23" s="4"/>
       <c r="BD23" s="4"/>
       <c r="BE23" s="4"/>
@@ -5933,7 +5988,9 @@
       <c r="BA24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB24" s="4"/>
+      <c r="BB24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC24" s="4"/>
       <c r="BD24" s="4"/>
       <c r="BE24" s="4"/>
@@ -6164,7 +6221,9 @@
       <c r="BA25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB25" s="4"/>
+      <c r="BB25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC25" s="4"/>
       <c r="BD25" s="4"/>
       <c r="BE25" s="4"/>
@@ -6395,7 +6454,9 @@
       <c r="BA26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB26" s="4"/>
+      <c r="BB26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC26" s="4"/>
       <c r="BD26" s="4"/>
       <c r="BE26" s="4"/>
@@ -6626,7 +6687,9 @@
       <c r="BA27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB27" s="4"/>
+      <c r="BB27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC27" s="4"/>
       <c r="BD27" s="4"/>
       <c r="BE27" s="4"/>
@@ -6857,7 +6920,9 @@
       <c r="BA28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB28" s="4"/>
+      <c r="BB28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC28" s="4"/>
       <c r="BD28" s="4"/>
       <c r="BE28" s="4"/>
@@ -7088,7 +7153,9 @@
       <c r="BA29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB29" s="4"/>
+      <c r="BB29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC29" s="4"/>
       <c r="BD29" s="4"/>
       <c r="BE29" s="4"/>
@@ -7319,7 +7386,9 @@
       <c r="BA30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB30" s="4"/>
+      <c r="BB30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC30" s="4"/>
       <c r="BD30" s="4"/>
       <c r="BE30" s="4"/>
@@ -7550,7 +7619,9 @@
       <c r="BA31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB31" s="4"/>
+      <c r="BB31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC31" s="4"/>
       <c r="BD31" s="4"/>
       <c r="BE31" s="4"/>
@@ -7781,7 +7852,9 @@
       <c r="BA32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB32" s="4"/>
+      <c r="BB32" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC32" s="4"/>
       <c r="BD32" s="4"/>
       <c r="BE32" s="4"/>
@@ -7955,7 +8028,9 @@
       <c r="BA33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB33" s="4"/>
+      <c r="BB33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BC33" s="4"/>
       <c r="BD33" s="4"/>
       <c r="BE33" s="4"/>
@@ -8129,7 +8204,9 @@
       <c r="BA34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BB34" s="4"/>
+      <c r="BB34" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BC34" s="4"/>
       <c r="BD34" s="4"/>
       <c r="BE34" s="4"/>
@@ -8149,6 +8226,11 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D3:N3 BE3:DG3 AV3:AZ4 BB3:BB22 O3:AT34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BC11:BJ22 AZ23:BJ31 G32:I32 AV32:AV34">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD82673-0F38-41C9-87ED-1BD0C34B4AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0748A8-A5E2-4F27-A555-BD2A1CFEB149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0748A8-A5E2-4F27-A555-BD2A1CFEB149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6628ED14-51A5-43D9-A696-DC7473176224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="49">
   <si>
     <t>TER</t>
   </si>
@@ -182,6 +182,9 @@
   <si>
     <t>QUA</t>
   </si>
+  <si>
+    <t>5P/F</t>
+  </si>
 </sst>
 </file>
 
@@ -276,7 +279,37 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6222,7 +6255,7 @@
         <v>5</v>
       </c>
       <c r="BB25" s="4" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="BC25" s="4"/>
       <c r="BD25" s="4"/>
@@ -8226,13 +8259,18 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D3:N3 BE3:DG3 AV3:AZ4 BB3:BB22 O3:AT34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BC11:BJ22 AZ23:BJ31 G32:I32 AV32:AV34">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB34">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB3:BB34">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BB3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6628ED14-51A5-43D9-A696-DC7473176224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C43844-6EF6-40DB-9878-92055FD0697D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="49">
   <si>
     <t>TER</t>
   </si>
@@ -279,17 +279,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -788,7 +778,9 @@
       <c r="BB1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BC1" s="1"/>
+      <c r="BC1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="BD1" s="1"/>
       <c r="BE1" s="1"/>
       <c r="BF1" s="1"/>
@@ -990,7 +982,9 @@
       <c r="BB2" s="1">
         <v>46252</v>
       </c>
-      <c r="BC2" s="1"/>
+      <c r="BC2" s="1">
+        <v>46254</v>
+      </c>
       <c r="BD2" s="1"/>
       <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
@@ -1191,7 +1185,9 @@
       <c r="BB3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC3" s="4"/>
+      <c r="BC3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD3" s="4"/>
       <c r="BE3" s="4"/>
       <c r="BF3" s="4"/>
@@ -1424,7 +1420,9 @@
       <c r="BB4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC4" s="4"/>
+      <c r="BC4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD4" s="4"/>
       <c r="BE4" s="4"/>
       <c r="BF4" s="4"/>
@@ -1657,7 +1655,9 @@
       <c r="BB5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC5" s="4"/>
+      <c r="BC5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD5" s="4"/>
       <c r="BE5" s="4"/>
       <c r="BF5" s="4"/>
@@ -1890,7 +1890,9 @@
       <c r="BB6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC6" s="4"/>
+      <c r="BC6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD6" s="4"/>
       <c r="BE6" s="4"/>
       <c r="BF6" s="4"/>
@@ -2105,7 +2107,9 @@
       <c r="BB7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC7" s="4"/>
+      <c r="BC7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD7" s="4"/>
       <c r="BE7" s="4"/>
       <c r="BF7" s="4"/>
@@ -2338,7 +2342,9 @@
       <c r="BB8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC8" s="4"/>
+      <c r="BC8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD8" s="4"/>
       <c r="BE8" s="4"/>
       <c r="BF8" s="4"/>
@@ -2571,7 +2577,9 @@
       <c r="BB9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC9" s="4"/>
+      <c r="BC9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD9" s="4"/>
       <c r="BE9" s="4"/>
       <c r="BF9" s="4"/>
@@ -2804,7 +2812,9 @@
       <c r="BB10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC10" s="4"/>
+      <c r="BC10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD10" s="4"/>
       <c r="BE10" s="4"/>
       <c r="BF10" s="4"/>
@@ -3037,7 +3047,9 @@
       <c r="BB11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC11" s="4"/>
+      <c r="BC11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD11" s="4"/>
       <c r="BE11" s="4"/>
       <c r="BF11" s="4"/>
@@ -3270,7 +3282,9 @@
       <c r="BB12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC12" s="4"/>
+      <c r="BC12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD12" s="4"/>
       <c r="BE12" s="4"/>
       <c r="BF12" s="4"/>
@@ -3494,7 +3508,9 @@
       <c r="BB13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC13" s="4"/>
+      <c r="BC13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD13" s="4"/>
       <c r="BE13" s="4"/>
       <c r="BF13" s="4"/>
@@ -3727,7 +3743,9 @@
       <c r="BB14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC14" s="4"/>
+      <c r="BC14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD14" s="4"/>
       <c r="BE14" s="4"/>
       <c r="BF14" s="4"/>
@@ -3960,7 +3978,9 @@
       <c r="BB15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC15" s="4"/>
+      <c r="BC15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD15" s="4"/>
       <c r="BE15" s="4"/>
       <c r="BF15" s="4"/>
@@ -4420,7 +4440,9 @@
       <c r="BB17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC17" s="4"/>
+      <c r="BC17" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BD17" s="4"/>
       <c r="BE17" s="4"/>
       <c r="BF17" s="4"/>
@@ -4653,7 +4675,9 @@
       <c r="BB18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC18" s="4"/>
+      <c r="BC18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD18" s="4"/>
       <c r="BE18" s="4"/>
       <c r="BF18" s="4"/>
@@ -5113,7 +5137,9 @@
       <c r="BB20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC20" s="4"/>
+      <c r="BC20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD20" s="4"/>
       <c r="BE20" s="4"/>
       <c r="BF20" s="4"/>
@@ -5346,7 +5372,9 @@
       <c r="BB21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC21" s="4"/>
+      <c r="BC21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD21" s="4"/>
       <c r="BE21" s="4"/>
       <c r="BF21" s="4"/>
@@ -5579,7 +5607,9 @@
       <c r="BB22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC22" s="4"/>
+      <c r="BC22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD22" s="4"/>
       <c r="BE22" s="4"/>
       <c r="BF22" s="4"/>
@@ -5807,12 +5837,14 @@
         <v>5</v>
       </c>
       <c r="BA23" s="4" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="BB23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC23" s="4"/>
+      <c r="BC23" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BD23" s="4"/>
       <c r="BE23" s="4"/>
       <c r="BF23" s="4"/>
@@ -6024,7 +6056,9 @@
       <c r="BB24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC24" s="4"/>
+      <c r="BC24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD24" s="4"/>
       <c r="BE24" s="4"/>
       <c r="BF24" s="4"/>
@@ -6257,7 +6291,9 @@
       <c r="BB25" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="BC25" s="4"/>
+      <c r="BC25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD25" s="4"/>
       <c r="BE25" s="4"/>
       <c r="BF25" s="4"/>
@@ -6490,7 +6526,9 @@
       <c r="BB26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC26" s="4"/>
+      <c r="BC26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD26" s="4"/>
       <c r="BE26" s="4"/>
       <c r="BF26" s="4"/>
@@ -6723,7 +6761,9 @@
       <c r="BB27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC27" s="4"/>
+      <c r="BC27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD27" s="4"/>
       <c r="BE27" s="4"/>
       <c r="BF27" s="4"/>
@@ -6956,7 +6996,9 @@
       <c r="BB28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC28" s="4"/>
+      <c r="BC28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD28" s="4"/>
       <c r="BE28" s="4"/>
       <c r="BF28" s="4"/>
@@ -7189,7 +7231,9 @@
       <c r="BB29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC29" s="4"/>
+      <c r="BC29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD29" s="4"/>
       <c r="BE29" s="4"/>
       <c r="BF29" s="4"/>
@@ -7422,7 +7466,9 @@
       <c r="BB30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC30" s="4"/>
+      <c r="BC30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD30" s="4"/>
       <c r="BE30" s="4"/>
       <c r="BF30" s="4"/>
@@ -7655,7 +7701,9 @@
       <c r="BB31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC31" s="4"/>
+      <c r="BC31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD31" s="4"/>
       <c r="BE31" s="4"/>
       <c r="BF31" s="4"/>
@@ -7888,7 +7936,9 @@
       <c r="BB32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC32" s="4"/>
+      <c r="BC32" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD32" s="4"/>
       <c r="BE32" s="4"/>
       <c r="BF32" s="4"/>
@@ -8064,7 +8114,9 @@
       <c r="BB33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BC33" s="4"/>
+      <c r="BC33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD33" s="4"/>
       <c r="BE33" s="4"/>
       <c r="BF33" s="4"/>
@@ -8240,7 +8292,9 @@
       <c r="BB34" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BC34" s="4"/>
+      <c r="BC34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BD34" s="4"/>
       <c r="BE34" s="4"/>
       <c r="BF34" s="4"/>
@@ -8258,19 +8312,24 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 AV3:AZ4 BB3:BB22 O3:AT34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BC11:BJ22 AZ23:BJ31 G32:I32 AV32:AV34">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 AV3:AZ4 BB3:BB22 O3:AT34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 G32:I32 AV32:AV34 BD11:BJ31 BC3:BC31 AZ23:BB31">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB34">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+  <conditionalFormatting sqref="BB3:BC34">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BB3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB34:BC34">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB3:BB34">
+  <conditionalFormatting sqref="BA23">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BB3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("F",BA23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C43844-6EF6-40DB-9878-92055FD0697D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60880DA1-4A2C-4E09-8808-1DE5DE11AEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="50">
   <si>
     <t>TER</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>5P/F</t>
+  </si>
+  <si>
+    <t>3/P</t>
   </si>
 </sst>
 </file>
@@ -2108,7 +2111,7 @@
         <v>5</v>
       </c>
       <c r="BC7" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD7" s="4"/>
       <c r="BE7" s="4"/>
@@ -2578,7 +2581,7 @@
         <v>5</v>
       </c>
       <c r="BC9" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD9" s="4"/>
       <c r="BE9" s="4"/>
@@ -5843,7 +5846,7 @@
         <v>5</v>
       </c>
       <c r="BC23" s="4" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="BD23" s="4"/>
       <c r="BE23" s="4"/>
@@ -8312,24 +8315,24 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 AV3:AZ4 BB3:BB22 O3:AT34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 G32:I32 AV32:AV34 BD11:BJ31 BC3:BC31 AZ23:BB31">
+  <conditionalFormatting sqref="D3:N3 BE3:DG3 AV3:AZ4 BB3:BB22 BC3:BC31 O3:AT34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BD11:BJ31 AZ23:BB31 G32:I32 AV32:AV34">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BA23">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BA23)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BB3:BC34">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BB3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB34:BC34">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BA23">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BA23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60880DA1-4A2C-4E09-8808-1DE5DE11AEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519E8E81-2FEE-46F7-BE6A-D9BCEDDF10D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="49">
   <si>
     <t>TER</t>
   </si>
@@ -181,9 +181,6 @@
   </si>
   <si>
     <t>QUA</t>
-  </si>
-  <si>
-    <t>5P/F</t>
   </si>
   <si>
     <t>3/P</t>
@@ -600,34 +597,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="39" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.7109375" customWidth="1"/>
-    <col min="42" max="46" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="39" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.6640625" customWidth="1"/>
+    <col min="42" max="46" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="7" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="7" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="7" style="4" bestFit="1" customWidth="1"/>
     <col min="52" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="106" width="7.7109375" customWidth="1"/>
+    <col min="55" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -784,8 +781,12 @@
       <c r="BC1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="BD1" s="1"/>
-      <c r="BE1" s="1"/>
+      <c r="BD1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="BF1" s="1"/>
       <c r="BG1" s="1"/>
       <c r="BH1" s="1"/>
@@ -821,7 +822,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1025,7 +1026,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1260,7 +1261,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1495,7 +1496,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1730,7 +1731,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -1965,7 +1966,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -2182,7 +2183,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2417,7 +2418,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2652,7 +2653,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -2887,7 +2888,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -3122,7 +3123,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -3357,7 +3358,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3583,7 +3584,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -3818,7 +3819,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -4053,7 +4054,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -4280,7 +4281,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -4515,7 +4516,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -4750,7 +4751,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -4977,7 +4978,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -5212,7 +5213,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -5447,7 +5448,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -5682,7 +5683,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -5840,13 +5841,13 @@
         <v>5</v>
       </c>
       <c r="BA23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="BB23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC23" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="BB23" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="BC23" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="BD23" s="4"/>
       <c r="BE23" s="4"/>
@@ -5917,7 +5918,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -6131,7 +6132,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -6292,7 +6293,7 @@
         <v>5</v>
       </c>
       <c r="BB25" s="4" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="BC25" s="4" t="s">
         <v>5</v>
@@ -6366,7 +6367,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -6601,7 +6602,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -6836,7 +6837,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -7071,7 +7072,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -7306,7 +7307,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -7541,7 +7542,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -7776,7 +7777,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -7954,7 +7955,7 @@
       <c r="BM32" s="4"/>
       <c r="BN32" s="4"/>
     </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -8132,7 +8133,7 @@
       <c r="BM33" s="4"/>
       <c r="BN33" s="4"/>
     </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -8343,13 +8344,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8357,7 +8358,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -8365,7 +8366,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -8373,7 +8374,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -8381,7 +8382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -8389,7 +8390,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -8397,7 +8398,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -8405,7 +8406,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -8413,7 +8414,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -8421,7 +8422,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -8429,7 +8430,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -8437,7 +8438,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -8445,7 +8446,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -8453,7 +8454,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -8461,7 +8462,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -8469,7 +8470,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -8477,7 +8478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -8485,7 +8486,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -8493,7 +8494,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -8501,7 +8502,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -8509,7 +8510,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -8517,7 +8518,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -8525,7 +8526,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -8533,7 +8534,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -8541,7 +8542,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -8549,7 +8550,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -8557,7 +8558,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -8565,7 +8566,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -8573,7 +8574,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -8581,7 +8582,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -8589,7 +8590,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -8597,7 +8598,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -8605,7 +8606,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519E8E81-2FEE-46F7-BE6A-D9BCEDDF10D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C524ED9E-D866-49C0-8A49-2F950DB7B5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="49">
   <si>
     <t>TER</t>
   </si>
@@ -597,34 +597,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="39" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.6640625" customWidth="1"/>
-    <col min="42" max="46" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="39" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.7109375" customWidth="1"/>
+    <col min="42" max="46" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="7" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="7" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="7" style="4" bestFit="1" customWidth="1"/>
     <col min="52" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="106" width="7.6640625" customWidth="1"/>
+    <col min="55" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -822,7 +822,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -989,7 +989,9 @@
       <c r="BC2" s="1">
         <v>46254</v>
       </c>
-      <c r="BD2" s="1"/>
+      <c r="BD2" s="1">
+        <v>46259</v>
+      </c>
       <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
       <c r="BG2" s="1"/>
@@ -1026,7 +1028,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1192,7 +1194,9 @@
       <c r="BC3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD3" s="4"/>
+      <c r="BD3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE3" s="4"/>
       <c r="BF3" s="4"/>
       <c r="BG3" s="4"/>
@@ -1261,7 +1265,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1427,7 +1431,9 @@
       <c r="BC4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD4" s="4"/>
+      <c r="BD4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE4" s="4"/>
       <c r="BF4" s="4"/>
       <c r="BG4" s="4"/>
@@ -1496,7 +1502,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1662,7 +1668,9 @@
       <c r="BC5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD5" s="4"/>
+      <c r="BD5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE5" s="4"/>
       <c r="BF5" s="4"/>
       <c r="BG5" s="4"/>
@@ -1731,7 +1739,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -1897,7 +1905,9 @@
       <c r="BC6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD6" s="4"/>
+      <c r="BD6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE6" s="4"/>
       <c r="BF6" s="4"/>
       <c r="BG6" s="4"/>
@@ -1966,7 +1976,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -2114,7 +2124,9 @@
       <c r="BC7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="BD7" s="4"/>
+      <c r="BD7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE7" s="4"/>
       <c r="BF7" s="4"/>
       <c r="BG7" s="4"/>
@@ -2183,7 +2195,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2349,7 +2361,9 @@
       <c r="BC8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD8" s="4"/>
+      <c r="BD8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE8" s="4"/>
       <c r="BF8" s="4"/>
       <c r="BG8" s="4"/>
@@ -2418,7 +2432,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2584,7 +2598,9 @@
       <c r="BC9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="BD9" s="4"/>
+      <c r="BD9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE9" s="4"/>
       <c r="BF9" s="4"/>
       <c r="BG9" s="4"/>
@@ -2653,7 +2669,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -2819,7 +2835,9 @@
       <c r="BC10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD10" s="4"/>
+      <c r="BD10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE10" s="4"/>
       <c r="BF10" s="4"/>
       <c r="BG10" s="4"/>
@@ -2888,7 +2906,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -3054,7 +3072,9 @@
       <c r="BC11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD11" s="4"/>
+      <c r="BD11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE11" s="4"/>
       <c r="BF11" s="4"/>
       <c r="BG11" s="4"/>
@@ -3123,7 +3143,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -3289,7 +3309,9 @@
       <c r="BC12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD12" s="4"/>
+      <c r="BD12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE12" s="4"/>
       <c r="BF12" s="4"/>
       <c r="BG12" s="4"/>
@@ -3358,7 +3380,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3515,7 +3537,9 @@
       <c r="BC13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD13" s="4"/>
+      <c r="BD13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE13" s="4"/>
       <c r="BF13" s="4"/>
       <c r="BG13" s="4"/>
@@ -3584,7 +3608,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -3750,7 +3774,9 @@
       <c r="BC14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD14" s="4"/>
+      <c r="BD14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE14" s="4"/>
       <c r="BF14" s="4"/>
       <c r="BG14" s="4"/>
@@ -3819,7 +3845,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -3985,7 +4011,9 @@
       <c r="BC15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD15" s="4"/>
+      <c r="BD15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE15" s="4"/>
       <c r="BF15" s="4"/>
       <c r="BG15" s="4"/>
@@ -4054,7 +4082,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -4281,7 +4309,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -4447,7 +4475,9 @@
       <c r="BC17" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BD17" s="4"/>
+      <c r="BD17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE17" s="4"/>
       <c r="BF17" s="4"/>
       <c r="BG17" s="4"/>
@@ -4516,7 +4546,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -4682,7 +4712,9 @@
       <c r="BC18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD18" s="4"/>
+      <c r="BD18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE18" s="4"/>
       <c r="BF18" s="4"/>
       <c r="BG18" s="4"/>
@@ -4751,7 +4783,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -4978,7 +5010,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -5144,7 +5176,9 @@
       <c r="BC20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD20" s="4"/>
+      <c r="BD20" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BE20" s="4"/>
       <c r="BF20" s="4"/>
       <c r="BG20" s="4"/>
@@ -5213,7 +5247,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -5379,7 +5413,9 @@
       <c r="BC21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD21" s="4"/>
+      <c r="BD21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE21" s="4"/>
       <c r="BF21" s="4"/>
       <c r="BG21" s="4"/>
@@ -5448,7 +5484,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -5614,7 +5650,9 @@
       <c r="BC22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD22" s="4"/>
+      <c r="BD22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE22" s="4"/>
       <c r="BF22" s="4"/>
       <c r="BG22" s="4"/>
@@ -5683,7 +5721,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -5849,7 +5887,9 @@
       <c r="BC23" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="BD23" s="4"/>
+      <c r="BD23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE23" s="4"/>
       <c r="BF23" s="4"/>
       <c r="BG23" s="4"/>
@@ -5918,7 +5958,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -6063,7 +6103,9 @@
       <c r="BC24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD24" s="4"/>
+      <c r="BD24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE24" s="4"/>
       <c r="BF24" s="4"/>
       <c r="BG24" s="4"/>
@@ -6132,7 +6174,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -6298,7 +6340,9 @@
       <c r="BC25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD25" s="4"/>
+      <c r="BD25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE25" s="4"/>
       <c r="BF25" s="4"/>
       <c r="BG25" s="4"/>
@@ -6367,7 +6411,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -6533,7 +6577,9 @@
       <c r="BC26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD26" s="4"/>
+      <c r="BD26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE26" s="4"/>
       <c r="BF26" s="4"/>
       <c r="BG26" s="4"/>
@@ -6602,7 +6648,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -6768,7 +6814,9 @@
       <c r="BC27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD27" s="4"/>
+      <c r="BD27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE27" s="4"/>
       <c r="BF27" s="4"/>
       <c r="BG27" s="4"/>
@@ -6837,7 +6885,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -7003,7 +7051,9 @@
       <c r="BC28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD28" s="4"/>
+      <c r="BD28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE28" s="4"/>
       <c r="BF28" s="4"/>
       <c r="BG28" s="4"/>
@@ -7072,7 +7122,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -7238,7 +7288,9 @@
       <c r="BC29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD29" s="4"/>
+      <c r="BD29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE29" s="4"/>
       <c r="BF29" s="4"/>
       <c r="BG29" s="4"/>
@@ -7307,7 +7359,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -7473,7 +7525,9 @@
       <c r="BC30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD30" s="4"/>
+      <c r="BD30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE30" s="4"/>
       <c r="BF30" s="4"/>
       <c r="BG30" s="4"/>
@@ -7542,7 +7596,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -7708,7 +7762,9 @@
       <c r="BC31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD31" s="4"/>
+      <c r="BD31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE31" s="4"/>
       <c r="BF31" s="4"/>
       <c r="BG31" s="4"/>
@@ -7777,7 +7833,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -7943,7 +7999,9 @@
       <c r="BC32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD32" s="4"/>
+      <c r="BD32" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE32" s="4"/>
       <c r="BF32" s="4"/>
       <c r="BG32" s="4"/>
@@ -7955,7 +8013,7 @@
       <c r="BM32" s="4"/>
       <c r="BN32" s="4"/>
     </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -8121,7 +8179,9 @@
       <c r="BC33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD33" s="4"/>
+      <c r="BD33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE33" s="4"/>
       <c r="BF33" s="4"/>
       <c r="BG33" s="4"/>
@@ -8133,7 +8193,7 @@
       <c r="BM33" s="4"/>
       <c r="BN33" s="4"/>
     </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -8299,7 +8359,9 @@
       <c r="BC34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BD34" s="4"/>
+      <c r="BD34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BE34" s="4"/>
       <c r="BF34" s="4"/>
       <c r="BG34" s="4"/>
@@ -8344,13 +8406,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8358,7 +8420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -8366,7 +8428,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -8374,7 +8436,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -8382,7 +8444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -8390,7 +8452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -8398,7 +8460,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -8406,7 +8468,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -8414,7 +8476,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -8422,7 +8484,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -8430,7 +8492,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -8438,7 +8500,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -8446,7 +8508,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -8454,7 +8516,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -8462,7 +8524,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -8470,7 +8532,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -8478,7 +8540,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -8486,7 +8548,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -8494,7 +8556,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -8502,7 +8564,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -8510,7 +8572,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -8518,7 +8580,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -8526,7 +8588,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -8534,7 +8596,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -8542,7 +8604,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -8550,7 +8612,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -8558,7 +8620,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -8566,7 +8628,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -8574,7 +8636,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -8582,7 +8644,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -8590,7 +8652,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -8598,7 +8660,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -8606,7 +8668,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C524ED9E-D866-49C0-8A49-2F950DB7B5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3DBFC2-CD72-402F-8933-4BA99A70323C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="49">
   <si>
     <t>TER</t>
   </si>
@@ -992,7 +992,9 @@
       <c r="BD2" s="1">
         <v>46259</v>
       </c>
-      <c r="BE2" s="1"/>
+      <c r="BE2" s="1">
+        <v>46261</v>
+      </c>
       <c r="BF2" s="1"/>
       <c r="BG2" s="1"/>
       <c r="BH2" s="1"/>
@@ -1197,7 +1199,9 @@
       <c r="BD3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE3" s="4"/>
+      <c r="BE3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF3" s="4"/>
       <c r="BG3" s="4"/>
       <c r="BH3" s="4"/>
@@ -1434,7 +1438,9 @@
       <c r="BD4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE4" s="4"/>
+      <c r="BE4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF4" s="4"/>
       <c r="BG4" s="4"/>
       <c r="BH4" s="4"/>
@@ -1671,7 +1677,9 @@
       <c r="BD5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE5" s="4"/>
+      <c r="BE5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF5" s="4"/>
       <c r="BG5" s="4"/>
       <c r="BH5" s="4"/>
@@ -1908,7 +1916,9 @@
       <c r="BD6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE6" s="4"/>
+      <c r="BE6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF6" s="4"/>
       <c r="BG6" s="4"/>
       <c r="BH6" s="4"/>
@@ -2127,7 +2137,9 @@
       <c r="BD7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE7" s="4"/>
+      <c r="BE7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF7" s="4"/>
       <c r="BG7" s="4"/>
       <c r="BH7" s="4"/>
@@ -2364,7 +2376,9 @@
       <c r="BD8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE8" s="4"/>
+      <c r="BE8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF8" s="4"/>
       <c r="BG8" s="4"/>
       <c r="BH8" s="4"/>
@@ -2601,7 +2615,9 @@
       <c r="BD9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE9" s="4"/>
+      <c r="BE9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF9" s="4"/>
       <c r="BG9" s="4"/>
       <c r="BH9" s="4"/>
@@ -2838,7 +2854,9 @@
       <c r="BD10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE10" s="4"/>
+      <c r="BE10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF10" s="4"/>
       <c r="BG10" s="4"/>
       <c r="BH10" s="4"/>
@@ -3075,7 +3093,9 @@
       <c r="BD11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE11" s="4"/>
+      <c r="BE11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF11" s="4"/>
       <c r="BG11" s="4"/>
       <c r="BH11" s="4"/>
@@ -3312,7 +3332,9 @@
       <c r="BD12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE12" s="4"/>
+      <c r="BE12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF12" s="4"/>
       <c r="BG12" s="4"/>
       <c r="BH12" s="4"/>
@@ -3540,7 +3562,9 @@
       <c r="BD13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE13" s="4"/>
+      <c r="BE13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF13" s="4"/>
       <c r="BG13" s="4"/>
       <c r="BH13" s="4"/>
@@ -3777,7 +3801,9 @@
       <c r="BD14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE14" s="4"/>
+      <c r="BE14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF14" s="4"/>
       <c r="BG14" s="4"/>
       <c r="BH14" s="4"/>
@@ -4014,7 +4040,9 @@
       <c r="BD15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE15" s="4"/>
+      <c r="BE15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF15" s="4"/>
       <c r="BG15" s="4"/>
       <c r="BH15" s="4"/>
@@ -4478,7 +4506,9 @@
       <c r="BD17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE17" s="4"/>
+      <c r="BE17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF17" s="4"/>
       <c r="BG17" s="4"/>
       <c r="BH17" s="4"/>
@@ -4715,7 +4745,9 @@
       <c r="BD18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE18" s="4"/>
+      <c r="BE18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF18" s="4"/>
       <c r="BG18" s="4"/>
       <c r="BH18" s="4"/>
@@ -5179,7 +5211,9 @@
       <c r="BD20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BE20" s="4"/>
+      <c r="BE20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF20" s="4"/>
       <c r="BG20" s="4"/>
       <c r="BH20" s="4"/>
@@ -5416,7 +5450,9 @@
       <c r="BD21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE21" s="4"/>
+      <c r="BE21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF21" s="4"/>
       <c r="BG21" s="4"/>
       <c r="BH21" s="4"/>
@@ -5653,7 +5689,9 @@
       <c r="BD22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE22" s="4"/>
+      <c r="BE22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF22" s="4"/>
       <c r="BG22" s="4"/>
       <c r="BH22" s="4"/>
@@ -5890,7 +5928,9 @@
       <c r="BD23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE23" s="4"/>
+      <c r="BE23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF23" s="4"/>
       <c r="BG23" s="4"/>
       <c r="BH23" s="4"/>
@@ -6106,7 +6146,9 @@
       <c r="BD24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE24" s="4"/>
+      <c r="BE24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF24" s="4"/>
       <c r="BG24" s="4"/>
       <c r="BH24" s="4"/>
@@ -6343,7 +6385,9 @@
       <c r="BD25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE25" s="4"/>
+      <c r="BE25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF25" s="4"/>
       <c r="BG25" s="4"/>
       <c r="BH25" s="4"/>
@@ -6580,7 +6624,9 @@
       <c r="BD26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE26" s="4"/>
+      <c r="BE26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF26" s="4"/>
       <c r="BG26" s="4"/>
       <c r="BH26" s="4"/>
@@ -6817,7 +6863,9 @@
       <c r="BD27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE27" s="4"/>
+      <c r="BE27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF27" s="4"/>
       <c r="BG27" s="4"/>
       <c r="BH27" s="4"/>
@@ -7054,7 +7102,9 @@
       <c r="BD28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE28" s="4"/>
+      <c r="BE28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF28" s="4"/>
       <c r="BG28" s="4"/>
       <c r="BH28" s="4"/>
@@ -7291,7 +7341,9 @@
       <c r="BD29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE29" s="4"/>
+      <c r="BE29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF29" s="4"/>
       <c r="BG29" s="4"/>
       <c r="BH29" s="4"/>
@@ -7528,7 +7580,9 @@
       <c r="BD30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE30" s="4"/>
+      <c r="BE30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF30" s="4"/>
       <c r="BG30" s="4"/>
       <c r="BH30" s="4"/>
@@ -7765,7 +7819,9 @@
       <c r="BD31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE31" s="4"/>
+      <c r="BE31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF31" s="4"/>
       <c r="BG31" s="4"/>
       <c r="BH31" s="4"/>
@@ -8002,7 +8058,9 @@
       <c r="BD32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE32" s="4"/>
+      <c r="BE32" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF32" s="4"/>
       <c r="BG32" s="4"/>
       <c r="BH32" s="4"/>
@@ -8182,7 +8240,9 @@
       <c r="BD33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE33" s="4"/>
+      <c r="BE33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF33" s="4"/>
       <c r="BG33" s="4"/>
       <c r="BH33" s="4"/>
@@ -8362,7 +8422,9 @@
       <c r="BD34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BE34" s="4"/>
+      <c r="BE34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BF34" s="4"/>
       <c r="BG34" s="4"/>
       <c r="BH34" s="4"/>
@@ -8378,7 +8440,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BE3:DG3 AV3:AZ4 BB3:BB22 BC3:BC31 O3:AT34 BE4:BJ10 D4:I31 K4:M31 BK4:DG31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BD11:BJ31 AZ23:BB31 G32:I32 AV32:AV34">
+  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BB3:BB22 BC3:BC31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 AZ23:BB31 G32:I32 AV32:AV34 BF3:DG31 BD11:BE31">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3DBFC2-CD72-402F-8933-4BA99A70323C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04494419-AC08-4609-944D-B3F7C254151A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1856" uniqueCount="49">
   <si>
     <t>TER</t>
   </si>
@@ -787,8 +787,12 @@
       <c r="BE1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="BF1" s="1"/>
-      <c r="BG1" s="1"/>
+      <c r="BF1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="BH1" s="1"/>
       <c r="BI1" s="1"/>
       <c r="BJ1" s="1"/>
@@ -995,8 +999,12 @@
       <c r="BE2" s="1">
         <v>46261</v>
       </c>
-      <c r="BF2" s="1"/>
-      <c r="BG2" s="1"/>
+      <c r="BF2" s="1">
+        <v>46266</v>
+      </c>
+      <c r="BG2" s="1">
+        <v>46268</v>
+      </c>
       <c r="BH2" s="1"/>
       <c r="BI2" s="1"/>
       <c r="BJ2" s="1"/>
@@ -1202,7 +1210,9 @@
       <c r="BE3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF3" s="4"/>
+      <c r="BF3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG3" s="4"/>
       <c r="BH3" s="4"/>
       <c r="BI3" s="4"/>
@@ -1441,7 +1451,9 @@
       <c r="BE4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF4" s="4"/>
+      <c r="BF4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG4" s="4"/>
       <c r="BH4" s="4"/>
       <c r="BI4" s="4"/>
@@ -1680,7 +1692,9 @@
       <c r="BE5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF5" s="4"/>
+      <c r="BF5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG5" s="4"/>
       <c r="BH5" s="4"/>
       <c r="BI5" s="4"/>
@@ -1919,7 +1933,9 @@
       <c r="BE6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF6" s="4"/>
+      <c r="BF6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG6" s="4"/>
       <c r="BH6" s="4"/>
       <c r="BI6" s="4"/>
@@ -2140,7 +2156,9 @@
       <c r="BE7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF7" s="4"/>
+      <c r="BF7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG7" s="4"/>
       <c r="BH7" s="4"/>
       <c r="BI7" s="4"/>
@@ -2379,7 +2397,9 @@
       <c r="BE8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF8" s="4"/>
+      <c r="BF8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG8" s="4"/>
       <c r="BH8" s="4"/>
       <c r="BI8" s="4"/>
@@ -2618,7 +2638,9 @@
       <c r="BE9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF9" s="4"/>
+      <c r="BF9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG9" s="4"/>
       <c r="BH9" s="4"/>
       <c r="BI9" s="4"/>
@@ -2857,7 +2879,9 @@
       <c r="BE10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF10" s="4"/>
+      <c r="BF10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG10" s="4"/>
       <c r="BH10" s="4"/>
       <c r="BI10" s="4"/>
@@ -3096,7 +3120,9 @@
       <c r="BE11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF11" s="4"/>
+      <c r="BF11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG11" s="4"/>
       <c r="BH11" s="4"/>
       <c r="BI11" s="4"/>
@@ -3335,7 +3361,9 @@
       <c r="BE12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF12" s="4"/>
+      <c r="BF12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG12" s="4"/>
       <c r="BH12" s="4"/>
       <c r="BI12" s="4"/>
@@ -3565,7 +3593,9 @@
       <c r="BE13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF13" s="4"/>
+      <c r="BF13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG13" s="4"/>
       <c r="BH13" s="4"/>
       <c r="BI13" s="4"/>
@@ -3804,7 +3834,9 @@
       <c r="BE14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF14" s="4"/>
+      <c r="BF14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG14" s="4"/>
       <c r="BH14" s="4"/>
       <c r="BI14" s="4"/>
@@ -4043,7 +4075,9 @@
       <c r="BE15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF15" s="4"/>
+      <c r="BF15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG15" s="4"/>
       <c r="BH15" s="4"/>
       <c r="BI15" s="4"/>
@@ -4509,7 +4543,9 @@
       <c r="BE17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF17" s="4"/>
+      <c r="BF17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG17" s="4"/>
       <c r="BH17" s="4"/>
       <c r="BI17" s="4"/>
@@ -4748,7 +4784,9 @@
       <c r="BE18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF18" s="4"/>
+      <c r="BF18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG18" s="4"/>
       <c r="BH18" s="4"/>
       <c r="BI18" s="4"/>
@@ -5214,7 +5252,9 @@
       <c r="BE20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF20" s="4"/>
+      <c r="BF20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG20" s="4"/>
       <c r="BH20" s="4"/>
       <c r="BI20" s="4"/>
@@ -5453,7 +5493,9 @@
       <c r="BE21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF21" s="4"/>
+      <c r="BF21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG21" s="4"/>
       <c r="BH21" s="4"/>
       <c r="BI21" s="4"/>
@@ -5692,7 +5734,9 @@
       <c r="BE22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF22" s="4"/>
+      <c r="BF22" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BG22" s="4"/>
       <c r="BH22" s="4"/>
       <c r="BI22" s="4"/>
@@ -5931,7 +5975,9 @@
       <c r="BE23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF23" s="4"/>
+      <c r="BF23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG23" s="4"/>
       <c r="BH23" s="4"/>
       <c r="BI23" s="4"/>
@@ -6149,7 +6195,9 @@
       <c r="BE24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF24" s="4"/>
+      <c r="BF24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG24" s="4"/>
       <c r="BH24" s="4"/>
       <c r="BI24" s="4"/>
@@ -6388,7 +6436,9 @@
       <c r="BE25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF25" s="4"/>
+      <c r="BF25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG25" s="4"/>
       <c r="BH25" s="4"/>
       <c r="BI25" s="4"/>
@@ -6627,7 +6677,9 @@
       <c r="BE26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF26" s="4"/>
+      <c r="BF26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG26" s="4"/>
       <c r="BH26" s="4"/>
       <c r="BI26" s="4"/>
@@ -6866,7 +6918,9 @@
       <c r="BE27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF27" s="4"/>
+      <c r="BF27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG27" s="4"/>
       <c r="BH27" s="4"/>
       <c r="BI27" s="4"/>
@@ -7105,7 +7159,9 @@
       <c r="BE28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF28" s="4"/>
+      <c r="BF28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG28" s="4"/>
       <c r="BH28" s="4"/>
       <c r="BI28" s="4"/>
@@ -7344,7 +7400,9 @@
       <c r="BE29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF29" s="4"/>
+      <c r="BF29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG29" s="4"/>
       <c r="BH29" s="4"/>
       <c r="BI29" s="4"/>
@@ -7583,7 +7641,9 @@
       <c r="BE30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF30" s="4"/>
+      <c r="BF30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG30" s="4"/>
       <c r="BH30" s="4"/>
       <c r="BI30" s="4"/>
@@ -7822,7 +7882,9 @@
       <c r="BE31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF31" s="4"/>
+      <c r="BF31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG31" s="4"/>
       <c r="BH31" s="4"/>
       <c r="BI31" s="4"/>
@@ -8061,7 +8123,9 @@
       <c r="BE32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF32" s="4"/>
+      <c r="BF32" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG32" s="4"/>
       <c r="BH32" s="4"/>
       <c r="BI32" s="4"/>
@@ -8243,7 +8307,9 @@
       <c r="BE33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF33" s="4"/>
+      <c r="BF33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG33" s="4"/>
       <c r="BH33" s="4"/>
       <c r="BI33" s="4"/>
@@ -8425,7 +8491,9 @@
       <c r="BE34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BF34" s="4"/>
+      <c r="BF34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BG34" s="4"/>
       <c r="BH34" s="4"/>
       <c r="BI34" s="4"/>
@@ -8440,7 +8508,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BB3:BB22 BC3:BC31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 AZ23:BB31 G32:I32 AV32:AV34 BF3:DG31 BD11:BE31">
+  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:DG31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BD11:BE31 AZ23:BB31 G32:I32 AV32:AV34">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04494419-AC08-4609-944D-B3F7C254151A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014ED230-260F-4A87-B9B1-36275E1756B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5735,7 +5735,7 @@
         <v>5</v>
       </c>
       <c r="BF22" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BG22" s="4"/>
       <c r="BH22" s="4"/>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014ED230-260F-4A87-B9B1-36275E1756B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB15A85-8C8A-4600-A7E1-AD28578BB0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1856" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="50">
   <si>
     <t>TER</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>3/P</t>
+  </si>
+  <si>
+    <t>P/7</t>
   </si>
 </sst>
 </file>
@@ -1213,7 +1216,9 @@
       <c r="BF3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG3" s="4"/>
+      <c r="BG3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH3" s="4"/>
       <c r="BI3" s="4"/>
       <c r="BJ3" s="4"/>
@@ -1454,7 +1459,9 @@
       <c r="BF4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG4" s="4"/>
+      <c r="BG4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH4" s="4"/>
       <c r="BI4" s="4"/>
       <c r="BJ4" s="4"/>
@@ -1695,7 +1702,9 @@
       <c r="BF5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG5" s="4"/>
+      <c r="BG5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH5" s="4"/>
       <c r="BI5" s="4"/>
       <c r="BJ5" s="4"/>
@@ -1936,7 +1945,9 @@
       <c r="BF6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG6" s="4"/>
+      <c r="BG6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH6" s="4"/>
       <c r="BI6" s="4"/>
       <c r="BJ6" s="4"/>
@@ -2159,7 +2170,9 @@
       <c r="BF7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG7" s="4"/>
+      <c r="BG7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH7" s="4"/>
       <c r="BI7" s="4"/>
       <c r="BJ7" s="4"/>
@@ -2400,7 +2413,9 @@
       <c r="BF8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG8" s="4"/>
+      <c r="BG8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH8" s="4"/>
       <c r="BI8" s="4"/>
       <c r="BJ8" s="4"/>
@@ -2641,7 +2656,9 @@
       <c r="BF9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG9" s="4"/>
+      <c r="BG9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH9" s="4"/>
       <c r="BI9" s="4"/>
       <c r="BJ9" s="4"/>
@@ -2882,7 +2899,9 @@
       <c r="BF10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG10" s="4"/>
+      <c r="BG10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH10" s="4"/>
       <c r="BI10" s="4"/>
       <c r="BJ10" s="4"/>
@@ -3123,7 +3142,9 @@
       <c r="BF11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG11" s="4"/>
+      <c r="BG11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH11" s="4"/>
       <c r="BI11" s="4"/>
       <c r="BJ11" s="4"/>
@@ -3364,7 +3385,9 @@
       <c r="BF12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG12" s="4"/>
+      <c r="BG12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH12" s="4"/>
       <c r="BI12" s="4"/>
       <c r="BJ12" s="4"/>
@@ -3596,7 +3619,9 @@
       <c r="BF13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG13" s="4"/>
+      <c r="BG13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH13" s="4"/>
       <c r="BI13" s="4"/>
       <c r="BJ13" s="4"/>
@@ -3837,7 +3862,9 @@
       <c r="BF14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG14" s="4"/>
+      <c r="BG14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH14" s="4"/>
       <c r="BI14" s="4"/>
       <c r="BJ14" s="4"/>
@@ -4078,7 +4105,9 @@
       <c r="BF15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG15" s="4"/>
+      <c r="BG15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH15" s="4"/>
       <c r="BI15" s="4"/>
       <c r="BJ15" s="4"/>
@@ -4546,7 +4575,9 @@
       <c r="BF17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG17" s="4"/>
+      <c r="BG17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH17" s="4"/>
       <c r="BI17" s="4"/>
       <c r="BJ17" s="4"/>
@@ -4787,7 +4818,9 @@
       <c r="BF18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG18" s="4"/>
+      <c r="BG18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH18" s="4"/>
       <c r="BI18" s="4"/>
       <c r="BJ18" s="4"/>
@@ -5255,7 +5288,9 @@
       <c r="BF20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG20" s="4"/>
+      <c r="BG20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH20" s="4"/>
       <c r="BI20" s="4"/>
       <c r="BJ20" s="4"/>
@@ -5496,7 +5531,9 @@
       <c r="BF21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG21" s="4"/>
+      <c r="BG21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH21" s="4"/>
       <c r="BI21" s="4"/>
       <c r="BJ21" s="4"/>
@@ -5737,7 +5774,9 @@
       <c r="BF22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG22" s="4"/>
+      <c r="BG22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH22" s="4"/>
       <c r="BI22" s="4"/>
       <c r="BJ22" s="4"/>
@@ -5978,7 +6017,9 @@
       <c r="BF23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG23" s="4"/>
+      <c r="BG23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH23" s="4"/>
       <c r="BI23" s="4"/>
       <c r="BJ23" s="4"/>
@@ -6198,7 +6239,9 @@
       <c r="BF24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG24" s="4"/>
+      <c r="BG24" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="BH24" s="4"/>
       <c r="BI24" s="4"/>
       <c r="BJ24" s="4"/>
@@ -6439,7 +6482,9 @@
       <c r="BF25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG25" s="4"/>
+      <c r="BG25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH25" s="4"/>
       <c r="BI25" s="4"/>
       <c r="BJ25" s="4"/>
@@ -6680,7 +6725,9 @@
       <c r="BF26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG26" s="4"/>
+      <c r="BG26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH26" s="4"/>
       <c r="BI26" s="4"/>
       <c r="BJ26" s="4"/>
@@ -6921,7 +6968,9 @@
       <c r="BF27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG27" s="4"/>
+      <c r="BG27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH27" s="4"/>
       <c r="BI27" s="4"/>
       <c r="BJ27" s="4"/>
@@ -7162,7 +7211,9 @@
       <c r="BF28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG28" s="4"/>
+      <c r="BG28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH28" s="4"/>
       <c r="BI28" s="4"/>
       <c r="BJ28" s="4"/>
@@ -7403,7 +7454,9 @@
       <c r="BF29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG29" s="4"/>
+      <c r="BG29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH29" s="4"/>
       <c r="BI29" s="4"/>
       <c r="BJ29" s="4"/>
@@ -7644,7 +7697,9 @@
       <c r="BF30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG30" s="4"/>
+      <c r="BG30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH30" s="4"/>
       <c r="BI30" s="4"/>
       <c r="BJ30" s="4"/>
@@ -7885,7 +7940,9 @@
       <c r="BF31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG31" s="4"/>
+      <c r="BG31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH31" s="4"/>
       <c r="BI31" s="4"/>
       <c r="BJ31" s="4"/>
@@ -8126,7 +8183,9 @@
       <c r="BF32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG32" s="4"/>
+      <c r="BG32" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH32" s="4"/>
       <c r="BI32" s="4"/>
       <c r="BJ32" s="4"/>
@@ -8310,7 +8369,9 @@
       <c r="BF33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG33" s="4"/>
+      <c r="BG33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH33" s="4"/>
       <c r="BI33" s="4"/>
       <c r="BJ33" s="4"/>
@@ -8494,7 +8555,9 @@
       <c r="BF34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BG34" s="4"/>
+      <c r="BG34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BH34" s="4"/>
       <c r="BI34" s="4"/>
       <c r="BJ34" s="4"/>
@@ -8508,7 +8571,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:DG31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BD11:BE31 AZ23:BB31 G32:I32 AV32:AV34">
+  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BB3:BB22 BC3:BC31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BD11:BE31 AZ23:BB31 G32:I32 AV32:AV34 BF3:DG31">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB15A85-8C8A-4600-A7E1-AD28578BB0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7E0E3B-5D3B-4DE9-B337-9DCA42B8051F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1950" uniqueCount="51">
   <si>
     <t>TER</t>
   </si>
@@ -188,6 +188,9 @@
   <si>
     <t>P/7</t>
   </si>
+  <si>
+    <t>FERIADO</t>
+  </si>
 </sst>
 </file>
 
@@ -282,7 +285,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -624,7 +637,9 @@
     <col min="50" max="50" width="7" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="7" style="4" bestFit="1" customWidth="1"/>
     <col min="52" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="106" width="7.7109375" customWidth="1"/>
+    <col min="55" max="59" width="7.7109375" customWidth="1"/>
+    <col min="60" max="60" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="61" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:123" x14ac:dyDescent="0.25">
@@ -796,8 +811,12 @@
       <c r="BG1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="BH1" s="1"/>
-      <c r="BI1" s="1"/>
+      <c r="BH1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -1008,8 +1027,12 @@
       <c r="BG2" s="1">
         <v>46268</v>
       </c>
-      <c r="BH2" s="1"/>
-      <c r="BI2" s="1"/>
+      <c r="BH2" s="1">
+        <v>46273</v>
+      </c>
+      <c r="BI2" s="1">
+        <v>46275</v>
+      </c>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -1219,8 +1242,12 @@
       <c r="BG3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH3" s="4"/>
-      <c r="BI3" s="4"/>
+      <c r="BH3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ3" s="4"/>
       <c r="BK3" s="4"/>
       <c r="BL3" s="4"/>
@@ -1462,8 +1489,12 @@
       <c r="BG4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH4" s="4"/>
-      <c r="BI4" s="4"/>
+      <c r="BH4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ4" s="4"/>
       <c r="BK4" s="4"/>
       <c r="BL4" s="4"/>
@@ -1705,8 +1736,12 @@
       <c r="BG5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH5" s="4"/>
-      <c r="BI5" s="4"/>
+      <c r="BH5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ5" s="4"/>
       <c r="BK5" s="4"/>
       <c r="BL5" s="4"/>
@@ -1948,8 +1983,12 @@
       <c r="BG6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH6" s="4"/>
-      <c r="BI6" s="4"/>
+      <c r="BH6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI6" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BJ6" s="4"/>
       <c r="BK6" s="4"/>
       <c r="BL6" s="4"/>
@@ -2173,8 +2212,12 @@
       <c r="BG7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH7" s="4"/>
-      <c r="BI7" s="4"/>
+      <c r="BH7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ7" s="4"/>
       <c r="BK7" s="4"/>
       <c r="BL7" s="4"/>
@@ -2416,8 +2459,12 @@
       <c r="BG8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH8" s="4"/>
-      <c r="BI8" s="4"/>
+      <c r="BH8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ8" s="4"/>
       <c r="BK8" s="4"/>
       <c r="BL8" s="4"/>
@@ -2659,8 +2706,12 @@
       <c r="BG9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH9" s="4"/>
-      <c r="BI9" s="4"/>
+      <c r="BH9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ9" s="4"/>
       <c r="BK9" s="4"/>
       <c r="BL9" s="4"/>
@@ -2902,8 +2953,12 @@
       <c r="BG10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH10" s="4"/>
-      <c r="BI10" s="4"/>
+      <c r="BH10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ10" s="4"/>
       <c r="BK10" s="4"/>
       <c r="BL10" s="4"/>
@@ -3145,8 +3200,12 @@
       <c r="BG11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH11" s="4"/>
-      <c r="BI11" s="4"/>
+      <c r="BH11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ11" s="4"/>
       <c r="BK11" s="4"/>
       <c r="BL11" s="4"/>
@@ -3388,8 +3447,12 @@
       <c r="BG12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH12" s="4"/>
-      <c r="BI12" s="4"/>
+      <c r="BH12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ12" s="4"/>
       <c r="BK12" s="4"/>
       <c r="BL12" s="4"/>
@@ -3622,8 +3685,12 @@
       <c r="BG13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH13" s="4"/>
-      <c r="BI13" s="4"/>
+      <c r="BH13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ13" s="4"/>
       <c r="BK13" s="4"/>
       <c r="BL13" s="4"/>
@@ -3865,8 +3932,12 @@
       <c r="BG14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH14" s="4"/>
-      <c r="BI14" s="4"/>
+      <c r="BH14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ14" s="4"/>
       <c r="BK14" s="4"/>
       <c r="BL14" s="4"/>
@@ -4108,8 +4179,12 @@
       <c r="BG15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH15" s="4"/>
-      <c r="BI15" s="4"/>
+      <c r="BH15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ15" s="4"/>
       <c r="BK15" s="4"/>
       <c r="BL15" s="4"/>
@@ -4335,7 +4410,9 @@
       <c r="BE16" s="4"/>
       <c r="BF16" s="4"/>
       <c r="BG16" s="4"/>
-      <c r="BH16" s="4"/>
+      <c r="BH16" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="BI16" s="4"/>
       <c r="BJ16" s="4"/>
       <c r="BK16" s="4"/>
@@ -4578,8 +4655,12 @@
       <c r="BG17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH17" s="4"/>
-      <c r="BI17" s="4"/>
+      <c r="BH17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ17" s="4"/>
       <c r="BK17" s="4"/>
       <c r="BL17" s="4"/>
@@ -4821,8 +4902,12 @@
       <c r="BG18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH18" s="4"/>
-      <c r="BI18" s="4"/>
+      <c r="BH18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ18" s="4"/>
       <c r="BK18" s="4"/>
       <c r="BL18" s="4"/>
@@ -5048,7 +5133,9 @@
       <c r="BE19" s="4"/>
       <c r="BF19" s="4"/>
       <c r="BG19" s="4"/>
-      <c r="BH19" s="4"/>
+      <c r="BH19" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="BI19" s="4"/>
       <c r="BJ19" s="4"/>
       <c r="BK19" s="4"/>
@@ -5291,8 +5378,12 @@
       <c r="BG20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH20" s="4"/>
-      <c r="BI20" s="4"/>
+      <c r="BH20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ20" s="4"/>
       <c r="BK20" s="4"/>
       <c r="BL20" s="4"/>
@@ -5534,8 +5625,12 @@
       <c r="BG21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH21" s="4"/>
-      <c r="BI21" s="4"/>
+      <c r="BH21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ21" s="4"/>
       <c r="BK21" s="4"/>
       <c r="BL21" s="4"/>
@@ -5777,8 +5872,12 @@
       <c r="BG22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH22" s="4"/>
-      <c r="BI22" s="4"/>
+      <c r="BH22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ22" s="4"/>
       <c r="BK22" s="4"/>
       <c r="BL22" s="4"/>
@@ -6020,8 +6119,12 @@
       <c r="BG23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH23" s="4"/>
-      <c r="BI23" s="4"/>
+      <c r="BH23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ23" s="4"/>
       <c r="BK23" s="4"/>
       <c r="BL23" s="4"/>
@@ -6242,8 +6345,12 @@
       <c r="BG24" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="BH24" s="4"/>
-      <c r="BI24" s="4"/>
+      <c r="BH24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ24" s="4"/>
       <c r="BK24" s="4"/>
       <c r="BL24" s="4"/>
@@ -6485,8 +6592,12 @@
       <c r="BG25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH25" s="4"/>
-      <c r="BI25" s="4"/>
+      <c r="BH25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ25" s="4"/>
       <c r="BK25" s="4"/>
       <c r="BL25" s="4"/>
@@ -6728,8 +6839,12 @@
       <c r="BG26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH26" s="4"/>
-      <c r="BI26" s="4"/>
+      <c r="BH26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ26" s="4"/>
       <c r="BK26" s="4"/>
       <c r="BL26" s="4"/>
@@ -6971,8 +7086,12 @@
       <c r="BG27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH27" s="4"/>
-      <c r="BI27" s="4"/>
+      <c r="BH27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ27" s="4"/>
       <c r="BK27" s="4"/>
       <c r="BL27" s="4"/>
@@ -7214,8 +7333,12 @@
       <c r="BG28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH28" s="4"/>
-      <c r="BI28" s="4"/>
+      <c r="BH28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI28" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BJ28" s="4"/>
       <c r="BK28" s="4"/>
       <c r="BL28" s="4"/>
@@ -7457,8 +7580,12 @@
       <c r="BG29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH29" s="4"/>
-      <c r="BI29" s="4"/>
+      <c r="BH29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ29" s="4"/>
       <c r="BK29" s="4"/>
       <c r="BL29" s="4"/>
@@ -7700,8 +7827,12 @@
       <c r="BG30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH30" s="4"/>
-      <c r="BI30" s="4"/>
+      <c r="BH30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ30" s="4"/>
       <c r="BK30" s="4"/>
       <c r="BL30" s="4"/>
@@ -7943,8 +8074,12 @@
       <c r="BG31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH31" s="4"/>
-      <c r="BI31" s="4"/>
+      <c r="BH31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ31" s="4"/>
       <c r="BK31" s="4"/>
       <c r="BL31" s="4"/>
@@ -8186,8 +8321,12 @@
       <c r="BG32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH32" s="4"/>
-      <c r="BI32" s="4"/>
+      <c r="BH32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI32" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BJ32" s="4"/>
       <c r="BK32" s="4"/>
       <c r="BL32" s="4"/>
@@ -8372,8 +8511,12 @@
       <c r="BG33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH33" s="4"/>
-      <c r="BI33" s="4"/>
+      <c r="BH33" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ33" s="4"/>
       <c r="BK33" s="4"/>
       <c r="BL33" s="4"/>
@@ -8558,8 +8701,12 @@
       <c r="BG34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BH34" s="4"/>
-      <c r="BI34" s="4"/>
+      <c r="BH34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BJ34" s="4"/>
       <c r="BK34" s="4"/>
       <c r="BL34" s="4"/>
@@ -8571,23 +8718,28 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BB3:BB22 BC3:BC31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BD11:BE31 AZ23:BB31 G32:I32 AV32:AV34 BF3:DG31">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BB3:BB22 BC3:BC31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BD11:BE31 AZ23:BB31 G32:I32 AV32:AV34 BF3:BG31 BI3:DG31">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA23">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BA23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB3:BC34">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BB3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB34:BC34">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BI32">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4semestre\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7E0E3B-5D3B-4DE9-B337-9DCA42B8051F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFE4A6BF-AC00-40C8-8669-13E3CC710A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="alunos" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1950" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1950" uniqueCount="52">
   <si>
     <t>TER</t>
   </si>
@@ -190,6 +191,9 @@
   </si>
   <si>
     <t>FERIADO</t>
+  </si>
+  <si>
+    <t>5P/F</t>
   </si>
 </sst>
 </file>
@@ -2463,7 +2467,7 @@
         <v>50</v>
       </c>
       <c r="BI8" s="4" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="BJ8" s="4"/>
       <c r="BK8" s="4"/>
@@ -2957,7 +2961,7 @@
         <v>50</v>
       </c>
       <c r="BI10" s="4" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="BJ10" s="4"/>
       <c r="BK10" s="4"/>
@@ -3689,7 +3693,7 @@
         <v>50</v>
       </c>
       <c r="BI13" s="4" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="BJ13" s="4"/>
       <c r="BK13" s="4"/>
@@ -8078,7 +8082,7 @@
         <v>50</v>
       </c>
       <c r="BI31" s="4" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="BJ31" s="4"/>
       <c r="BK31" s="4"/>
@@ -8718,7 +8722,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BB3:BB22 BC3:BC31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BD11:BE31 AZ23:BB31 G32:I32 AV32:AV34 BF3:BG31 BI3:DG31">
+  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 BI3:DG31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BD11:BE31 AZ23:BB31 G32:I32 AV32:AV34">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
